--- a/jobs_latest.xlsx
+++ b/jobs_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9389,492 +9389,9 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>expleo-jobs-gb-en</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Preston, LNH, GB</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>icims</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>As part of the Expleo Automotive &amp; Transportation Cybersecurity team, you will report to the Solution Architect / Head of Function and support client projects. Within the Automotive &amp; Transportation Cybersecurity Practice, you will be part of a dynamic and passionate team. You will work on a complex and captivating projects integrating the latest technological solutions and trends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Motorola Solutions</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Senior Software Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Uxbridge, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>Join our team as a Senior Software Cybersecurity Engineer. In this role, you will analyze software designs and implementations to identify and remediate security vulnerabilities across the software development lifecycle (SDLC). You will perform threat modeling, risk assessments, audits, and architecture reviews, focusing on cloud and container environments. You will also manage key management and IAM controls, support engineering teams by defining security requirements, and perform security code reviews. Additionally, you will drive vulnerability management, support product security incident response, and monitor emerging threats to ensure compliance with standards.
-- Analyser les conceptions et les mises en œuvre logicielles pour identifier et remédier aux vulnérabilités de sécurité tout au long du cycle de vie du développement logiciel (SDLC).
-- Effectuer des tests de sécurité, déployer et gérer des outils de sécurité automatisés dans les pipelines CI/CD, et recommander des améliorations aux outils de sécurité existants.
-- Gérer la gestion des vulnérabilités, en mettant l'accent sur Kubernetes (K8s) et les images de conteneurs, et communiquer les problèmes de sécurité aux parties prenantes.
- - Software Engineering: Hands-on development experience, specifically in Go and C#
-- Leadership: Proven track record in leading process change, mentoring on secure-by-design principles, and driving continuous improvement
-- Experience &amp; Education: 7+ years in Security/Application Engineering; Bachelor’s degree in Computer Science, Information Security, or a related field
-- AppSec &amp; DevSecOps: Deep understanding of threat modeling (STRIDE, PASTA), IAM, cryptography, web/network protocols (HTTP, REST, TLS, TCP/IP), and integrating security tooling (SCA, SAST, DAST) into CI/CD pipelines
-- Cloud &amp; Container Security: Strong knowledge of orchestration (AWS, Azure, GCP, Docker, Kubernetes) and container image vulnerability lifecycles
-- Standards &amp; Frameworks: Knowledge of NIST, ISO 27001, CIS, and OWASP (ASVS/Testing Guides)
-- Advanced Technical Skills: Deep vulnerability research, exploit R&amp;D, manual pentesting (cloud/web/embedded/mobile), SIEM/logging platforms (Splunk, OSQuery), AI/ML security, and distributed systems
-- Education &amp; Certifications: Master’s degree preferred; Cloud/Security certifications (CCSP, CCAK, AWS Security Specialty, OSCP, CISSP, SANS/GIAC)
-- Soft Skills: Strong communication across technical and non-technical groups, calm under pressure, and experience in high-growth SaaS environments</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>dLocal</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Principal Security Engineer (Identity &amp; Access)</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>Join our rapidly evolving fintech company as a Principal Security Engineer specializing in Identity &amp; Access. In this hands-on role, you will engineer a highly automated identity lifecycle, design and scale our authentication and authorization foundations, lead identity integration strategies for mergers and acquisitions, and codify governance. You will collaborate with various teams across the organization and have a strong impact on our identity transformation.
-- Conduire l'évolution de l'identité de l'entreprise en concevant et en mettant en œuvre des solutions d'automatisation pour le cycle de vie des identités.
-- Diriger la stratégie d'intégration des identités pour les fusions, acquisitions et initiatives de transformation d'entreprise.
-- Collaborer avec les équipes interfonctionnelles pour gouverner l'accès à travers l'entreprise et le cloud.
- - Pragmatic Operator Mindset: You understand that security cannot kill velocity. You know how to find the critical balance between enforcing strict, least-privilege security and maintaining high usability for the business
-- Disciplined Multi-Threading: You are ruthlessly organized, capable of driving an enterprise identity strategy while simultaneously troubleshooting an immediate, ground-level access escalation
-- Deep IGA &amp; Protocol Expertise: You possess solid, hands-on experience with modern workforce identity systems, lifecycle processes (JML, SoD, Certifications), protocols (SAML, OIDC, OAuth2, SCIM), RBAC/ABAC models, and enterprise identity platforms (e.g., SailPoint, Saviynt, Okta)
-- Force Multiplier: You elevate the engineers around you. You bring strong mentoring, leadership, and documentation capabilities, ensuring that the systems you design are highly scalable, well-understood, and easily maintained by the wider organization
-- Track Record Over Tenure: We do not care about arbitrary "years of experience." We care about outcomes. You must have a proven track record of designing, building, or scaling Identity and Access programs in fast-paced, complex environments
-- Resilient Problem Solver: You don't get stuck. Where others see a messy legacy setup, you see an exciting puzzle. You don't get paralyzed or frustrated by organizational friction; you thrive on using the latest technologies and original thinking to solve long-standing identity problems
-- Relevant industry certifications demonstrating your dedication to the identity domain
-- Familiarity with machine identity governance, secrets management, and API access
-- Experience navigating the identity and access requirements of highly regulated environments (PCI-DSS, SOX, SOC 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Software Security Engineer</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>USD 145,000–165,000 / year</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908)676-4399. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>careers.roche.com</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer -  Monitoring &amp; Incident Response</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>phenom</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>Become part of our team as a Cybersecurity Engineer in Monitoring &amp; Incident Response, where you will protect Roche’s global networks and users from evolving threats. You will monitor security information, respond to incidents, and support continuous improvement. Ideal candidates bring significant experience in information security and a strong background in SOC/CERT/CSIRT environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>careers.statestreet.com</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Cybersecurity Automation Engineer ,Assistant Vice President</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Kilkenny, Kilkenny, Ireland</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>phenom</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>We are looking for a Cybersecurity Automation Engineer, Assistant Vice President, to identify and implement automation opportunities within our SOC. You will collaborate with analysts to enhance incident response workflows and develop user stories. Ideal candidates have experience in cybersecurity and strong programming skills.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Neon</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Nuclear Security Engineer</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>$65–75/per-task</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>mercor</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>Apply</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>## About the work
-Mercor is assembling a panel of nuclear materials and safeguards experts to red-team frontier AI models. The goal is to test whether a model can correctly judge the misuse potential of a technical request — answering legitimate questions fully while refusing genuinely dangerous ones.
-You will:
-- Write challenging single-turn prompts in your domain, labelled across three levels: benign, dual-use, and adversarial.
-- Evaluate the responses that come back against a defined policy standard, and judge whether each was handled correctly.
-- Write the reference answer — what a correct response looks like, and the technical reasoning for why.
-This domain lives on the dual-use line more than most. The same material-balance calculation that closes an inspector's account can be used to hide what is missing from it; the same protection assessment that hardens a facility maps its weaknesses. A model that refuses a routine material-accounting question is failing as badly as one that answers a question it shouldn't. Drawing that line reliably is why we need practitioners rather than generalists.
-## Background we're looking for
-We're looking for people who have been responsible for keeping nuclear material where it belongs — material control and accountability, physical protection, and the assessments that test both. What matters most is being able to tell a routine professional question from one that's fishing for something else: the same vulnerability assessment that closes a gap also describes it. You will be writing prompts that sit exactly on that line, then judging whether the model held it.
-Examples of relevant backgrounds (ideally with red-teaming experience):
-- Material control and accountability (MC&amp;A) programme design, operation or assessment at a national laboratory or licensee
-- Physical protection system engineering — sensors, barriers, delay, response force, performance testing
-- Vulnerability assessment and adversary path analysis for nuclear facilities
-- Insider threat and human reliability programme work
-- Nuclear security policy, training or international assistance programmes
-## What this role demands beyond technical depth
-This is writing-intensive work. Every judgment you make needs a written rationale that a non-specialist can follow. Prior technical writing, published research, or expert witness experience is a strong signal; please include a sample or link. You will also be reading and writing about misuse scenarios in your field for sustained periods. We brief experts on this in advance, and you can pause or step away at any point without penalty.
-## Before you apply
-Your work here will not involve, and must not draw on, classified or export-controlled information, or anything covered by an NDA or prepublication review obligation. If you hold such obligations you may still be a good fit; tell us in your application and we will scope the work accordingly.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M106"/>
-  <conditionalFormatting sqref="A2:M106">
+  <autoFilter ref="A1:M99"/>
+  <conditionalFormatting sqref="A2:M99">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L2="New"</formula>
     </cfRule>
@@ -9889,7 +9406,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99 L100 L101 L102 L103 L104 L105 L106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid Status" error="Please select a valid status" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid Status" error="Please select a valid status" type="list">
       <formula1>"New,Opened,Applied,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9992,13 +9509,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs_latest.xlsx
+++ b/jobs_latest.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Latest Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Algorithmic Trading Developer Location: 100% Remote (Continental United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ Years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an experienced Algorithmic Trading Developer to build high-performance trading, pricing, and risk management systems for fintech applications. The ideal candidate will have expertise in C++, Java, or Python , low-latency systems, market data, financial markets, and quantitative development, with experience building scalable, production-grade trading platforms. Key Responsibilities: Design and develop low-latency trading, pricing, and risk systems. Build market data pipelines, backtesting frameworks, and trading tools. Optimize application performance, latency, and throughput. Develop risk, P&amp;L, and analytics solutions. Collaborate with quants, traders, and engineering teams. Troubleshoot production issues and maintain system reliability. Required Qualifications: 6+ years of software engineering experience, preferably in fintech. Strong programming skills in C++, Java, or Python . Experience with low-latency systems, market data, FIX protocol, and financial markets. Strong knowledge of risk management, performance optimization, and concurrency. Preferred Qualifications: Experience with QuantLib , kdb+/q , or GPU-accelerated computing. Familiarity with cloud-native fintech platforms or advanced quantitative methods. Interested in this opportunity? Apply today for immediate consideration! Email your updated resume: Call or Text: (908) 505-3545 Learn more: Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Algorithmic Trading Developer Location: 100% Remote (Continental United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ Years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an experienced Algorithmic Trading Developer to build high-performance trading, pricing, and risk management systems for fintech applications. The ideal candidate will have expertise in C++, Java, or Python , low-latency systems, market data, financial markets, and quantitative development, with experience building scalable, production-grade trading platforms. Key Responsibilities: Design and develop low-latency trading, pricing, and risk systems. Build market data pipelines, backtesting frameworks, and trading tools. Optimize application performance, latency, and throughput. Develop risk, P&amp;L, and analytics solutions. Collaborate with quants, traders, and engineering teams. Troubleshoot production issues and maintain system reliability. Required Qualifications: 6+ years of software engineering experience, preferably in fintech. Strong programming skills in C++, Java, or Python . Experience with low-latency systems, market data, FIX protocol, and financial markets. Strong knowledge of risk management, performance optimization, and concurrency. Preferred Qualifications: Experience with QuantLib , kdb+/q , or GPU-accelerated computing. Familiarity with cloud-native fintech platforms or advanced quantitative methods. Interested in this opportunity? Apply today for immediate consideration! Email your updated resume: &lt;jaya@bvteck.com&gt; Call or Text: (908) 505-3545 Learn more: &lt;www.bvteck.com&gt; Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Oracle Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$130,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+          <t>Oracle Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$130,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt; Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Jenny@bvteck.com&gt; or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
         </is>
       </c>
     </row>
@@ -5246,27 +5246,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>wabtec</t>
+          <t>Recare Deutschland GmbH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Product Security &amp; Network Manager (m/w/d)</t>
+          <t>Lead Security Engineer (m/w/d)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>St. Marienkirchen, Upper Austria, at</t>
+          <t>Remote job</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>smartrecruiters</t>
+          <t>recruitee</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Wabtec/3743990015637443-product-security-network-manager-m-w-d-?oga=true</t>
+          <t>https://careers.recaresolutions.com/o/lead-security-engineer-mwd/c/new</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5297,10 +5297,8 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Aufgaben, die dich bei uns erwarten Übernimm die fachliche und organisatorische Leitung des Product Security &amp; Network Teams und entwickle unsere Security-Prozesse, insbesondere nach Standards wie IEC 62443, kontinuierlich weiter Verantworte die Aktivitäten im Bereich Product Security Incident Response und unterstütze bei der Analyse und Bearbeitung von Cyber-Security-Vorfällen sowie bei Kundenanfragen zu Security-Themen Unterstütze unsere Entwicklungsteams bei der Analyse von Security-Anforderungen und überprüfe deren Umsetzung, unter anderem im Rahmen von Code Reviews Führe Risikoanalysen, Vulnerability Assessments und Penetrationstests durch Bewerte neue Services und Architekturen aus Security-Perspektive Plane und begleite interne sowie externe Cyber-Security-Audits und unterstütze bei der kontinuierlichen Verbesserung unserer Security-Standards und -Prozesse Analysiere regulatorische und technische Anforderungen und leite daraus konkrete Maßnahmen für unsere Produkte und Prozesse ab Konzipiere und führe Schulungen, Workshops und Awareness-Maßnahmen für unterschiedliche Zielgruppen durch
-Für diese Aufgaben bist du genau richtig, wenn du deine Expertise durch ein Studium oder eine Ausbildung sowie mindestens 5 Jahre einschlägige Berufserfahrung im Bereich Cyber Security, Informationssicherheit, Governance, Risk &amp; Compliance oder einem vergleichbaren Umfeld erworben hast – idealerweise mit Erfahrung im OT-Umfeld du über fundierte Netzwerkkenntnisse verfügst und idealerweise zusätzlich Programmierkenntnisse mitbringst du bereits Erfahrung mit Cyber-Security-Standards und regulatorischen Anforderungen wie IEC 62443, ISO 270xx und dem Cyber Resilience Act (CRA) gesammelt hast du bereits Erfahrung in der fachlichen oder disziplinarischen Führung eines Teams mitbringst du ein gutes Verständnis für rechtliche und regulatorische Fragestellungen im Security-Umfeld hast du Freude am direkten Austausch mit Kunden hast und durch deine ausgeprägte Kommunikationsfähigkeit sowie Kunden- und Serviceorientierung überzeugst du technische Themen sicher in die Sprache unterschiedlicher Zielgruppen übersetzen kannst du dich auf Deutsch und Englisch sicher und verständlich ausdrücken kannst
-Wir bieten dir einen sicheren Arbeitsplatz in einem internationalen Umfeld eine agile und offene Unternehmenskultur bis zu zwei Tage Homeoffice pro Woche vielfältige Weiterbildungs- und Entwicklungsmöglichkeiten sowie spannende Projekte, in denen du Verantwortung übernimmst, Gestaltungsspielraum hast und deine Führungskompetenzen gezielt weiterentwickeln kannst ein Firmen-iPhone zur Privatnutzung attraktive Sozialleistungen wie kostenloses Mittagessen, Obst und Kaffee, kostenlose Kinderbetreuung, zahlreiche Sportangebote, Firmenevents und vieles mehr ein Bruttojahresentgelt ab 70.000 EUR - das tatsächliche Entgelt orientiert sich am aktuellen Markt und berücksichtigt Qualifikation und Erfahrung Was könnten Sie erreichen an einem Ort, an dem der Mensch im Mittelpunkt steht? Bei Wabtec ist es mehr als nur ein Job - es geht darum, was Sie bewirken. Wenn wir als Team zusammenarbeiten, erweitern wir die Grenzen des Möglichen, indem wir ständig besser werden - in dem was wir tun und wie wir es tun - sowohl für unsere Kunden als auch füreinander. Wenn Sie bereit sind die Mobilität für kommende Generationen zu revolutionieren, dann sind Sie bei Wabtec genau richtig. Über uns Wabtec ist ein weltweit führender Anbieter von Ausrüstung, Systemen, digitalen Lösungen und Mehrwertdiensten für den Güter- und Nahverkehr. Mit über 150 Jahren Erfahrung setzen wir Maßstäbe in Sicherheit, Effizienz, Zuverlässigkeit, Innovation und Produktivität. Ob Güterverkehr, Nahverkehr, Häfen, Logistik, Bergbau, Industrie oder Schifffahrt – unser Fachwissen, unsere Technologien und unsere Mitarbeitenden gestalten gemeinsam die Zukunft des Transports. Mit Wurzeln, die bis zu George Westinghouse, Thomas Edison und Louis Faiveley zurückreichen, entwickelt Wabtec seit jeher Technologien und setzt Lösungen in wichtigen Branchen um, um den Anforderungen von Kunden und Regierungen gerecht zu werden. Mit rund 30.000 Teammitgliedern weltweit liefern wir Leistungen, die die Welt voranbringen. Wir hören nie auf zu lernen und sind ständig darauf aus, besser zu werden. Erfahren Sie mehr unter &lt;www.WabtecCorp.com&gt;. Unsere Kultur treibt uns und die Möglichkeiten voran Wir glauben, dass die besten Ideen aus einer Mischung unterschiedlicher Erfahrungen und Hintergründe entstehen. Bei Wabtec setzen wir uns jeden Tag dafür ein, einen Ort zu schaffen, an dem sich jeder zugehörig fühlt. Wir bauen eine Unternehmenskultur auf, in der Führung, Inklusion und deine einzigartige Perspektive den Fortschritt vorantreiben. Wir sind stolz darauf, ein Arbeitgeber mit Chancengleichheit zu sein. Wir heißen Talente aller Hintergründe, Erfahrungen und Identitäten willkommen, einschließlich Hautfarbe, Geschlecht, Alter, Behinderung, Veteranenstatus und mehr. Sie benötigen Unterstützung oder Anpassung? Sagen Sie uns einfach Bescheid – wir sind für Sie da.
-Hast du die Weichen für deine Zukunft gestellt? Wir geben grünes Licht! Denn bei Frauscher haben wir den Fortschritt stets fest im Blick. Lass uns diesen Weg gemeinsam gehen! Unsere Agilität und unsere Begeisterung für Neues spiegeln sich in unseren innovativen Technologien und Services wider – und natürlich auch in unserer Unternehmenskultur. Werde jetzt Teil von Frauscher und starte deine berufliche Zukunft beim Technologieführer! Bei Frauscher setzen wir uns dafür ein, die zuverlässigsten Lösungen für die Zugdetektion und die Steuerung von Objekten im Gleisbereich weltweit bereitzustellen. Unsere branchenführenden Feldkomponenten, Softwarelösungen, Konnektivitäts- und Datenzugriffslösungen in Kombination mit intelligenten Lifecycle-Services stellen sicher, dass systemkritische Komponenten zuverlässig funktionieren und Bahnbetreibern die Informationen zur Verfügung stehen, die sie benötigen, um die Sicherheit, Effizienz und Kapazität ihrer Schienennetze zu maximieren. Wir schaffen die verlässliche Grundlage, die Betreiber für einen sicheren und effizienten Bahnbetrieb benötigen – „Your partner for confidence.“</t>
+          <t>Lead Security Engineer (m/w/d) About Recare As one of the leading German HealthTech companies, we are reshaping discharge management – technology-driven, patient-centered, and free from bureaucracy. In addition to our market-leading SaaS platform, we develop AI solutions that radically simplify processes in hospitals and for aftercare providers, relieve healthcare professionals, and refocus attention on patients. Today, we already connect two-thirds of all German hospitals with over 650 rehabilitation clinics and 25,000 nursing and homecare providers. With currently around 120 employees from a broad range of nations, we continue to grow – and we're now going far beyond our core business, aiming to eliminate bureaucracy and admin in hospitals with a whole portfolio of AI products. What to expect as our Lead Security Engineer (m/w/d): Purposeful work – your role will have a positive impact on patients, their families, and healthcare professionals. Company culture – we believe in flat hierarchies that promote high performance and strong team dynamics. We foster an environment characterized by mutual respect, loyalty, and recognition. Together, we strive for our goals – and expect the same from you. Flexibility – want to pick up your child from daycare? Like to exercise during lunch? We'll support you. We are a remote-friendly company offering flexible working hours. Workations are also possible by arrangement. Edenred card – which you can use according to your needs. Extra vacation day – so you can celebrate your birthday with your loved ones, you'll have the day off. In this role, you can make an impact and grow with us as Lead Security Engineer (m/w/d): You'll be our first dedicated security engineer: a senior IC with no team at the start. You join as Deputy CISO, report to our Director of Technology (currently acting CISO), and build security engineering from scratch. The baseline is already in place – ISO 27001, C5 Type II, regular penetration tests, and encryption in the product. AI is adding new surfaces: voice documentation, document generation, and agentic workflows. You build and own the security program, the tooling, and the security story we tell customers. Vulnerability management – scanners and dependency updates across repos, plus the process that gets findings closed. Partner to Platform – review security-sensitive infrastructure decisions and explore options like customer-managed keys or HSMs. Platform still owns architecture. Certifications, technical side – control design and assessments for our ISO 27001 and C5 setup, the security case for a potential upcoming Class IIa medical device (MDR), and pentest scoping and follow-up, with regulation like the EU Cyber Resilience Act on the horizon. This is roughly a quarter to a third of the role, and we say it openly: for the right person in healthcare security, it's a draw, not a chore. Customer security – reusable docs, evidence, and AI-assisted questionnaires, so the tenth enterprise deal costs a fraction of the first. You join the call when a hospital CISO asks something new about our AI architecture. Incident response – process, runbooks, and escalation, and you lead when it's real. We're too small for a SOC, so you design on-call that fits a company our size. Product incidents and platform bugs have their own owners in engineering. Company-wide security – watch the threat landscape, turn this week's supply-chain mess into concrete actions, and set the baselines IT applies to devices and accounts. How we work: AI-native – our engineers use coding agents every day. Security should too: scanning, evidence, questionnaires. AI is also our attack surface – agent sandboxing, prompt injection, voice data, computer-use automation inside hospitals. We deal with security questions most companies will only meet in a few years. Human-in-the-loop by default – this is healthcare: AI proposes, people stay in control. Ship and observe – we ship continuously and debug from telemetry, including in the open when that's the fastest path.
+Here's how we picture you as our Lead Security Engineer (m/w/d): You're a hands-on security engineer with 6+ years across software and security engineering, and you can point to a security program (or a big part of one) you've owned. You've been the technical counterpart through at least one ISO 27001, C5, or SOC 2 certification cycle: you've designed controls, faced an auditor, and written the technical side of a Statement of Applicability. This is a hard requirement. You've run vulnerability management somewhere real: scanners, dependency bots, triage, and the follow-through that gets things fixed. You follow the security scene closely (podcasts, advisories, incident write-ups) and usually have an opinion on this week's incident before it reaches the news. You're genuinely curious about AI security – both securing AI systems (agents, sandboxing, data flows) and using AI tooling to work at leverage. You can talk to engineers, auditors, and hospital security teams in English without a slide deck translating for you. Nice to have: German language skills, since our customers and the C5 world are German-speaking. Experience in healthcare or another regulated domain. Offensive security experience. Security certifications such as OSCP, CISSP, or similar.</t>
         </is>
       </c>
     </row>
@@ -5312,60 +5310,123 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>wabtec</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Product Security &amp; Network Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>St. Marienkirchen, Upper Austria, at</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Wabtec/3743990015637443-product-security-network-manager-m-w-d-?oga=true</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Aufgaben, die dich bei uns erwarten Übernimm die fachliche und organisatorische Leitung des Product Security &amp; Network Teams und entwickle unsere Security-Prozesse, insbesondere nach Standards wie IEC 62443, kontinuierlich weiter Verantworte die Aktivitäten im Bereich Product Security Incident Response und unterstütze bei der Analyse und Bearbeitung von Cyber-Security-Vorfällen sowie bei Kundenanfragen zu Security-Themen Unterstütze unsere Entwicklungsteams bei der Analyse von Security-Anforderungen und überprüfe deren Umsetzung, unter anderem im Rahmen von Code Reviews Führe Risikoanalysen, Vulnerability Assessments und Penetrationstests durch Bewerte neue Services und Architekturen aus Security-Perspektive Plane und begleite interne sowie externe Cyber-Security-Audits und unterstütze bei der kontinuierlichen Verbesserung unserer Security-Standards und -Prozesse Analysiere regulatorische und technische Anforderungen und leite daraus konkrete Maßnahmen für unsere Produkte und Prozesse ab Konzipiere und führe Schulungen, Workshops und Awareness-Maßnahmen für unterschiedliche Zielgruppen durch Für diese Aufgaben bist du genau richtig, wenn du deine Expertise durch ein Studium oder eine Ausbildung sowie mindestens 5 Jahre einschlägige Berufserfahrung im Bereich Cyber Security, Informationssicherheit, Governance, Risk &amp; Compliance oder einem vergleichbaren Umfeld erworben hast – idealerweise mit Erfahrung im OT-Umfeld du über fundierte Netzwerkkenntnisse verfügst und idealerweise zusätzlich Programmierkenntnisse mitbringst du bereits Erfahrung mit Cyber-Security-Standards und regulatorischen Anforderungen wie IEC 62443, ISO 270xx und dem Cyber Resilience Act (CRA) gesammelt hast du bereits Erfahrung in der fachlichen oder disziplinarischen Führung eines Teams mitbringst du ein gutes Verständnis für rechtliche und regulatorische Fragestellungen im Security-Umfeld hast du Freude am direkten Austausch mit Kunden hast und durch deine ausgeprägte Kommunikationsfähigkeit sowie Kunden- und Serviceorientierung überzeugst du technische Themen sicher in die Sprache unterschiedlicher Zielgruppen übersetzen kannst du dich auf Deutsch und Englisch sicher und verständlich ausdrücken kannst Wir bieten dir einen sicheren Arbeitsplatz in einem internationalen Umfeld eine agile und offene Unternehmenskultur bis zu zwei Tage Homeoffice pro Woche vielfältige Weiterbildungs- und Entwicklungsmöglichkeiten sowie spannende Projekte, in denen du Verantwortung übernimmst, Gestaltungsspielraum hast und deine Führungskompetenzen gezielt weiterentwickeln kannst ein Firmen-iPhone zur Privatnutzung attraktive Sozialleistungen wie kostenloses Mittagessen, Obst und Kaffee, kostenlose Kinderbetreuung, zahlreiche Sportangebote, Firmenevents und vieles mehr ein Bruttojahresentgelt ab 70.000 EUR - das tatsächliche Entgelt orientiert sich am aktuellen Markt und berücksichtigt Qualifikation und Erfahrung Was könnten Sie erreichen an einem Ort, an dem der Mensch im Mittelpunkt steht? Bei Wabtec ist es mehr als nur ein Job - es geht darum, was Sie bewirken. Wenn wir als Team zusammenarbeiten, erweitern wir die Grenzen des Möglichen, indem wir ständig besser werden - in dem was wir tun und wie wir es tun - sowohl für unsere Kunden als auch füreinander. Wenn Sie bereit sind die Mobilität für kommende Generationen zu revolutionieren, dann sind Sie bei Wabtec genau richtig. Über uns Wabtec ist ein weltweit führender Anbieter von Ausrüstung, Systemen, digitalen Lösungen und Mehrwertdiensten für den Güter- und Nahverkehr. Mit über 150 Jahren Erfahrung setzen wir Maßstäbe in Sicherheit, Effizienz, Zuverlässigkeit, Innovation und Produktivität. Ob Güterverkehr, Nahverkehr, Häfen, Logistik, Bergbau, Industrie oder Schifffahrt – unser Fachwissen, unsere Technologien und unsere Mitarbeitenden gestalten gemeinsam die Zukunft des Transports. Mit Wurzeln, die bis zu George Westinghouse, Thomas Edison und Louis Faiveley zurückreichen, entwickelt Wabtec seit jeher Technologien und setzt Lösungen in wichtigen Branchen um, um den Anforderungen von Kunden und Regierungen gerecht zu werden. Mit rund 30.000 Teammitgliedern weltweit liefern wir Leistungen, die die Welt voranbringen. Wir hören nie auf zu lernen und sind ständig darauf aus, besser zu werden. Erfahren Sie mehr unter . Unsere Kultur treibt uns und die Möglichkeiten voran Wir glauben, dass die besten Ideen aus einer Mischung unterschiedlicher Erfahrungen und Hintergründe entstehen. Bei Wabtec setzen wir uns jeden Tag dafür ein, einen Ort zu schaffen, an dem sich jeder zugehörig fühlt. Wir bauen eine Unternehmenskultur auf, in der Führung, Inklusion und deine einzigartige Perspektive den Fortschritt vorantreiben. Wir sind stolz darauf, ein Arbeitgeber mit Chancengleichheit zu sein. Wir heißen Talente aller Hintergründe, Erfahrungen und Identitäten willkommen, einschließlich Hautfarbe, Geschlecht, Alter, Behinderung, Veteranenstatus und mehr. Sie benötigen Unterstützung oder Anpassung? Sagen Sie uns einfach Bescheid – wir sind für Sie da. Hast du die Weichen für deine Zukunft gestellt? Wir geben grünes Licht! Denn bei Frauscher haben wir den Fortschritt stets fest im Blick. Lass uns diesen Weg gemeinsam gehen! Unsere Agilität und unsere Begeisterung für Neues spiegeln sich in unseren innovativen Technologien und Services wider – und natürlich auch in unserer Unternehmenskultur. Werde jetzt Teil von Frauscher und starte deine berufliche Zukunft beim Technologieführer! Bei Frauscher setzen wir uns dafür ein, die zuverlässigsten Lösungen für die Zugdetektion und die Steuerung von Objekten im Gleisbereich weltweit bereitzustellen. Unsere branchenführenden Feldkomponenten, Softwarelösungen, Konnektivitäts- und Datenzugriffslösungen in Kombination mit intelligenten Lifecycle-Services stellen sicher, dass systemkritische Komponenten zuverlässig funktionieren und Bahnbetreibern die Informationen zur Verfügung stehen, die sie benötigen, um die Sicherheit, Effizienz und Kapazität ihrer Schienennetze zu maximieren. Wir schaffen die verlässliche Grundlage, die Betreiber für einen sicheren und effizienten Bahnbetrieb benötigen – „Your partner for confidence.“</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>thought-machine</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Application Security Engineer</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Portugal, Lisbon</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>€75K – €95K</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/thought-machine/32e446af-e8e2-43e0-90d0-d8cfbfcc0468/application</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>Thought Machine's mission is bold – to properly and permanently rid the world's banks of legacy technology. To achieve this, we have developed the foundations of modern banking through core and payments technology which run natively in the cloud. What we are attempting is hard and means we need great people working together to build great technology.
 We have grown rapidly in the past few years – growing our team to more than 550 individuals across offices in London, New York, Singapore, Sydney and our newly established Engineering Hub in Lisbon. We have raised more than £500m in funding and our investors include Molten Ventures, Eurazeo, Intesa Sanpaolo, Temasek, Nyca Partners, JPMorgan Chase Strategic Investments, Standard Chartered Ventures, and more.
@@ -5416,68 +5477,68 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>thought-machine</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Application  Security Engineer</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Portugal, Lisbon</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>€50K – €75K</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/thought-machine/04cb6076-8265-44d3-9aa6-5f8a2d4e371e/application</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>Thought Machine's mission is bold – to properly and permanently rid the world's banks of legacy technology. To achieve this, we have developed the foundations of modern banking through core and payments technology which run natively in the cloud. What we are attempting is hard and means we need great people working together to build great technology.
 We have grown rapidly in the past few years – growing our team to more than 550 individuals across offices in London, New York, Singapore, Sydney and our newly established Engineering Hub in Lisbon. We have raised more than £500m in funding and our investors include Molten Ventures, Eurazeo, Intesa Sanpaolo, Temasek, Nyca Partners, JPMorgan Chase Strategic Investments, Standard Chartered Ventures, and more.
@@ -5528,60 +5589,124 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sword Technologies N.V./S.A.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IT Operations and security engineer - Linux/Swift</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Brussels, Brussels, Belgium</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>https://swordtechnologies.recruitee.com/o/it-operations-and-security-engineer-linuxswift/c/new</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>The Expert in IT Operations will work mainly in the context of the various components managed by the client, covering the entire processes including the SWIFT/EastNets components. It will include NGEU and Bloomberg/Eurex support and local applications. Linux will be the main OS to support (included related tools and utilities). The Expert in IT Operations will, amongst other things, ensure the best practices for security are put in place, check the operational "good working" of the IT components, run periodic tests concerning the SWIFT/Bloomberg related processes, assist Treasury unit and Infrastructure unit in terms of Business Continuity and Security matters, participate to the evolution of the scope of activities concerned. He/she will assist on request the LISO the implementation of the security policies. He/she will support the monitoring and evolution of the products and will perform installations and upgrades; he will implement and setup new infrastructure and software and support; resolve technical bugs; he will support the publication/running of applications on various media and ensure the right security is put in place.
+Requirements Strong experience in Linux system administration Proven experience with SWIFT / EastNets and payment services Experience in IT Operations and infrastructure management Knowledge of Windows, virtualisation and SAN/storage Experience with monitoring, troubleshooting and 2nd-line support Knowledge of backup &amp; restore, security and SSL certificates Experience with infrastructure/software installation and upgrades Knowledge of Business Continuity and IT security practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>veeamsoftware</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Technical Program Manager, Application Security</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/veeamsoftware/jobs/4986547101</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>Veeam is the Data and AI Trust Company, specializing in helping organizations ensure their data and AI are fully understood, secured, and resilient to enable the acceleration of safe AI at scale. As the market leader in both data resilience and data security posture management, Veeam is built for the convergence of identity, data, security, and AI risk. Headquartered in Seattle with offices in more than 30 countries, Veeam protects over 550,000 customers worldwide, who trust Veeam to keep their businesses running. Join us as we go fearlessly forward together, growing, learning, and making a real impact for some of the world’s biggest brands.
 #### **About the Role**
@@ -5620,60 +5745,60 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>veeamsoftware</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Technical Program Manager, Application Security</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Warsaw, Poland</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/veeamsoftware/jobs/4986544101</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>Veeam is the Data and AI Trust Company, specializing in helping organizations ensure their data and AI are fully understood, secured, and resilient to enable the acceleration of safe AI at scale. As the market leader in both data resilience and data security posture management, Veeam is built for the convergence of identity, data, security, and AI risk. Headquartered in Seattle with offices in more than 30 countries, Veeam protects over 550,000 customers worldwide, who trust Veeam to keep their businesses running. Join us as we go fearlessly forward together, growing, learning, and making a real impact for some of the world’s biggest brands.
 #### **About the Role**
@@ -5716,60 +5841,60 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>veeamsoftware</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Technical Program Manager, Application Security</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Prague, Czechia</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/veeamsoftware/jobs/4763789101</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>Veeam is the Data and AI Trust Company, specializing in helping organizations ensure their data and AI are fully understood, secured, and resilient to enable the acceleration of safe AI at scale. As the market leader in both data resilience and data security posture management, Veeam is built for the convergence of identity, data, security, and AI risk. Headquartered in Seattle with offices in more than 30 countries, Veeam protects over 550,000 customers worldwide, who trust Veeam to keep their businesses running. Join us as we go fearlessly forward together, growing, learning, and making a real impact for some of the world’s biggest brands.
 #### **About the Role**
@@ -5811,60 +5936,60 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>axonius</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Copy of Product Security Architect- 9-month temp position</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>https://www.axonius.com/company/careers/open-jobs?gh_jid=8004240003</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>**This is a 9-month temporary position**
 As a **Product Security Architect**, you will join a highly technical, fast-moving Product Security team to advance and secure Axonius's platform and its modern AI-driven capabilities. Operating in an environment with deep R&amp;D collaboration and a hybrid schedule, you will own the development lifecycle's security strategy, ensuring modern cloud and distributed systems are engineered safely by design. This role directly supports core development teams across Israel and Portugal, ensuring robust posture alignment from initial planning through deployment.
@@ -5896,64 +6021,64 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>LACROIX1</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Security Architect (m/w/d)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Cologne, NRW, de</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/LACROIX1/744000151579557-security-architect-m-w-d-?oga=true</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>Du begeisterst dich für Cyber Security, denkst in Architekturen und möchtest aktiv dazu beitragen, kritische Infrastrukturen gegen Cyber-Angriffe zu schützen? Dann trage mit uns zum Gelingen der Energiewende bei! Für unser Entwicklungsteam suchen wir dich als Security Architect (m/w/d) . Dein Part Security Architecture &amp; Product Security Du gestaltest die sicherheitskritischen Aspekte und Security-Anforderungen der Software- und Hardware-Architektur unserer Produkte und begleitest deren Umsetzung im Team. Du unterstützt dabei, unsere Lösungen für die kritische Infrastruktur, insbesondere im Stromsektor, gegen Cyber-Angriffe abzusichern. Strategie &amp; Zusammenarbeit Du arbeitest eng mit Stakeholdern wie Product Management zusammen und gestaltest die strategische Ausrichtung unserer Security-Themen aktiv mit. Als Experte berätst und schulst du intern und extern verschiedenste Zielgruppen, von Entwicklung und QA über Management und Support bis hin zu unseren Kunden. Prozesse &amp; Vulnerability Management Du gestaltest Prozesse zur Verbesserung von Abläufen, Wissensmanagement und Informationsfluss und begleitest unseren Vulnerability-Management-Prozess von der technischen Analyse bis zur Nachverfolgung von Sicherheitslücken. Compliance &amp; Regulierung Du navigierst regulatorische Anforderungen und begleitest Compliance-Themen wie Zertifizierungen und Selbsterklärungen.
 Das bringst du mit: Erfahrung: Mehrjährige Berufserfahrung im Bereich IT Security in enger Zusammenarbeit mit der Softwareentwicklung; Erfahrung im Embedded- oder IoT-Umfeld ist von Vorteil. Technisches Know-how: Grundlegende Programmiererfahrung in hardwarenahen Sprachen wie C und C++. Methoden: Begeisterung für agile Arbeitsweisen und praktische Erfahrung in agilen Entwicklungsumgebungen. Kommunikation: Freude an der Zusammenarbeit mit Menschen unterschiedlicher Fachbereiche und Hintergründe. Compliance &amp; Standards: Erfahrung im Umgang mit Standards und regulatorischen Anforderungen; Kenntnisse von IEC 62443-4-1/-2, EU RED oder CRA sind von Vorteil. Sprachen: Fließende Deutsch- und Englischkenntnisse in Wort und Schrift.
@@ -5962,64 +6087,64 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>inetum2</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Lisbon, Lisbon, pt</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Inetum2/744000151573629-cybersecurity-engineer?oga=true</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>We are looking for a Cybersecurity Engineer to support security operations through SIEM administration, systems management, automation, and security solution integration. The role combines Windows and Linux administration with cybersecurity engineering activities and collaboration on security initiatives. Main Responsibilities Administer and maintain Windows and Linux environments. Manage and administer SIEM platforms. Implement and maintain security playbooks. Develop APIs to support cybersecurity initiatives. Integrate security solutions across the technology landscape. Support security monitoring and operational activities.
 Experience with Microsoft Sentinel. Experience administering Windows and Linux Systems. Experience with SIEM administration. Experience implementing playbooks. Experience developing APIs. Knowledge of Microsoft Azure and Python. Professional proficiency in English.
@@ -6028,64 +6153,64 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Betclic Group</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer -  Authentication, Identity &amp; Payments F/M</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Bordeaux, FR</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>breezy</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>https://betclic-group.breezy.hr/p/8f8ec99753ae01-cybersecurity-engineer-authentication-identity-payments-f-m</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>WE ARE BETCLIC
 🎯
@@ -6165,131 +6290,131 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>usfintech</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Lead, Security Engineer V&amp;CM</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>US-Remote</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Yes / Mentioned</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>icims</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>https://careers-usfintech.icims.com/jobs/2409/lead%2c-security-engineer-v%26cm/job?in_iframe=1</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>OVERVIEW The Company U.S. Financial Technology (U.S. FinTech) is seeking an experienced Lead, Security Engineer Vulnerability and Configuration Management to join our team of talented professionals. This is a full-time remote opportunity. U.S. FinTech built and operates the largest and most advanced mortgage securitization platform in the world, supporting the Uniform Mortgage-Backed Security (UMBS) of Fannie Mae and Freddie Mac. Supporting 70% of the mortgage-backed securities in the market, U.S. FinTech provides best-in-class single-family issuance, bond administration, disclosure, and tax services. We support a broad portfolio of products for our clients with full lifecycle management. Our market-leading, cloud-based, end-to-end platform executes transactions on an extraordinary scale which has bolstered liquidity in the secondary mortgage market, one of the largest and most important financial markets in the world. Our unique approach to securitization combines the best minds in financial services with the know-how, flexibility, and innovation of leading technologists. RESPONSIBILITIES Job Information The Lead Vulnerability and Compliance Analyst main responsibilities would be to act as a Subject Matter Expert for all programs within the VCM space. This would include conducting comprehensive vulnerability assessments using tools such as Wiz and Tenable. Leverage strong analytical and problem-solving skills to identify weaknesses in US FinTech’s IT Infrastructure. Communicate findings effectively, via reports/meetings to prioritize vulnerability remediation. Utilize the developed processes to track, prioritize, and ensure remediation of found vulnerability and compliance issues. Continuous monitor US FinTech infrastructure for Vulnerability and Compliance related issues. Make Improvements to monitors, scans, dashboards, and reporting. Ability to work independently and in a team environment, collaborate effectively with other InfoSec Teams and IT Infrastructure teams. Eager to learn and adapt to emerging cloud technologies and tools in a fast-paced environment. Key Job Functions Vulnerability Assessment Act as a Subject Matter Expert for the VCM program, processes, and tooling. Configure, tune, and maintain vulnerability management tools Work with Security Architecture on new build outs, new business, new technologies, new environments to ensure coverage of VCM programs, processes, and tooling. Build out new Security baselines for CIS, DISA STIG, and custom baselines. Correlate Vulnerabilities with threat intelligence to assess exploitability and risk. Work with Cyber Security Operations Center to ensure mitigations are in place while vulnerabilities are being remediated Provide detailed risk assessments for discovered vulnerabilities. Enforce remediation timelines in accordance with Standard Operating Procedures. Remediation Tracking &amp; Reporting Collaborate with IT and DevOps teams to ensure timely remediation of vulnerabilities Conduct regular and ad-hoc vulnerability scans using tools like Wiz or Tenable Integrate tools with all cloud environments. Ensure complete coverage of all IT environments. Ensure alignment with internal security policies, regulatory requirements (NIST/SOC), and industry best practices. Support audits and assessments by providing evidence and documentation. Stakeholder Engagement Act as a liaison between security, IT, development, and risk teams Provide clear, actionable recommendations tailored to technical and non-technical audiences. Mentor Junior Analysts Provide guidance and training to junior members of the VCM team. Process Improvements Identify potential gaps in the vulnerability or compliance management programs and propose improvements. Develop and maintain Standard Operating Procedures, Frameworks, and Job Aids/HowTos. QUALIFICATIONS Education Bachelor's Degree or equivalent &lt;required.BA/BS&gt; degree in Computer Science, Information Systems, Cyber Security or a related technical field. Master’s Degree is a plus. Minimum Experience Minimum of 7 years of experience with security engineering and operations, as well as experience managing and supporting large, complex mission-critical systems and with Vulnerability management tools, patching processes and tools, VM operation/workflow, or configuration/Baseline/File-integrity monitoring applications and processes. Applicants must be authorized to work in the US without requiring employer sponsorship currently or in the future. U.S. FinTech does not offer H-1B sponsorship for this position. Specialized Knowledge &amp; Skills Subject matter expert of cloud based critical infrastructure systems and security threats for these systems (AWS Cloud experience required). Subject matter expert with cyber security in the domains of vulnerability and compliance management. Familiarity with latest security vulnerabilities, advisories, incidents, penetration techniques, understanding of attacks, and determination of countermeasures. Strong understanding of AI Models, technologies, attack paths, vulnerabilities, and securing AI tools or technologies. Experience leveraging AI models to identify, research, or remediate vulnerabilities. Subject matter expert of network and system vulnerabilities, malware, networking protocols, multi-tiered applications, and attack methods to exploit vulnerabilities. Experience in senior technical security role, including network security, operating system security, Internet or Web security, and vulnerability testing. Strong knowledge of networking fundamentals such as TCP/IP and basic packet analysis, network engineering, and local and wide area (LAN/WAN) technologies and topologies. Must have experience conducting comprehensive vulnerability assessments with vulnerability monitoring tools (Wiz and Tenable). General knowledge and experience in Windows / Linux Operating Systems, baseline security configurations, audit, forensics, Patch Management for these OSs. Experience developing Standard Operating Procedures (SOPs), job aids, and hands-on training materials. Be able to work in fast paced environment with occasional on-call activities. Excellent interpersonal skills, presentation skills, and verbal / written communication skills. Self-starter; adaptable to change; motivated to set personal and program goals and pro-actively track performance against goals and initiatives. Ability to manage multiple priorities – projects, deliverables, and stakeholders. Ability to influence peers and management; ability to team cross-functionally and form relationships to achieve objectives. Active in the security industry; equipped with external networking relationships to maintain relevant knowledge of best practices, tactics, strategies and technologies. AWS Security, AWS Architect certifications desired. Pay Range $156,500 to $181,000 U.S. FinTech's pay range for this job level is a general guideline only and not a guarantee of compensation or salary. Additional factors considered in extending an offer include (but are not limited to) a candidate’s qualifications, skills, competencies, and experience, as well as internal equity, alignment with market data, applicable bargaining agreement (if any), or other law. U.S. FinTech offers a competitive total compensation package, which includes a performance bonus, 401k match, healthcare coverage, PTO, and a broad range of other benefits. Employment As a condition of employment with U.S. Financial Technology, any successful job applicant will be required to successfully complete a background investigation, which may also include a credit check for positions in some areas of our business. U.S. Financial Technology is an Equal Opportunity Employer. ##LI-Remote</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>OVERVIEW The Company U.S. Financial Technology (U.S. FinTech) is seeking an experienced Lead, Security Engineer Vulnerability and Configuration Management to join our team of talented professionals. This is a full-time remote opportunity. U.S. FinTech built and operates the largest and most advanced mortgage securitization platform in the world, supporting the Uniform Mortgage-Backed Security (UMBS) of Fannie Mae and Freddie Mac. Supporting 70% of the mortgage-backed securities in the market, U.S. FinTech provides best-in-class single-family issuance, bond administration, disclosure, and tax services. We support a broad portfolio of products for our clients with full lifecycle management. Our market-leading, cloud-based, end-to-end platform executes transactions on an extraordinary scale which has bolstered liquidity in the secondary mortgage market, one of the largest and most important financial markets in the world. Our unique approach to securitization combines the best minds in financial services with the know-how, flexibility, and innovation of leading technologists. RESPONSIBILITIES Job Information The Lead Vulnerability and Compliance Analyst main responsibilities would be to act as a Subject Matter Expert for all programs within the VCM space. This would include conducting comprehensive vulnerability assessments using tools such as Wiz and Tenable. Leverage strong analytical and problem-solving skills to identify weaknesses in US FinTech’s IT Infrastructure. Communicate findings effectively, via reports/meetings to prioritize vulnerability remediation. Utilize the developed processes to track, prioritize, and ensure remediation of found vulnerability and compliance issues. Continuous monitor US FinTech infrastructure for Vulnerability and Compliance related issues. Make Improvements to monitors, scans, dashboards, and reporting. Ability to work independently and in a team environment, collaborate effectively with other InfoSec Teams and IT Infrastructure teams. Eager to learn and adapt to emerging cloud technologies and tools in a fast-paced environment. Key Job Functions Vulnerability Assessment Act as a Subject Matter Expert for the VCM program, processes, and tooling. Configure, tune, and maintain vulnerability management tools Work with Security Architecture on new build outs, new business, new technologies, new environments to ensure coverage of VCM programs, processes, and tooling. Build out new Security baselines for CIS, DISA STIG, and custom baselines. Correlate Vulnerabilities with threat intelligence to assess exploitability and risk. Work with Cyber Security Operations Center to ensure mitigations are in place while vulnerabilities are being remediated Provide detailed risk assessments for discovered vulnerabilities. Enforce remediation timelines in accordance with Standard Operating Procedures. Remediation Tracking &amp; Reporting Collaborate with IT and DevOps teams to ensure timely remediation of vulnerabilities Conduct regular and ad-hoc vulnerability scans using tools like Wiz or Tenable Integrate tools with all cloud environments. Ensure complete coverage of all IT environments. Ensure alignment with internal security policies, regulatory requirements (NIST/SOC), and industry best practices. Support audits and assessments by providing evidence and documentation. Stakeholder Engagement Act as a liaison between security, IT, development, and risk teams Provide clear, actionable recommendations tailored to technical and non-technical audiences. Mentor Junior Analysts Provide guidance and training to junior members of the VCM team. Process Improvements Identify potential gaps in the vulnerability or compliance management programs and propose improvements. Develop and maintain Standard Operating Procedures, Frameworks, and Job Aids/HowTos. QUALIFICATIONS Education Bachelor's Degree or equivalent degree in Computer Science, Information Systems, Cyber Security or a related technical field. Master’s Degree is a plus. Minimum Experience Minimum of 7 years of experience with security engineering and operations, as well as experience managing and supporting large, complex mission-critical systems and with Vulnerability management tools, patching processes and tools, VM operation/workflow, or configuration/Baseline/File-integrity monitoring applications and processes. Applicants must be authorized to work in the US without requiring employer sponsorship currently or in the future. U.S. FinTech does not offer H-1B sponsorship for this position. Specialized Knowledge &amp; Skills Subject matter expert of cloud based critical infrastructure systems and security threats for these systems (AWS Cloud experience required). Subject matter expert with cyber security in the domains of vulnerability and compliance management. Familiarity with latest security vulnerabilities, advisories, incidents, penetration techniques, understanding of attacks, and determination of countermeasures. Strong understanding of AI Models, technologies, attack paths, vulnerabilities, and securing AI tools or technologies. Experience leveraging AI models to identify, research, or remediate vulnerabilities. Subject matter expert of network and system vulnerabilities, malware, networking protocols, multi-tiered applications, and attack methods to exploit vulnerabilities. Experience in senior technical security role, including network security, operating system security, Internet or Web security, and vulnerability testing. Strong knowledge of networking fundamentals such as TCP/IP and basic packet analysis, network engineering, and local and wide area (LAN/WAN) technologies and topologies. Must have experience conducting comprehensive vulnerability assessments with vulnerability monitoring tools (Wiz and Tenable). General knowledge and experience in Windows / Linux Operating Systems, baseline security configurations, audit, forensics, Patch Management for these OSs. Experience developing Standard Operating Procedures (SOPs), job aids, and hands-on training materials. Be able to work in fast paced environment with occasional on-call activities. Excellent interpersonal skills, presentation skills, and verbal / written communication skills. Self-starter; adaptable to change; motivated to set personal and program goals and pro-actively track performance against goals and initiatives. Ability to manage multiple priorities – projects, deliverables, and stakeholders. Ability to influence peers and management; ability to team cross-functionally and form relationships to achieve objectives. Active in the security industry; equipped with external networking relationships to maintain relevant knowledge of best practices, tactics, strategies and technologies. AWS Security, AWS Architect certifications desired. Pay Range $156,500 to $181,000 U.S. FinTech's pay range for this job level is a general guideline only and not a guarantee of compensation or salary. Additional factors considered in extending an offer include (but are not limited to) a candidate’s qualifications, skills, competencies, and experience, as well as internal equity, alignment with market data, applicable bargaining agreement (if any), or other law. U.S. FinTech offers a competitive total compensation package, which includes a performance bonus, 401k match, healthcare coverage, PTO, and a broad range of other benefits. Employment As a condition of employment with U.S. Financial Technology, any successful job applicant will be required to successfully complete a background investigation, which may also include a credit check for positions in some areas of our business. U.S. Financial Technology is an Equal Opportunity Employer. ##LI-Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>runway-ml</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Infrastructure Security Engineer</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>$240K – $290K</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/runway-ml/0c750d2f-f894-4c8d-8b47-f03ddbb794a6/application</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>We are building AI to simulate the world through merging art and science.  
 We believe that world models are at the frontier of progress in artificial intelligence. Language models alone won’t solve the world’s hardest problems – robotics, disease, scientific discovery. Real progress requires models that experience the world and learn from their mistakes, the same way that humans do. And this kind of trial and error can be massively accelerated when done in simulation, rather than in the real world.  
@@ -6342,64 +6467,64 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>ZoomInfo</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Senior Security Architecture Director</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/lrZsGX/jobs/senior-security-architecture-director_dublin_lvvewbyb</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>Join ZoomInfo as the Senior Director of Security Architecture, a leadership role responsible for overseeing the creation and ongoing maintenance of the company's security architecture. You will lead a team of security architects and engineers, develop and execute a vision for the organization's security architecture, and collaborate with stakeholders to drive the adoption of security practices. This role offers competitive compensation, bonuses, equity, flexible paid time off, and a hybrid working model.
 - Oversight of the creation and ongoing maintenance of ZoomInfo’s security architecture, leading the Security Architecture team.
@@ -6413,123 +6538,147 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/ZB4iFN/jobs/security-engineer_amsterdam_gacdzzgq</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Join as an Application Security Engineer, where you will play a crucial role in safeguarding the security and privacy of our customers. You will build and operate advanced security tooling, automate remediation, analyze security indicators, and partner with product teams to embed security throughout the software development lifecycle. Your expertise will directly contribute to the detection, prevention, and response to application security threats across our global platform. - Identifying and explaining common application security risks, providing practical remediation guidance to development teams. - Building and operating advanced security tooling, automating remediation, and analyzing security indicators to enhance application security. - Collaborating with software engineers, platform teams, and security colleagues to embed security throughout the software development lifecycle. - Some experience with application security tools, such as SAST, DAST, software composition analysis, vulnerability scanners, or secrets-scanning tools - Bachelor’s or Master’s degree in Computer Science or a related field - 3+ years of relevant industry experience - Familiarity with common risks such as injection, broken access control, authentication failures, security misconfiguration, cross-site scripting, and insecure dependencies - Ability to work effectively with developers and other technical teams - Ability to communicate security findings clearly and constructively - Basic to intermediate knowledge of application and web security - Familiarity with HTTP, APIs, authentication, authorization, and TLS - Analytical mindset, attention to detail, and willingness to learn - Basic scripting or automation skills in Python, Bash, or a similar language - Basic understanding of how LLM applications work, including prompts, model inputs and outputs, retrieval-augmented generation, and tool or API integrations - Understanding of the OWASP Top 10 and basic secure coding principles - Ability to read and understand code in at least one programming language - Basic understanding of how to secure LLM applications through input and output validation, data minimisation, access control, least privilege, rate limiting, logging, and human approval for high-impact actions - Experience with cloud platforms, containers, or infrastructure as code - Familiarity with API security or microservices - Experience with threat modelling or security testing - Experience or interest in securing AI or LLM-enabled applications - Familiarity with vulnerability management or incident response - Knowledge of privacy or security requirements relevant to software development - Security certifications or relevant practical projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Join &lt;Booking.com&gt; as an Application Security Engineer, where you will play a crucial role in safeguarding the security and privacy of our customers. You will build and operate advanced security tooling, automate remediation, analyze security indicators, and partner with product teams to embed security throughout the software development lifecycle. Your expertise will directly contribute to the detection, prevention, and response to application security threats across our global platform.
+- Identifying and explaining common application security risks, providing practical remediation guidance to development teams.
+- Building and operating advanced security tooling, automating remediation, and analyzing security indicators to enhance application security.
+- Collaborating with software engineers, platform teams, and security colleagues to embed security throughout the software development lifecycle.
+ - Some experience with application security tools, such as SAST, DAST, software composition analysis, vulnerability scanners, or secrets-scanning tools
+- Bachelor’s or Master’s degree in Computer Science or a related field
+- 3+ years of relevant industry experience
+- Familiarity with common risks such as injection, broken access control, authentication failures, security misconfiguration, cross-site scripting, and insecure dependencies
+- Ability to work effectively with developers and other technical teams
+- Ability to communicate security findings clearly and constructively
+- Basic to intermediate knowledge of application and web security
+- Familiarity with HTTP, APIs, authentication, authorization, and TLS
+- Analytical mindset, attention to detail, and willingness to learn
+- Basic scripting or automation skills in Python, Bash, or a similar language
+- Basic understanding of how LLM applications work, including prompts, model inputs and outputs, retrieval-augmented generation, and tool or API integrations
+- Understanding of the OWASP Top 10 and basic secure coding principles
+- Ability to read and understand code in at least one programming language
+- Basic understanding of how to secure LLM applications through input and output validation, data minimisation, access control, least privilege, rate limiting, logging, and human approval for high-impact actions
+- Experience with cloud platforms, containers, or infrastructure as code
+- Familiarity with API security or microservices
+- Experience with threat modelling or security testing
+- Experience or interest in securing AI or LLM-enabled applications
+- Familiarity with vulnerability management or incident response
+- Knowledge of privacy or security requirements relevant to software development
+- Security certifications or relevant practical projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>CACI</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>remote (any state)</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
         <is>
           <t>eightfold</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>https://caci.eightfold.ai/careers/job/1443153658946</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>Job Title: Cybersecurity EngineerJob Category: Information TechnologyTime Type: Full timeMinimum Clearance Required to Start: NoneEmployee Type: RegularPercentage of Travel Required: Up to 10%Type of Travel: Local\* \* \*
 **The Opportunity:**
@@ -6585,136 +6734,6 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Software Security Engineer</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>USD 145,000–165,000 / year</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/dWbVqQOoAF</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Harry@bvteck.com&gt; or contact us at (908)676-4399. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>dashealth</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://dashealth.applytojob.com/apply/jobs/details/biUYzO6aH9</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer – Remote DAS Health – Healthcare IT Managed Services &amp; Solutions Overview DAS Health is seeking a Cybersecurity Engineer to join our growing cybersecurity team. This role plays a critical part in protecting client and organizational data, with a strong focus on safeguarding patient health information (PHI) in a healthcare environment. The Cybersecurity Engineer will design, implement, and manage security controls across complex healthcare IT systems while ensuring compliance with key regulatory frameworks such as HIPAA, HITECH, and SOC 2. This role is ideal for someone who thrives in a fast-paced MSP environment and is passionate about security, compliance, and protecting critical healthcare systems. Key Responsibilities Design and implement security architecture across healthcare systems, including EHR platforms, medical devices, and healthcare information exchanges Configure and manage security tools such as firewalls, IDS/IPS, SIEM, DLP, MFA, EDR, and encryption technologies Conduct vulnerability assessments and penetration testing , identifying and mitigating risks across client environments Monitor and respond to security incidents , performing root cause analysis and implementing corrective actions Develop and maintain incident response plans , ensuring rapid and compliant response to security breaches Perform forensic analysis and support breach investigations, including HIPAA reporting requirements Monitor security systems and logs , proactively identifying threats and unusual activity Build and maintain reporting dashboards for clients and internal stakeholders Ensure compliance with industry standards , including HIPAA, HITECH, HITRUST, and SOC 2 Type II Support audit readiness and participation , including documentation and control maintenance Collaborate with internal teams and clients to integrate security into daily workflows and operations Support security awareness training and partner with vendors to ensure strong security practices Qualifications Bachelor’s degree in Computer Science, Information Security, or a related field (Master’s or certifications preferred) 3–5 years of cybersecurity engineering experience , ideally within a healthcare or MSP environment Hands-on experience with security technologies including firewalls, IDS/IPS, SIEM, DLP, MFA, EDR, and email security Experience securing cloud environments (AWS, Azure, or GCP) Experience supporting or preparing for SOC 2 Type II audits Strong knowledge of healthcare compliance frameworks (HIPAA, HITECH, HITRUST) Familiarity with network and security architecture in complex environments Experience with scripting tools such as Python or PowerShell Strong analytical and problem-solving skills with the ability to manage complex security challenges Ability to communicate technical concepts clearly to both technical and non-technical stakeholders High level of professionalism, attention to detail, and integrity Why DAS Health? At DAS Health, we’re helping healthcare organizations operate more efficiently and securely through innovative technology solutions. When you join our team, you’ll benefit from: Competitive compensation and benefits Career growth opportunities within a fast-growing organization Exposure to diverse client environments and technologies A collaborative, team-oriented culture The opportunity to make a meaningful impact in healthcare About DAS Health DAS Health is a leading healthcare IT managed services provider and technology partner. We support healthcare organizations with managed IT services, cybersecurity, and consulting solutions that improve operational efficiency, enhance patient experiences, and drive better outcomes Our Commitment to Diversity &amp; Inclusion DAS Health is an Equal Opportunity Employer. We celebrate diversity and are committed to creating an inclusive environment for all employees. All employment decisions are based on business needs, job requirements, and individual qualifications, without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, veteran status, disability status, age, or any other status protected by federal, state, or local laws. Accommodation Notice If you require reasonable accommodation in completing this application, interviewing, completing any pre-employment testing, or otherwise participating in the employee selection process, please direct your inquiries to &lt;recruitment@dashealth.com&gt;. Employment at Will Nothing in this job posting or description guarantees employment for any specific period or under any specific terms. Employment with DAS Health is "at-will."</t>
-        </is>
-      </c>
-    </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -6723,44 +6742,52 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>careers.mastercard.com</t>
+          <t>brightvisiontechnologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Director Security Engineering for Blockchain and Digital Solutions</t>
+          <t>Software Security Engineer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Dublin 18, Dublin, Ireland</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>USD 145,000–165,000 / year</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>jazzhr</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mastercard.com/job/R-291205</t>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/dWbVqQOoAF</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6770,72 +6797,194 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Exciting opportunity for a Director of Security Engineering to lead a team of security engineers in driving the security roadmap for Mastercard’s blockchain and digital solutions. Oversee security engineering initiatives, provide technical guidance, and collaborate with business leaders. Ideal for experienced cybersecurity professionals with expertise in blockchain and digital solutions.</t>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908)676-4399. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dashealth</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>https://dashealth.applytojob.com/apply/jobs/details/biUYzO6aH9</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer – Remote DAS Health – Healthcare IT Managed Services &amp; Solutions Overview DAS Health is seeking a Cybersecurity Engineer to join our growing cybersecurity team. This role plays a critical part in protecting client and organizational data, with a strong focus on safeguarding patient health information (PHI) in a healthcare environment. The Cybersecurity Engineer will design, implement, and manage security controls across complex healthcare IT systems while ensuring compliance with key regulatory frameworks such as HIPAA, HITECH, and SOC 2. This role is ideal for someone who thrives in a fast-paced MSP environment and is passionate about security, compliance, and protecting critical healthcare systems. Key Responsibilities Design and implement security architecture across healthcare systems, including EHR platforms, medical devices, and healthcare information exchanges Configure and manage security tools such as firewalls, IDS/IPS, SIEM, DLP, MFA, EDR, and encryption technologies Conduct vulnerability assessments and penetration testing , identifying and mitigating risks across client environments Monitor and respond to security incidents , performing root cause analysis and implementing corrective actions Develop and maintain incident response plans , ensuring rapid and compliant response to security breaches Perform forensic analysis and support breach investigations, including HIPAA reporting requirements Monitor security systems and logs , proactively identifying threats and unusual activity Build and maintain reporting dashboards for clients and internal stakeholders Ensure compliance with industry standards , including HIPAA, HITECH, HITRUST, and SOC 2 Type II Support audit readiness and participation , including documentation and control maintenance Collaborate with internal teams and clients to integrate security into daily workflows and operations Support security awareness training and partner with vendors to ensure strong security practices Qualifications Bachelor’s degree in Computer Science, Information Security, or a related field (Master’s or certifications preferred) 3–5 years of cybersecurity engineering experience , ideally within a healthcare or MSP environment Hands-on experience with security technologies including firewalls, IDS/IPS, SIEM, DLP, MFA, EDR, and email security Experience securing cloud environments (AWS, Azure, or GCP) Experience supporting or preparing for SOC 2 Type II audits Strong knowledge of healthcare compliance frameworks (HIPAA, HITECH, HITRUST) Familiarity with network and security architecture in complex environments Experience with scripting tools such as Python or PowerShell Strong analytical and problem-solving skills with the ability to manage complex security challenges Ability to communicate technical concepts clearly to both technical and non-technical stakeholders High level of professionalism, attention to detail, and integrity Why DAS Health? At DAS Health, we’re helping healthcare organizations operate more efficiently and securely through innovative technology solutions. When you join our team, you’ll benefit from: Competitive compensation and benefits Career growth opportunities within a fast-growing organization Exposure to diverse client environments and technologies A collaborative, team-oriented culture The opportunity to make a meaningful impact in healthcare About DAS Health DAS Health is a leading healthcare IT managed services provider and technology partner. We support healthcare organizations with managed IT services, cybersecurity, and consulting solutions that improve operational efficiency, enhance patient experiences, and drive better outcomes Our Commitment to Diversity &amp; Inclusion DAS Health is an Equal Opportunity Employer. We celebrate diversity and are committed to creating an inclusive environment for all employees. All employment decisions are based on business needs, job requirements, and individual qualifications, without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, veteran status, disability status, age, or any other status protected by federal, state, or local laws. Accommodation Notice If you require reasonable accommodation in completing this application, interviewing, completing any pre-employment testing, or otherwise participating in the employee selection process, please direct your inquiries to . Employment at Will Nothing in this job posting or description guarantees employment for any specific period or under any specific terms. Employment with DAS Health is "at-will."</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>careers.mastercard.com</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Director Security Engineering for Blockchain and Digital Solutions</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Dublin 18, Dublin, Ireland</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>phenom</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.mastercard.com/job/R-291205</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Exciting opportunity for a Director of Security Engineering to lead a team of security engineers in driving the security roadmap for Mastercard’s blockchain and digital solutions. Oversee security engineering initiatives, provide technical guidance, and collaborate with business leaders. Ideal for experienced cybersecurity professionals with expertise in blockchain and digital solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>mazedesign</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Senior Security Engineer (Remote, EU/CET)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>€110K – €130K • Offers Equity</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/mazedesign/9cc1aa89-faba-4610-86cb-b3c16a04a7f3/application</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>## About Maze
 **Maze is the user research platform that helps companies build the right products faster by making user insights available at the speed of product development.**
@@ -6916,60 +7065,60 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>alphasense</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Senior Product Security Engineer</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Remote - Ireland</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/alphasense/jobs/8839934002</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>## **About AlphaSense:**
 The world’s most sophisticated companies rely on AlphaSense to remove uncertainty from decision-making. With market intelligence and search built on proven AI, AlphaSense delivers insights that matter from content you can trust. Our universe of public and private content includes equity research, company filings, event transcripts, expert calls, news, trade journals, and clients’ own research content.
@@ -7033,60 +7182,60 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>alphasense</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Senior Product Security Engineer</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Remote - United Kingdom</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/alphasense/jobs/8839906002</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>## **About AlphaSense:**
 The world’s most sophisticated companies rely on AlphaSense to remove uncertainty from decision-making. With market intelligence and search built on proven AI, AlphaSense delivers insights that matter from content you can trust. Our universe of public and private content includes equity research, company filings, event transcripts, expert calls, news, trade journals, and clients’ own research content.
@@ -7150,60 +7299,60 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>alphasense</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Senior Product Security Engineer</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Remote - Canada</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/alphasense/jobs/8839604002</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>## **About AlphaSense:**
 The world’s most sophisticated companies rely on AlphaSense to remove uncertainty from decision-making. With market intelligence and search built on proven AI, AlphaSense delivers insights that matter from content you can trust. Our universe of public and private content includes equity research, company filings, event transcripts, expert calls, news, trade journals, and clients’ own research content.
@@ -7267,64 +7416,64 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>eightsleep</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/eightsleep/74b90c13-fe64-4bcd-9b5e-ebad6b5b4570/application</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>## **Join the Sleep Fitness Movement**
 At Eight Sleep, we’re on a mission to fuel human potential through optimal sleep. As the world’s first sleep fitness company, we’re redefining what it means to be well-rested and building the most advanced hardware, software, and AI technology to make it possible. Our products power peak mental, physical, and emotional performance by transforming every night of sleep into a personalized, data-driven recovery experience. We are trusted by high performers, professional athletes, and health-conscious consumers in over 30 countries worldwide. Recognized as one of Fast Company's Most Innovative Companies in 2019, 2022, and 2023, and twice named to TIME's “Best Inventions of the Year.” We operate like a high-performance team: fast, focused, and motivated by impact. We don’t just ship; we iterate, refine, and obsess over the details that help our members sleep better and wake up stronger.
@@ -7374,64 +7523,64 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>pingwind</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Technical Lead &amp; Chief Security Architect/Engineer</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/pingwind/5995aab6-1b06-45f9-9185-313e4b503fff/apply</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>**Location:** Remote; travel may be required in support of meetings, training, presentations, or briefings with project stakeholders **Required Clearance:** Ability to obtain and maintain the required VA background investigation/suitability determination **Certifications:** Certification in one or more of the following: PMP, IAT III, IAM III or IASAE III certifications and IAT III/ IAM III / IASAE III certifications may be substituted for a relevant Bachelor’s degree or 4 years of relevant experience **Required Education:** Master’s degree in Cybersecurity, Math, Engineering, Computer Science, Information Technology, Information Systems Architecture, Telecommunications Systems Design, Architecture Implementation, Information SystemsIntegration, Software Development Methodologies, Security Engineering, and Network Systems Communications Management.An additional advanced degree (e.g. Master’s or PhD) in an IT related field may substitute for up to 5 years of the required experience. **Required Experience:** Minimum of 15 years of Enterprise Security Architecture Information Security experience at a large company or Government agency similar in size/scope to GSA, IRS, DoD or VA
 **Description**
@@ -7470,68 +7619,68 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>shieldai</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Staff Application Security Engineer (R5949)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>143000 - 214000 USD</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/shieldai/57461bb3-9853-43d3-b2aa-f4b9e637fd41/apply</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>Shield AI is a venture-backed defense-tech company with the mission of protecting service members and civilians with intelligent systems. Its products include Hivemind autonomy software, V-BAT and X-BAT aircraft, and Aechelon simulation and synthetic reality technologies. With offices and facilities across the U.S., Europe, the Middle East, and Asia-Pacific, Shield AI’s technology actively supports operations worldwide. For more information, visit [&lt;www.shield.ai&gt;](https://shield.ai/). Follow Shield AI on [LinkedIn](https://www.linkedin.com/company/shield-ai), [X](https://x.com/shieldaitech), [Instagram](https://www.instagram.com/shield_ai), and [YouTube](https://www.youtube.com/@Shield_AI).
 We are seeking a Staff Application Security Engineer to build and advance a scalable, developer-centered application security program. This role will establish company-wide secure software development lifecycle (SDLC) policy and standards, translate them into practical engineering practices, and partner directly with product, platform, and development teams to improve secure development and software supply-chain maturity.
@@ -7596,132 +7745,6 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>monday.com</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Warsaw, Poland</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/dPbt3W/jobs/senior-devsecops-engineer_warsaw_kujeofhy</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Join , the AI work platform powering ambitious teams. As a Senior DevSecOps Engineer, you'll play a crucial role in securing our cloud infrastructure, with a strong focus on Kubernetes. You'll manage our Cloud Security Posture, harden our cloud-native environments, and support our AppSec team in securing CI/CD pipelines. This role is based in our Warsaw office, where you'll have the opportunity to grow your career while solving impactful, high-scale problems. - Zarządzanie bezpieczeństwem chmury i Kubernetes, w tym monitorowanie i twardnienie środowisk chmurowych. - Konfiguracja i zarządzanie zaporami aplikacyjnymi (WAF) oraz udział w odpowiedzi na incydenty bezpieczeństwa. - Rozwój narzędzi bezpieczeństwa w ramach wewnętrznej platformy deweloperskiej organizacji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>ramboll3</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>OT Security Engineer</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Warsaw, pl</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Ramboll3/744000151363065-ot-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>​We invite you to bring your skills into play as you contribute to the safety of our client’s automation systems. To succeed in this role, you must have experience with Cyber/OT security and management of stakeholders. Do you want to push the boundaries of your profession and develop your excellence in an open, collaborative and empowering culture? ​If this sounds like you, or you’re curious to learn more, then this role could be the perfect opportunity. Join our Automation and OT Security department as our new OT Security Engineer and work with us to close the gap to a sustainable future. ​Your new role ​As our new OT Security project engineer/manager you will be part of of an exceptional technical environment with 36 passionate colleagues in Denmark supported by our global engineering center. The department is highly experienced and delivers engineering and consultancy services globally within the energy sector for projects around the world. The area of responsibility for this position is mainly energy transition projects such as PtX plants, offshore energy, power generation, and gas infrastructure. ​Your key responsibilities will be: ​Act as OT engineer on OT security projects in close collaboration with clients. ​Perform specification and design of OT architecture and systems from an OT/cyber security point of view. We expect you have knowledge within some of the following areas: ​Cybersecurity (e.g., IEC62443, NERC CIP, ISO27001, NIS2) ​SCADA/Automation network ​About you ​A Bachelor’s- or Master’s degree in either Electrical Engineering, Electronic and computer, Information- and communication technology, or similar ​Few years of relevant experience ​Excellent communication skills in English are a must ​What we can offer you ​Commitment to your development ​Leaders guided by our Leadership Principles ​A culture that welcomes you as the unique person you are ​Inspiration from colleagues, clients, and projects ​The long-term thinking of a foundation-owned company ​​Ready to join us? ​Please submit your application and CV online. We invite diversity in all its forms and encourage applicants from all groups to apply. ​Deadline: 31/10/2026 ​​Work at the heart of sustainable change with Ramboll ​​Ramboll is a global architecture, engineering, and consultancy company. As a foundation-owned people company, founded in Denmark, we believe that the purpose of sustainable change is to create a thriving world for both nature and people. So, that’s where we start – and how we work. Our history is rooted in a clear vision of how a responsible company should act and being open and curious is a cornerstone of our culture. Ramboll employs more than 18,000 people globally across 35 countries. Ramboll experts deliver innovative solutions across Buildings, Transport, Water, Environment &amp; Health, Energy, Management Consulting, and Architecture &amp; Landscape. Combining local experience with global knowledge, we help shape the societies of tomorrow. ​Equality, Diversity, and Inclusion ​Equality, diversity, and inclusion are at the heart of what we do. At Ramboll, we believe that diversity is a strength and that different experiences and perspectives are essential to creating truly sustainable societies. We are committed to providing an inclusive and supportive work environment where everyone is able to flourish and reach their potential. We also know how important it is to achieve the right balance of where, when, and how much you work. At Ramboll, we offer flexibility as part of our positive and inclusive approach to work. We invite applications from candidates of all backgrounds and characteristics. Please let us know if there are any changes we could make to the application process to make it more comfortable for you. You can contact us at with such requests.​</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -7730,52 +7753,248 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>monday.com</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Warsaw, Poland</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>welcometothejungle</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/dPbt3W/jobs/senior-devsecops-engineer_warsaw_kujeofhy</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Join &lt;monday.com&gt;, the AI work platform powering ambitious teams. As a Senior DevSecOps Engineer, you'll play a crucial role in securing our cloud infrastructure, with a strong focus on Kubernetes. You'll manage our Cloud Security Posture, harden our cloud-native environments, and support our AppSec team in securing CI/CD pipelines. This role is based in our Warsaw office, where you'll have the opportunity to grow your career while solving impactful, high-scale problems.
+- Zarządzanie bezpieczeństwem chmury i Kubernetes, w tym monitorowanie i twardnienie środowisk chmurowych.
+- Konfiguracja i zarządzanie zaporami aplikacyjnymi (WAF) oraz udział w odpowiedzi na incydenty bezpieczeństwa.
+- Rozwój narzędzi bezpieczeństwa w ramach wewnętrznej platformy deweloperskiej organizacji.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ramboll3</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OT Security Engineer</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Warsaw, pl</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Ramboll3/744000151363065-ot-security-engineer?oga=true</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>​We invite you to bring your skills into play as you contribute to the safety of our client’s automation systems. To succeed in this role, you must have experience with Cyber/OT security and management of stakeholders. Do you want to push the boundaries of your profession and develop your excellence in an open, collaborative and empowering culture? ​If this sounds like you, or you’re curious to learn more, then this role could be the perfect opportunity. Join our Automation and OT Security department as our new OT Security Engineer and work with us to close the gap to a sustainable future. ​Your new role ​As our new OT Security project engineer/manager you will be part of of an exceptional technical environment with 36 passionate colleagues in Denmark supported by our global engineering center. The department is highly experienced and delivers engineering and consultancy services globally within the energy sector for projects around the world. The area of responsibility for this position is mainly energy transition projects such as PtX plants, offshore energy, power generation, and gas infrastructure. ​Your key responsibilities will be: ​Act as OT engineer on OT security projects in close collaboration with clients. ​Perform specification and design of OT architecture and systems from an OT/cyber security point of view. We expect you have knowledge within some of the following areas: ​Cybersecurity (e.g., IEC62443, NERC CIP, ISO27001, NIS2) ​SCADA/Automation network ​About you ​A Bachelor’s- or Master’s degree in either Electrical Engineering, Electronic and computer, Information- and communication technology, or similar ​Few years of relevant experience ​Excellent communication skills in English are a must ​What we can offer you ​Commitment to your development ​Leaders guided by our Leadership Principles ​A culture that welcomes you as the unique person you are ​Inspiration from colleagues, clients, and projects ​The long-term thinking of a foundation-owned company ​​Ready to join us? ​Please submit your application and CV online. We invite diversity in all its forms and encourage applicants from all groups to apply. ​Deadline: 31/10/2026 ​​Work at the heart of sustainable change with Ramboll ​​Ramboll is a global architecture, engineering, and consultancy company. As a foundation-owned people company, founded in Denmark, we believe that the purpose of sustainable change is to create a thriving world for both nature and people. So, that’s where we start – and how we work. Our history is rooted in a clear vision of how a responsible company should act and being open and curious is a cornerstone of our culture. Ramboll employs more than 18,000 people globally across 35 countries. Ramboll experts deliver innovative solutions across Buildings, Transport, Water, Environment &amp; Health, Energy, Management Consulting, and Architecture &amp; Landscape. Combining local experience with global knowledge, we help shape the societies of tomorrow. ​Equality, Diversity, and Inclusion ​Equality, diversity, and inclusion are at the heart of what we do. At Ramboll, we believe that diversity is a strength and that different experiences and perspectives are essential to creating truly sustainable societies. We are committed to providing an inclusive and supportive work environment where everyone is able to flourish and reach their potential. We also know how important it is to achieve the right balance of where, when, and how much you work. At Ramboll, we offer flexibility as part of our positive and inclusive approach to work. We invite applications from candidates of all backgrounds and characteristics. Please let us know if there are any changes we could make to the application process to make it more comfortable for you. You can contact us at &lt;job.advert.accessibility@ramboll.com&gt; with such requests.​</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LITIT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GERMAN SPEAKING SECURITY ENGINEER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Remote job</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>5000 - 7500 EUR</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>https://litit.recruitee.com/o/german-speaking-security-engineer/c/new</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>ABOUT THE COMPANY LITIT, a joint venture between NTT DATA and Reiz Tech, is a company with deep-rooted industry know-how, dedicated to innovation within the IT sector. Its primary focus is delivering high-quality solutions in the DACH region. With a commitment to excellence, LITIT combines the best of German precision, Japanese work ethics, and Lithuanian talent to provide unparalleled IT service and support to its clients. ABOUT THE CLIENT Our client is a well-established company in the financial and accounting sector, trusted by thousands of professionals and organizations. They focus on building secure and reliable digital solutions that make everyday work easier and more efficient. With a strong commitment to innovation, they are expanding their data platforms to support smarter services, modern architectures, and data-driven decision-making. ABOUT THE ROLE We are looking for German-speaking Security Engineers to support strategic and operational security initiatives within a large enterprise IT environment. With the growing importance of Agentic AI, SaaS integrations, and Security-by-Design , additional security expertise is needed to strengthen existing capabilities and accelerate the implementation of security requirements. In this role, you will work closely with internal security, IT, and business stakeholders across internal IT and internally operated applications , including platforms such as Workday and SAP. RESPONSIBILITIES Support strategic and operational security initiatives across internal IT and internally operated applications, including platforms such as Workday and SAP. Assess and address security requirements related to Agentic AI, SaaS integrations, cloud environments, and application security . Perform threat modeling, security assessments, and security reviews to identify and mitigate security risks. Drive the implementation of Security-by-Design principles throughout the development and integration lifecycle. Support vulnerability management , including the identification, assessment, prioritization, and remediation of security vulnerabilities. Develop and maintain security concepts, technical documentation, and security requirements . Provide security consulting to IT, engineering, and business stakeholders and translate security requirements into practical solutions. Collaborate with internal security teams and stakeholders to strengthen security controls and accelerate the implementation of security requirements. Contribute to the development and implementation of AI and Agentic AI security practices , where applicable. Communicate security risks, findings, and recommendations clearly to both technical and non-technical stakeholders. Help identify opportunities to improve security processes, standards, and engineering practices across the organization. REQUIREMENTS Several years of professional experience in Security Engineering or a closely related cybersecurity role. Strong knowledge of Cloud Security and SaaS Security . Practical experience with Application Security and secure architecture principles. Solid experience in Threat Modeling, Security Assessments, and Security Reviews . Strong understanding and practical application of Security-by-Design principles. Experience with Vulnerability Management and security risk assessment. Ability to create and maintain security concepts, requirements, and technical documentation . Strong security consulting and stakeholder communication skills. Ability to work independently on complex security topics and collaborate effectively with different teams. Experience working in large or enterprise IT environments is an advantage. Knowledge of AI Security / Agentic AI Security is preferred. Fluent German and good English communication skills . Senior-level professional experience with the ability to take ownership of security initiatives and provide expert guidance. Willingness and readiness to travel as required by project or client needs is expected. This may include occasional domestic or international travel, sometimes on short notice. WHAT WE OFFER Salary range: €5000 - €7500 (GROSS) / month. Learning opportunities with compensated certificates, learning lunches, and language lessons. Chance to switch projects after one year. Team building twice a year. Office in Vilnius, Lithuania that offers themed lunches and a pet-friendly environment. Remote work opportunities. Flexible time off depending on a project. Seasonal activities with colleagues. Additional health insurance and loyalty days for Lithuanian residents. Referral bonuses. Recognition of important occasions of your life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>form3</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Senior Cloud Security Engineer - AI Resilience &amp; Security Enhancements (Fixed-term contract)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>100% Remote (UK)</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>https://www.form3.tech/careers/vacancies/8836482002?gh_jid=8836482002</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>**THE PROJECT**📝 
 We're looking for an experienced **Senior Cloud Security Engineer** to join Form3 on a 12 month fixed term contract basis to deliver a strategic programme of security enhancements across our cloud-native payments platform. 
@@ -7844,68 +8063,68 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>nord-security</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Application Security Engineer | Senior</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>PLN 23K – PLN 30K per month</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/nord-security/d3457664-ad58-43c0-bc37-e4c55302849c/application</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>## **The world’s most advanced VPN, and a whole lot more.**
 If you’re a curious problem-solver who carves their own path, join the team behind Threat Protection Pro, the NordLynx protocol, and the fastest VPN on the planet—tools that put privacy, security, and control back in people’s hands.
@@ -7950,64 +8169,64 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>HaufeGroup</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Web-App Security Engineer (d/m/w) - Remote</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Freiburg im Breisgau, Baden-Württemberg, de</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/HaufeGroup/744000151310339-web-app-security-engineer-d-m-w-remote?oga=true</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>Deine Ideen, Entscheidungen und Tätigkeiten haben einen direkten Einfluss auf die Verbesserung der Sicherheit unserer Applikation. Du machst ein Produkt, das von über 450.000 Klein- und Kleinstunternehmen in Deutschland genutzt wird, Tag für Tag sicherer Du arbeitest eng mit unseren Feature-Teams zusammen, um sie bei Security-Fragestellungen während der Konzeption, der Umsetzung und dem Betrieb unserer Applikation zu unterstützen. Dabei tauchst du tief in die technische Materie ein. Außerdem entwickelst und betreust du teamübergreifende Sicherheitsmechanismen In unserem Security Enablement Team hast du die Möglichkeit, Neues zu erkunden, aufzubauen, aktiv mitzugestalten und Ideen einzubringen. Es erwarten dich unter anderem Hacking Days und gelegentliche After-Work -Sessions Bei uns findest du eine moderne, agile Arbeitsweise: von DevOps bis hin zu Scrum oder Kanban
 Du verfügst über gute Kenntnisse und umfangreiche Erfahrung im Bereich Web-Applikations- und Cloudsicherheit (bevorzugt mit AWS) und weißt außerdem, wie moderne Webapplikationen sicher konfiguriert, gebaut und released werden (IaC, CI/CD, SDLC) Du bist in der Lage, Schwachstellen im Kontext unserer Applikation zu bewerten und eine Handlungsempfehlung auszuarbeiten. Dabei kannst du auf deine Kenntnisse über Java Webanwendungen und Javascript (Typescript) Webclients zurückgreifen. Du verstehst die Funktionsweise und Konfiguration von bekannten Dependency Management Tools wie NPM und Gradle Du hast Entwicklungserfahrung und kannst schnell einschätzen, ob eine Aufgabe automatisiert werden sollte und kannst dafür Bash, Python-Skripte oder sonstige, nötige Tools schreiben Für dich sind Threat Models kein unbekanntes Thema und du begeisterst dich dafür, gemeinsam mit Kolleg:innen ein solches bspw. am Whiteboard zu entwerfen. Du kannst dich dabei in die Denkweise eines Widersachers versetzen und so Bedrohungen identifizieren Du kannst Verwundbarkeiten und Security-Empfehlungen verständlich und präzise vermitteln, um Feature-Teams effektiv bei Security-Fragestellungen zu unterstützen. Pluspunkt: Du konntest bereits Erfahrung im Incident Response Bereich sammeln Unsere Teamsprache ist Deutsch, daher sind sehr gute Deutschkenntnisse (mind. C2) ein Muss. Gleichzeitig solltest Du auch sehr gute Englischkenntisse mitbringen Wir setzen auf Team-Recruiting - Die Bewerbungsgespräche führt unser Team selbst. Wir freuen uns darauf, dich kennen zu lernen Lukas ist auf der Arbeit ebenso wie auch privat von Security-Themen fasziniert, bastelt viel in virtuellen Maschinen, trifft gerne Freunde, betreibt zum Ausgleich Kraftsport und tanzt leidenschaftlich Florian verbringt seine freie Zeit mit Vulnerability-Research, CTFs und beim CCC. Außerdem ist er leidenschaftlicher Hobbykoch und hat ein Faible für guten Kaffee Henrik begeistert sich generell für Security und alle Linux spezifischen Themen. Außerhalb der Arbeit verbringt er seine Zeit mit Sport, dem Aufsetzen von Home Servern oder greift zur Gitarre
@@ -8016,64 +8235,64 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Product Security Lead</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/4fafd06e-3485-4474-b754-c835042e319a/apply</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Product Security Lead based in Canada.**
 This role leads the Product Security function and reports directly to the Chief Information Security Officer.  
@@ -8137,195 +8356,6 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/KuvnK59p4a</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AI Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 8+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/NV0FdJgrVA</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Application Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Application Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$160,000 Annually Experience Required: 10+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Application Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Key Responsibilities Conduct threat modeling and security architecture reviews for new and existing applications and services. Perform manual code reviews, secure design consultations, and pair with engineering teams on hardening critical components. Operate and tune SAST, DAST, IAST, SCA, and secret-scanning tools across CI/CD pipelines. Drive vulnerability management workflows including triage, prioritization, owner assignment, and SLA tracking. Build paved-road libraries and frameworks that make secure patterns the default for engineering teams. Lead red-team and purple-team exercises against internal applications and drive remediation of identified weaknesses. Implement and operate runtime protections including WAF, RASP, bot protection, and abuse-detection mechanisms. Design and enforce secure authentication, authorization, session management, and cryptographic patterns. Partner with infrastructure and platform teams to harden container, Kubernetes, and cloud environments. Develop and deliver application security training, lunch-and-learns, and onboarding content for engineering staff. Respond to security incidents involving application vulnerabilities or active exploitation. Track and apply emerging threats and CVEs that may affect the application portfolio. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Stay current with application security research and emerging defensive tooling. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Ten or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer – Oracle</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/8mmKLsASH0</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cloud Security Engineer - Oracle Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Cloud Security Engineer - Oracle responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. Key Responsibilities Design and implement enterprise security architectures for OCI tenancies, including landing-zone guardrails, security zones, and compartment policies. Configure and operate OCI Identity Domains, federation with corporate IdPs, and strong RBAC strategies across the tenancy. Implement strong key management and secrets handling using OCI Vault, including key rotation and HSM integration where appropriate. Harden OCI compute, networking, and database workloads using CIS benchmarks, OCI Security Zones, and internal security standards. Operate OCI Cloud Guard for continuous detection and response, tuning detectors and remediating findings. Configure and operate OCI Logging, OCI Audit, and integration with SIEM platforms for centralized monitoring and forensics. Implement data security controls using OCI Data Safe, including data masking, sensitive data discovery, and privileged user analysis. Lead vulnerability management programs, including image scanning, patching, and remediation tracking. Drive compliance with regulatory frameworks such as PCI-DSS, HIPAA, SOC 2, ISO 27001, or FedRAMP. Conduct threat modeling and architecture reviews for new OCI workloads. Lead security incident response on OCI, including containment, investigation, and post-incident review. Develop security automation tooling using Python, Terraform, and OCI CLI/SDK. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Provide mentorship and security guidance across application and infrastructure teams. Required Qualifications 5+ years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3545. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -8334,17 +8364,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>careers.cencora.com</t>
+          <t>brightvisiontechnologies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Senior Cyber Security Engineer (SIEM)</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Vilnius, Lithuania</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8354,24 +8384,28 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>jazzhr</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>https://careers.cencora.com/job/R2610725</t>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/KuvnK59p4a</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8381,44 +8415,44 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hands-on engineering role spanning the security data pipeline and the detection content it powers. Onboards, parses, normalizes, and routes log and telemetry data into the SIEM and data lake, and...</t>
+          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AI Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 8+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>brightvisiontechnologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Detection &amp; Response</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -8429,20 +8463,205 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/NV0FdJgrVA</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Application Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Application Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$160,000 Annually Experience Required: 10+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Application Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Key Responsibilities Conduct threat modeling and security architecture reviews for new and existing applications and services. Perform manual code reviews, secure design consultations, and pair with engineering teams on hardening critical components. Operate and tune SAST, DAST, IAST, SCA, and secret-scanning tools across CI/CD pipelines. Drive vulnerability management workflows including triage, prioritization, owner assignment, and SLA tracking. Build paved-road libraries and frameworks that make secure patterns the default for engineering teams. Lead red-team and purple-team exercises against internal applications and drive remediation of identified weaknesses. Implement and operate runtime protections including WAF, RASP, bot protection, and abuse-detection mechanisms. Design and enforce secure authentication, authorization, session management, and cryptographic patterns. Partner with infrastructure and platform teams to harden container, Kubernetes, and cloud environments. Develop and deliver application security training, lunch-and-learns, and onboarding content for engineering staff. Respond to security incidents involving application vulnerabilities or active exploitation. Track and apply emerging threats and CVEs that may affect the application portfolio. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Stay current with application security research and emerging defensive tooling. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Ten or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer – Oracle</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/8mmKLsASH0</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cloud Security Engineer - Oracle Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Cloud Security Engineer - Oracle responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. Key Responsibilities Design and implement enterprise security architectures for OCI tenancies, including landing-zone guardrails, security zones, and compartment policies. Configure and operate OCI Identity Domains, federation with corporate IdPs, and strong RBAC strategies across the tenancy. Implement strong key management and secrets handling using OCI Vault, including key rotation and HSM integration where appropriate. Harden OCI compute, networking, and database workloads using CIS benchmarks, OCI Security Zones, and internal security standards. Operate OCI Cloud Guard for continuous detection and response, tuning detectors and remediating findings. Configure and operate OCI Logging, OCI Audit, and integration with SIEM platforms for centralized monitoring and forensics. Implement data security controls using OCI Data Safe, including data masking, sensitive data discovery, and privileged user analysis. Lead vulnerability management programs, including image scanning, patching, and remediation tracking. Drive compliance with regulatory frameworks such as PCI-DSS, HIPAA, SOC 2, ISO 27001, or FedRAMP. Conduct threat modeling and architecture reviews for new OCI workloads. Lead security incident response on OCI, including containment, investigation, and post-incident review. Develop security automation tooling using Python, Terraform, and OCI CLI/SDK. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Provide mentorship and security guidance across application and infrastructure teams. Required Qualifications 5+ years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;jaya@bvteck.com&gt; or contact us at (908) 505-3545. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt;. Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>careers.cencora.com</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Senior Cyber Security Engineer (SIEM)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Vilnius, Lithuania</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>phenom</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.cencora.com/job/R2610725</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Hands-on engineering role spanning the security data pipeline and the detection content it powers. Onboards, parses, normalizes, and routes log and telemetry data into the SIEM and data lake, and...</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer - Detection &amp; Response</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/Np0EcE/jobs/senior-security-engineer-detection-response_london_ilsacq2l</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>Join Klaviyo, a leading marketing automation platform, as a Senior Security Engineer in the Detection &amp; Response Team. In this engineering role, you will work on complex security challenges, develop high-fidelity detections, respond to cyber threats, and build security tooling. You will have the opportunity to shape how an engineering-first detection and response function uses automation and AI in production.
 - Leverage engineering practices to develop, test, and deploy high-fidelity rule-based and anomaly-based detections-as-code.
@@ -8451,60 +8670,60 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>guidepointsecurity</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Senior Cloud Security Automation &amp; AI Engineer- Remote (Anywhere in the U.S.)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6205784004?gh_jid=6205784004</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>GuidePoint Security provides trusted cybersecurity expertise, solutions and services that help organizations make better decisions and minimize risk. By taking a three-tiered, holistic approach for evaluating security posture and ecosystems, GuidePoint enables some of the nation’s top organizations, such as Fortune 500 companies and U.S. government agencies, to identify threats, optimize resources and integrate best-fit solutions that mitigate risk.
 ### General Description
@@ -8597,64 +8816,64 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>writer</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Security engineer, detection and response (UK)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/writer/a1d463ea-6139-495b-8c64-81acecc22f6f/application</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>**🚀 About WRITER**
 WRITER is where the world's leading enterprises orchestrate AI-powered work. Our vision is to expand human capacity through superintelligence. And we're proving it's possible – through powerful, trustworthy AI that unites IT and business teams together to unlock enterprise-wide transformation. With WRITER's end-to-end platform, hundreds of companies like Mars, Marriott, Uber, and Vanguard are building and deploying AI agents that are grounded in their company's data and fueled by WRITER's enterprise-grade LLMs. Valued at $1.9B and backed by industry-leading investors including Premji Invest, Radical Ventures, and ICONIQ Growth, WRITER is rapidly cementing its position as the leader in enterprise generative AI.
@@ -8693,64 +8912,64 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>writer</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Security engineer, application security (UK)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/writer/a8f25618-87b1-4475-bf94-d09f76b9c1fd/application</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>## **🚀 About WRITER**
 WRITER is where the world's leading enterprises orchestrate AI-powered work. Our vision is to expand human capacity through superintelligence. And we're proving it's possible – through powerful, trustworthy AI that unites IT and business teams together to unlock enterprise-wide transformation. With WRITER's end-to-end platform, hundreds of companies like Mars, Marriott, Uber, and Vanguard are building and deploying AI agents that are grounded in their company's data and fueled by WRITER's enterprise-grade LLMs. Valued at $1.9B and backed by industry-leading investors including Premji Invest, Radical Ventures, and ICONIQ Growth, WRITER is rapidly cementing its position as the leader in enterprise generative AI.
@@ -8791,60 +9010,60 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>censys</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/censys/jobs/8541287002</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>### Company Background
 Censys’ mission is to be the one place to understand everything on the internet. Frustrated by the lack of trustworthy Internet intelligence, we set out to create the industry’s most comprehensive, accurate, and up-to-date map of the Internet. Today, Censys delivers real-time Internet intelligence and actionable threat insights to global governments, over 50% of the Fortune 500, and leading threat intelligence providers worldwide.
@@ -8898,60 +9117,60 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>bloomreach</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Product Security Engineer</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bloomreach/jobs/8211026</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t>Bloomreach is building the world’s premier **agentic platform for personalization**.We’re revolutionizing how businesses connect with their customers, building and deploying AI agents to personalize the ***entire*** customer journey.
 - We're taking **autonomous search** mainstream, making product discovery more intuitive and conversational for customers, and more profitable for businesses.
@@ -9042,60 +9261,60 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>skyepointdecisionsinc</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Security Automation Engineer</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/skyepointdecisionsinc/jobs/4415215009</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>SkyePoint Decisions is a leading Cybersecurity Architecture and Engineering, Critical Infrastructure and Operations, and Applications Development and Maintenance IT service provider headquartered in Dulles, Virginia with operations across the U.S. We provide innovative enterprise-wide solutions as well as targeted services addressing the complex challenges faced by our federal government clients. Our focus is on enabling our clients to deliver their mission most efficiently and effectively – anytime, anywhere, securely. We combine technical expertise, mission awareness, and an empowered workforce to produce meaningful results.
 **This is a contingent position based upon contract win.**
@@ -9144,60 +9363,60 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>klaviyo</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Senior Security Engineer - Detection &amp; Response</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>https://www.klaviyo.com/careers/jobs/7994067003?gh_jid=7994067003</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t>*At Klaviyo, we value the unique backgrounds, experiences and perspectives each Klaviyo (we call ourselves Klaviyos) brings to our workplace each and every day. We believe everyone deserves a fair shot at success and appreciate the experiences each person brings beyond the traditional job requirements. If you’re a close but not exact match with the description, we hope you’ll still consider applying. Want to learn more about life at Klaviyo? Visit [&lt;klaviyo.com/careers&gt;](http://klaviyo.com/careers) to see how we empower creators to own their own destiny.*
 Klaviyo is looking for a **Senior Security Engineer** to add to our growing Detection &amp; Response Team. This is an engineering role that spans the full detection and response lifecycle - leveraging software development practices to build detections, triaging alerts, lead investigations, respond to incidents, perform threat hunting, and build the tooling that keeps us from doing the same work twice. As a member of the team, you will have the opportunity to work on complex large-scale security challenges across Klaviyo’s enterprise, cloud, and product environments, and shape how an engineering-first D&amp;R function uses automation and AI in production, at scale, alongside talented and ambitious colleagues spanning multiple regions and timezones.
@@ -9247,60 +9466,60 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>skyepointdecisionsinc</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>DevSecOps/Platform Engineer</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/skyepointdecisionsinc/jobs/4415190009</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t>SkyePoint Decisions is a leading Cybersecurity Architecture and Engineering, Critical Infrastructure and Operations, and Applications Development and Maintenance IT service provider headquartered in Dulles, Virginia with operations across the U.S. We provide innovative enterprise-wide solutions as well as targeted services addressing the complex challenges faced by our federal government clients. Our focus is on enabling our clients to deliver their mission most efficiently and effectively – anytime, anywhere, securely. We combine technical expertise, mission awareness, and an empowered workforce to produce meaningful results.
 **This is a contingent position based upon contract win.**
@@ -9347,60 +9566,60 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>quanata</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Staff Security Engineer [Remote-US]</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>remote</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/quanata/jobs/6205204004</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t>*To help keep everyone safe, we encourage all applicants to pay close attention to protect themselves during their job search. When applying for a position online you are at risk of being targeted by malicious actors looking for personal data. Please be aware we will only reach out via email using the domain &lt;quanata.com&gt;. Anything that does not match those domains should be ignored and considered a security risk.*
 **About Us**
@@ -9462,276 +9681,194 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>aecom2</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Lead DevSecOps Engineer</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>London, HOLBEIN GARDENS, gb</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/AECOM2/744000151073879-lead-devsecops-engineer?oga=true</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>In AECOM’s AI Engineering team, your work will help deliver technology that directly shapes the physical world around us. We build AI-driven products that change how infrastructure and buildings are designed and engineered, reducing waste, cutting CO₂, and making the built environment more efficient and sustainable. This role ensures those products and the platforms behind them are reliable, scalable, and secure by design. With our AI Engineering team we’ve created a unique setup: a lean, highly technical team with the speed and ownership of a start up, backed by the scale, resources, and domain expertise of one of the world’s leading engineering firms. There has never been a better time to be at AECOM. We are leading the industry’s AI transformation, and with our people and technology we deliver excellence and innovate with impact. We invite you to bring your bold ideas and big dreams to solve the world’s most complex challenges. We're one global team driven by our common purpose to deliver a better world. Join us. What You’ll Do As part of our AI Engineering team, you will lead the DevSecOps capabilities that help engineers build, release, and operate services across our multi-cloud platform. You will shape CI/CD, Infrastructure as Code, observability, reliability, cloud governance, and secure engineering across Microsoft Azure and Google Cloud Platform (GCP). You will also manage cloud-vendor service reviews, security advisories, escalations, and roadmap discussions. Evolve CI/CD pipelines and reusable workflows that enable fast, reliable, and repeatable testing and deployment, with automated quality and security controls Build observability and operational readiness through monitoring, logging, tracing, runbooks, and incident response, improving the reliability and performance of production services Define and track service reliability objectives, and recovery requirements for production services, using incident reviews to drive continuous improvement. Embed proportionate security into engineering workflows and cloud environments, including platform security reviews, threat modelling, access and secrets management, automated scanning, and vulnerability remediation Monitor cloud security posture across Azure and GCP, helping teams prioritise misconfigurations, vulnerabilities, and remediation work according to risk Manage technical and service relationships with Microsoft, Google Cloud, and other critical vendors, leading service reviews, security advisory responses, escalations, and roadmap and cost discussions Partner with platform, product, and AI/ML engineers on architecture decisions, mentor colleagues, and make clear trade-offs across developer experience, reliability, performance, cost, and security
-Must-Have Qualifications Demonstrated hands-on experience across DevOps, SRE, platform engineering, DevSecOps, or related roles, with experience guiding technical decisions or mentoring colleagues Experience building and maintaining CI/CD pipelines and release automation, ideally with GitHub Actions or similar tooling Hands-on experience with Infrastructure as Code and cloud platform automation using Terraform Demonstrated ownership of production reliability, including observability, service-level objectives, incident management, post-incident reviews, capacity planning, and disaster-recovery testing. Practical experience carrying out security reviews and implementing controls across identity, secrets management, software supply chains, and vulnerability management Experience working directly with cloud providers or technology vendors, ideally including Microsoft or Google Cloud, on service reviews, escalations, or roadmap discussions Practical experience monitoring and optimising cloud expenditure across large Azure or GCP environments. Preferred Skills Experience building internal developer platforms or self-service cloud capabilities Experience applying image scanning, artefact signing, or software provenance controls to containerised workloads Familiarity with cloud security posture management, policy-as-code, security monitoring, or compliance automation Experience supporting AI/ML workloads and SaaS platforms in production
-Our Hiring Process 25-minute screening call Take-home challenge: A hands-on task to assess your problem-solving and technical skills Combined technical and cultural interview (in-person) Technical Interview: 1-hour with 2 of our engineers to discuss your solution to the take-home challenge Culture fit: 30-minute meeting with our leadership team Why Join Us? Work on real-world problems where AI creates measurable impact. Be part of a team where your work matters, and your ideas become real. Collaborate with sharp, driven colleagues in a culture of trust, ownership, and high standards. Contribute to making the built environment smarter and more sustainable. At AECOM, we are committed to maintaining a secure and trustworthy recruitment process and take any fraudulent hiring activity seriously. To support this commitment, all newly hired employees are required to attend an in-person Day 1 onboarding at an AECOM office location as a condition of employment. About AECOM AECOM is proud to offer comprehensive benefits to meet the diverse needs of our employees. Depending on your employment status, AECOM benefits may include medical, dental, vision, life, AD&amp;D, disability benefits, paid time off, leaves of absences, voluntary benefits, perks, flexible work options, well-being resources, employee assistance program, business travel insurance, service recognition awards, retirement savings plan, and employee stock purchase plan. AECOM is the global infrastructure leader, committed to delivering a better world. As a trusted professional services firm powered by deep technical abilities, we solve our clients’ complex challenges in water, environment, energy, transportation and buildings. Our teams partner with public- and private-sector clients to create innovative, sustainable and resilient solutions throughout the project lifecycle — from advisory, planning, design and engineering to program and construction management. AECOM is a Fortune 500 firm that had revenue of $16.1 billion in fiscal year 2025. Learn more at &lt;aecom.com&gt; . What makes AECOM a great place to work You will be part of a global team that champions your growth and career ambitions. Work on groundbreaking projects—both in your local community and on a global scale—that are transforming our industry and shaping the future. With cutting-edge technology and a network of experts, you’ll have the resources to make a real impact. Our award-winning training and development programs are designed to expand your technical expertise and leadership skills, helping you build the career you’ve always envisioned. Here, you’ll find a welcoming workplace built on respect, collaboration and community—where you have the freedom to grow in a world of opportunity. We are a Disability Confident Employer and will offer an interview to applicants who have a disability or long-term condition, who meet the minimum/essential criteria for the role. Please let us know using this email address &lt;ReasonableAccommodationsUKI@aecom.com&gt; if you would like to apply through the Disability Confident Interview Scheme. All your information will be kept confidential according to EEO guidelines.
-Work with Us. Change the World. At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastructure consulting firm, partnering with clients to solve the world’s most complex challenges and build legacies for future generations. There has never been a better time to be at AECOM. With accelerating infrastructure investment worldwide, our services are in great demand. We invite you to bring your bold ideas and big dreams and become part of a global team of over 50,000 planners, designers, engineers, scientists, digital innovators, program and construction managers and other professionals delivering projects that create a positive and tangible impact around the world. We're one global team driven by our common purpose to deliver a better world. Join us.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>In AECOM’s AI Engineering team, your work will help deliver technology that directly shapes the physical world around us. We build AI-driven products that change how infrastructure and buildings are designed and engineered, reducing waste, cutting CO₂, and making the built environment more efficient and sustainable. This role ensures those products and the platforms behind them are reliable, scalable, and secure by design. With our AI Engineering team we’ve created a unique setup: a lean, highly technical team with the speed and ownership of a start up, backed by the scale, resources, and domain expertise of one of the world’s leading engineering firms. There has never been a better time to be at AECOM. We are leading the industry’s AI transformation, and with our people and technology we deliver excellence and innovate with impact. We invite you to bring your bold ideas and big dreams to solve the world’s most complex challenges. We're one global team driven by our common purpose to deliver a better world. Join us. What You’ll Do As part of our AI Engineering team, you will lead the DevSecOps capabilities that help engineers build, release, and operate services across our multi-cloud platform. You will shape CI/CD, Infrastructure as Code, observability, reliability, cloud governance, and secure engineering across Microsoft Azure and Google Cloud Platform (GCP). You will also manage cloud-vendor service reviews, security advisories, escalations, and roadmap discussions. Evolve CI/CD pipelines and reusable workflows that enable fast, reliable, and repeatable testing and deployment, with automated quality and security controls Build observability and operational readiness through monitoring, logging, tracing, runbooks, and incident response, improving the reliability and performance of production services Define and track service reliability objectives, and recovery requirements for production services, using incident reviews to drive continuous improvement. Embed proportionate security into engineering workflows and cloud environments, including platform security reviews, threat modelling, access and secrets management, automated scanning, and vulnerability remediation Monitor cloud security posture across Azure and GCP, helping teams prioritise misconfigurations, vulnerabilities, and remediation work according to risk Manage technical and service relationships with Microsoft, Google Cloud, and other critical vendors, leading service reviews, security advisory responses, escalations, and roadmap and cost discussions Partner with platform, product, and AI/ML engineers on architecture decisions, mentor colleagues, and make clear trade-offs across developer experience, reliability, performance, cost, and security Must-Have Qualifications Demonstrated hands-on experience across DevOps, SRE, platform engineering, DevSecOps, or related roles, with experience guiding technical decisions or mentoring colleagues Experience building and maintaining CI/CD pipelines and release automation, ideally with GitHub Actions or similar tooling Hands-on experience with Infrastructure as Code and cloud platform automation using Terraform Demonstrated ownership of production reliability, including observability, service-level objectives, incident management, post-incident reviews, capacity planning, and disaster-recovery testing. Practical experience carrying out security reviews and implementing controls across identity, secrets management, software supply chains, and vulnerability management Experience working directly with cloud providers or technology vendors, ideally including Microsoft or Google Cloud, on service reviews, escalations, or roadmap discussions Practical experience monitoring and optimising cloud expenditure across large Azure or GCP environments. Preferred Skills Experience building internal developer platforms or self-service cloud capabilities Experience applying image scanning, artefact signing, or software provenance controls to containerised workloads Familiarity with cloud security posture management, policy-as-code, security monitoring, or compliance automation Experience supporting AI/ML workloads and SaaS platforms in production Our Hiring Process 25-minute screening call Take-home challenge: A hands-on task to assess your problem-solving and technical skills Combined technical and cultural interview (in-person) Technical Interview: 1-hour with 2 of our engineers to discuss your solution to the take-home challenge Culture fit: 30-minute meeting with our leadership team Why Join Us? Work on real-world problems where AI creates measurable impact. Be part of a team where your work matters, and your ideas become real. Collaborate with sharp, driven colleagues in a culture of trust, ownership, and high standards. Contribute to making the built environment smarter and more sustainable. At AECOM, we are committed to maintaining a secure and trustworthy recruitment process and take any fraudulent hiring activity seriously. To support this commitment, all newly hired employees are required to attend an in-person Day 1 onboarding at an AECOM office location as a condition of employment. About AECOM AECOM is proud to offer comprehensive benefits to meet the diverse needs of our employees. Depending on your employment status, AECOM benefits may include medical, dental, vision, life, AD&amp;D, disability benefits, paid time off, leaves of absences, voluntary benefits, perks, flexible work options, well-being resources, employee assistance program, business travel insurance, service recognition awards, retirement savings plan, and employee stock purchase plan. AECOM is the global infrastructure leader, committed to delivering a better world. As a trusted professional services firm powered by deep technical abilities, we solve our clients’ complex challenges in water, environment, energy, transportation and buildings. Our teams partner with public- and private-sector clients to create innovative, sustainable and resilient solutions throughout the project lifecycle — from advisory, planning, design and engineering to program and construction management. AECOM is a Fortune 500 firm that had revenue of $16.1 billion in fiscal year 2025. Learn more at . What makes AECOM a great place to work You will be part of a global team that champions your growth and career ambitions. Work on groundbreaking projects—both in your local community and on a global scale—that are transforming our industry and shaping the future. With cutting-edge technology and a network of experts, you’ll have the resources to make a real impact. Our award-winning training and development programs are designed to expand your technical expertise and leadership skills, helping you build the career you’ve always envisioned. Here, you’ll find a welcoming workplace built on respect, collaboration and community—where you have the freedom to grow in a world of opportunity. We are a Disability Confident Employer and will offer an interview to applicants who have a disability or long-term condition, who meet the minimum/essential criteria for the role. Please let us know using this email address if you would like to apply through the Disability Confident Interview Scheme. All your information will be kept confidential according to EEO guidelines. Work with Us. Change the World. At AECOM, we're delivering a better world. Whether improving your commute, keeping the lights on, providing access to clean water, or transforming skylines, our work helps people and communities thrive. We are the world's trusted infrastructure consulting firm, partnering with clients to solve the world’s most complex challenges and build legacies for future generations. There has never been a better time to be at AECOM. With accelerating infrastructure investment worldwide, our services are in great demand. We invite you to bring your bold ideas and big dreams and become part of a global team of over 50,000 planners, designers, engineers, scientists, digital innovators, program and construction managers and other professionals delivering projects that create a positive and tangible impact around the world. We're one global team driven by our common purpose to deliver a better world. Join us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Marex</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>London, GB</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>breezy</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>https://marex.breezy.hr/p/c440218ba72501-security-engineer</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>About Marex
-Marex Group plc (NASDAQ: MRX) is a diversified global financial services platform providing essential liquidity, market access and infrastructure services to clients across energy, commodities and financial markets. The group provides comprehensive breadth and depth of coverage across four core services: clearing, agency and execution, market making, and hedging and investment solutions. It has a leading franchise in many major metals, energy and agricultural products, with access to 60 exchanges. The group provides access to the world’s major commodity markets, covering a broad range of clients that include some of the largest commodity producers, consumers and traders, banks, hedge funds and asset managers. With more than 40 offices worldwide, the group has over 3,000 employees across Europe, Asia and the Americas.
-For more information visit
-&lt;https://www.marex.com/&gt;
-Vacancy Number: VN3168
-Department description
-Marex has unique access across markets with significant share globally both on and off exchange. The depth of knowledge amongst its teams and divisions provides its customers with clear advantage, and its technology-led service provides access to all major exchanges, order-flow management via screen, voice and DMA, plus award-winning data, insights and analytics.
-The Technology Department delivers differentiation, scalability and security for the business. Technology provides digital tools, software services and infrastructure globally to all business groups. Software development and support teams work in agile ‘streams’ aligned to specific business areas. Our other teams work enterprise-wide to provide critical services including our global service desk, network and system infrastructure, IT operations, security, enterprise architecture and design.
-The Information Security team reports to the CISO and is responsible for protecting Marex data and assets, as well as providing security advice. The team is relatively small; therefore, its members have a chance to experience various areas of security.
-Role Summary
-The Security Engineer will work within the Cyber Security team, reporting to the Cyber Security Manager, and will be responsible for engineering, administering, and continually improving security capabilities across the Marex Group, with a primary focus on Identity Protection, Privileged Access Management, and associated access control environments.
-The role will support the secure management of privileged accounts, access workflows, credential rotation, platform onboarding, incident response, control monitoring, and operational governance relating to privileged access. In addition, the role will contribute to broader identity security capabilities, including secrets management, certificate and PKI-related controls, and the improvement of identity-related security processes.
-Beyond its core identity and PAM responsibilities, the role will support wider cyber security engineering activities, including security platform operations, automation, tooling enhancements, threat detection improvements, and response to security incidents as business and security priorities evolve.
-Responsibilities
-Role specific:
-Engineer security products to be production ready.
-Configure security toolset and controls to identify anomalies, potential incidents, network intrusions, and malware events, etc., ensuring confidentiality, integrity, and availability of Marex’s critical systems
-Find gaps in architecture, define objective and areas of improvement, engineer products to fit the gaps for an effective Threat detection and response.
-Developing and documenting cyber security standards and procedures
-Collaborates with technology teams for incident handling, patching disciplines, and system hardening frameworks
-Collaborates with the Information Technology team on deployment, operation, and continual improvements of security solutions
-Automation of tasks and creation of analytical tools
-Keeping up to date with security news and trends
-Threat Intelligence and Hunting
-Responding and investigating security incidents and exceptions
-Providing relevant KPI and KRI metrics.
-All staff:
-Ensuring compliance with the company’s regulatory requirements under the FCA, NFA, AMF, AFM, MAS.
-Adhere to the operational risk framework for your role ensuring that all regulatory or company determined parameters are complied with.
-Role model for demonstrating highest level standards of integrity and conduct and reflecting Company Values.
-At all times complying with the FCA’s Code of Conduct
-To ensure that you are fully aware of and adhere to internal policies that relate to you, your role or any other activities for which you have any level of responsibility
-To report any breaches of policy to Compliance and/ or your supervisor as required
-To escalate risk events immediately
-To provide input to risk management processes, as required.
-Competencies, Skills, Experience &amp; Qualifications:
-Skills and Experience:
-Essential:
-A minimum of 5 years’ experience in Information Security.
-Comprehensive knowledge of identity security and access control technologies, including Entra ID, Identity Protection, Privileged Access Management, Secrets Management, Key Management, PKI, and Certificate Management.
-Strong hands-on experience administering and supporting Privileged Access Management solution (tools such as CyberArk or equivalent), including account onboarding, safes, platforms, policies, credential rotation, session management, access workflows, operational troubleshooting, and control monitoring.
-Strong hands-on experience with Windows, Linux, cloud platforms, databases, directory services, and service accounts from an identity security perspective.
-Experience around Secrets &amp; Key management tools such as Hashicorp vault or Conjour or equivalent.
-Strong experience around PKI management tools such as Venafi or Digicert or equivalent.
-Experience with Identity &amp; privileged access governance, least privilege, break-glass processes, access reviews, privileged account lifecycle management, and audit evidence production.
-Experience producing operational metrics, control reporting, and audit evidence for identity - PAM, Secrets Management controls.
-Knowledge of security processes such as vulnerability management, penetration testing, incident response, and security control assurance.
-Knowledge of security standards and frameworks such as CIS and NIST.
-Experience supporting or improving security platforms, automation, tooling integrations, detection capabilities, or operational security processes.
-Excellent communication skills, with the ability to engage effectively with technical teams, control owners, auditors, and wider business stakeholders.
-** Candidates with less than 5 years’ experience will still be considered
-Competencies:
-A collaborative team player, approachable, self-efficient and influences a positive work environment
-Demonstrates curiosity
-Resilient in a challenging, fast-paced environment
-Ability to take a high level of responsibility in a fast pace and high-volume environment
-Excels at building relationships, networking and influencing others
-Strategic collaborator with insight and agility, able to anticipate future challenges, ensuring operational effectiveness
-Conduct Rules
-,
-You must:
-Act with integrity
-Act with due skill, care and diligence
-Be open and cooperative with the FCA, the PRA and other regulators
-Pay due regard to the interests of customers and treat them fairly
-Observe proper standard of market conduct
-Act to deliver good outcomes for retail customers
-Company Values
-Be collaborative
-- by working together across the organisation, we foster teamwork, can better respond to challenges and successfully deliver for our clients
-Act with integrity
-- we pride ourselves on our honesty and high ethical standards. We apply these values when working with all our clients, colleagues and other stakeholders
-Be adaptable and entrepreneurial
-- we embrace change as markets evolve to constantly increase our efficiency and create innovative solutions for our clients. We are interested in the world around us and inquisitive about understanding the challenges and opportunities our clients face.
-Be respectful
-– how we treat each other, and our clients says everything about who we are. We always act respectfully and treat people fairly in everything we do.
-Nurture talent
-– we aim to grow our own talent and make Marex the place ambitious, hardworking and talented people choose to build their career. This means giving and taking stretch opportunities, taking risks, and committing to career development and support – for ourselves, and our teams.
-Marex is fully committed to being an inclusive employer and providing an inclusive and accessible recruitment process for all. We will provide reasonable adjustments to remove any disadvantage to you being considered for this role. We value the differences that a diverse workforce brings to the company.  We welcome applications from candidates returning to the workforce.  Also, Marex is committed to avoiding circumstances in which the appearance or possibility of conflicts of interest may exist within the hiring process.
-If you would like to receive any information in a different way or would like us to do anything differently to help you, please include it in your application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>About Marex Marex Group plc (NASDAQ: MRX) is a diversified global financial services platform providing essential liquidity, market access and infrastructure services to clients across energy, commodities and financial markets. The group provides comprehensive breadth and depth of coverage across four core services: clearing, agency and execution, market making, and hedging and investment solutions. It has a leading franchise in many major metals, energy and agricultural products, with access to 60 exchanges. The group provides access to the world’s major commodity markets, covering a broad range of clients that include some of the largest commodity producers, consumers and traders, banks, hedge funds and asset managers. With more than 40 offices worldwide, the group has over 3,000 employees across Europe, Asia and the Americas. For more information visit Vacancy Number: VN3168 Department description Marex has unique access across markets with significant share globally both on and off exchange. The depth of knowledge amongst its teams and divisions provides its customers with clear advantage, and its technology-led service provides access to all major exchanges, order-flow management via screen, voice and DMA, plus award-winning data, insights and analytics. The Technology Department delivers differentiation, scalability and security for the business. Technology provides digital tools, software services and infrastructure globally to all business groups. Software development and support teams work in agile ‘streams’ aligned to specific business areas. Our other teams work enterprise-wide to provide critical services including our global service desk, network and system infrastructure, IT operations, security, enterprise architecture and design. The Information Security team reports to the CISO and is responsible for protecting Marex data and assets, as well as providing security advice. The team is relatively small; therefore, its members have a chance to experience various areas of security. Role Summary The Security Engineer will work within the Cyber Security team, reporting to the Cyber Security Manager, and will be responsible for engineering, administering, and continually improving security capabilities across the Marex Group, with a primary focus on Identity Protection, Privileged Access Management, and associated access control environments. The role will support the secure management of privileged accounts, access workflows, credential rotation, platform onboarding, incident response, control monitoring, and operational governance relating to privileged access. In addition, the role will contribute to broader identity security capabilities, including secrets management, certificate and PKI-related controls, and the improvement of identity-related security processes. Beyond its core identity and PAM responsibilities, the role will support wider cyber security engineering activities, including security platform operations, automation, tooling enhancements, threat detection improvements, and response to security incidents as business and security priorities evolve. Responsibilities Role specific: Engineer security products to be production ready. Configure security toolset and controls to identify anomalies, potential incidents, network intrusions, and malware events, etc., ensuring confidentiality, integrity, and availability of Marex’s critical systems Find gaps in architecture, define objective and areas of improvement, engineer products to fit the gaps for an effective Threat detection and response. Developing and documenting cyber security standards and procedures Collaborates with technology teams for incident handling, patching disciplines, and system hardening frameworks Collaborates with the Information Technology team on deployment, operation, and continual improvements of security solutions Automation of tasks and creation of analytical tools Keeping up to date with security news and trends Threat Intelligence and Hunting Responding and investigating security incidents and exceptions Providing relevant KPI and KRI metrics. All staff: Ensuring compliance with the company’s regulatory requirements under the FCA, NFA, AMF, AFM, MAS. Adhere to the operational risk framework for your role ensuring that all regulatory or company determined parameters are complied with. Role model for demonstrating highest level standards of integrity and conduct and reflecting Company Values. At all times complying with the FCA’s Code of Conduct To ensure that you are fully aware of and adhere to internal policies that relate to you, your role or any other activities for which you have any level of responsibility To report any breaches of policy to Compliance and/ or your supervisor as required To escalate risk events immediately To provide input to risk management processes, as required. Competencies, Skills, Experience &amp; Qualifications: Skills and Experience: Essential: A minimum of 5 years’ experience in Information Security. Comprehensive knowledge of identity security and access control technologies, including Entra ID, Identity Protection, Privileged Access Management, Secrets Management, Key Management, PKI, and Certificate Management. Strong hands-on experience administering and supporting Privileged Access Management solution (tools such as CyberArk or equivalent), including account onboarding, safes, platforms, policies, credential rotation, session management, access workflows, operational troubleshooting, and control monitoring. Strong hands-on experience with Windows, Linux, cloud platforms, databases, directory services, and service accounts from an identity security perspective. Experience around Secrets &amp; Key management tools such as Hashicorp vault or Conjour or equivalent. Strong experience around PKI management tools such as Venafi or Digicert or equivalent. Experience with Identity &amp; privileged access governance, least privilege, break-glass processes, access reviews, privileged account lifecycle management, and audit evidence production. Experience producing operational metrics, control reporting, and audit evidence for identity - PAM, Secrets Management controls. Knowledge of security processes such as vulnerability management, penetration testing, incident response, and security control assurance. Knowledge of security standards and frameworks such as CIS and NIST. Experience supporting or improving security platforms, automation, tooling integrations, detection capabilities, or operational security processes. Excellent communication skills, with the ability to engage effectively with technical teams, control owners, auditors, and wider business stakeholders. ** Candidates with less than 5 years’ experience will still be considered Competencies: A collaborative team player, approachable, self-efficient and influences a positive work environment Demonstrates curiosity Resilient in a challenging, fast-paced environment Ability to take a high level of responsibility in a fast pace and high-volume environment Excels at building relationships, networking and influencing others Strategic collaborator with insight and agility, able to anticipate future challenges, ensuring operational effectiveness Conduct Rules , You must: Act with integrity Act with due skill, care and diligence Be open and cooperative with the FCA, the PRA and other regulators Pay due regard to the interests of customers and treat them fairly Observe proper standard of market conduct Act to deliver good outcomes for retail customers Company Values Be collaborative - by working together across the organisation, we foster teamwork, can better respond to challenges and successfully deliver for our clients Act with integrity - we pride ourselves on our honesty and high ethical standards. We apply these values when working with all our clients, colleagues and other stakeholders Be adaptable and entrepreneurial - we embrace change as markets evolve to constantly increase our efficiency and create innovative solutions for our clients. We are interested in the world around us and inquisitive about understanding the challenges and opportunities our clients face. Be respectful – how we treat each other, and our clients says everything about who we are. We always act respectfully and treat people fairly in everything we do. Nurture talent – we aim to grow our own talent and make Marex the place ambitious, hardworking and talented people choose to build their career. This means giving and taking stretch opportunities, taking risks, and committing to career development and support – for ourselves, and our teams. Marex is fully committed to being an inclusive employer and providing an inclusive and accessible recruitment process for all. We will provide reasonable adjustments to remove any disadvantage to you being considered for this role. We value the differences that a diverse workforce brings to the company. We welcome applications from candidates returning to the workforce. Also, Marex is committed to avoiding circumstances in which the appearance or possibility of conflicts of interest may exist within the hiring process. If you would like to receive any information in a different way or would like us to do anything differently to help you, please include it in your application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>miovision</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Product Security Lead</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Canada Remote</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>CA$163K – CA$198K • Offers Equity • Offers Bonus</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/miovision/002b55dc-a82d-4e28-a4a9-b137b44b1e5a/application</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t>**About Miovision:**
 At Miovision, we’re unlocking transportation networks that move you. Our vision and mission is to enable smart, fast, safe communities that simply flow, as we drive the Intelligent Mobility Revolution. Backed by the world’s most advanced traffic AI, Miovision’s innovations in traffic signal planning and operations are making it possible for cities to improve the transportation experience for drivers, cyclists and pedestrians.  
@@ -9773,68 +9910,68 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>kin</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>$141,890 – $159,650 • Offers Equity</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/kin/c50d549c-24af-4f89-a449-62110b25fc0d/application</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t>## **Quick Summary**
 Own endpoint detection and cloud security at a fully cloud-based company. Tune out the noise, lock down AWS, and build security champions across Kin. 5+ years.
@@ -9930,64 +10067,64 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Ingénieure / Ingénieur Cloud Security - Stage</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Nancy, Grand Est, France</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/oGmK9Lp/jobs/ingenieure-ingenieur-cloud-security-stage_nancy</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t>Rejoignez Capgemini, un leader mondial de la transformation digitale. En tant que stagiaire en sécurité cloud, vous participerez à la sécurisation des environnements cloud, contribuerez à l'exploitation et à l'amélioration de la plateforme Splunk, et réaliserez des analyses de sécurité. Vous bénéficierez d'une communauté d'experts, d'opportunités d'évolution de carrière et d'un apprentissage continu.
 - Participer à la sécurisation des environnements Cloud et contribuer à l’exploitation de la plateforme Splunk.
@@ -10011,64 +10148,64 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Ingénieure / Ingénieur Cloud Security - stage</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Schiltigheim, Grand Est, France</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/oGmK9Lp/jobs/ingenieure-ingenieur-cloud-security-stage_schiltigheim</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t>Rejoignez Capgemini, un leader mondial de la transformation numérique. En tant que stagiaire en cybersécurité, vous participerez à l'analyse des risques liés aux environnements OT/IoT et Cloud, contribuerez à la sécurisation des infrastructures et architectures Cloud, et réaliserez des analyses de vulnérabilités. Vous bénéficierez d'un ensemble d'avantages, d'une qualité de vie au travail équilibrée, et d'un environnement inclusif.
 - Participer à l’analyse des risques liés aux environnements OT/IoT et Cloud, et contribuer à la sécurisation des infrastructures Cloud.
@@ -10093,64 +10230,64 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Ingénieure / Ingénieur Cloud Security - Stage</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Lille, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/oGmK9Lp/jobs/ingenieure-ingenieur-cloud-security-stage_lille</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t>Rejoignez Capgemini, un leader mondial de la transformation digitale. En tant que stagiaire en sécurité Cloud, vous travaillerez aux côtés d'experts en Cloud et cybersécurité, en vous concentrant sur l'analyse et l'amélioration de la sécurité des environnements Cloud, la mise en œuvre de bonnes pratiques de sécurité, la sécurisation des environnements Kubernetes, et bien plus encore. Vous bénéficierez d'une évolution de carrière, d'un apprentissage continu et d'un environnement de travail inclusif et multiculturel.
 - Participer à l'analyse et à l'amélioration de la sécurité des environnements Cloud, ainsi qu'à la mise en œuvre de bonnes pratiques de sécurité.
@@ -10173,2611 +10310,10 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>EVB</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Cyber Security Engineer</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Remote, xx</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/EVB/744000150977099-cyber-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>Job Title: Cyber Security Engineer Job Type: Contractor Schedule: Flexible, you pick the hours and days (including weekends if desired) Location: Remote About the hiring company: Our client is a rapidly growing, venture-backed AI company helping shape the next generation of intelligent systems. By combining world-class human expertise with advanced machine learning workflows, they enable leading AI organizations to build, evaluate, and improve cutting-edge models used across a wide range of industries. The company works with highly accomplished professionals in fields such as software engineering, finance, healthcare, legal, operations, research, and other specialized domains. These experts contribute directly to the development of advanced AI systems by providing real-world knowledge, evaluations, feedback, and domain-specific judgment that help models reason more accurately and perform more effectively. Leveraging a proprietary AI-driven talent assessment and matching platform, the organization identifies exceptional professionals globally and connects them with high-impact projects at the forefront of artificial intelligence. Backed by more than $40 million in funding and supported by a rapidly expanding international network of experts, the company is building critical human intelligence infrastructure for the AI economy and creating meaningful opportunities for professionals to apply their expertise in entirely new ways. Job Summary: Engaging Cyber Security Engineers to contribute technical expertise to a dynamic customer project. In this role, you'll apply your expertise to help train next-generation AI systems. Your work will shape how models learn, reason, and perform through high-quality, real-world input. No prior experience in AI is required — your domain knowledge is what matters. What we're looking for: Analyze, debug, and resolve software bugs and vulnerabilities across diverse codebases. Implement new features and enhance existing functionality in projects using Python3, Java, Rust, Go, C++, or TypeScript. Refactor legacy code to improve maintainability, security, and performance. Perform codebase audits, penetration testing, and other security assessments to identify and mitigate risks. Contribute to backend development and optimize application performance for scalability and security. Document findings, suggest improvements, and provide real-world insights to improve AI training datasets. Preferred Qualifications: Expertise in one or more languages: Python3, Java, Rust, Go, C++, or TypeScript. Proven experience in debugging, bug fixing, and backend development for complex systems. Strong background in cybersecurity practices, including pentesting, security audit, and vulnerability assessment. Proficiency in algorithms, codebase refactoring, and optimizing software for performance and security. Ability to communicate complex technical findings clearly and concisely. Familiarity with secure software development lifecycles and modern threat landscapes. Experience contributing to AI-related or data-driven projects is a plus, but not required. Process: Apply to the role, filling out the screening questions Complete AI Interview (approx. 30 minutes) Technical Assessment (Tentative) Hiring Manager review Compensation Structure Compensation is output-based; experts are paid per task that meets the project specifications. The time required to complete work may vary depending on the expert’s experience and workflow. Minimum submission requirements apply. Experts must submit a minimum of tasks per week. Start Timeline &amp; Availability We typically fill roles within 48 hours and are looking for experts ready to jump in right away. If selected, we expect you to start your first tasks within 24–48 hours of completing onboarding.
-A very attractive and competitive package is offered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>samsara</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - Threat Detection</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Remote - CA</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.samsara.com/company/careers/roles/8212787?gh_jid=8212787</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>**Who we are**
-Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping improve the safety, efficiency and sustainability of the physical operations that power our global economy. Representing more than 40% of global GDP, these industries are the infrastructure of our planet, including agriculture, construction, field services, transportation, and manufacturing — and we are excited to help digitally transform their operations at scale.
-Working at Samsara means you’ll help define the future of physical operations and be on a team that’s shaping an exciting array of product solutions, including Video-Based Safety, Vehicle Telematics, Apps and Driver Workflows, and Equipment Monitoring. As part of a recently public company, you’ll have the autonomy and support to make an impact as we build for the long term.
-### **About the role**
-Samsara Security is looking for a Senior Threat Detection Engineer. This is a hands-on engineering role: you will build and operate the signals, pipelines, and tooling that power how we discover threats against Samsara and our customers.
-The Threat Detection team owns the detection platform end to end — the data pipelines that feed it, the detection content that runs on it, the CI/CD that ships it, and the AI-assisted tooling that scales what a small team can cover. You will write detections, and you will also build the machinery that makes the next detection faster to develop, safer to deploy, and measurable in production.
-You will report to the Director of Threat Detection and Response and work closely with Security Operations, Application Security, and Enterprise Security, as well as engineering teams across the company.
-We are looking for someone who takes projects from idea to proof-of-concept to production, who is comfortable being the first person to build something, and who is genuinely interested in what AI can and cannot do for detection engineering — including where it introduces risk rather than removing it.
-This role is open to candidates residing in the US **except** the San Francisco Bay Metro Area, NYC Metro Area, and Washington, D.C. Metro Area.
-### **You should apply if:**
-- **You want to impact the industries that run our world:** Your efforts will result in real-world impact—helping to keep the lights on, get food into grocery stores, reduce emissions, and most importantly, ensure workers return home safely.
-- **You are the architect of your own career:** If you put in the work, this role won't be your last at Samsara. We set up our employees for success and have built a culture that encourages rapid career development, countless opportunities to experiment and master your craft in a hyper growth environment.
-- **You're energized by our opportunity:** The vision we have to digitize large sectors of the global economy requires your full focus and best efforts to bring forth creative, ambitious ideas for our customers.
-- **You want to be with the best:** At Samsara, we win together, celebrate together and support each other. You will be surrounded by a high-caliber team that will encourage you to do your best.
-### **In this role, you will:**
-- Build, deploy, and continuously improve MITRE ATT&amp;CK–aligned detections across cloud, endpoint, identity, email, and application telemetry, with clear false-positive thresholds.
-- Own the full detection lifecycle—from hypothesis, data validation, and baselining through deployment, tuning, validation, and retirement.
-- Advance our detection-as-code platform through version control, peer review, automated testing, CI/CD, and improved pipeline reliability and observability.
-- Identify emerging threat surfaces and build integrations that strengthen data ingestion, enrichment, and coverage across internal and third-party systems.
-- Evaluate AI-powered security capabilities, including secure MCP integrations, threat hunting, anomaly detection, and response automation.
-- Turn threat intelligence into actionable detection and retrospective scanning.
-- Partner closely with Security Operations during investigations, incidents, table top exercises, detection maintenance, and code pairing.
-- Champion, role model, and embed Samsara’s cultural principles (Focus on Customer Success, Build for the Long Term, Adopt a Growth Mindset, Be Inclusive, Win as a Team) as we scale globally and across new offices.
-### **Minimum requirements for the role:**
-- 6+ years in security engineering, detection engineering, or a related technology discipline.
-- Strong Python and SQL skills, with experience analyzing large datasets to build and validate detections.
-- Hands-on experience with detection-as-code, Git-based workflows, automated testing, and CI/CD deployment.
-- Deep experience with modern SIEM platforms, including data onboarding, advanced queries, dashboards, and threat intelligence enrichment.
-- Working knowledge of AWS, Linux, containers, and EDR.
-- Proven ability to build systems from scratch, lead projects independently, learn new technologies quickly, and communicate technical concepts clearly through documentation, RFCs, and presentations.
-### **An ideal candidate also has:**
-- Experience with data orchestration platforms such as Airflow or Databricks.
-- Applied experience with LLMs, agentic frameworks, and MCP integrations, including their security risks and failure modes.
-- Experience with behavioral analytics, anomaly detection, feature engineering, and model evaluation.
-- Familiarity with risk-based alerting, ChatOps, distributed alerting, and attack simulation.
-- Additional experience with Go, Terraform, malware analysis, digital forensics, or FedRAMP environments.
-#LI-Remote 
-The range of annual base salary for full-time employees for this position is below. Please note that base pay offered may vary depending on factors including your city of residence, job-related knowledge, skills, and experience. This role is also eligible for an initial RSU grant with no vesting cliff, and ongoing refresh opportunities tied to performance, subject to plan terms and conditions. Learn more about our total rewards and benefits below.
-Annual Base Salary
-$157,675—$238,500 USD
-**Total Rewards**
-At Samsara, we build for the people who keep the global economy moving. We want owners, not passengers, which is why [our rewards](https://www.samsara.com/company/careers/benefits) are designed to fuel high-impact builders. Our compensation program delivers above-market total compensation through a combination of base salary, performance-based bonus/variable pay, and equity (for eligible roles) in a high-growth public company. We meaningfully differentiate pay for our top performers, who have the opportunity to earn above-market compensation that can outpace the broader market over time.
-Beyond compensation, we provide the foundations that enable long-term success: a flexible, employee-led remote model, a professional development stipend, comprehensive health and parental leave plans, and more. If you’re ready to build for the long term and own the outcome, your journey starts here.
-**Flexible Working**
-At Samsara, we embrace a flexible working model that caters to the diverse needs of our teams. Our offices are open for those who prefer to work in-person and we also support remote work where it aligns with our operational requirements. For certain positions, being close to one of our offices or within a specific geographic area is important to facilitate collaboration, access to resources, or alignment with our service regions. In these cases, the job description will clearly indicate any working location requirements. Our goal is to ensure that all members of our team can contribute effectively, whether they are working on-site, in a hybrid model, or fully remotely. All offers of employment are contingent upon an individual’s ability to secure and maintain the legal right to work at the company and in the specified work location, if applicable.
-**Belonging at Samsara**
-At Samsara, we welcome everyone regardless of their background. All qualified applicants will receive consideration for employment without regard to race, color, religion, national origin, sex, gender, gender identity, sexual orientation, protected veteran status, disability, age, and other characteristics protected by law. We depend on the unique approaches of our team members to help us solve complex problems and want to ensure that Samsara is a place where people from all backgrounds can make an impact.
-**Accommodations**
-Samsara is an inclusive work environment, and we are committed to ensuring equal opportunity in employment for qualified persons with disabilities. Please email [accessibleinterviewing@samsara.com](mailto:accessibleinterviewing@samsara.com) or [click here](https://forms.gle/DrM6DFQUiSgfPtCVA) if you require any reasonable accommodations throughout the recruiting process.
-**Our Commitment to Authenticity**
-We use [Tofu](https://hiretofu.com/privacyPolicy), a fraud detection tool, to validate the authenticity of applications and protect against identity fraud. This ensures we are connecting with real people and allows us to prioritize genuine candidates. Please see Samsara’s [Candidate Privacy Notice](https://www.samsara.com/legal/candidate-privacy-notice) for more information.
-**Fraudulent Employment Offers**
-Samsara is aware of scams involving fake job interviews and offers. Please know we do not charge fees to applicants at any stage of the hiring process. Official communication about your application will only come from emails ending in @samsara.com, @us-greenhouse-mail.io or @mail3.guide.co. For more information regarding fraudulent employment offers, please visit our [blog post here](https://samsara.com/blog/avoiding-fake-job-offers).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>qualtrics</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Krakow, Poland</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.qualtrics.com/careers/us/en/job/8213878?gh_jid=8213878</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>At Qualtrics, we create software the world’s best brands use to deliver exceptional frontline experiences, build high-performing teams, and design products people love. But we are more than a platform—we are the creators and stewards of the Experience Management category serving over 18K clients globally. Building a category takes grit, determination, and a disdain for convention—but most of all it requires close-knit, high-functioning teams with an unwavering dedication to serving our customers.   
-When you join one of our teams, you’ll be part of a nimble group that’s empowered to set aggressive goals and move fast to achieve them. Strategic risks are encouraged and complex problems are solved together, by passing the microphone and iterating until the best solution comes to light. You won’t have to look to find growth opportunities—ready or not, they’ll find you. From retail to government to healthcare, we’re on a mission to bring humanity, connection, and empathy back to business. Join over 5,000 people across the globe who think that’s work worth doing.
-**Senior Security Engineer**
-**Why We Have This Role**
-Qualtrics is looking for a CDU Analyst to support the (AMR or KRK) team’s daily operations that are responsible for detecting, triaging, and responding to security threats across our global environment. You'll support the day-to-day operations of the team and continuously mature our detection and response capabilities to keep pace with an evolving threat landscape. This is a hands-on role — you'll support in guiding strategy while staying close enough to work alongside the team and manage incidents.
-**How You’ll Find Success**
-- Strategic Visionary: You possess an in-depth understanding of the cybersecurity threat landscape and proactively identify emerging risks. You help shape the Security Operations strategy, ensuring alignment with the organization's overall goals.
-- Technical Innovator: You drive continuous improvement by evaluating and implementing cutting-edge security tools, techniques, and automation. Your relentless pursuit of innovation keeps us ahead of evolving threats.
-- Collaborative Leader: You build strong cross-functional partnerships, championing security across the organization. You foster a collaborative environment where teams work seamlessly to achieve a strong security posture.
-- Resilient and Adaptive: You thrive in a dynamic environment, effectively managing complex security projects and leading teams through change. Your ability to adapt and problem-solve makes you a key asset during challenging situations.
-**How You’ll Grow**
-- Shape Industry Standards: Participate in leading security conferences, thought leadership initiatives, and industry working groups to shape the future of cybersecurity practices.
-- Executive Presence: Gain direct exposure to executive-level decision-making, refining your strategic communication and influencing skills.
-- Expand Your Leadership Toolkit: Lead a team of skilled security professionals, providing you with ample opportunities to enhance your mentorship, coaching, and talent development abilities.
-- Complex Problem-Solving: Tackle high-impact security challenges that will push your critical thinking, analysis, and strategy-building skills.
-**Things You’ll Do**
-- Respond in a Tier 2 role including 24x7 monitoring, detection, triage, and incident response functions
-- Support and develop CDU metrics and KPIs (MTTD, MTTR, alert volume/fidelity, coverage) and report on program health to security leadership
-- Drive continuous improvement of detection logic, playbooks, and automation in partnership with detection engineering and threat intelligence teams
-- Serve as an escalation point and incident commander for high-severity security incidents, coordinating cross-functional response
-- Partner with Threat Intelligence, Detection Engineering, IT, Legal, and Product/Engineering teams to close gaps in visibility and response
-- Manage relationships with any outsourced/MSSP or co-managed CDU partners, ensuring SLAs and quality standards are met
-- Evaluate and help select CDU tooling (SIEM, SOAR, EDR, XDR, ticketing) and drive adoption of automation to reduce analyst toil
-- Own CDU-related audit, compliance, and customer trust requirements (e.g., SOC 2, ISO 27001, FedRAMP as applicable)
-- Build and maintain incident response runbooks, tabletop exercises, and post-incident review processes
-- Participate in an on-call rotation for incidents and provide leadership presence during major security events
-**What We’re Looking For On Your Resume**
-- Required
-  - 5+ years in security operations, incident response, or a related security discipline, including 2+ years in a people-management or team-lead role
-  - Demonstrated experience scaling a 24x7 CDU function, whether in-house, hybrid, or via MSSP oversight
-  - Strong technical grounding in SIEM/SOAR platforms, EDR/XDR, network and cloud security monitoring, and the MITRE ATT&amp;CK framework
-  - Experience leading incident response for significant security events, including coordination with legal, communications, and executive stakeholders
-  - Track record of hiring, developing, and retaining security talent
-  - Excellent communication skills — able to translate technical detail into risk-based language for non-technical leaders
-  - Experience with cloud environments (AWS, Azure, or GCP) and SaaS security operations
-- Nice to Have  
-  - Experience in a SaaS or enterprise software company handling customer data at scale
-  - Familiarity with compliance frameworks relevant to Qualtrics' customer base (SOC 2, ISO 27001, FedRAMP, GDPR)
-  - Relevant certifications (CISSP, GCIH, GCFA, CISM, or similar)
-  - Experience building or maturing threat detection and threat hunting programs
-  - Background in scripting/automation (Python, PowerShell) to support SOAR workflows
-**What You Should Know About This Team**
-- Innovation at Our Core: Our Security Operations team embraces change and thrives on solving complex challenges. We value experimentation, continuous learning, and push the boundaries of conventional security practices.
-- Collaborative Environment: We believe in the power of teamwork and foster open communication across the team and the wider organization. Your ideas will be heard, and your collaboration will be essential.
-- Data-Driven Approach: We rely on data-driven insights to inform our security strategies, measure effectiveness, and continuously improve our posture.
-- Growth Mindset: We are committed to your professional development. You'll have opportunities to expand your expertise, contribute to high-visibility projects, and advance your career in cybersecurity.
-- Joining our team means stepping into a role that's vital, challenging, and deeply linked to Qualtrics' aim of reshaping industries by harnessing the power of Experience Management and AI.
-**Our Team’s Favorite Perks and Benefits**
-- Annual Leave: 20 or 26 annual leave days per annum plus an additional day for each year of service (to a max of 5).
-- Private Medical Insurance- Luxmed health &amp; dental cover for you and your dependants.
-- Commuter Assistance- Up to the value of 80 PLN net a month for public transport.
-- Savings Plan- Two company saving plans provided by Nationale Nederlanden: Employee Capital Plan (PPK) &amp; Employee Saving Plan (PPO),
-- QED PROGRAM- Qualtrics Engineer Development (QED) program: support, engineering learning activities up to 10% of engineering work time each quarter.
-- Wellness- Up to the value of 800PLN gross per quarter can be reimbursed for a variety of wellness activities via our dedicated platform Forma,
-- A choice of Multispot cards available.
-- Our employee assistance program with Unum provides counselling and wellbeing support to all employees
-- Experience bonus- 7000 PLN gross per annum. Qualtrics experience bonus is a program designed to provide experiences to our employees they might not otherwise have.
-- Group Life &amp; Income Protection Insurance
-- Glasses/Contact lenses Reimbursement
-- Free breakfasts, lunches, snacks, and drinks for everyone in the office
-- Tax-deductible expenses (up to 50% depending on role)
-**The Qualtrics Hybrid Work Model**: Our hybrid work model is elegantly simple: we all gather in the office three days a week; Mondays and Thursdays, plus one day selected by your organizational leader. These purposeful in-person days in thoughtfully designed offices help us do our best work and harness the power of collaboration and innovation. For the rest of the week, work where you want, owning the integration of work and life. #hybrid
-*Qualtrics is an equal opportunity employer meaning that all qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other protected characteristic.*
-*​​​​​​​Applicants in the United States of America have rights under Federal Employment Laws:[Family &amp; Medical Leave Act](https://www.dol.gov/agencies/whd/posters/fmla), [Equal Opportunity Employment](https://www.eeoc.gov/poster), [Employee Polygraph Protection Act](https://www.dol.gov/agencies/whd/posters/employee-polygraph-protection-act)*
-*Qualtrics is committed to the inclusion of all qualified individuals. As part of this commitment, Qualtrics will ensure that persons with disabilities are provided with reasonable accommodations. If reasonable accommodation is needed to participate in the job application or interview process, to perform essential job functions, and/or to receive other benefits and privileges of employment, please let your Qualtrics contact/recruiter know.*
-*Not finding a role that’s the right fit for now? Qualtrics Insiders is the one-stop shop for all things Qualtrics Life. Sign up for exclusive access to content created with you in mind and get the scoop on what we have going on at Qualtrics - upcoming events, behind the scenes stories from the team, interview tips, hot jobs, and more. No spam - we promise! You'll hear from us two times a month max with fresh, totally tailored info - so be sure to stay connected as you explore your best role and company fit.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>sentinellabs</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Researcher</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sentinelone.com/jobs/?gh_jid=7999397003</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>### Our Purpose
-At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
-### About Us
-SentinelOne is a company at the intersection of AI and security, pioneering a new operating model for cybersecurity. Our AI-native platform unifies protection across endpoint, cloud, identity, data, and AI systems to deliver autonomous detection and response with clarity and speed. By combining real-time analytics, intelligent automation, and a unified data foundation, we reduce noise, simplify complexity, and empower security teams to focus on what truly matters.
-Our teams are builders, problem-solvers, and innovators committed to shaping the future of security. If you are excited to solve hard problems alongside talented, mission-driven people, we invite you to help us build a safer future for humanity.
-### **What Are We Looking For?**
-We’re looking for people who are relentlessly curious and committed to continuous learning. AI is reshaping every function across our business, and we enable every team member, regardless of role or level, to build fluency in AI tools and concepts. Those who thrive here actively seek out new solutions, experiment thoughtfully, and apply what they learn to drive better, faster, smarter outcomes.
-As an Offensive Security Researcher, you will be tasked with proactively researching the newest and most sophisticated attack techniques and working closely with some of the best security researchers in the industry to shape the future of cyber security. You will bring curiosity, persistence, and a drive to leave no stone unturned in the search for the next bypass. By being part of our team, your work will impact protection of tens of millions of customer endpoints worldwide, incl. 4 of Fortune10 and hundreds of Global2000, and you will have a chance to work on a industry-leading endpoint security product (recognized 6x in-a-row as Gartner Leaders, scoring highly in Mitre Att&amp;ck, in Frost Radar, SE Labs and by others).
-### What Will You Do?
-Primary responsibilities include:
-- Proactively research and deeply understand the internals of the newest and most sophisticated attack techniques and exploits, and emulate these attacks to assess and improve our detection engines (incl. designing detections and writing behavioural detection signatures).
-- Build tools to support detection assessments, create proofs of concept for the newest techniques and exploits, and develop automation flows to automate unconventional attacks and offensive frameworks.
-- Work closely with the Threat Intelligence team and the research and engineering detection teams to provide guidance and highlight gaps in detection and visibility capabilities.
-### What Skills and Knowledge Will You Bring?
-Ideal candidates will have:
-- 4+ years of experience in Red Teaming / Security Research / Offensive Research with a deep understanding of Windows internals.
-- Hands-on experience with coding in Python and C/C++.
-- Deep understanding of the malware world (how malware operates, infamous families, evasion and exploitation techniques).
-- Experience in malware analysis (statically and dynamically) and reverse engineering (x86/x64)
-- Understanding of existing EDRs internals.
-- Experience writing detection signatures.
-- Experience leveraging agentic AI workflows for malware analysis and detection engineering tasks (reverse engineering, code auditing, signature writing).
-- Proven track record of conference speaking at security conferences or publications is an advantage
-### Why SentinelOne?
-AI is redefining how the world operates and rewriting the rules of security in real time, and SentinelOne was built for this moment. From day one, we architected an AI-native platform designed to operate at machine speed, not as an add-on to legacy systems but as the foundation itself. If you want to build where innovation and impact move together, this is that place.
-We invest in our Sentinels with comprehensive, competitive benefits designed to support you and your family:
-**Equity &amp; Rewards**
-- Restricted Stock Units (RSUs)
-- Employee Stock Purchase Plan (ESPP)
-**Time Off &amp; Wellbeing**
-- Competitive leave benefits
-- Gender-neutral parental leave
-**Insurance &amp; Financial Security**
-- Medical and insurance benefits
-- Pension scheme
-- Employee Assistance Program (EAP)
-**Work Perks &amp; Flexibility**
-- Global home office allowance
-- Mobile phone allowance
-**Wellness &amp; Lifestyle**
-- Wellness benefit
-SentinelOne is proud to be an Equal Employment Opportunity and Affirmative Action employer. We do not discriminate based upon race, religion, color, national origin, gender (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, or other applicable legally protected characteristics.
-SentinelOne participates in the E-Verify Program for all U.S. based roles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>sentinellabs</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Researcher</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sentinelone.com/jobs/?gh_jid=7999396003</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>### Our Purpose
-At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
-### About Us
-SentinelOne is a company at the intersection of AI and security, pioneering a new operating model for cybersecurity. Our AI-native platform unifies protection across endpoint, cloud, identity, data, and AI systems to deliver autonomous detection and response with clarity and speed. By combining real-time analytics, intelligent automation, and a unified data foundation, we reduce noise, simplify complexity, and empower security teams to focus on what truly matters.
-Our teams are builders, problem-solvers, and innovators committed to shaping the future of security. If you are excited to solve hard problems alongside talented, mission-driven people, we invite you to help us build a safer future for humanity.
-### **What Are We Looking For?**
-We’re looking for people who are relentlessly curious and committed to continuous learning. AI is reshaping every function across our business, and we enable every team member, regardless of role or level, to build fluency in AI tools and concepts. Those who thrive here actively seek out new solutions, experiment thoughtfully, and apply what they learn to drive better, faster, smarter outcomes.
-As an Offensive Security Researcher, you will be tasked with proactively researching the newest and most sophisticated attack techniques and working closely with some of the best security researchers in the industry to shape the future of cyber security. You will bring curiosity, persistence, and a drive to leave no stone unturned in the search for the next bypass. By being part of our team, your work will impact protection of tens of millions of customer endpoints worldwide, incl. 4 of Fortune10 and hundreds of Global2000, and you will have a chance to work on a industry-leading endpoint security product (recognized 6x in-a-row as Gartner Leaders, scoring highly in Mitre Att&amp;ck, in Frost Radar, SE Labs and by others).
-### What Will You Do?
-Primary responsibilities include:
-- Proactively research and deeply understand the internals of the newest and most sophisticated attack techniques and exploits, and emulate these attacks to assess and improve our detection engines (incl. designing detections and writing behavioural detection signatures).
-- Build tools to support detection assessments, create proofs of concept for the newest techniques and exploits, and develop automation flows to automate unconventional attacks and offensive frameworks.
-- Work closely with the Threat Intelligence team and the research and engineering detection teams to provide guidance and highlight gaps in detection and visibility capabilities.
-### What Skills and Knowledge Will You Bring?
-Ideal candidates will have:
-- 4+ years of experience in Red Teaming / Security Research / Offensive Research with a deep understanding of Windows internals.
-- Hands-on experience with coding in Python and C/C++.
-- Deep understanding of the malware world (how malware operates, infamous families, evasion and exploitation techniques).
-- Experience in malware analysis (statically and dynamically) and reverse engineering (x86/x64)
-- Understanding of existing EDRs internals.
-- Experience writing detection signatures.
-- Experience leveraging agentic AI workflows for malware analysis and detection engineering tasks (reverse engineering, code auditing, signature writing).
-- Proven track record of conference speaking at security conferences or publications is an advantage
-### Why SentinelOne?
-AI is redefining how the world operates and rewriting the rules of security in real time, and SentinelOne was built for this moment. From day one, we architected an AI-native platform designed to operate at machine speed, not as an add-on to legacy systems but as the foundation itself. If you want to build where innovation and impact move together, this is that place.
-We invest in our Sentinels with comprehensive, competitive benefits designed to support you and your family:
-**Equity &amp; Rewards**
-- Restricted Stock Units (RSUs)
-- Employee Stock Purchase Plan (ESPP)
-**Time Off &amp; Wellbeing**
-- Competitive leave benefits
-- Gender-neutral parental leave
-**Insurance &amp; Financial Security**
-- Medical and insurance benefits
-- Pension
-- Employee Assistance Program (EAP)
-**Work Perks &amp; Flexibility**
-- Global home office allowance
-- Monthly home office, internet and mobile phone allowance
-**Wellness &amp; Lifestyle**
-- Meal allowance
-- Transportation allowance
-SentinelOne is proud to be an Equal Employment Opportunity and Affirmative Action employer. We do not discriminate based upon race, religion, color, national origin, gender (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, or other applicable legally protected characteristics.
-SentinelOne participates in the E-Verify Program for all U.S. based roles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>sentinellabs</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Researcher</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sentinelone.com/jobs/?gh_jid=7999395003</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>### Our Purpose
-At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
-### About Us
-SentinelOne is a company at the intersection of AI and security, pioneering a new operating model for cybersecurity. Our AI-native platform unifies protection across endpoint, cloud, identity, data, and AI systems to deliver autonomous detection and response with clarity and speed. By combining real-time analytics, intelligent automation, and a unified data foundation, we reduce noise, simplify complexity, and empower security teams to focus on what truly matters.
-Our teams are builders, problem-solvers, and innovators committed to shaping the future of security. If you are excited to solve hard problems alongside talented, mission-driven people, we invite you to help us build a safer future for humanity.
-### **What Are We Looking For?**
-We’re looking for people who are relentlessly curious and committed to continuous learning. AI is reshaping every function across our business, and we enable every team member, regardless of role or level, to build fluency in AI tools and concepts. Those who thrive here actively seek out new solutions, experiment thoughtfully, and apply what they learn to drive better, faster, smarter outcomes.
-As an Offensive Security Researcher, you will be tasked with proactively researching the newest and most sophisticated attack techniques and working closely with some of the best security researchers in the industry to shape the future of cyber security. You will bring curiosity, persistence, and a drive to leave no stone unturned in the search for the next bypass.
-### What Will You Do?
-Primary responsibilities include:
-- Proactively research and deeply understand the internals of the newest and most sophisticated attack techniques, and emulate these attacks to assess and improve detection engines.
-- Build tools to support detection assessments, create proofs of concept for the newest techniques and exploits, and develop automation flows to automate unconventional attacks and offensive frameworks.
-- Work closely with the Threat Intelligence team and the research and engineering detection teams to provide guidance and highlight gaps in detection and visibility capabilities.
-### What Skills and Knowledge Will You Bring?
-Ideal candidates will have:
-- 4+ years of experience in Red Teaming / Security Research / Offensive Research with a deep understanding of Windows internals.
-- Hands-on experience with coding in Python and C/C++.
-- Deep understanding of the malware world (how malware operates, infamous families, evasion and exploitation techniques).
-- Experience in malware analysis (statically and dynamically) and reverse engineering (x86/x64)
-- Understanding of existing EDRs internals.
-- Experience writing detection signatures.
-- Experience leveraging agentic AI workflows for malware analysis and detection engineering tasks (reverse engineering, code auditing, signature writing).
-- Proven track record of conference speaking at security conferences or publications is an advantage
-### Why SentinelOne?
-AI is redefining how the world operates and rewriting the rules of security in real time, and SentinelOne was built for this moment. From day one, we architected an AI-native platform designed to operate at machine speed, not as an add-on to legacy systems but as the foundation itself. If you want to build where innovation and impact move together, this is that place.
-We invest in our Sentinels with comprehensive, competitive benefits designed to support you and your family:
-**Equity &amp; Rewards**
-- Restricted Stock Units (RSUs)
-- Employee Stock Purchase Plan (ESPP)
-**Time Off &amp; Wellbeing**
-- Competitive leave benefits
-- Gender-neutral parental leave
-**Insurance &amp; Financial Security**
-- Medical and insurance benefits
-- Pension
-- Employee Assistance Program (EAP)
-**Work Perks &amp; Flexibility**
-- Global home office allowance
-- Mobile phone reimbursement
-This role has a base pay range that applies consistently across Italy, regardless of candidate location. If you have any questions, please reach out to the recruiter.
-CBA: Contratto Collettivo Nazionale di Lavoro per i Dipendenti Di Aziende del Terziario della Distribuzione e dei Servizi"
-Classification as Quadro
-Base Salary Range
-€51.200—€70.000 EUR
-SentinelOne is proud to be an Equal Employment Opportunity and Affirmative Action employer. We do not discriminate based upon race, religion, color, national origin, gender (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, or other applicable legally protected characteristics.
-SentinelOne participates in the E-Verify Program for all U.S. based roles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>sentinellabs</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Researcher</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sentinelone.com/jobs/?gh_jid=7999393003</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>### Our Purpose
-At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
-### About Us
-SentinelOne is a company at the intersection of AI and security, pioneering a new operating model for cybersecurity. Our AI-native platform unifies protection across endpoint, cloud, identity, data, and AI systems to deliver autonomous detection and response with clarity and speed. By combining real-time analytics, intelligent automation, and a unified data foundation, we reduce noise, simplify complexity, and empower security teams to focus on what truly matters.
-Our teams are builders, problem-solvers, and innovators committed to shaping the future of security. If you are excited to solve hard problems alongside talented, mission-driven people, we invite you to help us build a safer future for humanity.
-### **What Are We Looking For?**
-We’re looking for people who are relentlessly curious and committed to continuous learning. AI is reshaping every function across our business, and we enable every team member, regardless of role or level, to build fluency in AI tools and concepts. Those who thrive here actively seek out new solutions, experiment thoughtfully, and apply what they learn to drive better, faster, smarter outcomes.
-As an Offensive Security Researcher, you will be tasked with proactively researching the newest and most sophisticated attack techniques and working closely with some of the best security researchers in the industry to shape the future of cyber security. You will bring curiosity, persistence, and a drive to leave no stone unturned in the search for the next bypass. By being part of our team, your work will impact protection of tens of millions of customer endpoints worldwide, incl. 4 of Fortune10 and hundreds of Global2000, and you will have a chance to work on a industry-leading endpoint security product (recognized 6x in-a-row as Gartner Leaders, scoring highly in Mitre Att&amp;ck, in Frost Radar, SE Labs and by others).
-### What Will You Do?
-Primary responsibilities include:
-- Proactively research and deeply understand the internals of the newest and most sophisticated attack techniques and exploits, and emulate these attacks to assess and improve our detection engines (incl. designing detections and writing behavioural detection signatures).
-- Build tools to support detection assessments, create proofs of concept for the newest techniques and exploits, and develop automation flows to automate unconventional attacks and offensive frameworks.
-- Work closely with the Threat Intelligence team and the research and engineering detection teams to provide guidance and highlight gaps in detection and visibility capabilities.
-### What Skills and Knowledge Will You Bring?
-Ideal candidates will have:
-- 4+ years of experience in Red Teaming / Security Research / Offensive Research with a deep understanding of Windows internals.
-- Hands-on experience with coding in Python and C/C++.
-- Deep understanding of the malware world (how malware operates, infamous families, evasion and exploitation techniques).
-- Experience in malware analysis (statically and dynamically) and reverse engineering (x86/x64)
-- Understanding of existing EDRs internals.
-- Experience writing detection signatures.
-- Experience leveraging agentic AI workflows for malware analysis and detection engineering tasks (reverse engineering, code auditing, signature writing).
-- Proven track record of conference speaking at security conferences or publications is an advantage
-### Why SentinelOne?
-AI is redefining how the world operates and rewriting the rules of security in real time, and SentinelOne was built for this moment. From day one, we architected an AI-native platform designed to operate at machine speed, not as an add-on to legacy systems but as the foundation itself. If you want to build where innovation and impact move together, this is that place.
-We invest in our Sentinels with comprehensive, competitive benefits designed to support you and your family:
-Salary starting from 3500 EUR/month. Annual bonus based on company performance, paid in two installments. The final base salary may be adjusted based on the individual skills and experience of the selected candidate.
-**Equity &amp; Rewards**
-- Restricted Stock Units (RSUs)
-- Employee Stock Purchase Plan (ESPP)
-- Performance-based bonus
-**Time Off &amp; Wellbeing**
-- Flexible time off, on top of the standard 5 weeks PTO
-- Paid company wellness days and fully paid short-term sick/nursing leave
-- Gender-neutral parental leave
-**Insurance &amp; Financial Security**
-- Life and disability insurance
-- Pension Insurance contribution
-- Global business travel medical insurance
-- Employee Assistance Program (EAP)
-**Work Perks &amp; Flexibility**
-- Global home office allowance
-- Meal allowance
-- Hybrid work in Prague (Karlin), Brno (Clubco) or remote in CZ/SK. Only Prague-based employees are required to work from the office at least 2 days/week.
-**Wellness &amp; Lifestyle**
-- Wellbeing allowance
-- MultiSport benefit program
-- Wellness Coach app
-SentinelOne is proud to be an Equal Employment Opportunity and Affirmative Action employer. We do not discriminate based upon race, religion, color, national origin, gender (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, or other applicable legally protected characteristics.
-SentinelOne participates in the E-Verify Program for all U.S. based roles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>sentinellabs</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Researcher</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Prague, Czech Republic</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sentinelone.com/jobs/?gh_jid=7999391003</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>### Our Purpose
-At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
-### About Us
-SentinelOne is a company at the intersection of AI and security, pioneering a new operating model for cybersecurity. Our AI-native platform unifies protection across endpoint, cloud, identity, data, and AI systems to deliver autonomous detection and response with clarity and speed. By combining real-time analytics, intelligent automation, and a unified data foundation, we reduce noise, simplify complexity, and empower security teams to focus on what truly matters.
-Our teams are builders, problem-solvers, and innovators committed to shaping the future of security. If you are excited to solve hard problems alongside talented, mission-driven people, we invite you to help us build a safer future for humanity.
-### **What Are We Looking For?**
-We’re looking for people who are relentlessly curious and committed to continuous learning. AI is reshaping every function across our business, and we enable every team member, regardless of role or level, to build fluency in AI tools and concepts. Those who thrive here actively seek out new solutions, experiment thoughtfully, and apply what they learn to drive better, faster, smarter outcomes.
-As an Offensive Security Researcher, you will be tasked with proactively researching the newest and most sophisticated attack techniques and working closely with some of the best security researchers in the industry to shape the future of cyber security. You will bring curiosity, persistence, and a drive to leave no stone unturned in the search for the next bypass. By being part of our team, your work will impact protection of tens of millions of customer endpoints worldwide, incl. 4 of Fortune10 and hundreds of Global2000, and you will have a chance to work on a industry-leading endpoint security product (recognized 6x in-a-row as Gartner Leaders, scoring highly in Mitre Att&amp;ck, in Frost Radar, SE Labs and by others).
-### What Will You Do?
-Primary responsibilities include:
-- Proactively research and deeply understand the internals of the newest and most sophisticated attack techniques and exploits, and emulate these attacks to assess and improve our detection engines (incl. designing detections and writing behavioural detection signatures).
-- Build tools to support detection assessments, create proofs of concept for the newest techniques and exploits, and develop automation flows to automate unconventional attacks and offensive frameworks.
-- Work closely with the Threat Intelligence team and the research and engineering detection teams to provide guidance and highlight gaps in detection and visibility capabilities.
-### What Skills and Knowledge Will You Bring?
-Ideal candidates will have:
-- 4+ years of experience in Red Teaming / Security Research / Offensive Research with a deep understanding of Windows internals.
-- Hands-on experience with coding in Python and C/C++.
-- Deep understanding of the malware world (how malware operates, infamous families, evasion and exploitation techniques).
-- Experience in malware analysis (statically and dynamically) and reverse engineering (x86/x64)
-- Understanding of existing EDRs internals.
-- Experience writing detection signatures.
-- Experience leveraging agentic AI workflows for malware analysis and detection engineering tasks (reverse engineering, code auditing, signature writing).
-- Proven track record of conference speaking at security conferences or publications is an advantage
-### Why SentinelOne?
-AI is redefining how the world operates and rewriting the rules of security in real time, and SentinelOne was built for this moment. From day one, we architected an AI-native platform designed to operate at machine speed, not as an add-on to legacy systems but as the foundation itself. If you want to build where innovation and impact move together, this is that place.
-We invest in our Sentinels with comprehensive, competitive benefits designed to support you and your family:
-**Equity &amp; Rewards**
-- Restricted Stock Units (RSUs)
-- Employee Stock Purchase Plan (ESPP)
-- Performance-based bonus
-**Time Off &amp; Wellbeing**
-- Flexible time off, on top of the standard 5 weeks PTO
-- Paid company wellness days and fully paid short-term sick/nursing leave
-- Gender-neutral parental leave
-**Insurance &amp; Financial Security**
-- Private medical care benefit
-- Life and disability insurance
-- Pension Insurance contribution
-- Global business travel medical insurance
-- Employee Assistance Program (EAP)
-**Work Perks &amp; Flexibility**
-- Global home office allowance
-- Meal allowance
-- Hybrid work in Prague (Karlin), Brno (Clubco) or remote in CZ/SK. Only Prague-based employees are required to work from the office at least 2 days/week.
-**Wellness &amp; Lifestyle**
-- Wellbeing allowance
-- MultiSport benefit program
-- Wellness Coach app
-SentinelOne is proud to be an Equal Employment Opportunity and Affirmative Action employer. We do not discriminate based upon race, religion, color, national origin, gender (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, or other applicable legally protected characteristics.
-SentinelOne participates in the E-Verify Program for all U.S. based roles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/n4VFga/jobs/product-security-engineer_gb_aiiiprtu</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Join Cloudflare as a Product Security Engineer, where you will support security assessments and vulnerability operations for our core software products. You will analyze system architecture, threat model new features, and ensure accurate triaging and mitigation of product-related security findings. Your work will involve conducting security reviews, managing the operational lifecycle of product security findings, performing bug bounty triage, coordinating penetration testing, and collaborating with engineering teams. You will also have the opportunity to implement AI-driven tools to automate processes and streamline workflows.
-- Conduct security assessments and vulnerability operations for Cloudflare’s core software products, including analyzing system architecture and threat modeling.
-- Manage the operational lifecycle of product security findings, ensuring vulnerabilities are verified, mapped to the correct engineering owner, and tracked to mitigation.
-- Identify process bottlenecks and build AI-driven tools or scripts to help automate code analysis, optimize triage, and streamline Product Security workflows.
- - Ideally, you have experience in conducting academic/vulnerability research with a focus on systems security
-- Threat Modeling &amp; Risk Analysis: Competency in threat modeling methodologies and the ability to evaluate code flaws to determine their actual engineering and security impact
-- Product/AppSec Expertise: 5+ years of experience in Product or Application Security within large-scale distributed cloud environments or SaaS platforms
-- Vulnerability Lifecycle Operations: Experience tracking, routing, and driving the remediation of software vulnerabilities across engineering groups while working against defined SLAs
-- Practical AI &amp; Automation Engineering: Demonstrated ability to build production-grade automation scripts and tools. Must possess hands-on engineering experience leveraging AI/LLMs to solve operational or technical challenges
-- Strong Collaboration &amp; Communication: Ability to collaborate effectively across teams, clearly communicating technical security risks to software engineers and resolving ownership ambiguity constructively
-- Offensive Security Tooling: Familiarity with modern exploitation techniques, fuzzing frameworks, or automated scanning utilities
-- Program Management Experience: Experience scaling crowdsourced security programs (e.g., HackerOne, Bugcrowd) or optimizing agile project management workflows within JIRA
-- Experience in integrating hardware security features into production code bases</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Senior Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/n4VFga/jobs/senior-product-security-engineer_gb_bdlbmjse</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Join Cloudflare as a Senior Product Security Engineer, where you will lead security assessments and vulnerability operations for our core software products. You will analyze system architecture, threat model new features, and ensure accurate triage and mitigation of product-related security findings. Your work will involve deep-dive security reviews, triaging complex bug bounty submissions, and collaborating with engineering teams to resolve vulnerabilities. You will also have the opportunity to drive AI security innovation, shape penetration testing strategies, and mentor junior engineers. Enjoy competitive pay, flexible vacation, paid parental leave, comprehensive benefits, and a supportive work environment.
-- Conduire des évaluations de sécurité et des opérations de vulnérabilité pour les produits logiciels de Cloudflare.
-- Analyser l'architecture système, modéliser les menaces des nouvelles fonctionnalités et s'assurer que les résultats de sécurité sont correctement triés.
-- Identifier de manière autonome les domaines où nos processus manuels ralentissent et écrire du code pour automatiser le triage initial.
- - Senior-Level Product/AppSec Expertise: Extensive, battle-tested experience in Product or Application Security within large-scale distributed cloud environments or SaaS platforms
-- Practical AI &amp; Automation Engineering: Demonstrated ability to build production-grade automation scripts and tools . Must possess hands-on engineering experience leveraging AI/LLMs to solve operational or technical challenges
-- High Influence &amp; Communication: Superb cross-functional leadership skills; the ability to confidently influence senior engineering leaders, resolve ownership ambiguity, and champion security initiatives without explicit authority
-- Vulnerability Lifecycle Ownership: Proven track record of managing, routing, and driving the remediation of vulnerabilities across multi-stakeholder engineering organizations while strictly enforcing SLAs
-- Advanced Threat Modeling &amp; Risk Analysis: Mastery of threat modeling methodologies (e.g., STRIDE) and an analytical mindset capable of translating complex theoretical risks into prioritized, actionable business context
-- Ideally, you have experience in conducting academic/vulnerability research with a focus on systems security
-- Offensive Mastery: Familiarity with offensive security tooling and modern exploitation techniques used during professional penetration testing
-- Program Management Experience: Experience scaling crowdsourced security programs (e.g., HackerOne, Bugcrowd) or optimizing agile project management workflows within JIRA
-- Experience in integrating hardware security features into production code bases</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Lead Vulnerability Management Engineer</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/n4VFga/jobs/lead-vulnerability-management-engineer_gb_o6sx536i</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Join Cloudflare as a Lead Vulnerability Management Engineer, where you will be the technical authority for the vulnerability management program. You will lead the evaluation and integration of advanced security technologies, collaborate with various teams to architect scalable remediation workflows, and leverage emerging technologies to enhance operational efficiency. This role requires a highly technical, proactive leader with experience in vulnerability management and a strong understanding of security frameworks.
-- Lead the architecture, systems design, technology evaluation, and systems integration for the global Vulnerability Management program, ensuring tooling is effectively embedded across the technology stack.
-- Oversee and conduct advanced vulnerability scanning, performing in-depth validation of findings to verify accuracy, filter false positives, and lead the triage and prioritization of critical risks.
-- Design and implement AI-driven solutions to manage the vulnerability lifecycle and automate repetitive operational tasks within the vulnerability management domain.
- - Bachelor's degree in Computer Science, Information Security, or security certifications in a related field
-- Demonstrated experience using AI to develop and manage complex workflows and applications
-- Solid understanding of cloud, enterprise, and government security frameworks, including DoD Impact Level (IL4), FedRAMP, SOC 2, PCI DSS, and NIST
-- Strong analytical skills to identify patterns in data and distinguish between theoretical risk and actual exploitability
-- The ability to translate high-level compliance policies and regulatory requirements into precise, technical vulnerability scanning configurations and remediation SLAs
-- Proven experience supporting GRC or external audit cycles (e.g., PCI-DSS, SOC-2, ISO 27001) by providing technical evidence, explaining compensating controls, or articulating risk-acceptance justifications
-- Strong communication (written and verbal) and interpersonal skills, with the ability to effectively collaborate with technical and non-technical teams
-- 5+ years of Vulnerability Management experience, with a proven track record in a senior or lead technical capacity
-- Hands-on experience with vulnerability scanning platforms (e.g., Qualys, Nessus, Rapid7 InsightVM)
-- A strong understanding of vulnerability risk scoring (e.g., CVSS, EPSS) and how to apply these risk assessment methodologies in a business context to support remediation
-- Proficiency in using ticketing tools like JIRA for managing tickets and tasks
-- Hands on experience with Infrastructure pentesting tools
-- Experience with scripting languages (e.g., Python) for automation
-- Experience with specific AI-development tooling such as Opencode or Windsurf</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>IAM Security Engineer</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/n4VFga/jobs/iam-security-engineer_gb_ab6625iw</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Join Cloudflare's Identity and Access Management (IAM) team as an IAM Security Engineer. In this role, you will design, implement, and scale IAM solutions for our internal workforce and workloads. You will be responsible for safeguarding our systems, applications, and data by ensuring secure user access, authentication, and authorization mechanisms. You will also provide operational support for IAM systems and participate in an on-call rotation. Enjoy a competitive pay package, flexible vacation policy, paid parental leave, comprehensive benefits, and commuter support.
-- Design, build, test, and deploy IAM solutions across authentication, authorization, and accounting.
-- Build SSO integrations leveraging SAML, OIDC, OAuth, and SCIM, and manage the Identity Governance and Administration platform.
-- Provide operational support of IAM systems including an on-call rotation that may include after hours calls.
- - Experience working with infrastructure as code and configuration management tools like Terraform, Ansible, etc
-- Experience with secure configuration of containerized application platforms (e.g. Kubernetes)
-- Demonstrated ability to build production-grade automation scripts and tools. Must possess hands-on engineering experience leveraging AI/LLMs to solve operational or technical challenges
-- Experience implementing Identity Governance and Administration (IGA) solutions including lifecycle management, SCIM, birthright access (RBAC, ABAC), and access certifications
-- Experience with Identity and Access Management policy application and enforcement
-- Experience working with Identity Threat Detection &amp; Response (ITDR)
-- Advanced scripting experience (Python, TypeScript, Bash, etc.)
-- Strong understanding of identity federation (SAML, OAuth, OpenID Connect, etc.)
-- Experience integrating with applications and SaaS solutions
-- Security engineers take part in a wide variety of tasks and projects in the team. One individual is not expected to know everything, but a working knowledge in several of the following areas is required:
-- Experience implementing Zero Trust controls</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AI Security Research &amp; Red Team Engineer</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>USD 166,000 - 208,000</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/n4VFga/jobs/ai-security-research-red-team-engineer_gb_7rma57tu</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>Join Cloudflare as an AI Security Research &amp; Red Team Engineer. In this critical role, you will be at the forefront of protecting the company and its customers from malicious threats. Your responsibilities will include driving security research, emulating real-world attackers, and improving Cloudflare's security posture. You will also collaborate with the Blue Team, mentor others, and report to executives. This position offers competitive pay, flexible vacation, paid parental leave, comprehensive benefits, and a supportive work environment.
-- Conduire des recherches sur la sécurité, des exercices et des activités qui imitent les attaquants et les attaques du monde réel pour améliorer la posture de sécurité de Cloudflare, en mettant l'accent sur l'IA.
-- Identifier les surfaces d'attaque liées à l'IA grâce à des tests rigoureux des mises en œuvre agentiques et de l'utilisation des LLM, et définir les exigences et les orientations de mise en œuvre.
-- Établir un cadre rigoureux pour tester l'efficacité de la sécurité, en mesurant exactement la performance de nos détections contre les TTP connus.
- - Operational Mindset: Experience using the MITRE ATT&amp;CK framework to map coverage and identify "blind spots" in defensive telemetry
-- Tooling Familiarity: Knowledge of automated breach and attack simulation (BAS) tools, as well as custom-built frameworks for payload delivery and C2 infrastructure
-- Experience: 4+ years in offensive security, application security or other relevant field
-- Technical Roots: A strong background in manual penetration testing, exploit development, or cloud security (AWS/GCP/Bare Metal)
-- Deep knowledge:  AI, Coding agents, LLMs, prompt engineering, AI-related attack vectors (e.g., prompt injection, jailbreaking), and Agentic concepts all for use in the red team but also testing Cloudflare  uses
-- Communication Skills: The ability to explain a complex "0-day" exploit to a non-technical stakeholder while maintaining the respect of a deep-dive engineering team</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Ki</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer (AI)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>London, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/lNcmq3/jobs/senior-application-security-engineer-ai_london_hatyplwl</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>Join Ki, the fastest growing algorithmic insurance carrier in the Lloyd's of London market. As a Senior Application Security Engineer, you will empower our engineering and product teams to safely adopt AI and embed robust technical security controls directly into our services and workflows. Your work will span our entire development lifecycle, protecting everything from agentic LLM integrations to the everyday tools we use.
-- Provide practical implementation advice and guidance on securing AI-powered applications, aligning with frameworks like OWASP ASVS and the OWASP Top 10 for LLM Applications.
-- Lead threat modelling sessions for AI and agentic systems during the technical design phase using STRIDE and AI-specific frameworks.
-- Establish secure guardrails, allowlists, telemetry, and safe-by-default configurations for developer AI tooling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AppSec Engineer</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/HL4Aj8Adc6</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>AppSec Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AppSec Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $80,000–$100,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are looking for an AppSec Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt; Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Security Engineer</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/9m8XBmUdRW</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Artificial Intelligence Security Engineer Location: 1 00% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $80,000–$105,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt;. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt;. Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>careers.tdsynnex.com</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Lead Security Automation Architect</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Barcelona, Barcelona, Spain</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>phenom</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.tdsynnex.com/job/R54091</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>Become part of our team as a Lead Security Automation Architect, designing and implementing robust security solutions across global infrastructure. Advise IT leaders, drive enhancements, and ensure security measures are integrated into all technology. Ideal for experienced cybersecurity professionals with expertise in cloud, AI, and security frameworks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>raya</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/raya/a6c56d98-cb43-42c8-8009-e229486bdfad/apply</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>At Raya, DevSecOps Engineers are passionate about building and maintaining robust, scalable infrastructure that empowers product engineering teams to innovate with confidence. You are excited to work with modern cloud platforms, Kubernetes, and infrastructure-as-code technologies. The ideal candidate will have 6-8+ years of experience with demonstrated growth in previous roles, showing both technical depth and leadership in infrastructure engineering. You will join the Platform Engineering team to help evolve our infrastructure foundation during this period of rapid growth.
-As a DevSecOps Engineer, you'll drive the technological advancement of our Infrastructure Platform within Raya. Leveraging best-in-class cloud technologies and container orchestration, your work will be central to delivering a reliable, secure, and scalable foundation that our product teams depend on daily. We prioritize learning and teamwork and love giving people the opportunity to champion infrastructure solutions to complex challenges while growing into the best versions of themselves.
-A great candidate is excited to support our infrastructure initiatives across multi-regional environments, Kubernetes orchestration, deployment automation, and observability. With a strong focus on performance optimization, you can design infrastructure that maximizes application efficiency and resource utilization. You're enthusiastic about leveraging AI to enhance your own infrastructure workflows, automate complex tasks, and maximize the scale and impact of your work. You design infrastructure architecture in a scalable, evidence-based manner while understanding the value of working within established systems and thoughtfully introducing improvements. Finally, you believe in Raya's vision of enriching lives by fostering relationships through quality, in-person interactions.
-We offer comprehensive medical and dental coverage, $50 a day food delivery budget, equity-based employment, a great culture, learning opportunities, unlimited vacation, 12 weeks paid parental leave, and we pay all employees $1,000 a year to go somewhere in the world that they've never been because of our values of human connection, empathy, and curiosity.
-### Responsibilties
-- Infrastructure Leadership: Design and build major new infrastructure components and platforms to support Raya's growing needs
-- Kubernetes &amp; Container Orchestration: Lead our Kubernetes strategy, designing and implementing container orchestration solutions that optimize for various application workloads
-- Performance Optimization: Design and optimize infrastructure for maximum application performance, focusing on memory management, resource allocation, network traffic optimization, and system efficiency
-- Reliability Engineering: Implement SLOs, monitoring, and observability solutions to ensure high reliability of our platform
-- Cloud Engineering: Apply your in-depth knowledge of AWS to design scalable, resilient architectures across multiple regions
-- Incident Response: Participate in on-call rotations and lead complex infrastructure incident resolution and post-incident analysis
-- System Evolution: Thoughtfully improve existing infrastructure through incremental enhancements while respecting operational constraints
-- Deployment Automation: Enhance our CI/CD pipelines and deployment strategies to enable faster, safer releases
-- AI-Enhanced Workflows: Integrate AI tools and capabilities into infrastructure workflows to automate complex tasks, enhance decision-making, and maximize operational efficiency
-- Infrastructure Security: Collaborate with security teams to implement secure-by-design infrastructure
-- Cost Optimization: Design cost-effective infrastructure solutions and implement optimization strategies
-- Team Mentorship: Contribute to engineering excellence by mentoring other infrastructure engineers
-### Qualifications
-- A BS/MS in Computer Science, Engineering, Systems Administration, or a related technical field (Professional experience can be substituted for candidates with non-engineering educational backgrounds)
-- 6-8+ years of hands-on experience with infrastructure engineering, with a track record of designing and implementing scalable infrastructure solutions
-- Strong expertise in Kubernetes and Docker, with experience designing and managing production container orchestration environments
-- Demonstrated expertise in AWS and infrastructure-as-code tools (Terraform, CloudFormation, Pulumi, Ansible)
-- Experience with performance tuning and optimization of both infrastructure and applications
-- Experience with monitoring and observability tools (Datadog, Prometheus, Grafana)
-- Proficiency in scripting and automation (Python, Bash, Go, Ruby)
-- Experience working with and incrementally improving established infrastructure environments
-- Strong collaborative instincts, emphasizing open communication, transparency, and cross-team interaction
-### Desired Qualifications
-- Background in SRE (Site Reliability Engineering) practices
-- Experience using AI tools to enhance infrastructure workflows, automate tasks, and improve operational efficiency
-- Knowledge of database administration and optimization (PostgreSQL, MongoDB, Redis, Elasticsearch)
-- Experience with multi-regional/global infrastructure deployment and operations
-- Track record of successfully modernizing legacy infrastructure components
-- Strong understanding of Node.js performance characteristics and experience optimizing infrastructure for Node.js workloads, including memory management, CPU utilization patterns, and scaling considerations
-- Proficiency in application profiling and performance analysis tools
-- Experience with network infrastructure and security
-- Experience with infrastructure security and compliance controls
-- Understanding of cost optimization strategies in cloud environments
-- Experience with service mesh technologies (Istio, Linkerd, Consul)
-- Experience with other cloud platforms (GCP, Azure) in addition to AWS
-- Familiarity with disaster recovery planning and implementation
-### What Set's You Apart
-- Reliability Focus: You have a passion for building systems that are resilient, self-healing, and maintainable
-- Performance Optimizer: You have a keen eye for identifying bottlenecks and optimizing system performance at all levels of the stack
-- Problem Solver: You excel at diagnosing complex infrastructure issues and implementing effective solutions
-- Application-Aware Infrastructure: You design infrastructure that maximizes application performance by understanding how applications actually behave in production, with particular expertise in Node.js workloads
-- Pragmatic Innovator: You can balance working within existing constraints while strategically introducing improvements where they'll have the most impact
-- Context Builder: You take time to understand existing systems and historical decisions before proposing changes, appreciating the journey that led to the current state
-- Infrastructure Vision: You think beyond immediate needs to design infrastructure that can scale and evolve with Raya's growth
-- Automation Mindset: You're driven to automate manual processes and eliminate operational toil
-- AI-Powered Efficiency: You're excited about leveraging AI to amplify your capabilities, automate complex workflows, and achieve greater scale and impact in your infrastructure work
-- Impact-driven: You prioritize infrastructure initiatives that maximize impact, aligning with Raya's overarching goals
-- Growth-oriented: You possess a perpetual learner's mindset, open to challenges, and always seeking opportunities to expand your technical horizons</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>guidepointsecurity</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Azure Security Engineer- Remote (Anywhere in the U.S.)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6204117004?gh_jid=6204117004</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>GuidePoint Security provides trusted cybersecurity expertise, solutions and services that help organizations make better decisions and minimize risk. By taking a three-tiered, holistic approach for evaluating security posture and ecosystems, GuidePoint enables some of the nation’s top organizations, such as Fortune 500 companies and U.S. government agencies, to identify threats, optimize resources and integrate best-fit solutions that mitigate risk.
-**General Description**
-We are looking for a skilled **Azure Security Engineer** to support our GuidePoint Microsoft Cloud Security Practice. This role will engage in the development of customer facing Azure security engineering services while providing “Wow Them” service to clients and/or internal customers or co-workers.
-The Azure Security Engineer is responsible for designing, implementing, and securing our customers Azure infrastructure. Azure Security Engineers operate primarily in a remote customer facing role with a focus on integrating cloud security technologies into either an existing or new environment while providing expertise in cloud computing to drive business efficiency and innovation. Azure Security Engineers evaluate existing cloud infrastructure and provide recommendations and or implement improvements to strengthen the cloud security posture of the environment. Azure Security Engineers demonstrate strong working knowledge across Azure Commercial and Azure Gov Cloud tenants, subscription management, landing zones, networking, security, and infrastructure through implementation of Microsoft Azure best practices and infrastructure as code (IaC). Azure Security Engineers work with cloud infrastructure team members as needed to provide secure configurations within the Microsoft Azure infrastructure. As a subject matter expert (SME), the Azure Security Engineer also brings deep, hands-on expertise across the broader Azure platform—including AI platform engineering with Azure AI Foundry and enterprise API management and governance with Azure API Management (APIM)—and serves as the technical authority for architecting, securing, and operationalizing these workloads for customers.
-**About the Cloud Practice**
-The Cloud Practice is responsible for providing advisory services as well as secure implementations specific to security tooling with the intent of protecting the customers' identities, endpoints, data, applications, and cloud infrastructure by designing, deploying, and operationalizing Cloud Solution Providers native security solutions. We focus specifically on ensuring cloud security, data security, identity and access management, as well as threat protection has been implemented following best practices across the organization.
-Our team of Microsoft specialists focus on deploying Microsoft security, compliance, and identity solutions to protect identities, devices, data, apps, and infrastructure. We partner with other internal Teams and resources to ensure the overall goals of the clients are achieved and align with industry standards and best practices.
-**Roles and Responsibilities:**
-- Design Azure cloud solutions with a secure-by-design approach
-- Collaborate with customer IT teams to implement and secure cloud resources, implement configurations based on security policies, standards, and best practices
-- Develop and implement scalable and resilient cloud architecture solutions within Azure Commercial or Azure Gov Cloud environments
-- Develop and implement migration strategies for local on premises hosted environments to Azure cloud tenants
-- Work with customers to secure Microsoft Entra ID
-- Create and implement migration plans for each Azure infrastructure service, system, and/or application that will be deployed to Azure as part of a migration project
-- Create architectural and data flow diagrams for Azure environments
-- Develop and deploy infrastructure as code (IaC) using tools like Terraform, Azure Resource Manager (ARM) templates, Bicep, and PowerShell
-- Ensure systems, applications, and data meet high availability design principles and/or are replicated to meet organizational requirements for disaster and business recovery
-- Analyze and ensure that proper monitoring and alerting systems are in place for systems, services, and applications in customer Azure environments
-- Evaluate and recommend Azure services based on business requirements and industry best practices
-- Collaborate with software developers, system administrators, and other stakeholders to integrate Azure solutions into either new or existing systems and applications
-- Ensure seamless interoperability between on-premises and cloud environments
-- Implement and enforce security requirements to protect Azure-based systems and data
-- Serve as the subject matter expert (SME) for Azure AI Foundry, architecting, deploying, and securing generative AI and machine learning workloads, including model catalog selection, model deployments, AI agents, and prompt flow orchestration
-- Design and implement enterprise-grade Retrieval-Augmented Generation (RAG) and grounding solutions using Azure AI Foundry, Azure AI Search, and integrated customer data sources
-- Establish Responsible AI, content safety, evaluation, and guardrail practices for AI workloads to ensure alignment with governance, data protection, and regulatory requirements
-- Secure Azure AI Foundry workloads through network isolation (private endpoints), managed identities, customer-managed keys, and least-privilege access controls
-- Serve as the subject matter expert (SME) for Azure API Management (APIM), designing and operating secure, scalable API gateways, products, versions, and revisions across Azure Commercial and Azure Gov Cloud environments
-- Author and manage APIM policies for authentication and authorization (OAuth 2.0, JWT validation, mutual TLS), rate limiting, caching, request/response transformation, and backend routing
-- Design and implement APIM as a GenAI gateway in front of Azure AI Foundry and Azure OpenAI endpoints, including token-based rate limiting, semantic caching, load balancing across model deployments, and centralized monitoring of AI consumption
-- Integrate APIM with Microsoft Entra ID, Application Gateway / Web Application Firewall (WAF), private networking, and self-hosted gateways to enforce Zero Trust and secure hybrid connectivity
-- Establish API governance, lifecycle management, developer portal experiences, and end-to-end observability (logging, metrics, and diagnostics) for customer API estates
-- Define and maintain Azure Governance policies including Subscription Management, Cost Management, Security, Resource Consistency, Identity Baseline, Deployment Acceleration, etc.
-- Ensure compliance of architectural and engineering policies, standards, and procedures
-- Stays current with emerging cloud technologies and trends and advise on the adoption of new Azure features and services
-- Works closely with development teams to support DevOps practices and implement continuous integration and continuous deployment (CI/CD) pipelines
-- Leads technical discussions and presentations for internal teams as well as customers
-- Recommends strategies to streamline Azure native technologies for effectiveness and efficiency, considering client needs.
-- Consistently produce work product in conformance with GuidePoint Security standards
-- Approaches problem solving collectively with senior staff and internal and external clients to achieve a mutually beneficial result
-- Participates in the development of the Microsoft Cloud team’s strategic plans, training materials and tools
-- Effectively trains and mentors staff on new and emerging Azure specific technologies
-- Demonstrate ability to author professional documentation that serve as customer deliverables and internal standard operating procedures and delivery playbooks
-- Performs other duties and responsibilities as required
-**Required Experience and Education:**
-- Bachelor’s Degree and 5 years of experience building or managing cloud environments in medium to large companies
-- Professional certification in Azure, such as Azure Solutions Architect Expert or similar preferred
-- Strong understanding of cloud computing technologies, business drivers, and emerging computing trends
-- Proficient in Azure services, including but not limited to Entra ID, Azure Virtual Networks / Machines, Azure App Services, Azure Kubernetes Service, Azure Key Vault, Azure Private Link/Private Endpoint
-- Subject matter expert (SME)–level proficiency in Azure AI Foundry, including model catalog and model deployment, AI agents, prompt flow, Retrieval-Augmented Generation (RAG) architectures, evaluations, and Responsible AI / content safety controls
-- Subject matter expert (SME)–level proficiency in Azure API Management (APIM), including gateway architecture, policy authoring, API security and versioning, developer portal, self-hosted gateways, and use of APIM as a GenAI / AI gateway (token limiting, semantic caching, and load balancing) in front of Azure AI Foundry and Azure OpenAI endpoints
-- Experience with Azure OpenAI and generative AI solution patterns, including prompt engineering, embeddings, and vector / semantic search (e.g., Azure AI Search)
-- Hands-on experience with containerization and orchestration using Azure Kubernetes Service (AKS), Azure Container Registry (ACR), and Azure Container Apps
-- Working knowledge of Azure observability and operations tooling, including Azure Monitor, Log Analytics, Application Insights, and Microsoft Defender for Cloud
-- Familiarity with the Azure Well-Architected Framework and Cloud Adoption Framework (CAF) landing zones
-- Proficiency with scripting and automation using PowerShell, Azure CLI, and at least one general-purpose language such as Python for AI and API integration
-- Experience designing Zero Trust architectures and implementing security controls for AI and API workloads
-- Experience with FinOps and Azure cost management practices, including governance of AI token consumption and API usage costs
-- Relevant certifications such as Azure AI Engineer Associate (AI-102), Azure Security Engineer Associate (AZ-500), or Azure Network Engineer Associate (AZ-700) are a plus
-- Must pass either the Cloud Security Alliance Certificate of Cloud Security Knowledge (CCSK) or the (ISC)2 Certified Cloud Security Professional within 6 months of joining the team.
-- Experience with cloud security, networking, and disaster recovery best practices
-- Strong knowledge of infrastructure as code (IaC) tools such as Azure Resource Manager (ARM) templates or Terraform
-- Experience with network security best practices and configurations
-- Strong troubleshooting skills and attention to detail
-- Strong written and verbal communication skills
-- Ability to solve technical, managerial, or operational problems and evaluate options based on relevant information, resources, well-rounded experience, and knowledge
-- Demonstrated ability to communicate clearly and concisely, both orally and in writing, and lead presentations, training courses, and effective working sessions
-- Embraces emerging technologies, including AI tools, to work smarter, solve problems, and drive better business outcomes.
-**Travel Requirements:**
-- Up to 10 % travel
-**Physical Requirements:**
-- Sedentary work
-- Substantial movement of the wrists, hands, and/or fingers for a minimum of 8 hours a day
-- Required to have close visual acuity to view computer terminal and/or extensive reading for a minimum of 8 hours a day
-**We use Greenhouse Software as our applicant tracking system and Zoom Scheduler for HR screen request scheduling. At times, your email may block our communication with you. Please be sure to check your SPAM folder so that you don't miss updates on your application.**
-**Why GuidePoint?**GuidePoint Security is a rapidly growing, profitable, privately-held value added reseller that focuses exclusively on Information Security. Since its inception in 2011, GuidePoint has grown to over 1,300 employees, established strategic partnerships with leading security vendors, and serves as a trusted advisor to more than 6,200 customers.
-Firmly-defined core values drive all aspects of the business, which have been paramount to the company’s success and establishment of an enjoyable workplace atmosphere. At GuidePoint, your colleagues are knowledgeable, skilled, and experienced and will seek to collaborate and provide mentorship and guidance at every opportunity.
-This is a unique and rare opportunity to grow your career along with one of the fastest growing companies in the nation.  
-**Some added perks….**
-- Remote workforce primarily (U.S. based only, some travel may be required for certain positions, working on-site may be required for Federal positions)
-- Group Medical Insurance options: Zero Deductible PPO Plan (GuidePoint pays 90% of the premium for employees and 70% for family plans (spouse/children/family) or High Deductible Health Plan with HSA (GuidePoint pays 100% of the employees premiums and 75% for family plans (spouse/children/family). If you choose the High Deductible / HSA plan, GPS will contribute in 4 equal quarterly installments: ($850 per EE annually / $1750 per family annually (includes spouse/children/family options)
-- Group Dental Insurance: GuidePoint pays 100% of the premium for employees and 75% of family plans
-- 12 corporate holidays and a Flexible Time Off (FTO) program
-- Healthy mobile phone and home internet allowance
-- Eligibility for retirement plan after 2 months at open enrollment
-- Pet Benefit Option</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>phantom</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Staff Product Security Engineer (Security)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/phantom/7a9e300a-14bd-489f-aad8-7d1360941e80/application</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>[Phantom](https://phantom.com) is on a mission to connect the world to the freedom of open markets. Tens of millions of people all over the world use Phantom to access global markets that never close, including perpetuals, prediction markets, tokenized assets, stablecoins and memes. Phantom users are able to discover the markets that matter and the cultural moments that shape them, building conviction through real-time data and the verified performance of top traders. With self-custody and access to open networks at its core, Phantom lets them control their financial moves in the same app they use to safely store or spend money worldwide.
-Phantom has reached #1 in Google Play's finance category and consistently ranks in the top 50 apps across all categories. Phantom partners with many of the most trusted and influential names in finance like Hyperliquid, Stripe, Kalshi and Visa, to make the most popular and innovative financial products accessible to everyone.
-We are around 180 people, fully remote, backed by a $150M Series C investment from a16z, Sequoia Capital and Paradigm.
-Security is core to Phantom’s product and the trust millions of users place in us. We’re building an AI-native security team that aggressively uses AI to expand the speed, depth, and reach of our work—from code review and threat modeling to vulnerability discovery and security automation. We’re looking for strong security engineers with high agency who can identify the risks that matter, build practical solutions, and take ownership from initial discovery through verified remediation.
-This is a hands-on, high-impact role spanning architecture, source code, testing, and production systems across Phantom’s mobile, web, and backend products. You’ll work directly with engineering and product teams, lead complex security initiatives, and build capabilities that scale across the company. At the Staff level, you’ll set technical direction and raise the bar for how Phantom designs, builds, and ships secure products.
-This role is fully remote and open to candidates based in the US, UK and Canada.
-## Responsibilities
-- **Product Security Ownership:** Partner with engineering teams to identify and address security risks across Phantom’s mobile applications, web products, APIs, and backend services.
-- **Architecture and Threat Modeling:** Lead security reviews for new products and major architectural changes, with particular attention to authorization boundaries, sensitive data, transaction integrity, key material, and third-party integrations.
-- **Secure Product Development:** Embed practical security controls into the software development lifecycle, from design and implementation through testing, release, and production operation.
-- **Code Review and Security Testing:** Perform AI assisted security code reviews and targeted testing of high-risk features. Build repeatable approaches that help find vulnerabilities before they reach production.
-- **Security Tooling:** Develop and improve tooling that gives engineers fast, actionable security feedback without creating unnecessary friction. Use automation and AI-assisted workflows where they materially improve coverage or speed.
-- **Software Supply Chain Security:** Harden CI/CD, build, and release systems against supply chain threats, including dependency risk, secrets exposure, build provenance, artifact integrity, and compromised developer or automation workflows.
-- **Vulnerability Management:** Triage findings from internal testing, researchers, bug bounty submissions, and third-party assessments. Work with owners to determine real-world impact and drive issues through verified remediation.
-- **Incident Response:** Support the investigation of product security incidents and suspicious activity. Turn lessons from incidents into durable improvements to product architecture, detection, and engineering standards.
-- **Technical Leadership:** Establish product security patterns and expectations across engineering. At the Staff level, lead ambiguous, cross-functional initiatives and influence architecture beyond any single product team.
-## Qualifications
-- 5+ years of experience in product security, application security, security engineering, or software engineering, including experience operating at a senior or staff level.
-- Strong understanding of web, mobile, API, and distributed-system security, including authentication, authorization, session management, cryptography, and common vulnerability classes.
-- Hands-on experience building or applying AI-assisted security tooling to test applications and APIs, combining automated analysis with source-code review and manual validation.
-- Demonstrated ability to review production code in one or more languages such as TypeScript, JavaScript, Rust, Python and Go.
-- Experience securing software supply chains and CI/CD systems, including dependencies, build infrastructure, secrets, artifacts, signing, and release integrity.
-- Experience threat modeling complex products and translating security risks into concrete engineering requirements.
-- Strong judgment when evaluating exploitability, business impact, and appropriate remediation.
-- Track record of partnering effectively with engineering and product teams while maintaining a high security bar.
-- Clear written and verbal communication, including the ability to explain technical risk to both engineers and non-security stakeholders.
-## Nice To Haves
-- Experience securing consumer financial products, wallets, payments, or other systems where client integrity and transaction safety are critical.
-- Familiarity with blockchain systems, smart-contract interactions, transaction simulation, signing workflows, or self-custodial wallet architecture.
-- Experience securing browser extensions or native mobile applications.
-- Experience building and integrating application-security tooling, static or dynamic analysis, security test infrastructure, or policy-as-code controls.
-- Familiarity with AWS, Kubernetes, CI/CD systems, and cloud-native service architectures.
-- Experience working with bug bounty programs or coordinating external security assessments.
-## Why Work with Us
-Phantom is built by a team of experienced product and engineering leaders working to make crypto-powered finance safer and easier to use. Our products serve a large and rapidly growing global community, which makes security engineering here both technically challenging and directly consequential.
-This role offers the opportunity to:
-- Protect products used by tens of millions of people.
-- Work on security problems spanning mobile, browser, backend, cloud, and blockchain systems.
-- Shape product architecture early rather than reviewing security only at the end.
-- Build durable security capabilities while the company and product surface continue to grow.
-- Work with engineers who care deeply about product quality, user experience, and security.
-## Benefits
-- Competitive salary and equity
-- Eligibility to participate in the company’s performance bonus program
-- Comprehensive medical, dental, and vision insurance with 100% coverage
-- Stipend for your ideal remote setup
-- Flexible hours and a supportive remote environment
-- Unlimited vacation—take time when you need it
-- 401(k) retirement plan
-- Monthly wellness benefit
-- Weekly meal benefit
-- Global off-sites
-The target base salary for this role will range between $200,000 to $250,000 with the addition of equity and benefits. This is determined by a few factors including your skillset, prior relevant experience, quality of interviews and market factors (such as location) at the point in time of offer.
-**We strongly encourage candidates of all backgrounds to apply.** We believe that our work is stronger with a variety of perspectives, and we’re eager to further diversify our company. If you have a background that you feel would make an impact at Phantom, please consider applying. We’re committed to building an inclusive, supportive place for you to do the best work of your career.
-*By submitting your resume and application materials, you acknowledge and agree that Phantom Technologies, Inc. ("Phantom") collects and processes your personal information (including application materials, interview records, and related data) to evaluate your candidacy. Phantom may use AI-powered tools and third-party service providers for transcription, note-taking, scheduling, and other administrative tasks. Phantom does not sell your information and your materials will be handled securely and in accordance with applicable data protection laws.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>artemis</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Security Research Engineer</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/artemis/84ee5dcf-4d1d-48c7-ada0-14322a5be35d/application</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>Artemis is building the future of AI-driven defense - helping companies detect and defend themselves effectively in an era where AI is fighting AI on the cyber battlefield.
-We’re backed by First Round Capital, Brightmind, and a group of the cybersecurity industry’s most prominent Operators.
-Our founders, [Shachar](https://dxfpdd04.na2.hs-sales-engage.com/Ctc/UF+23284/dxFPDD04/Jl22-6qcW7lCdLW6lZ3pTW33zjJn1Qc_-GN2Qz8lvlmwCkW3cmwKD33n4mRW2CvjVP7R4ysxW7zCyhm5wC_R8W7r_nnl5B3dv9W8Tt1yw1dKmtHVfCgPh8LbF65W45tGmb8QTgj9W6bw-BR6kTK8fW4HTHrC9dWJnvW2-RcHX5Z2-L9N7CRPhHsDXVcVCdgFb2f_W2sN60HzC1yJN4vW5m0wb875ZRX8W2m0MY49lh9HmW7dSpgn3Kfxb7W7YWzTd7w9VCSW23SPbT3JtJsrW21-Lg32gcGY_W7VNhG28Xxs2sW7KZbqT1jggp-W2S7VL36xYZQ0f3PNQSz04) (ex-Palo Alto Networks, AWS, Demisto) and [Dan](https://dxfpdd04.na2.hs-sales-engage.com/Ctc/UF+23284/dxFPDD04/Jl22-6qcW7lCdLW6lZ3mlW6LgjcZ4tbNhmW6c409M6FyDHZW5n0vGf83-dFdW8KXHGS3SDzYSVnb4CP2g8mPcW2kqmdK2H-DBnW7xYg4f1BvxnKW1Xcg353zBv8GW96SZzR4t2Q0cW4mJBmD2fG2vhW43tdz48rm09dW4dvlbL7g9FTLW9dR9jl8vjrtHW96F3PJ5z70sKW3rpT8Q2Xk1zGW6BZvLX7pws10W8nnFxM1Rw_cBW2dkB873Xc48XW7tkchY6z4lc5W1dqTLk2XB6rKW3dXQcJ6kVRGjVM1cyM8spdtZW4zs_PH1KcLKQW2nhL9G3QY3Ltf8Cgm_q04) (ex-Abnormal Security, Twitter) have previously built, launched, and scaled cybersecurity products loved and trusted by tens of thousands of customers, and have the customer, technology, and security know-hows to deliver this vision.
-Our exceptionally strong team includes software engineers, AI researchers, security engineers, and product designers hailing from Google, Abnormal AI, Wiz, Meta, AWS, CERN, SentinelOne, and more.
-We are growing our team and looking for passionate builders to join us and support our expanding customer base.
-**Job Overview**
-We're looking for a Security Research Engineer to drive detection research, threat hunting, and AI-powered security automation. You'll work at the intersection of security expertise and cutting-edge AI—researching data sources, building detections, investigating real incidents, and engaging directly with customers to deliver security value. This is a hands-on, high-impact role where your work directly shapes what threats we catch and how we catch them.
-**Responsibilities**
-- **Develop AI-powered detection tooling** - Build automation that leverages AI to accelerate detection creation, tuning, and validation at scale.
-- **Conduct security research -**  Analyze cloud, identity, and SaaS data sources (AWS CloudTrail, Okta, Entra ID, and more) to extract security value and identify detection opportunities.
-- **Perform attack simulations -**  Execute authorized attack simulations to validate detection coverage and identify gaps in our defenses.
-- **Hunt for threats** - Proactively search for malicious activity across customer environments using our platform and tooling.
-- **Investigate potential cases** - Analyze security incidents to demonstrate product value, refine detection logic, and deliver actionable findings.
-- **Engage with customers** - Join customer calls to present analysis results, walk through findings, and gather feedback that shapes the product.
-- **Tune customer detections** - Reduce false positives and improve detection accuracy based on real-world data and customer context.
-- **Build investigation automation** - Create AI-powered tools that scale investigation and threat hunting workflows across our platform.
-**Qualifications**
-- **7+ years of hands-on cybersecurity experience**
-- Hands-on experience in incident response including cloud environments (AWS, Azure, GCP) and identity providers (Okta, Entra ID)
-- Strong knowledge of threat actor tactics, techniques, &amp; procedures and demonstrated understanding uncovering threat actor activity in various environments
-- Strong experience with log-based analysis and demonstrated ability to identify malicious activity across a variety of log sources
-- Ability to translate security research into actionable detections or threat hunt investigations
-- Strong communication skills—comfortable explaining technical findings to engineers and customers
-- Experience with detection engineering at scale
-- **Bonus:**
-  - Background working in a SOC environment or Managed Detection and Response.
-  - Familiarity with a wide range of security tools (SIEM, EDR, SOAR)
-  - Customer-facing technical experience
-  - Experience with AI tools and models
-**Why Work at Artemis?**
-- **Make a real world impact**. Help empower cybersecurity teams around the world to keep people safe from the most advanced cyber threats.
-- **Be challenged to be better than ever before.** Our team includes some of the smartest and most driven people in the world. We guarantee you will learn more in 1 year here than 10 years in another place.
-- **Push the boundaries of technology**. Work with and build the most advanced AI capabilities in the world of cybersecurity, including cutting-edge analytics and agentic platforms. Your ideas will shape the product and the industry.
-- **Innovative culture.** We obsess about customers, move fast with high quality, and value open communication, mentorship and learning. You will have autonomy to drive projects and support to grow.If you are passionate about building resilient distributed systems and want to apply your expertise to defend against AI‑powered adversaries, we’d love to hear from you.
-  If you are passionate about cybersecurity and want to apply your expertise to build AI-powered defenses against advanced threats, we'd love to hear from you.
-**Compensation**  
-We offer a competitive compensation of 160,000$- 190,000$ per year, and a top-of-market equity component. A variety of factors are considered when determining the compensation, including a candidate’s professional experience. Final offer amounts may vary from the amounts listed.
-**Equal Opportunity**At Artemis, we believe the best ideas come from diverse teams. We’re committed to creating an inclusive environment where people of all backgrounds, experiences, and perspectives can do their best work. We welcome everyone, regardless of race, gender, age, religion, identity, or anything else that makes you, you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Bouygues Telecom</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ingénieur DevSecOps Kubernetes / ELK F/H</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Nantes, Loire Region, France</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>EUR 55,000 - 65,000</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/yXRyW27/jobs/ingenieur-devsecops-kubernetes-elk-f-h_nantes</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Rejoignez Bouygues Telecom, une entreprise engagée dans la modernisation de ses infrastructures techniques. En tant qu'Ingénieur DevSecOps Kubernetes / ELK, vous serez responsable de l'administration, de la sécurité et de l'industrialisation de nos plateformes de production. Vous travaillerez dans un environnement technique exigeant, axé sur l'automatisation, la sécurité et la fiabilité.
-- Administrer et sécuriser les plateformes Kubernetes et Elasticsearch de production, en garantissant leur performance et leur disponibilité.
-- Automatiser les déploiements et l'exploitation grâce à Helm, GitLab CI et ArgoCD, dans une logique GitOps.
-- Concevoir et faire évoluer les stacks ELK mises à disposition des métiers pour l'observabilité de la DATA Bouygues Telecom.
-Description du profil :  
-**À propos de vous :**
-Qui êtes-vous ? Comment ferez-vous la différence dans ce poste ?
-- Vous justifiez d'une **expertise Kubernetes** en environnement de production, ainsi que d'une **expérience confirmée sur Elasticsearch**, dans des contextes à forte volumétrie et à forts enjeux de disponibilité.
-- Vous maîtrisez **Helm**, **GitLab CI** et **ArgoCD**, ainsi que les pratiques **GitOps** et l'**Infrastructure as Code**.
-- Vous êtes à l'aise avec les enjeux de **sécurité** (RBAC, TLS, gestion des secrets) et de **supervision** (Prometheus, Grafana).
-- Votre rigueur vous permet de garantir la fiabilité et la traçabilité des interventions sur des environnements critiques.
-- Votre esprit analytique vous aide à diagnostiquer rapidement des incidents complexes touchant réseau, stockage ou indexation.
-- Votre sens du service vous pousse à accompagner les équipes utilisatrices et à contribuer à leur montée en compétence.
-- Votre culture **DevOps** et **SRE** vous amène naturellement à rechercher l'amélioration continue de nos plateformes.
-**Les prochaines étapes pour nous rejoindre :**
-Notre processus de recrutement est conçu pour être transparent et rapide :
-- Sélection de votre candidature par notre équipe de recrutement.
-- Deux à trois entretiens maximum avec nos équipes pour mieux vous connaître et vous présenter l'entreprise.
-- Prise de contact par Chloé, votre interlocutrice dédiée.
-&lt;
-Nous proposons :  
-Chez Bouygues Telecom, vous apprécierez :
-- Les modalités de votre future rémunération : selon votre expérience, une rémunération fixe annuelle sur 13,1 mois + participation/intéressement + Plan Epargne Entreprise (PEE) et PERCO abondés + avantages CSE + subvention restaurant.
-- Un pacte de télétravail proposant jusqu’à 2 jours par semaine pour les contrats en CDI.
-- Rejoindre une entreprise engagée socialement qui propose à ses collaboratrices et collaborateurs de passer 4 demi-journées par an au sein d'associations pour réduire la fracture numérique, par exemple.
-- La culture centrée sur l'humain et qui prône l'innovation au titre de la satisfaction de ses clients et de ses collaborateurs.
-Et après ? Au sein de Bouygues Telecom nous facilitons la mobilité interne. Vous pourrez ensuite évoluer vers d’autres postes au sein du groupe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>gdmsi</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Principal Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Hastings, England, gb</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/GDMSI/744000150735654-principal-product-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>Join our security engineering team and help deliver future combat-air capability as part of the GCAP programme. You will work on complex, safety-critical mission-computing systems, embedding security into the product architecture and engineering lifecycle. Working alongside specialists across systems, software, hardware, safety and certification, you will help ensure that security risks are identified, understood and addressed through robust engineering solutions. This is an opportunity to influence the design of advanced airborne technology while contributing to a strategically important UK defence programme. This is a product and systems security engineering role , focused on embedding security into complex, safety-critical airborne mission systems. In this role you will: Own and lead the product-security architecture for complex airborne mission systems Define the security strategy, requirements and secure-by-design approach across the programme lifecycle Lead threat modelling, vulnerability analysis, security risk assessment and accreditation activities Provide technical authority and informed security advice across systems, software and hardware engineering Make and communicate proportionate security decisions, balancing operational capability, technical risk and programme constraints Lead engagement with customers, programme partners and relevant assurance stakeholders Review security evidence and ensure that proposed designs and mitigations support the required assurance outcomes Coach and provide technical guidance to security and multidisciplinary engineering teams Drive the adoption of consistent product-security methods, tools and good practice across the programme Essential experience Significant experience developing or leading product-security or systems-security architecture for complex engineered products Knowledge of Secure by Design principles and relevant product and systems security standards, ideally gained within defence, aerospace or another safety-critical engineering environment Strong experience defining security requirements and secure-by-design approaches at system or product level Experience leading threat modelling, security risk assessment and vulnerability-analysis activities Experience providing technical leadership and making security architecture decisions across multidisciplinary engineering teams Knowledge of cryptographic principles and their application within secure products or systems Experience engaging with customers, partners and assurance stakeholders on complex security matters Ability to translate security threats and risks into practical engineering requirements and design decisions Degree-level qualification in engineering, computer science, cyber security or a related discipline, or equivalent relevant experience Desirable experience Experience in aerospace, defence, avionics, mission systems, embedded systems or other safety-critical products Experience acting as a product-security technical authority, security architect or engineering lead Knowledge of accreditation, certification and security-assurance approaches within regulated environments Experience coaching or technically leading security engineers Familiarity with digital engineering, model-based systems engineering or requirements-management tools Experience working with or familiarity with AI/ML models is preferred This role has a salary of between £59,200 and £80,000 plus our flexible benefits package. We are open to this role being spent with time working from home and in the office (hybrid - typically 3 days working in office) on a weekly basis or fully in our offices. We pride ourselves in being a great place to work with a shared sense of purpose, offering impressive benefits: A compressed nine-day fortnight and compressed hours - which means every other Friday off. A personalized career development plan, alongside regular progress reviews - supporting and valuing your progression within the Company. A flexible working environment where your contributions are recognized and rewarded with flexible benefits We believe in maintaining a diverse workplace - inclusive of beliefs, cultural background, job experiences, thoughts and ideas. If who we are and what we do resonates with you, we welcome you to join our inclusive team! Our success is fuelled by our colleagues and the wide variety of backgrounds, perspectives, and skills they bring to the Company. We are a Disability Confident Employer, as such we offer an interview to disabled people who meet the minimum criteria for the job. Please email if you would like your application to be considered under the DC Scheme. All successful/appointed applicants must be able to obtain a level of UK Security clearance that is appropriate for the role and undertake suitable Right to work checks. Every application matters to us. We want you to know that each application we receive is reviewed by a real person—not just an algorithm. Our screening questions are also carefully considered to help us understand your experience and fit for the role. We appreciate the time you take to apply. General Dynamics Mission Systems engineers a diverse portfolio of high technology solutions, products and services that enable customers to successfully execute missions across all domains of operation. With a global team of more than 13,000 top professionals, we partner with the best in industry to expand the bounds of innovation in the defence and scientific arenas. In the UK, we are leading the way in avionics and communication systems. Given the nature of our work and who we are, we value trust, honesty, alignment and transparency. General Dynamics in St Leonards-on-Sea currently provide avionic mission computing systems for a wide range of military fast jets, helicopters, and UAV’s. Recent success has resulted in General Dynamics developing the next generation of Advanced High Performance, Safety Critical Mission Computer Systems to meet the needs of latest platforms in development by several aircraft manufacturers. These Mission Computing Systems provide the functionality that integrates aircraft systems, sensor systems and stores management systems with the information and control systems required by the aircrew to meet the demanding operational needs of these aircraft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>gdmsi</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Senior Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Hastings, England, gb</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/GDMSI/744000150730654-senior-product-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>Join our security engineering team and help deliver future combat-air capability as part of the GCAP programme. You will work on complex, safety-critical mission-computing systems, embedding security into the product architecture and engineering lifecycle. Working alongside specialists across systems, software, hardware, safety and certification, you will help ensure that security risks are identified, understood and addressed through robust engineering solutions. This is an opportunity to influence the design of advanced airborne technology while contributing to a strategically important UK defence programme. This is a product and systems security engineering role , focused on embedding security into complex, safety-critical airborne mission systems. In this role you will: Develop and maintain security requirements for complex airborne electronic and mission-computing systems Undertake threat modelling, vulnerability analysis and security risk assessments throughout the engineering lifecycle Support the development of security architectures and secure-by-design solutions Produce the security evidence, documentation and assurance arguments needed to support accreditation Work closely with systems, software, hardware, safety and certification engineers to ensure security is embedded within the overall product design Review proposed designs and identify security weaknesses, risks and proportionate mitigations Engage with customers, partners and internal engineering teams on product-security requirements and technical decisions Contribute to the development of technologies that will support future combat-air capability Essential experience Experience in product security, systems security, cyber-security engineering or security assurance within a complex engineering environment Knowledge of Secure by Design principles and relevant product and systems security standards, with experience embedding security throughout an engineering lifecycle Experience undertaking security risk assessments, threat modelling, vulnerability analysis or security requirements development Ability to interpret technical designs and communicate security risks and mitigations to multidisciplinary engineering teams Experience producing clear technical documentation and security assurance evidence Degree-level qualification in engineering, computer science, cyber security or a related discipline, or equivalent relevant experience Desirable experience Experience within aerospace, defence, safety-critical systems, embedded systems or another highly regulated sector Knowledge of mission systems, avionics, embedded computing, real-time systems or secure communications Experience supporting product accreditation, certification or formal security-assurance activities Experience using requirements-management, risk-management or security-analysis tools within a structured engineering environment Experience working within a model-based or requirements-led systems-engineering environment Experience working with or familiarity with AI/ML models is preferred This role has a salary of between £45,600 - £60,000 plus our flexible benefits package. We are open to this role being spent with time working from home and in the office (hybrid - typically 3 days working in office) on a weekly basis or fully in our offices. We pride ourselves in being a great place to work with a shared sense of purpose, offering impressive benefits: A compressed nine-day fortnight and compressed hours - which means every other Friday off. A personalized career development plan, alongside regular progress reviews - supporting and valuing your progression within the Company. A flexible working environment where your contributions are recognized and rewarded with flexible benefits We believe in maintaining a diverse workplace - inclusive of beliefs, cultural background, job experiences, thoughts and ideas. If who we are and what we do resonates with you, we welcome you to join our inclusive team! Our success is fuelled by our colleagues and the wide variety of backgrounds, perspectives, and skills they bring to the Company. We are a Disability Confident Employer, as such we offer an interview to disabled people who meet the minimum criteria for the job. Please email if you would like your application to be considered under the DC Scheme. All successful/appointed applicants must be able to obtain a level of UK Security clearance that is appropriate for the role and undertake suitable Right to work checks. Every application matters to us. We want you to know that each application we receive is reviewed by a real person—not just an algorithm. Our screening questions are also carefully considered to help us understand your experience and fit for the role. We appreciate the time you take to apply. General Dynamics Mission Systems engineers a diverse portfolio of high technology solutions, products and services that enable customers to successfully execute missions across all domains of operation. With a global team of more than 13,000 top professionals, we partner with the best in industry to expand the bounds of innovation in the defence and scientific arenas. In the UK, we are leading the way in avionics and communication systems. Given the nature of our work and who we are, we value trust, honesty, alignment and transparency. General Dynamics in St Leonards-on-Sea currently provide avionic mission computing systems for a wide range of military fast jets, helicopters, and UAV’s. Recent success has resulted in General Dynamics developing the next generation of Advanced High Performance, Safety Critical Mission Computer Systems to meet the needs of latest platforms in development by several aircraft manufacturers. These Mission Computing Systems provide the functionality that integrates aircraft systems, sensor systems and stores management systems with the information and control systems required by the aircrew to meet the demanding operational needs of these aircraft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>netcompany1</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer (Freelancer)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Strasbourg, Grand Est, fr</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Netcompany1/744000150716869-devsecops-engineer-freelancer-?oga=true</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>Are you ready to discover the role of a DevSecOps Engineer in Netcompany? As a DevSecOps Engineer, you will: Effectively implement a DevSecOps strategy and processes. Develop tools and infrastructures in support of the system/component development. Analyse code and communicate reviews to development teams. Implement and maintain security controls throughout the software development lifecycle (SDLC), integrating security testing and vulnerability scanning into CI/CD pipelines. Monitor and analyse system and application performance, security events, and vulnerabilities, identifying potential risks and coordinating remediation actions with development teams. Automate deployment, configuration, and infrastructure management processes using Infrastructure as Code (IaC) and containerization technologies, ensuring secure, scalable, and reliable environments. What would make you a fit for the role: Bachelor's degree and minimum 5 years of relevant hands-on experience in DevSecOps or other similar fields. Thorough understanding of the SLDC. Knowledge of automation tools used to create continuous integration and continuous delivery Working knowledge of known DevSecOps tools like Git and GitHub, OpenShift, Helm, Kafka, Istio Capability for writing and presenting documents. Experience in network, server, and application-status monitoring. Excellent communication skills in English. Experience in working in an international/multicultural environment. If you are looking forward to be part of a diverse environment, and have the opportunity to work alongside well-experienced professionals, on challenging, large-scale projects that directly impact millions of citizens around the globe, then this is the place to be! #LI-CF Please upload your CV in English via the Apply button. All applications will be treated as strictly confidential. We ensure equal opportunities, treatment, and consideration to all candidates. Discrimination based on sex, racial or ethnic origin, religion or belief, disability, age, sexual orientation or marital status, physical or mental disability, or any other factor protected by applicable laws and regulations is prohibited. As part of the Netcompany culture, we respect human rights and focus on creating a positive workplace, where all employees are valued, and where diversity and inclusion are a vital part of our everyday working experience. In the following link you may find our CV Submission privacy notice: Are you ready to shape the future technological landscape in Europe? We are dedicated to responsible digitalisation, building innovative, inclusive solutions that drive meaningful impact. With over 8,900 professionals across Europe, we help EU institutions, public and private organisations thrive in a rapidly evolving digital world. Are you ready to shape the future through technology? Your journey starts here. Take a look at some of our impactful projects here:</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>garnerhealth</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/garnerhealth/jobs/6201112004</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>## **What you’ll be part of**
-Garner is on a mission to transform the U.S. healthcare system — and we’re the only proven player doing exactly that. We partner with employers to redesign how healthcare works: applying 550+ proprietary clinical metrics across 80+ specialties to a dataset of 320M+ patients to identify the best-performing doctors, then using compelling incentives to steer members to the care that helps them get healthier, faster.
-The result is a rare “win win” — better care and lower costs for both members and employers. In just five years, our work has helped over 2.5 million people access higher-quality care and saved $1B in healthcare costs. We recently raised our Series E and have doubled five years running. If you've ever wanted your work to solve a problem that touches every person in this country, this is the opportunity to do exactly that. You'd be joining a team fundamentally reimagining healthcare in the U.S. — and using AI to scale that impact further and faster than anyone else can.
-### **About the role:**
-We are looking for a Senior Security Engineer to join our Security Engineering team. As a Senior Security Engineer, you will play a key part in the protection of our most important asset: patient data. The Security Engineering team at Garner is responsible for securing cloud infrastructure, creating secure code guardrails, and maintaining trust with clients. This is a role that will have diverse projects that address multiple areas of security.
-### Where you will work:
-This role is open to remote candidates across the U.S. For candidates based in New York City, the position follows a hybrid schedule with in-office work required Tuesday, Wednesday, and Thursday each week.
-### **What you will do:**
-- Provide technical leadership in securing networks, systems, applications, and databases
-- Participate in our Security Engineering on-call rotation to respond to security incidents
-- Embed security into the build pipeline through automated SAST/DAST testing and policy enforcement
-- Oversee vulnerability management and associated remediation efforts
-- Educate engineers and advocate for a Security oriented culture across the engineering organization
-### **The ideal candidate has:**
-- 3-5 years in Security Engineering, ideally with at least 2 years in a B2B organization
-- Strong proficiency in cloud security (e.g., AWS IAM, Crowdstrike, Wiz, etc.)
-- Experience with Infrastructure as Code, preferably as a platform engineer
-- Background in Application Security and securing RESTful APIs
-- Familiarity with modern IAM solutions
-### **Technologies we use:**
-- Python, Kubernetes, AWS, Terraform, Wiz, Exaforce, Crowdstrike
-This is a unique opportunity to join a fast-growing company in a transformative role, helping shape the future of healthcare.
-### **Compensation Transparency:**
-The target salary range for this position is $209,000 - $250,000. Individual compensation for this role will depend on various factors, including qualifications, skills, and applicable laws. In addition to base compensation, this role is eligible to participate in our equity incentive and competitive benefits plans, including but not limited to: flexible PTO, Medical/Dental/Vision plan options, 401(k), Teladoc Health and more.
-### **Fraud and Security Notice:**
-Please be aware of recent job scam attempts. Our recruiters use [&lt;getgarner.com&gt;](http://getgarner.com/) and &lt;garnerhealth.com&gt; email domains exclusively. If you have been contacted by someone claiming to be a Garner recruiter or a hiring manager from a different domain about a potential job, please report it to law enforcement [here](https://www.ic3.gov/Home/ComplaintChoice) and to [candidateprotection@garnerhealth.com](mailto:candidateprotection@getgarner.com).
-### **Equal Employment Opportunity:**
-Garner Health is proud to be an Equal Employment Opportunity employer and values diversity in the workplace. We do not discriminate based upon race, religion, color, national origin, sex (including pregnancy, childbirth, reproductive health decisions, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, genetic information, political views or activity, or other applicable legally protected characteristics.
-Garner Health is committed to providing accommodations for qualified individuals with disabilities in our recruiting process. If you need assistance or an accommodation due to a disability, you may contact us at [talent@garnerhealth.com](mailto:talent@getgarner.com).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>wetravel</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/wetravel/dd45b468-3973-4236-8028-b02290223ba2/application</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Hi! I’m George 👋 Head of Platform &amp; Infrastructure here at WeTravel.
-I joined WeTravel to help build a secure, reliable, and scalable IT environment as we grow. Our team’s mission is to empower every WeTravel employee with the tools and support they need to work efficiently, securely, and without friction - no matter where they are in the world.
-## **About WeTravel:**
-Think of the most incredible adventures imaginable: trekking to Machu Picchu, cycling through Tuscany, or going on a safari in Kenya. For years, the small businesses and local experts who run these trips have been stuck using messy spreadsheets, countless emails, and complicated payment methods.
-WeTravel is changing that. We build the tools that empower any entrepreneur to launch and grow their own travel business. Our platform makes it simple for organizers to create beautiful trip proposals, securely process payments, and manage their customers, so they can focus on what they do best: creating amazing experiences.
-This is one of the last great frontiers of travel to come online, and as the category leader, we are at the forefront of this change. Last year alone, our platform was trusted by 8,000 organizers to lead over a million travelers on adventures in 150+ countries. Now, we're on an exciting journey to grow from powering $1B to $10B in travel experiences per year.
-We believe that every trip, when done right, can be a force for good - and we're building the engine to make more of that possible.
-## **What's the role:**
-- Own infrastructure vulnerability management. One central register across infrastructure dependencies, containers, images, and cloud infrastructure. Risk-based SLAs, tracking to closure, exception handling, and reporting we can put in front of engineering leadership and an enterprise customer's security team — operating within the Product Security severity and risk framework. One register, one scoring model.
-- Prioritize infrastructure remediation using contextual risk signals such as KEV, EPSS, exposure, asset criticality, and relevant compensating controls, within the common severity model..
-- Automate infrastructure-security workflows: scanner integrations, finding pipelines, normalization, ticket routing, and reporting. If a number has to be assembled by hand every quarter, it's not done. Contribute to shared security finding workflows where appropriate.
-- Build our detection foundation. Security logging coverage and retention across production, cloud, and identity systems; select and run the managed detection and response partner; make sure the telemetry they need exists and survives. You cannot detect what you do not record, and closing that gap is yours.
-- Lead infrastructure and cloud security posture management with our platform team: cloud account guardrails, hardening baselines, CSPM findings triage, internet-facing surface inventory, image and container security.
-- Coordinate security incident response: incident classification runbooks, tabletop exercises, and post-incident corrective actions.. Partner with Product Security on incidents involving product-security vulnerabilities or customer-facing product risk.
-- Partner with product, platform engineering and IT on remediation. Findings arrive triaged, deduplicated, and explained. A queue engineers don't trust is worse than no queue.
-- Supply the technical evidence behind our SOC 2, PCI DSS, and customer due diligence obligations — access reviews, scan results, patch compliance. You won't own the questionnaires or the audit relationship.
-- Collaborate with Product &amp; Platform teams, and support customer-facing security discussions with accurate technical evidence and context.
-**AI Related**
-- Participate in maintaining and operationalizing the Internal AI Use Policy and application
-- Secure internal AI tooling and agentic workflows: what data agents can reach, how identities, credentials and tool permissions are scoped, what gets logged, and how inappropriate agent behavior is detected
-- Make agentic workflows auditable: who or what acted, what data and tools were accessed, and under which identity.
-## **How We Work:**
-We’re focused on the impact. We don’t subscribe to any one framework or execution ideology, and we adapt based on what’s impactful.We’re using the latest hardware and constantly on the look out for better tools &amp; ways to work
-Stack: We’re using React/ReactNative/TypeScript + Ruby on Rails, Go and Python Microservices on Kubernetes. We also use and love MongoDB, MySQL, Postgres, Snowflake and we’re working with the major LLM providers.
-## **You should apply if you have:**
-- 8+ years in security engineering, with real depth in security operations: vulnerability management, cloud security posture, detection, or incident response.
-- Experience with AWS and Kubernetes, and the ability to reason about infrastructure as code.
-- Expertise with security logging and SIEM-class tooling, and with working through a managed detection provider.
-- Hands-on experience running infrastructure vulnerability management at scale: scanning fleets, images, containers and dependencies, prioritizing by exploitability (KEV, EPSS, exposure, asset criticality), and driving remediation through the teams that own the systems
-- Experience with SOC 2 and/or PCI DSS technical controls.
-**Nice to have**
-- Experience securing payments or regulated fintech systems.
-- Detection engineering, threat modeling, or DFIR experience.
-- Exposure to EU regulatory obligations (GDPR Art. 33/34, the Cyber Resilience Act), and ISO27001
-- Experience in a product company scaling from mid-market to enterprise customers.
-## Benefits Section
-- Competitive salary
-- Generous "Time to Recharge" policy - enjoy unlimited paid time off to rest, recharge, and show up as your best self.
-- Our Work From Anywhere perk provides eligible employees with up to four weeks per calendar year to work temporarily from another approved location.
-- 2-week cross-functional onboarding program.
-- Annual team off-site (often somewhere sunny 🌊).
-- Cycle-to-work scheme (Swapfiets subscription) or commuting reimbursement.
-- Extensive paid family leave.
-- Three paid volunteer days per year - take time to give back to causes you care about, on us.
-- Cutting-edge equipment and tools to set you up for success.
-- Join an international, travel-loving team with a passion for adventure and innovation.
-**Please note:**
-- As a member of our international team, you’ll work full-time under a B2B contractor agreement, with monthly payments in USD.
-## Equal Opportunities
-WeTravel is an equal opportunity employer. We celebrate diversity and are committed to creating an inclusive environment for all employees. We welcome applicants from all backgrounds, experiences, and perspectives. If you're excited about this opportunity and believe you're a good fit, we encourage you to apply and join us in transforming the travel industry!</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>SopraSteria1</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Software Delivery Architect (DevSecOps &amp; Generative AI)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ASSAGO, MILANO, it</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/SopraSteria1/744000150710214-software-delivery-architect-devsecops-generative-ai-?oga=true</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>Se anche tu vuoi dare forma al futuro con noi lavorando su importanti progetti per prestigiosi brand e ti riconosci nel profilo che stiamo cercando, accetta la sfida e candidati! Stiamo cercando: Software Delivery Architect (DevSecOps &amp; Generative AI) (Industrialization &amp; AI-assisted Software Development) Per rafforzare la nostra Direzione Tecnica siamo alla ricerca di un Software Delivery Architect che contribuisca ad aumentare l’efficacia e la redditività dei progetti attraverso l’industrializzazione dei processi di sviluppo e l’adozione della Generative AI lungo l’intero ciclo di vita del software. La figura avrà un ruolo chiave nel disegno dei processi di delivery, nella guida tecnica dei team di sviluppo e nell’implementazione di pipeline DevSecOps e soluzioni di AI-assisted development, operando a stretto contatto con Project Manager, architetti e team di progetto. Principali responsabilità: Disegnare l’organizzazione del team e il processo di produzione Definire la struttura operativa del team e i flussi di lavoro lungo l’intero ciclo di sviluppo, integrazione, testing e rilascio. Documentare processi, procedure e linee guida, garantendo coerenza con gli standard aziendali e del cliente. Definire i processi di gestione di modifiche, versioni e rilasci in ambienti complessi. Guidare l'adozione e l'integrazione della Generative AI Promuovere l’utilizzo della Generative AI per coding, code review, documentazione e creazione automatica di test. Introdurre modelli e workflow di AI-assisted development per migliorare produttività e qualità. Formare e supportare il team nell’adozione quotidiana delle tecnologie di AI generativa nei modi e con gli strumenti messi a disposizione dalla corporate. Implementare l'automazione del processo produttivo Implementare/manutenere le pipeline DevSecOps e MLOps. Implementare/manutenere soluzioni AI ad uso del team (custom agents, use case MAIA, …) Sfruttare e integrare strumenti AI nei toolchain DevOps per CI/CD, code quality, monitoring e incident analysis. Supervisionare il ciclo di vita del software Monitorare pianificazione, avanzamento e qualità delle attività in tutte le fasi del ciclo di vita del software. Garantire la qualità del prodotto attraverso metriche, test automation e processi di continuous integration/delivery. Rilevare automaticamente KPI per valutare l’impatto della Generative AI su tempi, costi e qualità. Supportare le attività di governance, conformità e supporto operativo Verificare l’aderenza agli standard tecnici, di sicurezza e di processo. Identificare e risolvere tempestivamente criticità organizzative, tecniche o relazionali. Supportare il team di progetto nell’adozione dei processi industrializzati, della AI e in generale nella gestione del cambiamento. Promuovere la cultura del miglioramento continuo Promuovere una cultura orientata a qualità, efficienza e innovazione. Condurre revisioni periodiche di processo e retrospettive per individuare aree di ottimizzazione. Favorire il feedback continuo e la condivisione della conoscenza all’interno del team. IL TUO PROFILO: Esperienza di almeno 4 anni nel ruolo di Technical Leader o Team Leader in progetti complessi, con responsabilità di coordinamento su team di 5–10 risorse e riporto diretto al Project Manager . Comprovata esperienza nell’implementazione di pipeline CI/CD in progetti cloud-native di medio-lungo periodo ( almeno 12 mesi di durata). Solida esperienza nello sviluppo di codice enterprise e nell’utilizzo di modelli e strumenti di Generative AI per la generazione assistita di codice e documentazione tecnica. LE TUE COMPETENZE: Conoscenza approfondita dei principali modeli di ciclo di vita del software (waterfall, agile, iterative, incrementali, tdd, bdd, etc.) e relativi strumenti di gestione quali Jira / Cofluence Padronanza di tool di DevSecOps quali GitLab, GitLab CI/CD, SonarQube, Checkmarx o equivalenti e delle pratiche di gestione industrializzata del codice (branching, pipeline di CI/CD, release management, etc.) Ambienti disviluppo software che integrino component di generazione di codice attraverso modelli di AI quali GitHub Copilot, Cursor, Windsurf, Claude Code, etc. Conoscenza delle pratiche di gestione di progetto e relativi KPI economici e tecnici Conoscenza di modelli architetturali (single-page-application, micro-servizi, monoliti, etc.), design pattern e almeno un paio di linguaggi di programmazione fra Java, .NET, Javascript/Typescript e Python Il candidato deve altresì avere comprovate capacità comunicative e spirito di squadra, spiccato senso del risultato, orientamento proattivo al problem solving. Inglese B2 LA NOSTRA PROPOSTA: Ti offriamo l’opportunità di lavorare in un ambiente dinamico, su progetti nazionali ed internazionali, che ti permetta di approfondire continuamente le tue conoscenze e di sviluppare le tue competenze. Se vuoi dare una spinta alla tua carriera ed entrare a far parte di una società di servizi IT leader in Europa ed in continua crescita, inviaci il tuo curriculum! Per questa posizione è prevista una RAL compresa tra € 55.0000 e € 65.000. La sede di lavoro è ASSAGO con possibilità, compatibilmente con l'attività svolta, di aderire all’accordo di smart working secondo quanto previsto dalla nostra policy aziendale. E’ comunque richiesta la disponibilità a compiere trasferte sul territorio nazionale e internazionale. Scopri Sopra Steria! Visita il nostro sito e rimani aggiornato attraverso il blog e le pagine social Il presente annuncio è rivolto ad entrambi i sessi, ai sensi delle leggi 903/77 e 125/91 e a persone di tutte le età e tutte le nazionalità, ai sensi dei decreti legislativi 215/03 e 216/03. Tutte le regole relative ai tuoi dati raccolti in questo modo sono dettagliate nell'Informativa sulla Protezione dei Dati dei Candidati (). In conformità con la legislazione / i regolamenti vigenti in materia di tecnologia dell'informazione, documenti e libertà civili, hai diritti di accesso, rettifica, cancellazione, portabilità, limitazione, opposizione e definizione di istruzioni riguardanti la sorte dei tuoi Dati personali dopo la tua morte. Questi diritti saranno esercitati inviando un'e-mail al responsabile della protezione dei dati (DPO) all'indirizzo o per posta a questo indirizzo: Sopra Steria Group S.p.A. - Ufficio legale - Strada 4 Palazzo A7 - 20090 Assago (MI). Hai anche il diritto di presentare un reclamo Garante per la Protezione dei Dati Personali (Piazza di Monte Citorio n. 121 00186 Roma), se il titolare del trattamento non rispetta gli obblighi previsti dalla legislazione in vigore. Sopra Steria - fra i maggiori player tecnologici in Europa, con 50.000 dipendenti in circa 30 paesi - è riconosciuta per i suoi servizi di consulenza, per i suoi servizi digitali e per le sue soluzioni IT. Sopra Steria supporta i propri clienti nel loro percorso di trasformazione digitale, garantendo loro benefici concreti e sostenibili. Nel 2024, il Gruppo ha registrato un fatturato di 5,8 miliardi di euro. Con circa 1.200 persone e un fatturato 2024 di €104,8 milioni, Sopra Steria opera sul mercato italiano attraverso le sue sedi di Assago (MI), Roma, Collecchio (PR), Padova, Ariano Irpino (AV) e Pozzuoli (NA). The world is how we shape it</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>clearroute</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AI Security Engineer (Agentic Systems)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>London, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>teamtailor</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>https://clearroute.teamtailor.com/jobs/8428265-ai-security-engineer-agentic-systems</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>About Us: ClearRoute is an engineering consultancy bridging Quality Engineering, Cloud Platforms and Developer Experience. We help enterprises reliably bring high-impact digital products to market faster, cheaper, and safer, working with technology leaders facing complex business challenges. We take as much pride in our people, culture and work-life balance as we do in making better software. We’re not just making better software. We’re making the making of software better. Collaborative, entrepreneurial and dedicated to problem solving, we bring the step change our customer need to sustain innovation. Our values challenge us to do the best we can for ClearRoute, our customers and most importantly our team. This is an opportunity for you to build the organisation from the ground up, use your voice to drive change and help transform organisations and problem domains. Role This role sits apart from our traditional cloud security engineering positions: it is centred on AI and agentic systems rather than infrastructure alone. You will test and secure AI use cases across an account, not a single application or user set, building a broad, first-hand picture of how ClearRoute should approach testing, risk and governance for agentic AI. You will work across teams rather than within one delivery stream, owning the question of what "good" looks like for agentic security testing across the account, and helping ClearRoute build a repeatable, defensible approach that other engagements can adopt. The role is deliberately hands-on in its first phase: you will implement and run the testing yourself, so you understand the detail before asking anyone else to follow it. As that practice matures, the role shifts toward governance across the account, training and upskilling existing security engineers to implement and automate the strategy themselves, so agentic security testing becomes something the wider team can run, not something that depends on one person. Key Responsibilities Agentic Red Teaming &amp; Adversarial Testing: Design and run red-team exercises against AI agents and agentic workflows, probing for prompt injection (direct and indirect), tool-call and argument manipulation, agent hijacking, memory/context poisoning, and privilege or credential escalation. Build repeatable evaluation approaches for non-deterministic systems, including how to test, measure and report against outputs that vary run to run. Define and own an approach for detecting, measuring and mitigating hallucinations in agent and LLM outputs, distinct from traditional functional-testing methods. Agentic Governance &amp; Risk: Own agentic AI risk identification and governance across an account, not a single application: build the risk view, the test strategy and the tooling recommendations that other teams can reuse. Map findings and controls to recognised external frameworks (for example OWASP's agent-specific risk taxonomy, NIST's AI Risk Management Framework Govern function, and MITRE ATLAS) so ClearRoute's approach is defensible and auditable, Distinguish and design controls for internal versus external (client-facing) views of agent behaviour, including how outputs are reviewed, sanitised or gated before release. Define rollback and incident-response procedures for agentic systems, so a compromised or misbehaving agent can be safely withdrawn or reverted. Track emerging regulatory expectations relevant to AI testing (for example EU AI Act provisions on adversarial and robustness testing) and translate them into practical test and governance requirements. Cross-Team &amp; Organisational Scope: Work across delivery teams and accounts, acting as the connective view on agentic security testing rather than being embedded in a single application or team Recommend and help select tooling for agentic security testing and monitoring, and advise delivery teams on how to embed it into their workflow Represent ClearRoute's agentic security posture with internal stakeholders and, where relevant, clients Train and upskill existing security engineers over time so agentic testing and automation becomes a capability the wider team owns, not a single specialist Required Skills &amp; Experience Must Have: Hands-on experience red-teaming or adversarially testing LLM or agentic AI systems, including prompt injection, jailbreaking and tool-misuse scenarios Practical understanding of how to test non-deterministic systems and how to detect, quantify and mitigate hallucination Working knowledge of agentic-AI-specific risk frameworks and taxonomies, such as OWASP's agent risk categories and MITRE ATLAS Experience with the OWASP Top 10 for LLM Applications, including prompt injection and system-prompt-leakage risk categories Experience designing or applying an AI governance framework (for example NIST's AI Risk Management Framework) to translate identified risks into organisational controls Ability to operate across accounts and teams, building test strategy and tooling recommendations that generalise beyond a single application Threat modelling and security review experience Strong communication skills, able to explain agentic AI risk clearly to technical and non-technical stakeholders, including on what should and shouldn't be released to clients Comfortable being hands-on first — implementing and running agentic security tests directly — then mentoring and training other security engineers to take the practice on themselves Nice to Have: Familiarity with agent-hijacking or agent-specific evaluation tooling (for example open-source agent-security benchmarks) Awareness of emerging AI regulation relevant to security testing, such as the EU AI Act's adversarial and robustness-testing requirements Experience with multi-agent or agent-mesh systems and the trust/authentication issues between agents Cloud security background (Azure preferred) and Terraform and CI/CD Experience in a regulated sector (for example financial services) Working at ClearRoute We have grown from six founders to 200+ people across five countries in three years, and what sets us apart isn't the pace, it's how we grow. Real flexibility, in practice. We trust you to perform at your best and still have a life outside of work, with genuine hybrid working, a home office budget, an open feedback culture where your voice shapes decisions, and time off when life needs it (birthday included). When ClearRoute wins, you win. We offer profit share so success is shared, meaningful recognition for great work, and benefits that look after you and your family, including private healthcare, competitive salary benchmarking, and a confidential employee assistance program covering counselling, mental health support, and financial wellbeing. A community you'll genuinely want to be part of. Interest based communities like running and book clubs, Women in Tech group, monthly socials, and cross regional events bring people together across the company. An inclusive, collaborative culture where you don't need to conform to succeed, where people support one another and feel comfortable being themselves. Where meaningful work meets real growth. You will tackle complex, real world problems at the forefront of platform engineering, AI, security, and scalable systems. Your growth is supported by learning budgets, Udemy access, a clear career framework, internal mobility, and thought leadership opportunities that take your impact beyond ClearRoute. At ClearRoute, we believe diverse perspectives lead to better outcomes, and inclusion creates the conditions for everyone to thrive. We are proud to have built a family friendly working environment and have many employees who have caring responsibilities alongside work. We welcome applications from people who require flexibility and will be happy to discuss needs on an individual basis. We are committed to fostering a culture where all team members feel respected, supported, and empowered to do their best work. We celebrate individuality and our differences and understand that some differences may mean that you require changes made to the interview process. We are happy to cater to your needs to make the interview accessible, if this is something you require please let us know by emailing us at</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>CENTREON</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Paris, Île-de-France, France</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>65000 - 75000 EUR</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>recruitee</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>https://centreon.recruitee.com/o/senior-security-engineer/c/new</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>Centreon cherche à renforcer l'équipe sécurité en intégrant un senior security engineer. Au cœur du produit Centreon, la team security a un impact fort. Elle joue un rôle central au sein de la R&amp;D composée d’environ 50 tech. Elle collabore notamment étroitement avec les équipes infra cloud et software engineers. Pluridisciplinaire, vous intégrez une équipe composée de 2 personnes au profils riches et variés. Vous êtes expert sur la partie Cloud et notamment AWS . Vous accompagnerez l’ensemble de la tech (dev, product, SRE) pour apporter les best practices, construire la plateforme, automatiser les process, déployer des composants, opérer des solutions etc Vos missions seront diverses et toujours guidées par l’envie de partager les succès mais avec un ownership fort. Missions : Intégrer les pratiques de sécurité dans le cycle complet de notre infrastructure et de notre plateforme cloud en interne ainsi que dans nos produits SaaS. Contribuer au développement d'une architecture de sécurité robuste qui s'aligne sur le modèle zéro trust. Renforcer la sécurité du cloud (AWS, on-prem), participer au hardening de l’infra, à la protection contre les menaces avancées et à la conception de SaaS sécurisés. Participer activement à une équipe d'ingénieurs diversifiée composée d'ingénieurs en sécurité, d'ingénieurs logiciels, de devops et de SRE. Construire et opérer la stratégie de sécurisation des usages et technologies d'IA au sein de l'entreprise; Garantir la maintenabilité et l'évolutivité des différents composants, en diffusant les best practices de sécurité à l'état de l'art ; Collaborer avec les software engineers, l'équipe infra et le produit pour construire des produits et des services secure by design ; Construire une stratégie de réponse aux incidents efficace et solide à l’aide de systèmes d'alerting et de détection modernes ; corriger et mitiger les problèmes de sécurité en collaboration avec l'équipe Infra.. Faire évoluer les capacités de l'équipe sécurité en s'appuyant sur l'IA agentique pour automatiser le traitement des tâches répétitives (alertes, triage, reporting) Être un membre actif de la guilde de sécurité Bug Bounty management Stack technique : AWS – Terraform – Zero trust : Okta, Teleport - SSLDC - SIEM Profil et compétences Vous êtes autonome et faites preuve d’ownership, êtes capable de leader des projet transverses Vous avez une expérience significative en sécurité des infra cloud : système, réseau et notamment AWS. Vous avez une bonne compréhension de la sécurité dans les systèmes distribués à l'échelle.. Vous avez une bonne connaissance de la gestion de l'IAM sur les fournisseurs de cloud (AWS, Auth0). Vous maîtrisez un ou plusieurs langages de notre stack tech. Vous avez un intérêt pour l'écosystème OpenSource et pour le monitoring. Vous aimez innover et faire évoluer les architectures des plateformes vers une plus grande scalabilité. Vous voulez être un membre actif d'une équipe d'ingénieurs diversifiée composée d'ingénieurs en sécurité, d'ingénieurs logiciels, de devops et de SRE. Les plus qui feront la différence : Vous avez des compétences ou expériences et intérêt pour la sécurité corporate IT (SSO/IAM, EDR, MDM...) Vous êtes sensible à la culture de l’open-source Vous êtes sensible à l’expérience utilisateur (performance, ergonomie, utilisabilité, etc.) Vous aimez défier vos collègues au babyfoot ! Ce que nous offrons Société en forte croissance (+20% en 2025) dans un environnement international Venez apprécier nos locaux à Paris avec terrasse à Olympiade - Métro ligne 14 ou à Toulouse quartier Compans Caffarelli (immeubles accessibles PMR) RTT et Carte Tickets restaurant Events mensuels et semestriels Petits dej mensuels Un programme d'Onboarding Pleins d'autres avantages --&gt; Nous avons à cœur de mettre en avant la diversité au sein de notre entreprise. Tous les candidats qualifiés seront pris en considération pour un emploi sans distinction de race, de couleur, de religion, de sexe, d'orientation sexuelle, d'identité de genre, de nationalité ou de toute autre caractéristique protégée par la loi dans le pays où le candidat postule. Ce poste est ouvert aux personnes en situation de handicap.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M110"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"New,Applied,Interview,Rejected,Offer,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12891,33 +10427,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs_latest.xlsx
+++ b/jobs_latest.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Latest Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -520,27 +520,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Naval Group [FR]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Senior Security Engineer (Data Platform)</t>
+          <t>CDI – Ingénieur Infrastructure DevSecOps Data Platform – H/F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Brest, Brittany, France</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -566,15 +566,162 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>https://www.welcometothejungle.com/en/companies/jj6huE/jobs/cdi-ingenieur-infrastructure-devsecops-data-platform-h-f_brest</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Rejoignez Naval Group, un leader mondial de l'industrie navale. En tant qu'Ingénieur Infrastructure DevSecOps Data Platform, vous serez responsable de la mise en œuvre et de la maintenance de nouvelles solutions informatiques, ainsi que de l'évolution des infrastructures existantes. Vous travaillerez dans un environnement moderne et dynamique, en contribuant à la transformation digitale de l'entreprise.
+- Participer à la transformation et à la modernisation du Système d'Information, en tant qu'ingénieur devSecOps.
+- Maintenir en conditions opérationnelles et en conditions de sécurité l’infrastructure de la data platform, en faisant évoluer le socle d’infrastructure.
+- Concevoir, développer et maintenir des projets logiciels d'infrastructure, notamment des collections et des rôles Ansible, des modules Terraform.
+Diplômé(e) d’une école d’Ingénieur ou équivalent Bac +5, vous justifiez d’une expérience d'au moins 5 ans dans l’ingénierie de la data au sein d’un secteur industriel (Naval/Défense, aéronautique, automobile…) en tant qu’Ingénieur Infrastructure DevSecOps / Automation où vous avez pu développer et mettre en pratique les connaissances et compétences suivantes :
+Expérience devsecops au sein d’une équipe de développement dans un environnement cloud moderne,  
+Vous avez des connaissances spécialisées des systèmes d’exploitation Linux (RHEL), et des outils de scripting et de développement d'API (bash, python, ansible, powershell, Golang),
+Vous maîtriser la mise en œuvre du durcissement et de la sécurisation des systèmes (ex: OpenSCAP) ainsi que les outils de conteneurisations/orchestration de conteneurs (Docker, Kubernetes) et des infrastructures virtuelles (VMWare, KVM)
+Connaissance approfondie de Git, GitLab, GitLab CI/CD et des workflows Git tels que le GitHub Flow et data : gestion d’une data platform, mise en place des data services.  
+Connaissance approfondie de l'Infrastructure as Code (IaC), en se concentrant notamment sur Ansible, Terraform, Packer.  
+Connaissance de la suite logicielle Cloudera   
+Vous avez d'excellentes compétences analytiques et aptitude à résoudre des problèmes complexes, travail en équipe,   
+NOTRE PROCESSUS DE RECRUTEMENT
+Après réception de votre CV, si votre profil retient notre attention, l'un de nos recruteurs vous contactera pour un entretien téléphonique. À l'issue de ce premier échange, vous pourrez être contacté·e pour passer un entretien (physique ou visioconférence) avec le manager du service concerné et/ou notre HR Business Partner. Enfin, dès que nous aurons fait notre choix final, vous en serez informé·e dans les plus brefs délais. Dans le cadre de ce recrutement, l’accès au site donne lieu à une enquête administrative de sécurité.
+Le poste pouvant nécessiter d'accéder à des informations relevant du secret de la Défense Nationale, la personne retenue fera l'objet d'une procédure d'habilitation, conformément aux dispositions des articles R.2311-1 et suivants du Code de la Défense et de l'IGI 1300 SGDSN/PSE du 09 août 2021.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Crédit Mutuel Arkéa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Product Owner DevSecOps H/F</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bordeaux, Nouvelle-Aquitaine, France</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>welcometothejungle</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/zDakzV3/jobs/product-owner-devsecops-h-f_bordeaux</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Rejoignez notre équipe en tant que Product Owner DevSecOps. Vous serez responsable de la gestion fonctionnelle globale des produits liés à l'amélioration continue de la sécurité tout au long du cycle de développement logiciel. Vous travaillerez en étroite collaboration avec le Product Manager pour élaborer la trajectoire des produits et identifier les impacts des sujets à venir. Une expérience de 3 ans dans un rôle agile est requise, ainsi qu'une connaissance de la méthodologie Agile et des pratiques de développement applicatif.
+- Assurer le pilotage fonctionnel global des produits liés à l'amélioration continue de la sécurité sur l'ensemble du SDLC.
+- Traduire les besoins métiers en fonctionnalités produits, établir et respecter la priorisation des sujets, produire une roadmap lisible des produits.
+- Collaborer avec le Product Manager pour élaborer la trajectoire des produits, identifier les impacts des sujets à venir et estimer la capacité à faire nécessaire à leur réalisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Deutsche Bank</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer (Data Platform)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>welcometothejungle</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>https://www.welcometothejungle.com/en/companies/37tGzn/jobs/senior-security-engineer_berlin_lzb2wpri</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Join DWS's data infrastructure team as a Senior Security Engineer. In this role, you will focus on understanding the threat landscape, architecting integrations with security tools, collaborating with vendors, security monitoring, threat remediation, and cloud infrastructure automation. You will design and integrate secure cloud and on-premises infrastructure, deploy and manage scalable cloud infrastructure solutions, and configure and manage internal security solutions. The ideal candidate will have extensive experience in securing critical enterprise data flows, hands-on experience in cloud security, and strong collaboration and communication skills.
 - Understand the threat landscape and architect integrations with security tools to enhance security monitoring and threat remediation.
@@ -590,68 +737,68 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Atos</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Principal Security Architect - H/F</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Hérouville-Saint-Clair, Normandy, France</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>EUR 80,000 - 95,000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bKGYqPm/jobs/principal-security-architect-h-f_sophia-antipolis_ATOS_dWMgOeZ</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Rejoignez une entreprise innovante à la pointe de l'IA et des usines souveraines. En tant que Principal Security Architect, vous serez responsable de la définition de l'architecture de sécurité, de la préparation aux certifications, de la souveraineté cloud et IA, de l'avant-vente et de la sécurité de la chaîne d'approvisionnement logicielle. Vous aurez un impact direct sur le succès commercial et technologique de la Business Unit &lt;E.AI&gt;.
 - Définir l'architecture de sécurité à travers la plateforme, établir les exigences de contrôle et les modèles de référence adoptés par défaut par les équipes produit.
@@ -677,123 +824,123 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Vercel</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Security Engineer, Cloud</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Anywhere in the World</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>weworkremotely</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/vercel-security-engineer-cloud</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Headquarters: Remote - United States About Vercel: Vercel is the agentic infrastructure company, freeing people and agents to ship what's next. For more than a decade we've helped builders move from idea to production with speed, security, and exceptional developer experience. Now we're scaling our products for both agents and people to ship and run software, built in the open and trusted by OpenAI, PayPal, Ramp, Supreme, and millions of developers worldwide. About the role: We're looking for a Security Engineer to join our Cloud Security Engineering team. In this role, you'll help strengthen the security of our platform by building and improving the controls that protect our infrastructure. You'll play a key role in making security a core part of how we build, deploy, and scale our systems, while helping the company grow securely and confidently. You'll report to the Security Operations Manager, and this is a hybrid or fully remote within the United States. If you're based within commuting distance of our SF or NY offices, the role includes in-office anchor days on Monday, Tuesday, and Friday. What you will do: Design and implement scalable security controls across our cloud-native platform. Harden infrastructure components using infrastructure-as-code, policy enforcement, and service isolation. Build secure by default infrastructure and code CI/CD pipelines. Collaborate with platform and infrastructure teams to integrate security best practices into architecture and workflows. Stay ahead of cloud security trends and adopt cutting-edge technologies to enhance platform resilience. Conduct threat modeling, risk analysis, and mitigation planning for critical systems. Drive improvements in monitoring, detection, and incident response at the platform level. Build, deploy and maintain relevant tooling. About you: 8+ years of experience in infrastructure or platform security roles. Deep understanding of secure cloud infrastructure (AWS/GCP), identity and access management, and system hardening. Proficient with tools like Terraform, CDK, Kubernetes, and CI/CD security. Skilled at balancing engineering realities with principled security practices. Proven track record of shipping secure, resilient systems at scale. Bonus if you: Have built or scaled security automation pipelines. Contributed to open-source security projects or tools. Hold certifications such as GCP Security Engineer, AWS certifications, CISSP, or OSCP. Hold a bachelors or masters degree in Cybersecurity or similar disciplines. Benefits &amp; Compensation: Competitive compensation package, including equity. Inclusive Healthcare Package. Learn and Grow - we provide mentorship and send you to events that help you build your network and skills. Flexible Time Off. We will provide you the gear you need to do your role, and a WFH budget for you to outfit your space as needed. The San Francisco, CA base pay range for this role is $208,000.00 - $312,000.00. This salary range is an estimate. Actual salary will be based on job related skills, experience and location. Pay ranges outside San Francisco may be adjusted based on employee location. The total compensation package also includes benefits and equity-based compensation. Your recruiter can share more about the specific pay range for your location during the hiring process. Disclosures: Privacy: Please review our Job Applicant Privacy Policy for more information on how we handle your data. Equal Opportunity: Vercel is committed to fostering and empowering an inclusive community within our organization. We do not discriminate on the basis of race, religion, color, gender expression or identity, sexual orientation, national origin, citizenship, age, marital status, veteran status, disability status, or any other characteristic protected by law. Vercel encourages everyone to apply for our available positions, even if they don't necessarily check every box on the job description. To apply: &lt;https://weworkremotely.com/remote-jobs/vercel-security-engineer-cloud&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Headquarters: Remote - United States About Vercel: Vercel is the agentic infrastructure company, freeing people and agents to ship what's next. For more than a decade we've helped builders move from idea to production with speed, security, and exceptional developer experience. Now we're scaling our products for both agents and people to ship and run software, built in the open and trusted by OpenAI, PayPal, Ramp, Supreme, and millions of developers worldwide. About the role: We're looking for a Security Engineer to join our Cloud Security Engineering team. In this role, you'll help strengthen the security of our platform by building and improving the controls that protect our infrastructure. You'll play a key role in making security a core part of how we build, deploy, and scale our systems, while helping the company grow securely and confidently. You'll report to the Security Operations Manager, and this is a hybrid or fully remote within the United States. If you're based within commuting distance of our SF or NY offices, the role includes in-office anchor days on Monday, Tuesday, and Friday. What you will do: Design and implement scalable security controls across our cloud-native platform. Harden infrastructure components using infrastructure-as-code, policy enforcement, and service isolation. Build secure by default infrastructure and code CI/CD pipelines. Collaborate with platform and infrastructure teams to integrate security best practices into architecture and workflows. Stay ahead of cloud security trends and adopt cutting-edge technologies to enhance platform resilience. Conduct threat modeling, risk analysis, and mitigation planning for critical systems. Drive improvements in monitoring, detection, and incident response at the platform level. Build, deploy and maintain relevant tooling. About you: 8+ years of experience in infrastructure or platform security roles. Deep understanding of secure cloud infrastructure (AWS/GCP), identity and access management, and system hardening. Proficient with tools like Terraform, CDK, Kubernetes, and CI/CD security. Skilled at balancing engineering realities with principled security practices. Proven track record of shipping secure, resilient systems at scale. Bonus if you: Have built or scaled security automation pipelines. Contributed to open-source security projects or tools. Hold certifications such as GCP Security Engineer, AWS certifications, CISSP, or OSCP. Hold a bachelors or masters degree in Cybersecurity or similar disciplines. Benefits &amp; Compensation: Competitive compensation package, including equity. Inclusive Healthcare Package. Learn and Grow - we provide mentorship and send you to events that help you build your network and skills. Flexible Time Off. We will provide you the gear you need to do your role, and a WFH budget for you to outfit your space as needed. The San Francisco, CA base pay range for this role is $208,000.00 - $312,000.00. This salary range is an estimate. Actual salary will be based on job related skills, experience and location. Pay ranges outside San Francisco may be adjusted based on employee location. The total compensation package also includes benefits and equity-based compensation. Your recruiter can share more about the specific pay range for your location during the hiring process. Disclosures: Privacy: Please review our Job Applicant Privacy Policy for more information on how we handle your data. Equal Opportunity: Vercel is committed to fostering and empowering an inclusive community within our organization. We do not discriminate on the basis of race, religion, color, gender expression or identity, sexual orientation, national origin, citizenship, age, marital status, veteran status, disability status, or any other characteristic protected by law. Vercel encourages everyone to apply for our available positions, even if they don't necessarily check every box on the job description. To apply:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>xAI</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Infrastructure Security Engineer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/JBHAzj/jobs/infrastructure-security-engineer_ie_ceqs7o3s</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Join our security team as an Infrastructure Security Engineer. In this role, you will design, implement, and maintain secure cloud and hybrid infrastructure, ensuring the integrity of our cloud-native applications. You will work across multi-cloud and hybrid environments, focusing on securing critical infrastructure. Your responsibilities will include designing secure cloud architectures, developing Infrastructure as Code templates, managing cloud security tools, and collaborating with development teams to integrate security best practices.
 - Design, implement, and maintain secure cloud and hybrid infrastructure, ensuring the integrity of cloud-native applications.
@@ -826,64 +973,64 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>PASQAL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>IT Security Engineer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/4uAgeC/jobs/it-security-engineer_gb_3ojbzy3l</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Join PASQAL, a leading company in the Neutral Atom Quantum Computing space, as a Senior IT Security Engineer. In this role, you will design, operate, and continuously improve security across various environments, including workplace, identity, networks, SaaS, infrastructure, and cloud. You will work closely with the Information Security Manager to turn security requirements and risks into pragmatic solutions that support business needs. This is a full-time, direct hire position with a hybrid work model and competitive benefits.
 - Concevoir, exploiter et améliorer continuellement la sécurité des environnements de travail, d'identité, de réseau, de SaaS, d'infrastructure et de cloud.
@@ -906,68 +1053,68 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Trainline</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Senior Product Security Engineer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>GBP 90,000 - 100,000</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/3TgGLb/jobs/senior-product-security-engineer_london_n3i4chnd</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Join Trainline, Europe's leading independent rail platform, as a Senior Product Security Engineer. In this role, you will define and own the product security roadmap, establish and manage the application security vulnerability management process, and work with teams across the business to carry out threat modeling. You will also assess the security posture of our applications and APIs, strengthen the security of our mobile apps, and implement and automate security tools. Additionally, you will build secure coding and deployment knowledge across the organization and ensure our product security practices align with relevant frameworks and standards.
 - Definir y ser responsable de la hoja de ruta de seguridad del producto, alineando prioridades con los objetivos comerciales.
@@ -976,127 +1123,127 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>jobs.msd.com</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Senior Cyber Security Engineer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Prague, Central Bohemian, Czechia</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>phenom</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://jobs.msd.com/job/R419147</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>We are seeking a Senior Cyber Security Engineer to lead the deployment and enhancement of secrets management and privileged access systems for a global biopharmaceutical leader. Drive innovation in security, collaborate with international teams, and apply your expertise in identity management and cloud security. Ideal for experienced professionals in IT security.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>turquoise-health</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Senior Application Security Engineer</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>$172K – $200K • Offers Equity</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/turquoise-health/21ccc42d-aa61-47d0-8764-aee7cf6ff7ba/application</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>*This is a fully remote role in the United States.*
 Turquoise is hiring a Senior Application Security Engineer to drive security for the applications and data our customers rely on. This role owns application-layer security across Turquoise's platform and is the software counterpart to our infrastructure security. You'll build and tune our code scanning program, driving vulnerabilities from discovery to remediation. Day to day, you'll work closely with engineering teams on the design, architecture, and services our product teams build.
@@ -1147,68 +1294,68 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>namespace</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>$200K – $250K • Offers Equity</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/namespace/41599db0-2a55-4d97-bc92-62636eb3c5bd/application</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t># **Join our mission**
 **We're proud to work with many incredible companies, accelerating their ability to build their products.**
@@ -1244,60 +1391,60 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>wizinc</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Sr. Manager, Security Engineering</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Remote - United Kingdom</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Yes / Mentioned</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>https://www.wiz.io/careers/job/4671799006/:title?gh_jid=4671799006</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Come join the organization that is redefining security for the AI era. As one of the [fastest-growing startups ever,](https://www.wiz.io/blog/100m-arr-in-18-months-wiz-becomes-the-fastest-growing-software-company-ever) we enable teams to secure cloud and AI applications by connecting code, cloud, and runtime into a single shared context. Trusted by security teams all over the world, we have a proven [track record of success](https://www.g2.com/products/wiz-wiz/reviews) and a culture that values world-class talent. Not to mention, we're now [powered by Google](https://cloud.google.com/blog/products/identity-security/google-completes-acquisition-of-wiz), meaning we offer our customers an AI-powered platform that harnesses Google’s Threat Intelligence and Security Operations to better detect, prevent, and respond to threats across all environments, allowing for further innovation.
 Our Wizards from all over the globe work together to protect the infrastructure of our customers, including over 65% of the Fortune 100, who trust us to scan and secure over 230 billion files daily. We’re honored to be a leading player in a massive and growing market, and we continue to look for exceptional Wizards who are eager to make a significant impact on our team. At Wiz, you’ll have the freedom to think creatively, dream big, and use your full range of skills to contribute to our momentous growth. Come join our team and help us create secure cloud environments that allow even the best companies to move faster, all while having some fun!
@@ -1329,123 +1476,123 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>millgroupinc</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer – DevSecOps</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>US-Remote</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>icims</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>https://careers-millgroupinc.icims.com/jobs/3134/cybersecurity-engineer-%e2%80%93-devsecops/job?in_iframe=1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Millennium is proud to be part of the Markon enterprise, a network of specialized organizations united in support of critical national security missions. This partnership strengthens our ability to deliver results by expanding our technical depth, operational reach, and access to a broader bench of proven experts, ensuring our customers continue to receive best-in-class cybersecurity support. Since 2004, Millennium has operated at the forefront of cybersecurity. Our elite team of over 300 professionals brings an unmatched record of performance across Red Team Operations, Defensive Cyber Operations, Software Engineering, and Technical Engineering. As home to the...</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>InPost</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>AI Security Engineer (m/f/n)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Warszawa, Województwo mazowieckie, pl</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/InPost/744000153204239-ai-security-engineer-m-f-n-?oga=true</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>Your responsibilities: Work on the security assessment and secure design review of AI, LLM and agentic systems across InPost's technology estate. Identify, reproduce and reason about real vulnerabilities in AI-powered and agentic systems, and work with engineering teams to fix them at the root cause. Define and build engineered security controls for AI/ML and LLM-related risks. Build security automation and developer-facing tooling that helps product and engineering teams build securely by default. Review new AI solutions and system architectures for security risk, and represent security in AI governance forums and the AI solutions catalogue. Apply hands-on cloud and container security practices across AWS, Azure and GCP to secure the infrastructure AI systems run on. Act as a go-to expert on AI-specific attack classes, keeping InPost's defences ahead of an evolving threat landscape. Translate complex technical and security findings into clear, practical guidance for stakeholders across the business.
 Must have: 5+ years of experience in application security or product security. 5+ years of coding experience in one or more general-purpose languages , including shipping and operating production services. 5+ years of experience with security assessments, secure design reviews or threat modelling. Solid understanding of generative AI, LLMs and AI agents , and how they're built and deployed in production. Deep knowledge of AI-specific attack classes and how they apply to real systems. Experience securing agentic, code-execution or LLM-integrated systems. A track record of finding and reasoning about real vulnerabilities in real systems. Experience building engineered security controls, not just flagging issues. Hands-on cloud and container security experience on AWS, Azure or GCP. Strong presentation skills, with the ability to translate complex technical and security topics into clear business terms for a wide range of stakeholders. Good English skills , enabling confident communication in an international environment. Nice to have: Background building security automation or developer-facing security tooling. Working knowledge of the OWASP Top 10 for LLM Applications and OWASP Top 10 for Agentic Applications. Working knowledge of MITRE ATLAS.
@@ -1454,64 +1601,64 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/8812b7f5-0d7f-4a7a-bc69-2730071a26d8/apply</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Netherlands.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1562,64 +1709,64 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/564da8a5-89ec-4536-9e5f-c86a99793f3d/apply</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Ireland.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1670,64 +1817,64 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/b52ca408-713f-4d50-b4ee-3fd8b866bd80/apply</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Switzerland.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1778,64 +1925,64 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/4ba6089c-3318-4188-b146-82ba27cff1fd/apply</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in France.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1886,64 +2033,64 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/c9b6d010-a351-4e24-a51e-3f50effcf13f/apply</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Spain.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1994,64 +2141,64 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/0cb3482e-758e-4af2-8aba-1dff0aae89d3/apply</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in United Kingdom.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2102,64 +2249,64 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/8770cdc2-d817-4516-89ca-c82aa0889904/apply</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Germany.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2210,187 +2357,187 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Enjoy Gaming LLC</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Application Security Engineer</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Remote job</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>recruitee</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>https://enjoygaming.recruitee.com/o/application-security-engineer/c/new</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>Enjoy Gaming is a software provider focused on creating high-quality digital entertainment experiences, including Slots and Live Games. Our team brings together experienced professionals in game development, product, and design, driven by a passion for innovation and quality. At Enjoy Gaming , we value ownership , excellence , and drive . These principles shape the way we work, collaborate, and build products. Join us and be part of our innovative journey in the gaming world! We’re looking for a sharp Application Security Engineer to join our team and act as the technical guardian for our games and platforms. If you have an attacker's mindset but know how to build and defend alongside engineering teams, this role is for you. In this position, you won’t just be sending reports to the teams or management. You’ll be diving deep into web and desktop applications, hunting down game-level vulnerabilities, and collaborating closely with our Architects, Studio, Slots, and Platform Developers to engineer more resilient systems.
 What we're looking for: 5+ years of Application Security Engineer experience Background in red teaming, penetration testing, application security, and software development Able to independently find vulnerabilities in web and desktop applications, triage them, and, where needed, fix them Solid grounding in data structures, algorithms, and systems architecture designs Previous security testing experience with Kafka/Redis/BullMQ/PubSub as message/streaming tools Codes independently, can navigate unfamiliar web application frameworks Experience using AI tools to aid with vulnerability hunting Comfortable talking to developers and turning findings into practical, actionable advice Nice to have: CRTO, OSCP, or OSWE certifications or similar Knowledge of Cloud Platforms (GCP/AWS) Understanding of CI/CD pipelines Hands-on experience with Trivy, Nessus, Acunetix, or Wiz Experience in iGaming or another regulated industry What You Will Do: Own and maintain our application security pipelines: SCA (Github/Trivy), DAST (Nessus, Acunetix, Wiz), and SAST Triage findings from these tools and drive them to remediation Perform penetration tests on new platform features, new internal applications, and new slots and live games Run basic red team activities, including leaked credential reviews and external attack surface audits Review complex auth flows with various third parties for cryptographic and security issues Review/Triage application code for security issues ( 85% NestJS / 15% .NET ) Own security risk in existing code and applications Act as the application-level security expert during incident response and be ready to deliver hotfixes yourself when needed Prepare our quarterly SAST/DAST vulnerability scan reports for stakeholders/regulators and take part in audit meetings Own the Secure Coding and Application Security areas of our ISMS Meet regularly with development teams, learn about upcoming features early, and advise on secure design What We Offer: Competitive Salary in EUR : with annual performance reviews to recognize your growth Flexible Remote Work : balance productivity and comfort Comprehensive Benefits : including medical insurance, psychologist support, and Polish, Slovak-speaking clubs Generous Paid Time Off : 20 working days of paid vacation, plus 10 additional paid days off, 10 paid sick days, and all national holidays in your country Professional Development Support : reimbursement for courses, trainings, and certifications Well-being Perks: support for language classes, sports, massages, or life coaching Please note that feedback on your application will be provided within two weeks if a positive decision is made regarding your candidacy. I give my consent following the Law on the Protection of Personal Data dated June 1, 2010, No. 2297, effective from January 1, 2011, for the processing of information classified as personal data.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>cyberone-security</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Senior Azure Security Engineer</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>teamtailor</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>https://cyberone-security.teamtailor.com/jobs/8491321-senior-azure-security-engineer</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>“I am hugely excited about my future and the future of CyberOne. I have enjoyed my time here immensely and have learnt a huge amount in a short space of time, year-for-year I've learnt more here than I have at Microsoft and PwC.” - CyberOne Consultant About CyberOne CyberOne is a pure-play Microsoft security partner dedicated to helping enterprises realise the full value of the Microsoft Security portfolio—across Defender XDR, Sentinel, Entra, Purview, Intune, Copilot for Security and more. We combine deep technical expertise with outcome-driven services that accelerate secure cloud adoption, modernise threat protection and simplify compliance. Job Title: Senior Azure Security Engineer Location: Hybrid ; 1 day per month reporting in London office Employment Type: Full-time Purpose of Role We are seeking an experienced Senior Azure Security Engineer to join the Cyber Security team. The role is responsible for designing, implementing, securing and supporting Microsoft security technologies across cloud, identity, endpoint, infrastructure and security monitoring platforms. The engineer will work closely with Security Operations, Infrastructure, Cloud Engineering, Architecture, Identity and Application teams to strengthen security controls, improve monitoring capabilities, automate security processes and support the organisation's cyber resilience. The role combines Azure security engineering, Microsoft Sentinel, Microsoft Defender, cloud security architecture, automation and operational support across a hybrid enterprise environment. Main Duties and Responsibilities Act as a Subject Matter Expert for Microsoft Azure security, Microsoft Sentinel, Microsoft Defender XDR and associated Microsoft security technologies. Design, implement and support enterprise security controls across Azure, Microsoft Entra ID and the Microsoft security ecosystem. Engineer and maintain Microsoft Sentinel capabilities, including data connectors, analytics rules, KQL queries, workbooks, watchlists, automation rules and playbooks. Design, implement and optimise Microsoft Defender capabilities, including Defender for Endpoint, Defender for Identity, Defender for Cloud, Defender for Office 365 and Defender XDR. Develop security monitoring use cases, threat detections and hunting queries aligned to business risks, threat intelligence and MITRE ATT&amp;CK. Design secure cloud and hybrid architecture patterns and provide practical technical guidance to projects and engineering teams. Engineer telemetry and logging solutions using Azure Monitor, Log Analytics, Azure Monitor Agent, Data Collection Rules, custom tables and API-based integrations. Design and implement security automation using Logic Apps, Azure Functions, REST APIs, PowerShell and Python. Perform technical security assessments and review cloud solutions against enterprise security standards, control requirements and secure-by-design principles. Implement and maintain cloud security baselines, hardening standards, policy controls and configuration-management practices. Support vulnerability and configuration-risk remediation across Azure and Microsoft security platforms. Support cyber incident investigations and provide security expertise during critical incidents and major technology changes. Produce and maintain High-Level Designs, Low-Level Designs, engineering standards, operating procedures, support documentation and implementation records. Lead platform enhancements, proof-of-concepts, migrations, upgrades, troubleshooting and service-improvement activities. Build platform health monitoring, operational dashboards and KPI/KRI reporting for the Proactive Security function. Person Specification Essential Experience Proven Azure security engineering experience within a large, complex enterprise environment. Strong hands-on experience implementing and supporting Azure security services across IaaS, PaaS and hybrid environments. Practical experience with Microsoft Entra ID security, including Conditional Access, Privileged Identity Management, Identity Protection and hybrid identity controls. Strong experience with Microsoft Sentinel and Microsoft Defender XDR, including Endpoint, Identity, Cloud and Office 365 security capabilities. Experience designing and implementing cloud security architecture, platform hardening, technical security controls and security baselines. Experience onboarding and validating infrastructure, cloud, application, identity and security telemetry. Experience developing KQL queries, analytics rules, workbooks, automation and threat-hunting content. Experience conducting technical risk assessments, security-control validation and vulnerability-remediation support. Experience with REST APIs, PowerShell, Python, automation, enterprise troubleshooting and operational support. Experience working with Security Operations, Incident Response, Cloud, Infrastructure, Identity and Architecture teams. Technical Knowledge and Skills Azure security and governance: Azure Policy, Defender for Cloud, Azure Monitor, Log Analytics, Azure Arc, Key Vault, managed identities, role-based access control, landing-zone security and cloud security posture management. Cloud and network security: Virtual Networks, Network Security Groups, Azure Firewall, Private Endpoints, Private Link, secure connectivity, segmentation and hybrid-cloud security patterns. Identity security: Microsoft Entra ID, Conditional Access, Privileged Identity Management, Identity Protection, authentication, access control, federation and identity governance. Microsoft security platform: Microsoft Sentinel, Defender XDR, Defender for Endpoint, Defender for Identity, Defender for Office 365 and Defender for Cloud. Security monitoring: KQL, analytics rules, hunting queries, workbooks, data connectors, Data Collection Rules, watchlists, automation rules, playbooks and ingestion optimisation. Automation and engineering: Logic Apps, Azure Functions, REST APIs, PowerShell, Python, Azure DevOps, Git, CI/CD and Infrastructure-as-Code concepts. Secure engineering: Security architecture, technical risk assessment, platform hardening, vulnerability remediation, control validation, secure development practices and operational readiness. Desirable Experience Experience securing Azure landing zones and enterprise-scale cloud platforms. Experience with Security Orchestration, Automation and Response solutions and automated control validation. Experience with Privileged Access Management and Zero Trust security principles. Experience supporting security platforms in a regulated financial-services environment. Exposure to multi-cloud or hybrid-cloud environments, including AWS or GCP. Qualifications Degree or equivalent professional experience in Information Technology, Cyber Security, Engineering or a related discipline. Microsoft AZ-500 and SC-200 certifications are strongly preferred. Microsoft SC-100, SC-300 or AZ-104 certifications are desirable. Additional cloud-security certifications such as CISSP, CCSP or relevant GIAC qualifications are advantageous.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Security Engineer (Threat Response), Sophos Security Team (IDR)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Yes / Mentioned</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/6627c9a0-ec93-442d-89de-f9d7202f13a5/apply</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Security Engineer (Threat Response), Sophos Security Team (IDR) based in Canada.**
 This is a senior security engineering role combining hands-on incident response with detection engineering, automation, and threat research. You will investigate complex cyber threats across endpoints, identity, cloud, networks, and security products while helping strengthen internal detection and response capabilities. The role goes beyond traditional incident response, with a strong focus on building scalable automations, reusable workflows, and agentic security tooling. You will use modern AI-assisted development tools while applying rigorous safety, observability, and validation practices. Collaboration spans security, engineering, product, and business teams in a globally coordinated environment. The position is remote-first and offers the opportunity to shape how advanced security operations evolve through engineering and responsible AI adoption.
@@ -2441,60 +2588,60 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>purestorage</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/purestorage/jobs/8191920</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Everpure (NYSE: P) has evolved from storage pioneer to data platform, closing fiscal 2026 with $3.7 billion in revenue, its first billion-dollar quarter, and accelerating growth into FY27. Our strategic agenda spans the companies defining the next era of technology - hyperscalers, AI labs, the AI hardware supply chain, data platform providers, and the broader AI ecosystem.
 This type of work—work that changes the world—is what the tech industry was founded on. So, if you're ready to seize the endless opportunities and leave your mark, come join us.
@@ -2528,60 +2675,60 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>align</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>DevSecOps Engineer</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Panama - Remote</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/align/jobs/8859924002</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>#### **About the Role**
 The DevSecOps Engineer works to execute security engineering activities across A-LIGN's cloud infrastructure, CI/CD pipelines, and production applications. In this role, you will be responsible for implementing and continuously validating security controls, delivering infrastructure and application improvements, and supporting continuous audit readiness. As the DevSecOps Engineer, you will provide exceptional technical and security strategies to help support the continued growth of our fast-paced company. A-LIGN will depend on you as the DevSecOps Engineer to support management, translate security and compliance requirements into practical engineering solutions, and automate security and audit evidence workflows.
@@ -2647,64 +2794,64 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Ki</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Senior Application Security Engineer (AI)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/lNcmq3/jobs/senior-application-security-engineer-ai_london_hatyplwl</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Join Ki, the fastest growing algorithmic insurance carrier in the Lloyd's of London market. As a Senior Application Security Engineer, you will empower our engineering and product teams to safely adopt AI and embed robust technical security controls directly into our services and workflows. Your work will span our entire development lifecycle, protecting everything from agentic LLM integrations to the everyday tools we use.
 - Provide practical implementation advice and guidance on securing AI-powered applications, aligning with frameworks like OWASP ASVS and the OWASP Top 10 for LLM Applications.
@@ -2713,64 +2860,64 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Naval Group [FR]</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>CDI - Developpeur DevSecOps Programme Sous-Marin - H/F</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ollioules, Provence-Alpes-Cote d'Azur, France</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/jj6huE/jobs/cdi-developpeur-devsecops-programme-sous-marin-h-f_ollioules</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>Rejoignez Naval Group, un leader mondial de l'industrie navale de défense. En tant que Développeur DevSecOps, vous serez responsable de la conception, du développement, de l'intégration et du déploiement d'applications, en intégrant les exigences de sécurité dès les premières étapes du cycle de développement. Vous travaillerez en étroite collaboration avec les équipes de développement, d'intégration, d'exploitation et de cybersécurité.
 - Concevoir, développer et maintenir des composants logiciels et des scripts d’automatisation.
@@ -2807,116 +2954,6 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CACI</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SAP Security Engineer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>remote (any state)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>eightfold</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://caci.eightfold.ai/careers/job/1443153781490</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CACI</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DevSecOps Lead Engineer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>remote (any state)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>eightfold</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://caci.eightfold.ai/careers/job/1443153785475</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -2925,17 +2962,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>brightvisiontechnologies</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ML Security Engineer</t>
+          <t>DevSecOps Lead Engineer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>remote (any state)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2950,23 +2987,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>jazzhr</t>
+          <t>eightfold</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/5Izo29N73O</t>
+          <t>https://caci.eightfold.ai/careers/job/1443153785475</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2974,11 +3007,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2988,27 +3017,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jobs.msd.com</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Senior Specialist - SAP Authorizations and Security Architect</t>
+          <t>SAP Security Engineer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Boxmeer, North Brabant, Netherlands</t>
+          <t>remote (any state)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3020,12 +3049,12 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>phenom</t>
+          <t>eightfold</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.msd.com/job/R390393</t>
+          <t>https://caci.eightfold.ai/careers/job/1443153781490</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3033,66 +3062,184 @@
           <t>New</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>We are currently hiring a Senior Specialist - SAP Authorisations and Security Architect to support the strategy, design, and implementation of SAP authorisations and security across multiple platforms. You will collaborate with cross-functional teams and lead technical projects. Ideal candidates have significant SAP authorisation and security experience.</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ML Security Engineer</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/5Izo29N73O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Jenny@bvteck.com&gt; or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>jobs.msd.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Senior Specialist - SAP Authorizations and Security Architect</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Boxmeer, North Brabant, Netherlands</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>phenom</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.msd.com/job/R390393</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>We are currently hiring a Senior Specialist - SAP Authorisations and Security Architect to support the strategy, design, and implementation of SAP authorisations and security across multiple platforms. You will collaborate with cross-functional teams and lead technical projects. Ideal candidates have significant SAP authorisation and security experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>samsara</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Senior AI Security Engineer</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Remote - Dallas</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/8247429?gh_jid=8247429</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>**Who we are**
 Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping improve the safety, efficiency and sustainability of the physical operations that power our global economy. Representing more than 40% of global GDP, these industries are the infrastructure of our planet, including agriculture, construction, field services, transportation, and manufacturing — and we are excited to help digitally transform their operations at scale.
@@ -3143,60 +3290,60 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>bloomreach</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bloomreach/jobs/8247118</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>Bloomreach is building the world’s premier **agentic platform for personalization**.We’re revolutionizing how businesses connect with their customers, building and deploying AI agents to personalize the ***entire*** customer journey.
 - We're taking **autonomous search** mainstream, making product discovery more intuitive and conversational for customers, and more profitable for businesses.
@@ -3290,60 +3437,60 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>bloomreach</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bloomreach/jobs/8247117</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>Bloomreach is building the world’s premier **agentic platform for personalization**.We’re revolutionizing how businesses connect with their customers, building and deploying AI agents to personalize the ***entire*** customer journey.
 - We're taking **autonomous search** mainstream, making product discovery more intuitive and conversational for customers, and more profitable for businesses.
@@ -3437,60 +3584,60 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>catawiki</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Lead Security Engineer</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/8245606</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>At Catawiki, every day brings the extraordinary! Whether it’s [Daniel Ricciardo’s Formula 1 Car](https://www.catawiki.com/en/c/583-sports-memorabilia), a [Woolly Mammoth’s Skeleton](https://www.catawiki.com/en/c/579-fossils), [Lady Gaga's Jumpsuit](https://www.catawiki.com/en/l/10035805) or [Usain Bolt’s running shoe](https://www.catawiki.com/en/c/583-sports-memorabilia), we encounter exceptional objects every day.
 We’re a one-of-a-kind marketplace for buying and selling special objects. Each week, more than 100,000 unique items are auctioned, all carefully curated by our passionate in-house experts.
@@ -3537,68 +3684,68 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>The Adecco Group</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>CYBERSECURITY ENGINEER H/F</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Montpellier, Occitanie, France</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/ZMet0N/jobs/cybersecurity-engineer-h-f_montpellier</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>Rejoignez Akkodis, une entreprise leader dans le domaine de la technologie et de l'ingénierie. En tant qu'Ingénieur Cybersécurité, vous serez au cœur d'un projet industriel majeur dans le secteur de l'énergie. Vous serez responsable de la supervision et de l'analyse du trafic réseau, du développement et de la mise en œuvre de mesures de sécurité, ainsi que de la gestion des outils et technologies de sécurité. Vous travaillerez dans un environnement exigeant et collaborerez avec les équipes IT et opérationnelles pour garantir la cohérence et la sécurité des installations.
 - Superviser et analyser le trafic réseau afin de détecter et répondre aux incidents de sécurité.
@@ -3609,64 +3756,64 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>aboutyougmbh</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Junior Application Security Engineer (all genders)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Hamburg, HH, de</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/ABOUTYOUGmbH/744000152882199-junior-application-security-engineer-all-genders-?oga=true</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>Wir suchen einen Junior Application Security Engineer (all genders) zur Verstärkung unseres Application-Security-Teams innerhalb der IT-Sicherheitseinheit, die sich dem Schutz unseres Onlineshops, unserer Unternehmenssysteme und unserer Kunden widmet. In dieser Rolle gehst du gezielt gegen interne Systeme vor (Pentesting/Ethical Hacking) sowie planst und implementierst Sicherheitsmaßnahmen zum Schutz unserer Infrastruktur, Anwendungen und Daten. Du arbeitest eng mit anderen Security Engineers, Entwickler:innen und IT-Teams zusammen, um Security Best Practices zu gewährleisten, Sicherheitsprozesse zu automatisieren und auf neue Bedrohungen zu reagieren. Die Stelle umfasst folgende Aufgaben: Durchführung regelmäßiger Penetrationstests und Code-Reviews Beratung bei der Einrichtung und Wartung von Anwendungen und Infrastruktur (in der Regel gehostet in AWS/Kubernetes) Triage und Behebung/Verfolgung von Überwachungsereignissen (Monitoring Events) Optimierung und Automatisierung von Sicherheitsprüfprozessen. Dies kann auch den Aufbau von Angriffsinfrastruktur, das Schreiben von Python-Skripten und die Implementierung von Security Scans in GitLab CI beinhalten Mitwirkung an Incident-Response-Aktivitäten im SOC, einschließlich gelegentlicher 24/7-Rufbereitschaft
 Mindestens ein Jahr Erfahrung im Bereich Application Security Fähigkeit zur Durchführung aktiver Sicherheitsbewertungen von Anwendungen (Application Security Assessments) und Penetrationstests Nice to have: Entwicklung und Scripting in Python (erforderlich; PHP, JavaScript oder Go bevorzugt) Architektur sicherer Systeme mittels Bedrohungsmodellierung (Threat Modeling) und Security-Engineering-Praktiken Durchführung sicherer Code-Reviews über verschiedene Cloud-Umgebungen hinweg (AWS/GCP bevorzugt; Azure von Vorteil) Durchführung von Red-Teaming-Operationen und offensiven Sicherheitsstrategien Zertifikate: z. B. OSCP, OSWP etc. Kenntnisse in Laravel / PHP Fähigkeit, JavaScript zu lesen und zu verstehen Fähigkeit, Go zu lesen und zu verstehen Erfahrung mit Incident-Response-Aktivitäten Erfahrung mit Web Application Firewalls (WAF) und CDN-Anbietern (z. B. Cloudflare, Akamai) Erfahrung mit GitLab CI/CD-Pipelines
@@ -3675,64 +3822,64 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Senior Software Engineer (Product Security)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/9664e737-bd33-49c7-82c7-62b370e3cddb/apply</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Senior Software Engineer (Product Security) based in Canada.**
 This role combines senior-level software engineering with a strong product security focus in a cloud-native infrastructure environment. You will design, build, and maintain production features while helping embed security directly into the product and engineering lifecycle. Your work will span vulnerability response, threat modeling, security-sensitive design reviews, and technical decision-making across the platform. You will work deeply within the codebase and architecture rather than focusing primarily on security tooling or compliance operations. The role offers significant technical ownership and the opportunity to influence secure engineering practices across a distributed, remote-first team.
@@ -3766,140 +3913,6 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Accso – Accelerated Solutions GmbH</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Senior Software Security Engineer*</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Frankfurt am Main, Hessen, Deutschland</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>87500 - 125500 EUR</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>recruitee</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>https://accso.recruitee.com/o/senior-software-security-engineer-4/c/new</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über langjährige Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Du repräsentierst Accso als verlässlicher Partner entlang des gesamten Projektlebenszyklus - von der Akquise bis zur Abnahme - und gibst dein Wissen proaktiv weite r Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst fundierte, tiefgreifende Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über profundes Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du handelst unternehmerisch, übernimmst Verantwortung und überzeugst durch souveräne, zielgruppengerechte Kommunikation mit unterschiedlichsten Stakeholdern bis auf Vorstandsebene Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email: &lt;bewerben@accso.de&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Accso – Accelerated Solutions GmbH</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Software Security Engineer*</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Frankfurt am Main, Hessen, Deutschland</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>61500 - 85500 EUR</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>recruitee</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>https://accso.recruitee.com/o/software-security-engineer-6/c/new</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst tiefgehende, praktische Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du arbeitest eigenverantwortlich und trägst aktiv zum Erfolg deines Projektteams bei Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email: &lt;bewerben@accso.de&gt;</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -3908,52 +3921,186 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>Accso – Accelerated Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Senior Software Security Engineer*</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main, Hessen, Deutschland</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>87500 - 125500 EUR</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>https://accso.recruitee.com/o/senior-software-security-engineer-4/c/new</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über langjährige Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Du repräsentierst Accso als verlässlicher Partner entlang des gesamten Projektlebenszyklus - von der Akquise bis zur Abnahme - und gibst dein Wissen proaktiv weite r Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst fundierte, tiefgreifende Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über profundes Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du handelst unternehmerisch, übernimmst Verantwortung und überzeugst durch souveräne, zielgruppengerechte Kommunikation mit unterschiedlichsten Stakeholdern bis auf Vorstandsebene Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accso – Accelerated Solutions GmbH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Software Security Engineer*</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main, Hessen, Deutschland</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>61500 - 85500 EUR</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>https://accso.recruitee.com/o/software-security-engineer-6/c/new</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst tiefgehende, praktische Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du arbeitest eigenverantwortlich und trägst aktiv zum Erfolg deines Projektteams bei Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email:</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008035003</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4005,60 +4152,60 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008034003</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4109,60 +4256,60 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008033003</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4216,60 +4363,60 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008030003</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4326,60 +4473,60 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008029003</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4437,64 +4584,64 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>System Engineer – Data &amp; Cloud Security</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Milan, Lombardy, Italy</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bVBkJa/jobs/system-engineer-data-cloud-security_milan_ND_8VrqXdV</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>Unisciti a NTT DATA, un'azienda globale leader nei servizi di business e tecnologici. Stiamo cercando un Cybersecurity System Engineer da inserire in attività di System Integration e Managed Security Services (MSS) in ambito Data &amp; Cloud Security. In questo ruolo, supporterai la progettazione e realizzazione di infrastrutture di sicurezza per clienti enterprise, lavorando su soluzioni CNAPP, progetti DLP, PKI e crittografia. La sede di lavoro è Milano e Roma, con possibilità di modalità di lavoro ibrida.
 - Supportare la progettazione e realizzazione di infrastrutture di sicurezza per clienti enterprise, in affiancamento a figure senior di Security Architecture.
@@ -4503,64 +4650,64 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Architect Cloud Security (w/m/x)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Erfurt, Thuringia, Germany</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bVBkJa/jobs/architect-cloud-security-w-m-x_erfurt_ND_PlrW1dL</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>Werde Teil von NTT DATA, einem führenden Anbieter von Unternehmens- und Technologiedienstleistungen. In der Rolle des Cloud Security Architects berätst du unsere Kunden bei der technischen Konzeption, Beratung und Implementierung von Cloud-Sicherheitsmaßnahmen. Du konzipierst und implementierst robuste Public und Hybrid-Cloud-Architekturen und steuerst aktiv unsere Projekte. Du solltest über mehrjährige Erfahrung im IT-Sicherheitsumfeld, insbesondere in den Bereichen Cloud- und Sicherheitsarchitektur, verfügen.
 - Beratung von Kunden bei der technischen Konzeption, Beratung und Implementierung von Cloud Security Maßnahmen.
@@ -4569,68 +4716,68 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Our Future Health</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Security Architect</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>GBP 90,000 - 103,500</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/VHxfW6/jobs/security-architect_london_epmiiacl</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>Join our team as a Security Architect, where you'll play a key role in supporting our Researcher pillar. In this hands-on position, you'll influence the security architecture that underpins our products, platforms, and cloud-first environment. You'll act as a trusted advisor to squads, partner with engineers to build security into solutions from the outset, and lead threat modeling activities. You'll also communicate security risks, opportunities, and recommendations to different audiences and support strategic Researcher initiatives.
 - Collaborer avec les équipes pour façonner l'architecture sécurisée de l'organisation, influencer les décisions de conception et garantir la cohérence de l'approche de sécurité.
@@ -4654,68 +4801,68 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Thought Machine</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Senior Application  Security Engineer</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Lisbonne, Portugal</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>EUR 75,000 - 95,000</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/JNjyxB/jobs/senior-application-security-engineer_lisbonne_qikdpj4z</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>Join Thought Machine, a rapidly growing fintech company on a mission to revolutionize banking technology. As a Senior Application Security Engineer, you will play a key role in ensuring the security of our products and protecting customer data. You will have the opportunity to engage and lead cross-functionally, and contribute to the development of cutting-edge security measures. This is a full-time, permanent position based in our Lisbon office.
 - Drive improvements to Thought Machine's product security posture through strategic planning and collaboration with both development and infrastructure teams.
@@ -4724,124 +4871,6 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CACI</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Information Systems Security Engineer (ISSE)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>remote (any state)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>eightfold</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>https://caci.eightfold.ai/careers/job/1443153775821</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Oracle Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/UBjJgjGK6n</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Oracle Cybersecurity Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Cybersecurity Engineer Location: 100% Remote (United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Cloud Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;jaya@bvteck.com&gt; or contact us at (908) 505-3545 . Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -4850,39 +4879,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>brightvisiontechnologies</t>
+          <t>Centre for Information Resilience</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Software Security Engineer</t>
+          <t>IT Systems &amp; Security Engineer - London (Westminster)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London, England, United Kingdom</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>USD 145,000–165,000 / year</t>
-        </is>
-      </c>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
@@ -4890,12 +4915,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>jazzhr</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/HfvUed4IZs</t>
+          <t>https://apply.workable.com/j/53829801C1/apply</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4903,70 +4928,251 @@
           <t>New</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Harry@bvteck.com&gt; or contact us at (908)676-4399. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Information Systems Security Engineer (ISSE)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>remote (any state)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>eightfold</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>https://caci.eightfold.ai/careers/job/1443153775821</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oracle Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/UBjJgjGK6n</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Oracle Cybersecurity Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Cybersecurity Engineer Location: 100% Remote (United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Cloud Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3545 . Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Software Security Engineer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>USD 145,000–165,000 / year</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/HfvUed4IZs</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908)676-4399. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Schneider Electric</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Stage – Stratégie DevSecOps – F/H</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Grenoble, Auvergne-Rhone-Alpes, France</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/WRUVr2/jobs/stage-strategie-devsecops-f-h_grenoble</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>Rejoignez Schneider Electric, une entreprise engagée pour l'inclusion et la diversité. En tant que stagiaire dans notre équipe EcoStruxure Control Engineering, vous participerez à la mise en œuvre de pratiques DevOps et bénéficierez d'un environnement d'apprentissage stimulant.
 - Réaliser un état des lieux de l'existant sur la base de code et l'environnement GitHub, et analyser les bonnes pratiques DevOps adaptées au contexte.
@@ -4975,60 +5181,60 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>guidepointsecurity</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Vulnerability Management Engineer (ServiceNow) - Mid-Atlantic region (Remote)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6212201004?gh_jid=6212201004</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>GuidePoint Security provides trusted cybersecurity expertise, solutions and services that help organizations make better decisions and minimize risk. By taking a three-tiered, holistic approach for evaluating security posture and ecosystems, GuidePoint enables some of the nation’s top organizations, such as Fortune 500 companies and U.S. government agencies, to identify threats, optimize resources and integrate best-fit solutions that mitigate risk.
 **General Description**
@@ -5113,60 +5319,60 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>isaraerospace</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer (m/f/d)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4994562101</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>**Mission Brief**
 You are a technical guardian of our digital environment. At Isar Aerospace, the systems, data and people that build our rockets are mission critical and protecting them takes someone who builds controls and then proves they hold. 
@@ -5215,60 +5421,60 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>mongodb</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Senior Software Engineer, Product Security</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>https://www.mongodb.com/careers/job/?gh_jid=8241351</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>The MongoDB Product Security team is looking for a full-stack senior software engineer to help us build and scale the next generation of security practices, enabling hundreds of MongoDB engineers to build secure products for our customers.
 The Product Security team empowers product teams to build secure products for MongoDB customers by providing security enablement, such as AI-powered code analysis, threat modeling and security finding triaging and verification, fuzzing infrastructure, and finding management solutions. Our goal is to incorporate security early in product development at scale without introducing friction. With the emerging capabilities of AI models, we are proactively adopting our security practices to be prepared for the newly introduced challenges.
@@ -5305,60 +5511,60 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>brandwatch</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Remote - Hungary; Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/brandwatch/jobs/4994458101</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>At Cision, we believe in empowering every individual to make an impact. Here, your voice is heard, your ideas are valued, and your unique perspective fuels our collective success. As part of our global team, you'll thrive in an environment that champions curiosity, collaboration, and innovation, all while making meaningful contributions to the brands we accelerate.
 Join us in shaping the future of communication and building authentic connections that matter. Whether you're solving complex problems or driving bold innovations, your growth is our success, and together, we’ll create the conversations of tomorrow.
@@ -5402,60 +5608,60 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>cision</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Remote - Hungary; Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/cision/jobs/4889283101</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>At Cision, we believe in empowering every individual to make an impact. Here, your voice is heard, your ideas are valued, and your unique perspective fuels our collective success. As part of our global team, you'll thrive in an environment that champions curiosity, collaboration, and innovation, all while making meaningful contributions to the brands we accelerate.
 Join us in shaping the future of communication and building authentic connections that matter. Whether you're solving complex problems or driving bold innovations, your growth is our success, and together, we’ll create the conversations of tomorrow.
@@ -5499,64 +5705,64 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Meilleurtaux</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Cloud Security Engineer F/H</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Courbevoie, IDF, fr</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Meilleurtaux/744000152686070-cloud-security-engineer-f-h?oga=true</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>Contexte L'équipe Engineering Platform porte l'architecture cloud hub &amp; spoke du groupe, les landing zones mises à disposition des équipes, et l'administration des outils transverses (GitHub, SonarCloud, Datadog). Dans une démarche d'homogénéisation des pratiques de sécurité, nous recherchons un profil capable de structurer la gouvernance Cloud Security à l'échelle du groupe. Missions Vous concevez et faites évoluer les briques de la plateforme (landing zones, modules Terraform, pipelines CI/CD) au même titre que l'ensemble de l'équipe, en y intégrant les exigences de sécurité. Vous mettez en place et faites évoluer les outils de sécurité Cloud du groupe relevant des approches CSPM et CNAPP (posture de sécurité, scanning de configuration et d'infrastructure as code, protection des workloads, gestion des vulnérabilités, gestion des secrets). Vous définissez en relation avec l'équipe cyber les policies de sécurité applicables aux landing zones et aux workloads (politiques d'accès, segmentation réseau, chiffrement, gestion des identités). Vous intégrez ces policies dans les modules d'infrastructure as code et les pipelines CI/CD afin de les rendre natives et non bloquantes pour les équipes. Vous accompagnez les équipes dans la mise en conformité de leurs environnements et participez aux audits de sécurité Cloud.
 Vous avez une expérience confirmée (5 ans et plus) en sécurité Cloud (Azure et/ou GCP), idéalement dans un rôle de type Cloud Security Engineer, DevSecOps ou Platform Engineer avec une forte composante sécurité, en contexte multi-équipes. Vous maîtrisez les approches zéro trust et moindre privilège, la gestion des identités (IAM, SSO, CIEM), ainsi que les outils de policy as code (type Azure Policy, OPA, Checkov ou équivalents). Vous avez une bonne pratique de Terraform, GitHub et CI/CD, et savez intégrer des contrôles de sécurité dans des pipelines et modules sans dégrader l'expérience développeur. Une expérience avec des plateformes CSPM/CNAPP (Microsoft Defender for Cloud, Wiz, Prisma Cloud, Orca Security ou équivalents) est un atout. Une connaissance des référentiels de sécurité Cloud (CIS Benchmarks, NIST, ISO 27001) est un plus.
@@ -5565,68 +5771,68 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>thought-machine</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Senior Application  Security Engineer</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Portugal, Lisbon</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>€75K – €95K</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/thought-machine/ab2745ac-35d2-4639-a957-fefbb2b17867/application</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>Thought Machine's mission is bold – to properly and permanently rid the world's banks of legacy technology. To achieve this, we have developed the foundations of modern banking through core and payments technology which run natively in the cloud. What we are attempting is hard and means we need great people working together to build great technology.
 We have grown rapidly in the past few years – growing our team to more than 550 individuals across offices in London, New York, Singapore, Sydney and our newly established Engineering Hub in Lisbon. We have raised more than £500m in funding and our investors include Molten Ventures, Eurazeo, Intesa Sanpaolo, Temasek, Nyca Partners, JPMorgan Chase Strategic Investments, Standard Chartered Ventures, and more.
@@ -5677,60 +5883,60 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>grafanalabs</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, Spain)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Spain (Remote)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211674004</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
 We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
@@ -5784,60 +5990,60 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>grafanalabs</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, Ireland)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Republic of Ireland (Remote)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211672004</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
 We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
@@ -5891,60 +6097,60 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>grafanalabs</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, UK)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>United Kingdom (Remote)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211670004</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
 We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
@@ -5998,64 +6204,64 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Network &amp; Security Engineer Senior Aix-en-Provence</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Aix-en-Provence, Provence-Alpes-Cote d'Azur, France</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/oGmK9Lp/jobs/network-security-engineer-senior-aix-en-provence_aix-en-provence_CAPGE_rDlJRNO</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>Rejoignez notre équipe en tant qu'Ingénieur Réseau et Sécurité Senior. Vous serez responsable de l'exploitation et de la maintenance des équipements et services réseau, de la gestion de projets réseaux, du traitement des incidents N2/N3, de l'administration des équipements de sécurité, et de l'élaboration des architectures techniques. Vous devez avoir au moins 3 ans d'expérience dans un poste similaire et être autonome, impliqué et avoir un bon esprit d'équipe.
 - Assurer l'exploitation et la MCO des équipements et services réseau, gestion du BUILD et pilotage de projets réseaux.
@@ -6075,64 +6281,64 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Security Engineer (Incident Response)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/oRcFvn/jobs/security-engineer-incident-response_ie_ktrn554v</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>Join Twilio's Security Incident Response Team (SIRT) as a Security Engineer. In this role, you will lead the technical response to security events and incidents across Twilio's global infrastructure, services, and applications. You will work collaboratively with R&amp;D Engineering and R&amp;D Business teams to develop scalable processes and technical solutions. Your responsibilities will include documenting incidents and projects, improving Twilio's security and reliability posture, and providing mentorship and support to the team. Enjoy benefits such as work-from-home opportunities, generous annual time off, comprehensive health programs, and more.
 - Lead and support the response to all security events and incidents across Twilio’s complex global infrastructure, services, and applications.
@@ -6155,64 +6361,64 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Pantheon</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/fdsSTg/jobs/security-engineer_ca_emny6wrd</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>Join Pantheon's Security Engineering team as a Security Engineer II. In this hands-on engineering role, you will be responsible for safeguarding, auditing, and testing the security of Pantheon's entire platform. You will own security domains end-to-end, build automation and processes, and write detection rules. This position offers a flexible work environment, health and wellness benefits, and opportunities for professional development.
 - Assurer la sécurité, l'audit et les tests de la plateforme cloud de Pantheon, en mettant l'accent sur la sécurité dès la conception.
@@ -6234,249 +6440,249 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/0F3Za69HVM</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AI Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 8+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Eight or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/S5bS7lykdZ</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Application Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Application Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$160,000 Annually Experience Required: 10+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Application Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Key Responsibilities Conduct threat modeling and security architecture reviews for new and existing applications and services. Perform manual code reviews, secure design consultations, and pair with engineering teams on hardening critical components. Operate and tune SAST, DAST, IAST, SCA, and secret-scanning tools across CI/CD pipelines. Drive vulnerability management workflows including triage, prioritization, owner assignment, and SLA tracking. Build paved-road libraries and frameworks that make secure patterns the default for engineering teams. Lead red-team and purple-team exercises against internal applications and drive remediation of identified weaknesses. Implement and operate runtime protections including WAF, RASP, bot protection, and abuse-detection mechanisms. Design and enforce secure authentication, authorization, session management, and cryptographic patterns. Partner with infrastructure and platform teams to harden container, Kubernetes, and cloud environments. Develop and deliver application security training, lunch-and-learns, and onboarding content for engineering staff. Respond to security incidents involving application vulnerabilities or active exploitation. Track and apply emerging threats and CVEs that may affect the application portfolio. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Stay current with application security research and emerging defensive tooling. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Ten or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer – Oracle</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/qLisMzMIxC</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cloud Security Engineer - Oracle Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Cloud Security Engineer - Oracle responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. Key Responsibilities Design and implement enterprise security architectures for OCI tenancies, including landing-zone guardrails, security zones, and compartment policies. Configure and operate OCI Identity Domains, federation with corporate IdPs, and strong RBAC strategies across the tenancy. Implement strong key management and secrets handling using OCI Vault, including key rotation and HSM integration where appropriate. Harden OCI compute, networking, and database workloads using CIS benchmarks, OCI Security Zones, and internal security standards. Operate OCI Cloud Guard for continuous detection and response, tuning detectors and remediating findings. Configure and operate OCI Logging, OCI Audit, and integration with SIEM platforms for centralized monitoring and forensics. Implement data security controls using OCI Data Safe, including data masking, sensitive data discovery, and privileged user analysis. Lead vulnerability management programs, including image scanning, patching, and remediation tracking. Drive compliance with regulatory frameworks such as PCI-DSS, HIPAA, SOC 2, ISO 27001, or FedRAMP. Conduct threat modeling and architecture reviews for new OCI workloads. Lead security incident response on OCI, including containment, investigation, and post-incident review. Develop security automation tooling using Python, Terraform, and OCI CLI/SDK. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Provide mentorship and security guidance across application and infrastructure teams. Required Qualifications 5+ years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3545. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/0F3Za69HVM</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AI Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 8+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Eight or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/S5bS7lykdZ</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Application Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Application Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$160,000 Annually Experience Required: 10+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Application Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Key Responsibilities Conduct threat modeling and security architecture reviews for new and existing applications and services. Perform manual code reviews, secure design consultations, and pair with engineering teams on hardening critical components. Operate and tune SAST, DAST, IAST, SCA, and secret-scanning tools across CI/CD pipelines. Drive vulnerability management workflows including triage, prioritization, owner assignment, and SLA tracking. Build paved-road libraries and frameworks that make secure patterns the default for engineering teams. Lead red-team and purple-team exercises against internal applications and drive remediation of identified weaknesses. Implement and operate runtime protections including WAF, RASP, bot protection, and abuse-detection mechanisms. Design and enforce secure authentication, authorization, session management, and cryptographic patterns. Partner with infrastructure and platform teams to harden container, Kubernetes, and cloud environments. Develop and deliver application security training, lunch-and-learns, and onboarding content for engineering staff. Respond to security incidents involving application vulnerabilities or active exploitation. Track and apply emerging threats and CVEs that may affect the application portfolio. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Stay current with application security research and emerging defensive tooling. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Ten or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer – Oracle</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/qLisMzMIxC</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cloud Security Engineer - Oracle Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Cloud Security Engineer - Oracle responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. Key Responsibilities Design and implement enterprise security architectures for OCI tenancies, including landing-zone guardrails, security zones, and compartment policies. Configure and operate OCI Identity Domains, federation with corporate IdPs, and strong RBAC strategies across the tenancy. Implement strong key management and secrets handling using OCI Vault, including key rotation and HSM integration where appropriate. Harden OCI compute, networking, and database workloads using CIS benchmarks, OCI Security Zones, and internal security standards. Operate OCI Cloud Guard for continuous detection and response, tuning detectors and remediating findings. Configure and operate OCI Logging, OCI Audit, and integration with SIEM platforms for centralized monitoring and forensics. Implement data security controls using OCI Data Safe, including data masking, sensitive data discovery, and privileged user analysis. Lead vulnerability management programs, including image scanning, patching, and remediation tracking. Drive compliance with regulatory frameworks such as PCI-DSS, HIPAA, SOC 2, ISO 27001, or FedRAMP. Conduct threat modeling and architecture reviews for new OCI workloads. Lead security incident response on OCI, including containment, investigation, and post-incident review. Develop security automation tooling using Python, Terraform, and OCI CLI/SDK. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Provide mentorship and security guidance across application and infrastructure teams. Required Qualifications 5+ years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;jaya@bvteck.com&gt; or contact us at (908) 505-3545. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt;. Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Remote Sweden</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237824</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -6533,60 +6739,60 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Remote Netherlands</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237818</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -6643,60 +6849,60 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Remote Spain</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237816</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -6753,60 +6959,60 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Remote Belgium</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237815</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -6863,60 +7069,60 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Remote Finland</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237812</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -6973,60 +7179,60 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Remote UK</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8237810</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -7083,60 +7289,60 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Remote Germany</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8191473</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>**Why Mozilla?**
 Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
@@ -7193,60 +7399,60 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>mozilla</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Senior Security Engineer - SecOps</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/mozilla/jobs/8189048</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>To learn the Hiring Ranges for this position, please select your location from the **Apply Now** dropdown menu.
 To learn more about our Hiring Range System, please click this [**link.**](https://docs.google.com/document/d/1ylUe7Ou0EbsOtGRBtUv1sSld3lbZ4mrYzo59tEkSjY8/edit?usp=sharing)
@@ -7302,266 +7508,6 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>netcompany1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Purple Security Engineer</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Copenhagen, dk</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Netcompany1/744000152447554-purple-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Do you find Threat Hunting, Threat Intelligence, SIEM, and EDR exciting, and do you want to be a deciding factor in IT Security in our internal as well as our customers’ environments? As a Purple Security Engineer, you will ensure operations can perform their security-related tasks based on guidelines you help define. Responsibilities and technologies As a Purple Security Engineer, you will be a part of Netcompany Operations and our dedicated Security team. Your work will involve defending critical infrastructure such as airports, large financial institutions, government systems, and other essential sectors. You will handle tasks ranging from identifying improvements and monitoring servers and applications to optimizing response strategies and advising colleagues. You will be encouraged to solve technical problems creatively to find the best solutions. Open dialogue about different approaches to enhancing security is an important part of your work as a Purple Security Engineer. You will be a trusted advisor for Netcompany’s delivery and project teams regarding how to solve security-related tasks. Your responsibilites will typically include: Implementing safeguards to protect critical solutions and the data infrastructure of Denmark from cyber threats. Engaging in proactive threat hunting to identify and mitigate potential vulnerabilities. Developing and implementing response strategies to effectively handle security incidents. Responding to and following up on alerts generated by our SIEM and EDR solutions, including adjusting these to ensure precision. About you To succeed in this role, you: You hold a degree or diploma in engineering, either bachelor's, master's, or have a similar qualification level in IT. You are motivated by delivering optimal business and critical societal solutions. Full professional proficiency in Danish and English (written and spoken) is a must. Employment is contingent upon your ability to obtain and maintain security clearance from the Danish Security and Intelligence Service (PET). Continue developing with us At Netcompany, we focus on your personal and professional development. When you join us, you will be assigned a personal mentor who will guide you through your development and help you achieve your goals. The close relationship with an experienced colleague helps ensure the well-being of each employee and provides you with concrete insights into the many different career opportunities as you build your experience. Additionally, you will be enrolled in our internal training programme, Netcompany Academy, where you are offered courses and seminars on everything from technologies to customer management. All courses are taught by experienced Netcompany colleagues, ensuring that all content is highly relevant and builds upon your professional skills, preparing you for various tasks and continuously improving your expertise throughout your career with us. Join an inclusive community At Netcompany, we highly prioritise an inclusive community. We actively promote an open and welcoming work culture based on collaboration and mutual trust, where there is always an opportunity for sparring. As part of our culture and values, all employees, regardless of background, identity, and experience, are met with understanding and respect and given equal opportunities for development and well-being. As we are an international company with offices in many countries, you will have the opportunity to learn and collaborate internationally with colleagues from across the world. We offer a shared environment where we engage with each other across departments and projects. Additionally, we have a wide range of social and professional events that provide you with the best opportunities to expand and build a network early in your career. Send us your application Upload your resume and a motivational letter to our recruitment system via the link. If you have unanswered questions, feel free to write to &lt;hr.dk@netcompany.com&gt;. All qualified candidates are encouraged to apply regardless of gender, gender expression, sexuality, disability, age, religion and belief, political views, nationality, ethnicity, or social background. We are committed to creating an inclusive and diverse environment. Our recruitment processes are based on individual merit. If you require any reasonable adjustments or additional support during the interview process, please email our recruiters at &lt;reasonableadjustments@netcompany.com&gt; for assistance. #LI-SA1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>purestorage</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer,Detection &amp; Incident Response</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Prague, Czech Republic</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/purestorage/jobs/8225837</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Everpure (NYSE: P) has evolved from storage pioneer to data platform, closing fiscal 2026 with $3.7 billion in revenue, its first billion-dollar quarter, and accelerating growth into FY27. Our strategic agenda spans the companies defining the next era of technology - hyperscalers, AI labs, the AI hardware supply chain, data platform providers, and the broader AI ecosystem.
-This type of work—work that changes the world—is what the tech industry was founded on. So, if you're ready to seize the endless opportunities and leave your mark, come join us.
-**THE ROLE**
-Everpure is seeking a hands-on **Senior Security Engineer** to drive security operations from our Prague, Czech Republic location. In this role, you will contribute to operational excellence across incident response, threat hunting, threat intelligence integration, detection engineering, and security automation, bringing real-time visibility and rapid response to our 24/7 global security operations environment.
-This is a **technical delivery and execution role**, not a traditional monitoring position. You will work closely with detection engineers, threat intelligence analysts, incident response leadership, and our global Security Operations teams to build and refine detections, improve signal quality, execute threat hunts, automate workflows, and respond to complex security incidents with speed and precision.
-Success in this role is measured not by alert volume, but by **signal quality, real threat detection, incident containment speed, automation maturity, and the effectiveness of response workflows**.
-**WHAT YOU'LL DO**
-- **Detection Engineering:** Design, implement, and maintain detections in Splunk and related security platforms. Develop detection-as-code content using formats such as YAML/JSON, incorporate unit and regression testing, map coverage to MITRE ATT&amp;CK, and contribute to Sigma/YARA-L coverage expansion.
-- **Incident Response &amp; Triage:** Investigate suspicious activity and participate in incident triage, scoping, containment, eradication, recovery, and post-incident reviews. Use lessons from investigations to continuously improve detection and response processes.
-- **Threat Hunting:** Execute hypothesis-driven threat hunts using MITRE ATT&amp;CK, the Diamond Model, kill chains, threat intelligence, behavioral baselines, and anomaly detection. Correlate signals across endpoint, cloud, identity, SaaS, network, and other security telemetry to identify real threats and operational blind spots.
-- **Detection Quality:** Continuously tune detections to improve true-positive rates and reduce alert fatigue. Identify which signals provide meaningful security value and refine detection logic based on investigation outcomes and changes in the threat landscape.
-- **Threat Intelligence Integration:** Operationalize cyber threat intelligence (CTI) by mapping adversary tools, techniques, TTPs, and indicators to the Everpure environment and translating relevant intelligence into detection and hunting strategies.
-- **Automation &amp; Orchestration:** Build Python scripts, API integrations, enrichment workflows, and SOAR automation using platforms such as Tines, XSOAR, or equivalent. Develop workflows that reduce manual effort and accelerate investigation and containment while maintaining appropriate guardrails and logging.
-- **Cloud &amp; Container Security Monitoring:** Monitor and investigate security signals across AWS, GCP, and Azure, including CloudTrail, GuardDuty, and cloud audit logs. Identify container and Kubernetes runtime anomalies and contribute to monitoring cloud-native attack surfaces.
-- **Agentic &amp; AI-Assisted Workflows:** Evaluate and implement AI-assisted security workflows, including LLM-based investigation and autonomous triage capabilities. Assess AI-generated detection logic while maintaining appropriate human oversight and guardrails.
-- **Playbooks &amp; Documentation:** Develop and refine detection playbooks, investigation procedures, automated security playbooks, and operational runbooks to improve consistency, investigation rigor, and response effectiveness.
-- **Security Operations Development:** Help build detection content addressing threats such as credential abuse, privilege escalation, lateral movement, cloud misuse, insider risk, sensitive data movement, and unauthorized access.
-- **Detection-as-Code &amp; Automation Infrastructure:** Contribute to Git-backed detection repositories, CI/CD processes, testing frameworks, enrichment pipelines, remediation workflows, and response automation designed to reduce analyst toil and improve response times.
-- **Global Collaboration:** Partner with global Security Operations teams and contribute to a SOC culture focused on operational excellence, collaboration, knowledge sharing, and continuous improvement.
-- We are primarily an in-office environment and therefore, you will be expected to work from the **Prague, Czech Republic** office in compliance with Everpure's policies, unless you are on PTO, work travel, or other approved leave.
-**WHAT YOU BRING**
-- 6+ years of experience in cybersecurity, incident response, detection engineering, security operations, or a related security discipline.
-- 3+ years of hands-on experience executing threat hunts, complex incident investigations, or detection engineering within a SOC or SIEM environment.
-- Deep hands-on experience with **Splunk**, including search, dashboards, alerts, correlation searches, saved searches, deployment server, and forwarder management.
-- Strong understanding of the complete incident response lifecycle, including triage, scoping, containment, eradication, recovery, and post-incident learning.
-- Strong knowledge of networking, operating systems, cloud environments, and security architecture across identity, endpoint, network, and cloud.
-- Experience developing **Python scripts** for data processing, API integrations, security tooling, and automation.
-- Strong understanding of threat intelligence and attacker frameworks, including **MITRE ATT&amp;CK, the Diamond Model, kill chains, and TTPs**.
-- Hands-on experience with threat hunting methodologies, including hypothesis-driven hunting, behavioral baselines, and anomaly detection.
-- Excellent written and verbal communication skills in English.
-- Bachelor's degree in Computer Science, Information Security, Engineering, or a related technical field, or equivalent practical experience.
-**Strongly Preferred:**
-- Detection-as-code experience, including Sigma, ECMA/JSON detection formats, Git-backed detection repositories, unit testing, MITRE ATT&amp;CK coverage mapping, Splunk Security Content, or similar detection frameworks.
-- Hands-on experience with security automation and SOAR platforms such as **Tines, XSOAR, Splunk SOAR**, or equivalent, including API-driven enrichment and response workflows.
-- Cloud security operations experience across **AWS, GCP, and/or Azure**, including CloudTrail, GuardDuty, cloud audit logs, and cloud-native attack surfaces.
-- Container and Kubernetes security experience, including Falco, container runtime monitoring, image scanning, vulnerability management, or software supply chain security.
-- Experience evaluating or implementing **agentic or AI-assisted security workflows**, including LLM-assisted investigations, autonomous triage, or AI-generated detections, with an understanding of appropriate guardrails and human oversight.
-- Experience operationalizing threat intelligence, including PIRs, CTI-to-detection pipelines, and intelligence-driven threat hunting.
-- Experience with Python, Bash, Go, or similar languages and exposure to infrastructure-as-code technologies such as Terraform or CloudFormation.
-- Experience working within follow-the-sun security operations models and with security operations metrics such as MTTD, MTTA, and MTTC.
-- Experience with **Attack Surface Management**, including secret hygiene, identity attack surface, and Shadow AI.
-- Relevant certifications such as **GCIH, GCIA, AWS Security Specialty, CKS**, or equivalent.
-#LI-ONSITE
-**WHAT YOU CAN EXPECT FROM US:**
-- **Innovation**: We celebrate those who think critically, like a challenge, and aspire to be trailblazers.
-- **Growth**: We give you the space and support to grow along with us and to contribute to something meaningful. We have been named Fortune's Best Workplaces in Technology™, Fortune's Best Workplaces in the Bay Area™, and certified as a Great Place to Work®!
-- **Team**: We build each other up and set aside ego for the greater good.
-And because we understand the value of bringing your full and best self to work, we offer a variety of perks to manage a healthy balance, including flexible time off, wellness resources, and company-sponsored team events. Check out &lt;http://benefits.everpuredata.com/&gt;for more information.
-**ACCOMMODATIONS AND ACCESSIBILITY:**
-Candidates with disabilities may request accommodations for all aspects of our hiring process. For more on this, contact us at [TA-Ops@purestorage.com](mailto:TA-Ops@purestorage.com) if you’re invited to an interview.
-**OUR COMMITMENT TO A STRONG AND INCLUSIVE TEAM:**
-We’re forging a future where everyone finds their rightful place and where every voice matters. Where uniqueness isn’t just accepted but embraced. That’s why we are committed to fostering the growth and development of every person, cultivating a sense of community through our Employee Resource Groups and advocating for inclusive leadership.
-Everpure is proud to be an equal opportunity employer. We do not discriminate based upon race, religion, color, national origin, sex (including pregnancy, childbirth, or related medical conditions), sexual orientation, gender, gender identity, gender expression, transgender status, sexual stereotypes, age, status as a protected veteran, status as an individual with a disability, or any other characteristic legally protected by the laws of the jurisdiction in which you are being considered for hire.
-**Join us and bring your best.**
-**Bring your bold.**
-**Pure and simple.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>axonius</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Senior Product Security Architect</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>UK, Remote</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.axonius.com/company/careers/open-jobs?gh_jid=8007963003</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>As a **Senior Product Security Architect**, you will join a highly technical, fast-moving Product Security team to advance and secure Axonius's platform and its modern AI-driven capabilities. Operating in an environment with deep R&amp;D collaboration and a hybrid schedule, you will own the development lifecycle's security strategy, ensuring modern cloud and distributed systems are engineered safely by design. This role directly supports core development teams across Israel and Portugal, ensuring robust posture alignment from initial planning through deployment.
-## **Responsibilities**
-- Collaborate with R&amp;D teams to identify, prioritize, and drive security requirements and mitigation strategies throughout the development lifecycle.
-- Conduct architecture, design, and threat modeling security reviews for web, cloud (AWS), and distributed systems.
-- Produce explicit, actionable security architecture documents, design specifications, and technical guidelines for engineering.
-- Lead incident response efforts during active product cyber security events, driving cross-functional remediation across engineering teams.
-## **Minimum Qualifications**
-- 5+ years of hands-on software development experience with at least 3 years dedicated to application security or product security roles.
-- Professional experience analyzing, reading, and evaluating codebase architecture within a product-centric tech stack.
-- Hands-on experience working directly in AWS cloud environments and building application threat models.
-- Active experience utilizing AI/LLM-based tools (e.g., Claude, Augment) to optimize development workflows, research, or productivity.
-- Professional fluency in both written and verbal communication in English.
-## **Preferred Qualifications**
-- Hands-on security architecture experience integrating and securing AI/LLM technologies directly within modern commercial B2B products.
-- Professional experience designing security frameworks for both modern cloud/SaaS stacks and legacy medical device/hardware environments.
-- Industry-recognized security certifications such as CISSP, OSCP, or CCSP.
-- Proven track record of published security research, CVE submissions, bug bounty participation, or security conference presentations.
-- Bachelor’s or Master’s degree in Computer Science, Engineering, or a related technical discipline.
-#LI-REMOTE, #LI-AZ1
-**About Axonius:**
-Axonius transforms cyber asset intelligence into actionability. With the Axonius Asset Cloud, customers preemptively tackle high-risk and hard-to-spot threat exposures, misconfigurations, and overspending. The integrated platform brings together data from every system in an organization’s IT infrastructure to optimize mission-critical risk, performance, and cost measures via actionable intelligence.
-Covering cyber assets, software, SaaS applications, identities, vulnerabilities, infrastructure, and more, Axonius is the one place to go for Security, IT, and GRC teams to continuously drive actionability across the organization. Cited as one of the fastest-growing cybersecurity startups, with accolades from CNBC, Forbes, and Fortune, Axonius supports millions of assets for leading customers across industries and around the world.
-Axonius makes it a priority to invest in our people with competitive compensation and benefits, growth opportunities, community-building, and so much more. Learn more about [**benefits at Axonius**](https://www.axonius.com/company/careers#benefits-and-perks).
-At Axonius we support a diverse and inclusive workplace and believe in equal employment opportunity. We welcome people of different backgrounds, experiences, abilities and perspectives to apply. All qualified applicants will receive consideration for employment without regard torace, color, ancestry, religion, age, sex, gender identity, national origin, sexual orientation, citizenship, marital status, disability, or Veteran status.
-****Axonius participates in E-Verify. To learn more, please review the** **[E-Verify Participation Poster (PDF)](https://www.e-verify.gov/sites/default/files/everify/posters/EVerifyParticipationPoster.pdf)** **and the** **[Right to Work Poster (PDF)](https://www.e-verify.gov/sites/default/files/everify/posters/IER_RightToWorkPoster%20Eng_Es.pdf)****.** By submitting your application to us, you acknowledge that your personal data will be processed in accordance with our [Global Job Candidate Privacy Notice.](https://www.axonius.com/global-job-candidate-privacy-notice)**</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -7570,27 +7516,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>axonius</t>
+          <t>netcompany1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Senior Product Security Architect</t>
+          <t>Purple Security Engineer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Portugal, Remote</t>
+          <t>Copenhagen, dk</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7599,15 +7545,19 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>smartrecruiters</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>https://www.axonius.com/company/careers/open-jobs?gh_jid=8007962003</t>
+          <t>https://jobs.smartrecruiters.com/Netcompany1/744000152447554-purple-security-engineer?oga=true</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7617,2478 +7567,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>As a **Senior Product Security Architect**, you will join a highly technical, fast-moving Product Security team to advance and secure Axonius's platform and its modern AI-driven capabilities. Operating in an environment with deep R&amp;D collaboration and a hybrid schedule, you will own the development lifecycle's security strategy, ensuring modern cloud and distributed systems are engineered safely by design. This role directly supports core development teams across Israel and Portugal, ensuring robust posture alignment from initial planning through deployment.
-## **Responsibilities**
-- Collaborate with R&amp;D teams to identify, prioritize, and drive security requirements and mitigation strategies throughout the development lifecycle.
-- Conduct architecture, design, and threat modeling security reviews for web, cloud (AWS), and distributed systems.
-- Produce explicit, actionable security architecture documents, design specifications, and technical guidelines for engineering.
-- Lead incident response efforts during active product cyber security events, driving cross-functional remediation across engineering teams.
-## **Minimum Qualifications**
-- 5+ years of hands-on software development experience with at least 3 years dedicated to application security or product security roles.
-- Professional experience analyzing, reading, and evaluating codebase architecture within a product-centric tech stack.
-- Hands-on experience working directly in AWS cloud environments and building application threat models.
-- Active experience utilizing AI/LLM-based tools (e.g., Claude, Augment) to optimize development workflows, research, or productivity.
-- Professional fluency in both written and verbal communication in English.
-## **Preferred Qualifications**
-- Hands-on security architecture experience integrating and securing AI/LLM technologies directly within modern commercial B2B products.
-- Professional experience designing security frameworks for both modern cloud/SaaS stacks and legacy medical device/hardware environments.
-- Industry-recognized security certifications such as CISSP, OSCP, or CCSP.
-- Proven track record of published security research, CVE submissions, bug bounty participation, or security conference presentations.
-- Bachelor’s or Master’s degree in Computer Science, Engineering, or a related technical discipline.
-#LI-REMOTE, #LI-AZ1
-**About Axonius:**
-Axonius transforms cyber asset intelligence into actionability. With the Axonius Asset Cloud, customers preemptively tackle high-risk and hard-to-spot threat exposures, misconfigurations, and overspending. The integrated platform brings together data from every system in an organization’s IT infrastructure to optimize mission-critical risk, performance, and cost measures via actionable intelligence.
-Covering cyber assets, software, SaaS applications, identities, vulnerabilities, infrastructure, and more, Axonius is the one place to go for Security, IT, and GRC teams to continuously drive actionability across the organization. Cited as one of the fastest-growing cybersecurity startups, with accolades from CNBC, Forbes, and Fortune, Axonius supports millions of assets for leading customers across industries and around the world.
-Axonius makes it a priority to invest in our people with competitive compensation and benefits, growth opportunities, community-building, and so much more. Learn more about [**benefits at Axonius**](https://www.axonius.com/company/careers#benefits-and-perks).
-At Axonius we support a diverse and inclusive workplace and believe in equal employment opportunity. We welcome people of different backgrounds, experiences, abilities and perspectives to apply. All qualified applicants will receive consideration for employment without regard torace, color, ancestry, religion, age, sex, gender identity, national origin, sexual orientation, citizenship, marital status, disability, or Veteran status.
-****Axonius participates in E-Verify. To learn more, please review the** **[E-Verify Participation Poster (PDF)](https://www.e-verify.gov/sites/default/files/everify/posters/EVerifyParticipationPoster.pdf)** **and the** **[Right to Work Poster (PDF)](https://www.e-verify.gov/sites/default/files/everify/posters/IER_RightToWorkPoster%20Eng_Es.pdf)****.** By submitting your application to us, you acknowledge that your personal data will be processed in accordance with our [Global Job Candidate Privacy Notice.](https://www.axonius.com/global-job-candidate-privacy-notice)**</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Security Architect</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/709d9e9c-cc09-4f6f-9339-05a288bf5794/application</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Define security architecture across BJAK products, applications, cloud platforms, and infrastructure. Partner with Engineering, Product, Cloud, Compliance, and Security to build secure systems and meet regulatory requirements.
-# **What You Will Build**
-- Define security architecture, patterns, and standards across products, applications, APIs, cloud environments, and integrations.
-- Own architecture implementation and ongoing alignment with SC TRM and BNM RMiT, including control evidence, reviews, remediation, and audit support.
-- Lead threat modeling and security design reviews for new products, major changes, third-party integrations, and critical systems.
-- Design and review IAM, privileged access, network security, encryption, key management, secrets, logging, and threat detection controls.
-- Review web, API, native mobile, AI-enabled, and data processing architectures for security and privacy risks.
-- Guide secure architecture across TypeScript/Node.js, Python, Swift, and Kotlin applications and services on AWS and GCP.
-- Evaluate security technologies, advise engineering leaders, and track remediation of material architecture risks.
-# **What We Look For**
-- Degree in Computer Science, Information Security, or related field, or equivalent experience.
-- 5+ years in security engineering, security architecture, or a related security role.
-- Experience implementing and owning SC TRM and BNM RMiT requirements, including control operation, evidence, and audit remediation.
-- Strong knowledge of cloud and application security, IAM, networking, encryption, secure design, and distributed systems.
-- Hands-on familiarity with AWS and GCP and architectures using TypeScript/Node.js, Python, Swift, and Kotlin.
-- Experience with threat modeling, architecture reviews, risk assessments, and frameworks such as ISO 27001, NIST, CIS, or OWASP.
-- Able to translate regulatory and technical risks into clear, actionable plans for technical and non-technical stakeholders.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Mobile App Security Engineer</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/6be2788d-92ce-4e29-b1fc-ad58fc488917/application</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Protect BJAK's native iOS and Android applications and their connections to backend services. Work with mobile, backend, and security teams to build mobile security into development and release processes.
-# **What You Will Build**
-- Assess and review native iOS and Android applications built with Swift and Kotlin.
-- Apply OWASP MASVS and MASTG to define mobile security requirements, test coverage, and remediation priorities.
-- Assess secure local storage, Keychain and Keystore use, sensitive data handling, sessions, tokens, and data leakage.
-- Implement and test transport security, including certificate validation and certificate pinning where appropriate.
-- Evaluate tamper detection, jailbreak and root detection, anti-debugging, and runtime protection controls proportionate to risk.
-- Work with API and backend teams on authentication, authorization, API exposure, and secure mobile communication.
-- Own mobile security controls for SC TRM and BNM RMiT, including testing evidence, vulnerability remediation, release controls, and audit support.
-# **What We Look For**
-- Degree in Computer Science, Cybersecurity, or related field, or equivalent experience.
-- 3+ years in mobile development, mobile security, or mobile penetration testing.
-- Experience implementing and owning SC TRM and BNM RMiT controls relevant to mobile applications and secure technology delivery.
-- Hands-on native iOS development or review using Swift and Android using Kotlin.
-- Practical knowledge of OWASP MASVS and MASTG, mobile threat modeling, and mobile testing tools.
-- Experience with secure storage, certificate pinning, jailbreak/root detection, tamper resistance, authentication, and mobile API security.
-- Able to work with mobile developers and communicate findings, trade-offs, and remediation steps.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Data Privacy Security Engineer</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/4e7b3e1f-4f8a-49f5-b89a-5bc70ed7576b/application</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Protect BJAK's sensitive customer and business data across products, data platforms, and third-party services. Partner with Data, Engineering, Product, Legal, and Compliance to apply privacy-by-design and reduce risks.
-# **What You Will Build**
-- Protect sensitive data across collection, processing, storage, sharing, retention, and deletion.
-- Map data flows and assess privacy and security risks across applications, analytics, integrations, and third-party providers.
-- Implement encryption, tokenization, masking, anonymization, retention, and least-privilege data access controls.
-- Work with data engineering teams to secure pipelines, databases, warehouses, and cloud data services on AWS and GCP.
-- Assess customer data shared with third-party AI model vendors and define minimization, approved use, retention, and access controls.
-- Own data and privacy controls for SC TRM and BNM RMiT, including assessments, evidence, remediation, and audit support.
-- Support privacy impact assessments, access reviews, monitoring, incident response, and privacy-by-design reviews.
-# **What We Look For**
-- Degree in Computer Science, Information Security, Data Engineering, or related field, or equivalent experience.
-- 3+ years in data security, privacy engineering, security engineering, or data platform engineering.
-- Experience implementing and owning SC TRM and BNM RMiT controls relevant to data protection and technology risk.
-- Understanding of privacy-by-design, data classification, retention, access management, and third-party data sharing.
-- Knowledge of encryption, key management, masking, tokenization, anonymization, and secure data processing.
-- Experience securing databases, data pipelines, and AWS or GCP data platforms; familiarity with AI vendor data flows is beneficial.
-- Familiarity with applicable privacy and security frameworks and ability to collaborate across technical and compliance teams.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/543e1620-c9d5-453b-8103-2ddc17e93bc7/application</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Integrate security into BJAK's software delivery and infrastructure workflows. Work with Platform, Cloud, and Engineering to automate controls and support secure delivery across AWS and GCP.
-# **What You Will Build**
-- Embed code, dependency, container, infrastructure-as-code, and secrets scanning into CI/CD pipelines.
-- Maintain security guardrails for builds, releases, artifacts, deployment identities, and infrastructure changes.
-- Secure containerized workloads, orchestration platforms, and deployment environments across AWS and GCP.
-- Implement least-privilege access, secrets management, artifact integrity, and secure configuration practices.
-- Own DevSecOps implementation for SC TRM and BNM RMiT, including evidence, testing, remediation, and audit support.
-- Partner with teams using TypeScript/Node.js, Python, Swift, and Kotlin to integrate security checks into delivery workflows.
-- Improve monitoring, vulnerability reporting, incident readiness, and secure delivery guidance.
-# **What We Look For**
-- Degree in Computer Science, Information Security, or related field, or equivalent experience.
-- 3+ years in DevOps, platform engineering, cloud security, or DevSecOps.
-- Experience implementing and owning SC TRM and BNM RMiT controls for technology operations, change management, and secure delivery.
-- Hands-on with GitHub Actions, GitLab CI, Jenkins, or similar CI/CD tools.
-- Experience with AWS, GCP, Docker, Kubernetes, infrastructure as code, and cloud security controls.
-- Knowledge of security scanning, software supply chain security, secrets management, IAM, logging, and monitoring.
-- Scripting or programming skills in Python, TypeScript/Node.js, Bash, or Go and ability to collaborate across teams.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Security Engineer</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/10b34bc8-bdad-4650-a0eb-f3e2cb8a27cf/application</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Protect BJAK's cloud environments, networks, compute platforms, and core infrastructure across AWS and GCP. Strengthen configuration, access controls, monitoring, resilience, and technology risk management.
-# **What You Will Build**
-- Design and maintain security controls across AWS and GCP infrastructure, networks, compute, storage, and platform services.
-- Review cloud configurations and infrastructure changes for misconfigurations, excessive permissions, exposure, and resilience risks.
-- Manage IAM, privileged access, network segmentation, encryption, key management, secrets, and secure connectivity.
-- Improve cloud security monitoring, logging, alerting, threat detection, and incident response.
-- Own cloud and infrastructure controls for SC TRM and BNM RMiT, including evidence, testing, remediation, and audit support.
-- Automate security checks and infrastructure guardrails using infrastructure-as-code and scripting tools.
-- Improve vulnerability management, backup, recovery, business continuity, and secure operations with engineering teams.
-# **What We Look For**
-- Degree in Computer Science, IT, Cybersecurity, or related field, or equivalent experience.
-- 3+ years in cloud, infrastructure, systems, or security engineering.
-- Experience implementing and owning SC TRM and BNM RMiT controls for cloud and technology infrastructure.
-- Hands-on experience securing AWS and GCP environments and cloud-native architectures.
-- Strong knowledge of IAM, networking, firewalls, encryption, key management, hardening, and cloud security posture management.
-- Experience with infrastructure as code, automation, vulnerability scanning, logging, and incident response.
-- Strong troubleshooting and communication skills across platform, application, and compliance teams.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Application Security Engineer AppSec</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/b25dfd2e-b875-4a5a-8c33-77e522cb0d2f/application</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Secure BJAK's web applications, APIs, and backend services, coordinating with mobile stakeholders on cross-platform risks. Embed security into design, development, testing, and release workflows.
-# What You Will Build
-- Perform security reviews, code reviews, and testing for web applications, APIs, and backend services.
-- Identify, prioritize, and help remediate injection, broken access control, authentication, and configuration vulnerabilities.
-- Integrate SAST, DAST, software composition analysis, and secrets scanning into CI/CD pipelines.
-- Conduct threat modeling and design reviews for features, APIs, third-party integrations, and major changes.
-- Coordinate with mobile engineers on cross-platform findings and backend controls protecting native iOS and Android clients.
-- Own application security implementation for SC TRM and BNM RMiT, including secure SDLC evidence, vulnerability management, testing, and audit remediation.
-- Provide secure coding guidance, track remediation, retest fixes, and improve developer security awareness.
-# What We Look For
-- Degree in Computer Science, Cybersecurity, or related discipline, or equivalent experience.
-- 3+ years in application security, penetration testing, or secure software development.
-- Experience implementing and owning SC TRM and BNM RMiT application security and secure SDLC requirements.
-- Strong understanding of OWASP Top 10, OWASP API Security Top 10, web vulnerabilities, API security, and secure design.
-- Hands-on experience with Burp Suite, OWASP ZAP, SAST, DAST, and dependency scanning tools.
-- Experience reviewing TypeScript/Node.js and Python services; familiarity with Swift, Kotlin, AWS, and GCP.
-- Able to work closely with developers, explain findings, and support remediation.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>bjakcareer</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/60def69d-14bc-44e9-af57-2f87fb3a827e/application</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>## **About BJAK**
-The original mission of BJAK is we believe people deserve smarter ways to plan, save and grow their money. This is the origin of our name.
-Started in 2019, we built the first mobile-first, insurance platform, enabling insurance to be accessible online by millions in the region. Today, its the leading insurance platform in Southeast Asia.
-Today, we are expanding ways to help people in the region — this includes spending, saving, investing, exchanging, travelling, and more. Our mission is help people get more from their money every day.
-We have teams working around the world, with over 20 nationalities from our offices and remotely, who truly enjoys their work. We are looking for the most talented and driven people we can find. We are looking for people who work for their passion, not counting hours. Who loves building great next-generation products, not status quo. Who cares about redefining how everyone around us can get the best financial applications, not for an exclusive few.
-If you're this person, we'd love to talk to you.
-# The Role
-Secure BJAK's AI-enabled products and agent workflows using third-party models. Focus on customer data shared with model providers, agent permissions, user data isolation, and prompt injection through uploaded documents and other untrusted content.
-# **What You Will Build**
-- Assess customer data sent to third-party model vendors, including minimization, vendor controls, retention, logging, and approved use.
-- Design controls limiting AI agent permissions, tools, actions, and system access using least privilege and explicit authorization.
-- Implement and test tenant and user data isolation across prompts, conversation history, retrieval, memory, and AI-connected services.
-- Threat model and test prompt injection and indirect injection through uploaded documents, retrieved content, links, and other untrusted inputs.
-- Partner with Product and Engineering on safe document ingestion, content handling, output validation, and approval for sensitive actions.
-- Support SC TRM and BNM RMiT for AI technology risks, including assessments, third-party oversight, control evidence, and remediation.
-- Build security tests, monitoring, and response procedures for AI misuse, data exposure, unauthorized actions, and vendor incidents.
-# **What We Look For**
-- Degree in Computer Science, Cybersecurity, AI, or related field, or equivalent experience.
-- 3+ years in application security, product security, security engineering, or AI system security.
-- Experience implementing or owning SC TRM and BNM RMiT controls, technology risk, or regulatory control evidence.
-- Understanding of third-party LLM integrations, model APIs, agent tools, RAG, and AI application architectures.
-- Knowledge of prompt injection, indirect injection, cross-user data leakage, excessive agent permissions, and vendor data disclosure risks.
-- Programming or scripting skills, preferably Python and TypeScript/Node.js, plus APIs and AWS or GCP.
-- Able to collaborate with Product, Legal, Compliance, Data, and Engineering on practical controls and risk communication.
-## **Language**
-English is our main working language across global teams. Strong English communication is required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Application Security</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Anywhere in the World</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Yes / Mentioned</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>weworkremotely</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>https://weworkremotely.com/remote-jobs/discord-senior-software-engineer-application-security</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Headquarters: San Francisco Bay Area or Remote Discord has a highly engaged community of millions of daily active users who use the platform for many different reasons, but there’s one thing that nearly everyone does: play video games. Discord plays a uniquely important role in the future of gaming, and we are focused on making it easier and more fun for people to hang out before, during, and after playing games. Discord empowers people to create spaces where they can find a sense of belonging in their lives. Millions of people trust Discord to keep their communications secure, private, and out of the hands of evildoers, so security and privacy are necessary to Discord's success. We are looking for a Senior Software Engineer to join our Application Security team and protect Discord’s users where it matters most, their accounts. If you are an engineer with a wealth of experience making the secure way the easy way, a deep sense of curiosity, and an endless desire to improve Discord, read on! This role is open to remote locations within the Pacific Standard Time Zone. What you'll do Join an engineering team designing and implementing full-stack, user-facing security solutions that protect hundreds of millions of Discord users. Lead full-stack work to strengthen session security and authentication for Discord’s users. Improve, operate, and maintain security-critical authentication services, owning their correctness and security. Partner with Product teams to drive adoption of stronger authentication and to ship user-facing account security tools. Identify and design solutions for emerging threats to user account security. Research and implement new security capabilities for the Discord platform, staying current on the authentication and session security landscape. Build security controls and tools that emphasize self-service, automation, and performance to help identify and mitigate account security flaws. Who you are You have 5+ years of experience securing production applications. You have 3+ years of experience programming in at least one general-purpose programming language (e.g., Python, Go, Java, or Rust). You have hands-on experience building and shipping production software, including security features, controls, frameworks, or guardrails. You have hands-on experience with authentication and account security, such as WebAuthn, passkeys, FIDO2, MFA, and session management. You are comfortable reasoning about the security of complex systems, even if they contain components you aren’t familiar with, and can give engineers clear, sound guidance on secure design and implementation. You have experience leading security projects with a cross-functional group. You have experience building or hardening client applications, such as desktop or native mobile apps. You have experience operating in cloud-based environments (we use Google Cloud, but experience with other platforms is okay too). Bonus points Experience programming in at least one systems programming language (e.g. C, C++). Experience developing, operating, and debugging production systems. Familiarity with common application vulnerabilities on the platforms Discord ships on (that's all of them). Candidates must reside in or be willing to relocate to the San Francisco Bay Area (Alameda, Contra Costa, Marin, Napa, San Francisco, San Mateo, Santa Clara, Solano, and Sonoma counties). Relocation assistance may be available. The US base salary range for this full-time position is $196,000 to $245,000 + equity + benefits. Our salary ranges are determined by role and level. Within the range, individual pay is determined by additional factors, including job-related skills, experience, and relevant education or training. Please note that the compensation details listed in US role postings reflect the base salary only, and do not include equity, or benefits. Why Discord? Discord plays a uniquely important role in the future of gaming. We're a multiplatform, multigenerational and multiplayer platform that helps people deepen their friendships around games and shared interests, and helps developers build and grow their businesses. We believe games give us a way to have fun with our favorite people, whether listening to music together or grinding in competitive matches for diamond rank. Join us in our mission! Your future is just a click away! Discord is committed to inclusion and providing reasonable accommodations during the interview process. We want you to feel set up for success, so if you are in need of reasonable accommodations, please let your recruiter know. Please see our Applicant and Candidate Privacy Policy for details regarding Discord’s collection and usage of personal information relating to the application and recruitment process by clicking HERE. To apply: &lt;https://weworkremotely.com/remote-jobs/discord-senior-software-engineer-application-security&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>jobgether</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Offensive Security Engineer (Red Team)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/jobgether/90a33ab2-9fb2-4a33-a247-18d421e36ee5/apply</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for an Offensive Security Engineer (Red Team) based in Canada.**
-This remote role sits within a Product Security team and focuses on strengthening security through hands-on offensive testing and adversary emulation. You will assess modern cloud environments, infrastructure, identity architectures, CI/CD pipelines, containers, and cloud-native services. The role combines technical investigation with close collaboration across security, engineering, blue team, and detection functions. You will simulate realistic attacker behavior to uncover vulnerabilities, validate security controls, and identify practical attack paths. Your findings will help engineering teams prioritize remediation and improve organizational resilience. The position is suited to an experienced offensive security professional who enjoys exploring emerging cloud attack techniques and translating complex findings into actionable improvements.
-### Accountabilities:
-- Plan and execute red team operations, adversary simulations, penetration tests, and targeted offensive security assessments across cloud environments.
-- Evaluate the security posture of cloud infrastructure, identity architectures, CI/CD pipelines, containerized workloads, and cloud-native services.
-- Identify and validate realistic attack paths involving IAM misconfigurations, excessive privileges, exposed secrets, metadata services, insecure automation, and cloud configuration weaknesses.
-- Conduct security assessments designed to replicate relevant attacker behaviors and techniques in modern enterprise environments.
-- Validate the effectiveness of security monitoring and detection capabilities by testing logging, alerting, monitoring, and incident-response processes.
-- Partner with blue team and detection engineering functions to identify gaps in defensive coverage and improve detection and response capabilities.
-- Document vulnerabilities, attack paths, and security weaknesses in concise, actionable reports.
-- Work with software and engineering teams to communicate findings, support remediation efforts, and help reduce security risk.
-- Track emerging attacker tactics, cloud exploitation techniques, and new abuse paths that could affect cloud-native environments.
-- Map offensive security findings and adversary behaviors to established frameworks such as MITRE ATT&amp;CK.
-- Serve as a trusted security partner to engineering teams, helping strengthen security practices through practical offensive expertise.
-## Requirements:
-- 5+ years of professional experience in offensive security, red teaming, penetration testing, detection validation, or closely related security disciplines.
-- Strong understanding of adversary tactics, techniques, and procedures, with the ability to apply them to realistic security assessments.
-- Experience conducting offensive security assessments in cloud environments and evaluating modern cloud infrastructure and services.
-- Practical understanding of cloud identity and access management, CI/CD security, containers, secrets management, and cloud-native architectures.
-- Ability to identify and validate complex attack paths involving IAM weaknesses, overprivileged identities, exposed credentials or secrets, metadata services, insecure automation, and configuration issues.
-- Experience evaluating security monitoring and detection capabilities through adversary simulation or detection-validation exercises.
-- Ability to map findings and attacker behavior to frameworks such as MITRE ATT&amp;CK.
-- Strong written and verbal communication skills, including the ability to explain complex technical security issues to engineering teams and other stakeholders.
-- Ability to produce concise, actionable security reports that clearly communicate technical findings, business relevance, and remediation considerations.
-- Strong analytical and investigative mindset with a willingness to explore emerging attack techniques and unfamiliar technologies.
-- Relevant industry certifications such as OSCP, OSEP, GXPN, GPEN, or recognized cloud security certifications are valued.
-- Ability to work effectively in a remote environment and collaborate across technical and security teams.
-- Authorization to work in Canada and meet applicable requirements for accessing controlled technologies and commodities.
-## Benefits:
-- Competitive annual compensation range of **CAD $146,000–$190,000**, depending on location and factors such as education, professional experience, and certifications.
-- Potential eligibility for restricted stock units as part of total compensation.
-- Health and pharmacy benefits.
-- Optical and dental coverage.
-- Paid time off and sick time off.
-- Short-term and long-term disability coverage.
-- Life insurance.
-- Employer-supported retirement contributions, subject to eligibility.
-- Fully remote work arrangement within Canada.
-- Opportunity to work on cloud security, adversary simulation, and modern offensive security challenges.
-- Collaborative environment involving Product Security, engineering, blue team, and detection engineering professionals.
-- Opportunities to develop expertise in emerging attacker techniques and cloud exploitation trends.
-- Inclusive workplace committed to diverse backgrounds, experiences, abilities, and perspectives.
-- Potential for occasional in-person interviews or new-hire training sessions at global offices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>jobgether</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Principal Security Architect</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/jobgether/8d63aedc-5fcc-49f7-b836-395e40e10f1d/apply</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Principal Security Architect based in Canada.**
-This role is focused on shaping security architecture across products, cloud infrastructure, integrations, and emerging technologies. You will evaluate complex security designs, conduct code and vulnerability reviews, and help ensure enterprise-grade protection throughout the product lifecycle. The position combines deep technical expertise with hands-on security engineering and strategic architectural guidance. You will work across AWS, web and browser technologies, cryptography, operating systems, networks, and third-party technologies. You will also collaborate with customers, compliance teams, sales teams, and engineering stakeholders on complex security topics. The role provides an opportunity to influence product security, develop innovative security capabilities, and contribute to technical thought leadership.
-### Accountabilities:
-- Conduct security design reviews covering broad product architecture, individual product changes, cloud infrastructure, and AWS integrations.
-- Perform security-focused code reviews and identify potential weaknesses, vulnerabilities, and secure coding improvements.
-- Design and document processes for integrating and deploying enterprise Hardware Security Modules and key management solutions.
-- Assess third-party software, SaaS providers, and external technologies from a security and architectural perspective.
-- Review the design and implementation of integrations with third-party software and SaaS platforms, identifying security risks and recommending appropriate controls.
-- Oversee internal and external security assessments and coordinate technical follow-up on identified findings.
-- Perform in-depth analysis of vulnerabilities, assessing the potential impact of both third-party and product-specific security issues.
-- Monitor emerging technologies, web standards, and browser behavior changes and assess their potential impact on products and security architecture.
-- Support compliance and sales teams with technical security expertise related to regulations, customer requirements, RFPs, and security questionnaires.
-- Participate in detailed technical discussions with customers regarding security architecture, controls, vulnerabilities, and product capabilities.
-- Contribute to patent development through technical invention documentation, review, and collaboration with relevant teams.
-- Create and review technical materials for external audiences, including security blogs, white papers, presentations, and other technical content.
-- Collaborate with engineering and R&amp;D teams to develop innovative product features and capabilities within the security domain.
-- Maintain a strong awareness of evolving cybersecurity threats, technologies, standards, and best practices.
-## Requirements:
-- Advanced knowledge of applied cryptography, including technologies such as Hardware Security Modules (HSMs) and Trusted Platform Modules (TPMs).
-- Strong understanding of the complete key management lifecycle, including key generation, storage, distribution, backup, rotation, revocation, and destruction.
-- Deep expertise in web and browser security technologies, including the Same-Origin Policy, XSS, CSRF, HTTP security headers, browser architecture, and JavaScript engine internals.
-- Thorough understanding of networking and operating-system fundamentals, including TCP, HTTP, TLS, DNS, firewalls, WAFs, discretionary and mandatory access controls, and sandboxing.
-- Strong AWS security experience, including IAM, AWS Organizations, EC2, VPC, and related cloud security capabilities.
-- Familiarity with static and dynamic application analysis concepts, methodologies, and tools.
-- Advanced proficiency in C/C++, particularly secure coding practices, along with strong experience in at least one additional programming language, preferably Python or JavaScript.
-- Demonstrated ability to investigate complex technical security problems hands-on and take ownership of finding practical solutions.
-- Strong architectural thinking and the ability to evaluate security implications across products, infrastructure, integrations, and emerging technologies.
-- Excellent communication skills and the ability to explain complex security concepts to engineering teams, customers, executives, compliance teams, and other non-specialist audiences.
-- Ability to collaborate effectively across technical and business functions and contribute to high-impact security decisions.
-- Master's degree in computer science, engineering, cybersecurity, or a related discipline, or equivalent experience; a PhD is preferred.
-- A proactive, ownership-oriented approach with a willingness to work hands-on when required to solve challenging security problems.
-## Benefits:
-- Competitive base salary of approximately **CAD $158,000–$263,000** annually.
-- Actual compensation may vary based on factors such as experience, knowledge, skills, abilities, and location.
-- Eligibility for stock-based compensation grants based on company and individual performance.
-- Remote-first work environment for employees based in Canada.
-- Opportunity to work on complex security challenges spanning cloud infrastructure, browser technologies, cryptography, networking, and emerging technologies.
-- Exposure to enterprise customers and large-scale security environments.
-- Opportunities to contribute to security innovation, technical publications, patents, and new product capabilities.
-- Collaborative environment emphasizing ownership, direct communication, cross-functional teamwork, technical excellence, and customer-focused outcomes.
-- Equal opportunity employment environment focused on merit, competence, performance, and business needs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>sig</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Technical Project Manager - Security Engineering</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Dublin, UNAVAILABLE, IE</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>icims</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>https://careers-sig.icims.com/jobs/11567/technical-project-manager---security-engineering/job?in_iframe=1</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>We are seeking a Senior Technical Project Manager to lead the delivery of security engineering projects for SIG's Dublin based Security team, which operates as part of a global infrastructure organisation supporting a fast moving, business critical trading environment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>jobgether</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/jobgether/4708fda8-793e-441e-bde8-f8cc4adac77e/apply</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Senior Software Engineer - Infrastructure Security based in Canada.**
-This is a senior security engineering role focused on protecting cloud infrastructure, systems, and products at scale.  
-You’ll partner with engineering teams to embed security into architecture, development workflows, and operational practices.  
-The role combines hands-on software engineering with cloud infrastructure security, automation, threat modeling, and incident response.  
-You’ll help strengthen AWS and Kubernetes environments while building tools and controls that identify and mitigate security risks.  
-You’ll also influence secure development practices and mentor engineering teams on building resilient applications and infrastructure.  
-The position offers broad technical scope within a remote-first, collaborative engineering environment that values learning and experimentation.  
-You’ll have significant ownership, balancing deep technical investigation with pragmatic solutions and clear prioritization.
-### Accountabilities:
-- Partner with engineering teams to review cloud and compute architecture changes and identify security implications.
-- Develop threat models for cloud and compute platforms to identify risks and inform appropriate security controls.
-- Build, adopt, and maintain tools that monitor and harden cloud infrastructure and operating systems.
-- Develop security logging and monitoring pipelines and support intrusion detection capabilities.
-- Apply AWS and Kubernetes security expertise to guide remediation efforts and shape the security control roadmap.
-- Define and implement security policies, monitor compliance, and help ensure infrastructure remains aligned with established controls.
-- Develop automation and security tooling for threat detection, incident containment, network access management, and other security requirements.
-- Integrate security practices into engineering workflows and CI/CD environments to identify vulnerabilities earlier.
-- Conduct initial security incident triage, assessing scope, urgency, and potential impact, and participate in incident response activities.
-- Contribute to secure coding practices, technical standards, and knowledge sharing across engineering teams.
-### Requirements:
-- Strong experience as a software engineer, with deep technical capability in at least one infrastructure or security domain.
-- Hands-on experience securing large-scale cloud environments, particularly AWS.
-- Strong understanding of infrastructure-as-code and tools such as Terraform or CloudFormation.
-- Knowledge of AWS IAM policies, network segmentation, VPC design, cloud-native monitoring, and logging.
-- Experience identifying cloud misconfigurations, assessing security risks, and driving remediation.
-- Experience with security automation and integrating security tooling into CI/CD pipelines.
-- Familiarity with SAST, DAST, dependency scanning, and secure software development practices.
-- Strong Linux and systems security knowledge, including container security, POSIX capabilities, SECCOMP, and Linux Security Modules.
-- Kubernetes security experience is valuable, as is familiarity with serverless architectures, OSQuery, or eBPF.
-- Ability to balance technical detail with effective prioritization and right-size solutions for the problem at hand.
-- Strong ownership, problem-solving, time management, communication, and ability to navigate complex technical challenges.
-- Product security experience is a plus, including knowledge of secure web applications, APIs, OWASP Top 10, XSS, CSRF, and SQL injection.
-- Availability for meetings and impromptu communication during coordination hours, Monday–Friday, 9:00 AM–3:00 PM Pacific Time.
-### Benefits:
-- For Toronto and Vancouver-based candidates: **$221,209–$256,433 CAD + equity + benefits**.
-- For candidates in other Canadian locations: **$206,461–$239,337 CAD + equity + benefits**.
-- Flexible equity program in eligible countries, allowing a portion of equity compensation to be taken as cash.
-- Medical, dental, and vision coverage.
-- Equity refreshers.
-- Remote work reimbursement.
-- Paid time off.
-- Employee assistance programs.
-- Fully remote work within eligible locations in Canada.
-- Opportunity to work across cloud infrastructure, systems security, automation, and product security.
-- Broad technical ownership and collaboration with engineering teams on security-critical initiatives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>FOP EXPERTS CONSEILS INC.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>information technology (IT) security architect</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Brossard (QC)</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>$60,000.00 annually</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>jobbankca</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.jobbank.gc.ca/jobsearch/jobposting/50391601</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AppSec Engineer</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/Nqf4hFJPqa</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>AppSec Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AppSec Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $80,000–$100,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are looking for an AppSec Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt; Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Security Engineer</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/mL68pofz6c</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Artificial Intelligence Security Engineer Location: 1 00% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $80,000–$105,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt;. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt;. Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>creditsesame</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>https://creditsesame.applytojob.com/apply/jobs/details/wTckD6V60E</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Credit Sesame is a leading financial wellness platform dedicated to helping consumers achieve better financial health through cutting-edge technology and data-driven solutions. With a decade of credit expertise and a proven track record of serving over 18 million users, Credit Sesame leverages AI and advanced analytics to empower individuals to better understand and manage their credit. Our recently launched Sesame Platform extends our mission by providing financial institutions with a turnkey AI-powered credit intelligence solution. As our security engineer, you'll own security end-to-end for our platform — standing up open-source tooling, writing your own scripts and automation, and running assessments. You'll... Run security reviews for new tools, vendors, and projects — data handling, AI usage, DPAs, PII, authentication/authorization, and third-party security reports (SOC 2, PCI, ISO, pentest results); Own access and infrastructure security — IAM least-privilege reviews, S3/database access controls, environment segregation, service-to-service authentication, and network configuration audits (VPC flow logs, inbound/outbound rules); Run vulnerability management across cloud and endpoints, and manage IDS/IPS (e.g., Palo Alto Panorama, AWS WAF) and EDR/MDR tooling; Lead security incident response end to end — triage, investigate, contain, document, and build the runbooks as you go; Implement and maintain the technical controls supporting our PCI DSS and SOC 2 / ISO 27001 compliance programs, including internal audits, risk metrics, and disaster recovery planning; Partner with DevOps/IT on patch management and secure infrastructure defaults, and present tooling and risk recommendations to engineering leadership; Build our in-house AppSec scanning program — evaluate and pilot SAST/SCA/IaC tooling (Semgrep, Trivy, Upwind), integrate into GitLab CI and Jenkins, define severity-based remediation SLAs, and drive rollout across services; Build internal security tooling and automation — custom scripts and integrations (Python/boto3, APIs) that pull data from tools without native integrations into shared dashboards and reports; Build and tune detection pipelines — for example, feeding traffic/bot-protection alerts (Datadome) into our log platform (ELK/Kibana) and writing rules that catch real attack patterns; Threat-model and pentest our AI/LLM systems — scope risks like prompt injection and data exfiltration through MCP servers, coordinate external pentests where needed, and drive remediation; Maintain security policies and practices and drive training and adoption throughout the company. You're a great fit because... You have 7+ years of hands-on security engineering experience across application security, cloud security, and network/penetration testing — not just one lane; You've driven tooling or architecture decisions independently (evaluated options, made the call, defended it to leadership); You're self-directed, pragmatic, and ruthless about prioritization; You've built production automation from scratch — API integrations, custom collectors, or internal tooling — not just one-off scripts; You have hands-on experience deploying and running OSS security tools — Burp Suite Community/OWASP ZAP, Nmap, Nuclei, Metasploit, Semgrep, Trivy, Wazuh/OSSEC, ELK/Kibana, Prowler/ScoutSuite, HashiCorp Vault, or similar; You have solid AWS security experience; You have working knowledge of PCI DSS, SOC 2, and ISO 27001 — enough to implement controls and support audits; You're curious about emerging security domains and comfortable threat-modeling systems (like AI/LLM applications) that don't have an established playbook yet; You're an excellent communicator who can translate cost/coverage tradeoffs and technical risk for both engineers and executives; Bonus: OSCP, GPEN, or similar certifications; bug bounty experience; prior experience at a startup; or experience securing LLM/AI-based systems; BS in Computer Science or related field, or equivalent hands-on experience. You'll love it here because... You’ll have equity in a pre-IPO company backed by top VCs; We offer comprehensive medical, dental, and vision insurance; We offer a monthly home office stipend; We offer a professional development program to support your continued growth We offer flexible paid time off; We have 10 paid holidays and additional 6 Sesame Wellness days; We prize EQ and empathy, and have a culture that emphasizes total wellness, including work-life harmony. At Credit Sesame, base pay is one part of our total compensation package. The estimated pay range for this role is $170,000 - $215,000 with actual salary based on a candidate’s location, qualifications, skills, and experience. Additionally, this role is eligible to participate in Credit Sesame’s equity plans. We are open to hiring for this role in the following states where we are set up to hire employees: CA, CO, NC, NJ, NV, and TX. Artificial Intelligence Notice: Credit Sesame may use artificial intelligence tools to assist in reviewing application materials against job-related qualifications. These tools support the recruiting process and are not used to automatically select, reject, or evaluate candidates. Humans, including our recruiters and hiring managers, make all final decisions regarding interviews and offers. Applicants may contact People Operations to request a reasonable accommodation. By clicking "Submit Application" (or related call to action), you acknowledge that you have read the Credit Sesame Employment Privacy Notice and hereby freely and unambiguously give informed consent to the collection, processing, use, and storage of your personal information as described therein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>beyondtrust</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Sr Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Remote Canada</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/beyondtrust/jobs/8231788</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>BeyondTrust is a place where you can bring your purpose to life through the work that you do, creating a safer world through our cybersecurity SaaS portfolio.
-Our culture of flexibility, trust, and continual learning means you will be recognized for your growth, and for the impact you make on our success. You will be surrounded by people who challenge, support, and inspire you to be the best version of yourself.
-The Role
-We're hiring a Senior Product Security Engineer to build and operate the modern security tooling pipeline that underpins everything our Product Security team does. You'll establish and maintain the SDLC security infrastructure using Claude Code Security, Codex Security, GitHub Advanced Security, Wiz CLI, and integrated tooling that gives engineering teams fast, reliable security feedback on every commit, every PR, and every release. You bring an automation-first mindset. When you see a manual security review process, your instinct is to build a workflow that handles the repeatable parts and surfaces only the decisions that need a human. You'll design and operate product security reviews with human-in-the-loop checkpoints, ensuring coverage scales with the engineering organization without becoming a bottleneck.
-You'll be a trusted partner to engineers. That means your tooling works reliably, your findings are accurate, your integrations respect their workflow, and when something breaks or creates noise, you fix it fast. You'll partner closely with Security Testers, Architects, the TPM, and engineering teams across the product portfolio. You'll also support product incident response when security issues arise, working alongside the broader Product Security team to investigate, scope, and remediate.
-What You’ll Do
-- **SDLC Security Pipeline:** Build and maintain the product security tooling pipeline integrated across the software development lifecycle. Implement and tune Claude Code Security, Codex Security, GitHub Advanced Security (code scanning, secret scanning, Dependabot), and Wiz CLI across repositories and CI/CD pipelines. Own the configuration, policy enforcement, and continuous improvement of these tools so engineering teams get accurate, actionable security feedback at the speed of development.
-- **Automated Security Reviews Design:** and operate automated product security review workflows with human-in-the-loop checkpoints. Use Claude and LLM platforms to automate initial review triage, risk classification, and recommendation generation, escalating to Security Architects or senior engineers for decisions that require judgment. The goal is every change gets appropriate security review coverage without manual review becoming the bottleneck.
-- **Tooling Integration &amp; Engineering Experience:** Ensure security tooling integrates cleanly into engineering workflows: GitHub PRs, CI/CD pipelines, IDE plugins, and developer dashboards. Reduce false positives, tune rulesets to the product's actual risk profile, and build feedback loops so findings improve over time. You own the engineering experience of security tooling. When a developer interacts with a security gate, it should be clear, fast, and useful.
-- **AI-First Automation:** Leverage Claude Code Security, Codex Security, and LLM platforms to build automation that scales security engineering. This includes automated code review triage, vulnerability pattern detection, fix suggestion generation, policy-as-code enforcement, and security review summarization. Contribute reusable prompts, skills, and plugins back to the Product Security team's shared library.
-- **Product Incident Response Support:** Support product incident response alongside the Product Security team. Help investigate security incidents affecting products, scope impact, coordinate with engineering on emergency fixes, and contribute to root cause analysis and post-incident improvements.
-- **Cross-Team Partnership:** Work closely with Security Testers to ensure scanning and automated tooling feed validated findings into their workflow. Partner with Architects on translating secure design standards into enforceable pipeline policies. Coordinate with the TPM on tracking and reporting for tooling-generated findings. Be the go-to person for engineering teams on security tooling questions, configuration, and troubleshooting.
-What You’ll Bring
-- 4+ years in Application Security, Product Security, DevSecOps, or Security Engineering with hands-on experience building and operating security tooling in CI/CD pipelines
-- Experience implementing and tuning SAST, DAST, SCA, and secret scanning tools in GitHub-integrated environments (GitHub Advanced Security, CodeQL, Dependabot, or equivalent)
-- Hands-on experience with AI-powered security tooling such as Claude Code Security, Codex Security, or similar LLM-based code analysis platforms
-- Strong understanding of CI/CD pipeline architecture and how security controls integrate without disrupting developer velocity
-- Experience building automation workflows: scripting, pipeline configuration, policy-as-code, webhook integrations, and workflow orchestration
-- Familiarity with container security scanning tools (Wiz CLI, Trivy, Snyk Container, or equivalent) and cloud security fundamentals (AWS preferred)
-- You understand common vulnerability classes well enough to tune tooling, triage findings, and have credible conversations with engineers about severity and remediation
-- Strong collaboration skills. You'll work across Security Testers, Architects, TPM, and engineering teams daily and need to communicate effectively with all of them
-- Automation-first mindset. You default to building repeatable, scalable workflows and reach for manual processes only when automation genuinely falls short
-Nice To Have
-- Experience with GitHub Advanced Security at scale: CodeQL custom queries, secret scanning custom patterns, and organization-wide rollout
-- Background operating Wiz CLI or similar cloud/container security scanning integrated into CI/CD
-- Experience supporting product incident response or security incident investigation
-- Familiarity with policy-as-code frameworks (OPA/Rego, Kyverno, or similar)
-- Background in securing endpoint technologies, identity systems, or enterprise security platforms
-- Experience building developer enablement programs, security documentation, or self-service security tooling
-- Cloud security experience across AWS, Azure, or Kubernetes environments
-How We'll Measure Success
-- Security tooling coverage across repositories and pipelines is comprehensive and consistently maintained
-- Automated security review workflows handle the majority of reviews with human-in-the-loop escalation for high-risk changes
-- False positive rates decrease over time through tuning and feedback loops you build
-- Engineering teams experience security tooling as fast, accurate, and integrated into their existing workflow
-- Reusable automation, prompts, and plugins you build are adopted across the Product Security team
-- You're the person engineering teams reach out to for security tooling support because they trust your responsiveness and expertise
-Better Together
-Diversity. Inclusion. They’re more than just words for us. They are the guiding values of how we build our teams, cultivate leaders, and create a culture where people feel connected.
-We take care of our employees so they can take care of our customers. Customers who come from all walks of life just like us. We hire incredible people from diverse backgrounds because when we are different together, we are stronger together.
-About Us
-BeyondTrust is the global identity security leader protecting Paths to Privilege™. Our identity-centric approach goes beyond securing privileges and access, empowering organizations with the most effective solution to manage the entire identity attack surface and neutralize threats, whether from external attacks or insiders.
-BeyondTrust is leading the charge in transforming identity security to prevent breaches and limit the blast radius of attacks, while creating a superior customer experience and operational efficiencies. We are trusted by 20,000 customers, including 75 of the Fortune 100, and our global ecosystem of partners.
-Learn more at [&lt;www.beyondtrust.com&gt;](http://www.beyondtrust.com/).
-#LI-BS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>menlosecurity</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Principal Security Architect</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Canada - Distributed</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/menlosecurity/35e73f66-53ed-436f-a5ff-c45177952fae/application</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Menlo Security is the leader in Browser Security for human and agentic workforces. Our mission is to enable humans and agents to connect, communicate, and collaborate securely, without compromise. The Menlo Browser Security Platform protects organizations from cyberattacks by stopping threats across the web, documents, and email before they reach the user. With Menlo Agent Runtime Security (MARS), that protection now extends to the AI agents working alongside every employee. Menlo Security is trusted by major global businesses, including Fortune 500 companies and government agencies, to protect their most valuable asset, their data, and is backed by top-tier investors.
-**Responsibilities**
-- Security Design reviews, both broad product architecture and more minor changes. Includes integration/interaction with Cloud infrastructure (AWS).Security Code reviews.
-- Designing and documenting the process of integration and deployment of enterprise Hardware Security Module and Key Management.
-- Conducting assessments of third party software / SaaS offerings.
-- Conducting assessments of integration with third party software / SaaS, both design and actual implementation.
-- Overseeing internal and third party security assessments.
-- In-depth assessment of vulnerability impact, both third party vulnerabilities and product vulnerabilities.
-- Keeping abreast of and assessing product impact of upcoming technologies (e.g., new web standard or browser behavior changes).
-- Assisting compliance and sales teams on technical aspects of regulations / RFPs
-- Participating in in-depth technical conversations with customers around security topics.
-- Assisting with patent writing and review.
-- Creating and reviewing technical material meant for external consumption, both written (blogs, white papers...) and oral (presentations…).
-- Developing novel product features in the security space.
-### **Requirements**
-- Advanced knowledge of applied cryptography (e.g. HSMs, TPMs) and Key Management Life Cycle (e.g. Key Generation, Storage, Distribution, Backup, Rotation, Revocation, Destruction)
-- Deep knowledge of web and browser technologies: Same Origin Policy, XSS, CSRF, HTTP security headers, browser architecture, JavaScript engine internals.
-- Thorough understanding of network and OS fundamentals: TCP, HTTP, TLS, DNS, Firewalls, WAFs…; DAC/MAC, Sandboxing.
-- AWS security experience: IAM, Organizations, EC2, VPC...
-- Familiarity with static and dynamic analysis concepts and tools.
-- Advanced knowledge of C/C++, with focus on secure coding, and at least one other language (Python or JS preferred).
-- Willingness to get your hands dirty to get things done.
-- Minimum MSc/MEng or equivalent, PhD preferred.
-**Our Compensation and Benefits**
-At Menlo Security, Base Salary is one part of our competitive total compensation and benefits package and is determined using a salary range. The base salary range for this role is 158,000 CAD - 263,000 CAD.
-In accordance with Canadian law, the range provided is Menlo Security’s reasonable estimate of the base compensation for this role. The actual amount may be higher or lower, based on non-discriminatory factors such as experience, knowledge, skills, abilities, and location. All employees may be eligible to become Menlo Security shareholders through eligibility for stock-based compensation grants, which are awarded to employees based on company and individual performance.
-Menlo Security does not accept unsolicited resumes from search firm recruiters. Fees will not be paid in the event a candidate submitted by a recruiter without an agreement in place is hired; such resumes will be deemed the sole property of Menlo Security.
-Menlo Security is an equal opportunity employer. All aspects of employment will be based on merit, competence, performance, and business needs. We do not discriminate on the basis of race, color, religion, marital status, age, national origin, ancestry, physical or mental disability, medical condition, pregnancy, genetic information, gender, sexual orientation, gender identity or expression, veteran status, or any other status protected under federal, state, or local law.
-MSGL-I4
-Follow us on [LinkedIn](https://www.linkedin.com/company/menlo-security/)!
-**Why Menlo?**
-At Menlo, we don't settle for the status quo — in our technology or our culture. How we think and act is just as important as what we build. Our culture is defined by five core mindsets: **Proactive Leadership**, **Straight Talk**, **United Impact**, **Elevated Talent**, and **Customer-Compelled**. We take ownership and drive outcomes without waiting to be told. We communicate directly and seek hard truths. We break down silos and win together. We hold a high bar for ourselves and the people around us. And we treat every customer interaction as mission-critical. If you're someone who sees it, owns it, solves it, and does it — you'll thrive here.
-**All qualified applicants will receive consideration for employment without regard to race, sex, color, religion, sexual orientation, gender identity, national origin, protected veteran status, or on the basis of disability**.
-***TO ALL AGENCIES: Please, no phone calls or emails to any employee of Menlo Security outside of the Talent organization. Menlo Security’s policy is to only accept resumes from agencies via Ashby (ATS). Agencies must have a valid services agreement executed and must have been assigned by the Talent team to a specific requisition. Any resume submitted outside of this process will be deemed the sole property of Menlo Security. In the event a candidate submitted outside of this policy is hired, no fee or payment will be paid.***</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>oddball</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/oddball/jobs/8007048003</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Oddball believes that the best products are built when companies understand and value the things they are working on. We value learning and growth and the ability to make a big impact at a small company. We believe that we can make big changes happen and improve the daily lives of millions of people by bringing quality software to the federal space.
-We're looking for a **Security Engineer** to join our SEC team, working alongside our DevSecOps engineers to harden our cloud environment, maintain our ATO, and actively drive down the program's POAM backlog.
-**What you'll be doing:**
-- Deploy and automate **CI/CD pipelines** and establish **IaC** using modern **DevSecOps** techniques including serverless and **Zero Trust** patterns
-- Own the **POAM** process end to end — develop a plan of attack with target dates, track progress in real time, and close findings proactively
-- Assess incoming security findings, identify duplicates and dependencies, and develop LOEs for remediation
-- Conduct **Security Impact Analyses (SIAs)** to achieve and maintain **ATO**
-- Implement data tagging and sensitivity management practices to reduce the SEC's ATO management burden
-- Engage directly with engineers and external stakeholders to drive remediation forward
-- Maintain a live dashboard and tracker for all security findings and POAM status
-**What you’ll bring:**
-- Hands-on experience remediating **POAMs** and navigating the federal **ATO** process
-- Proficiency with **AWS** environments and cloud security practices
-- Experience with **CI/CD pipelines**, **CloudFormation**, and infrastructure as code
-- Familiarity with **Zero Trust** principles and federal cybersecurity frameworks including **FISMA** and **NIST 800-53**
-- Strong organizational skills with the ability to manage multiple findings, timelines, and stakeholders simultaneously
-- Comfortable engaging directly with engineers and external stakeholders to move remediation forward
-- Experience with **Docker** and containerized environments is a plus
-- Thrives in a remote, collaborative **Agile** environment and genuinely enjoys working closely with a cross-functional team
-- Communicates clearly and openly, whether updating a tracker or presenting findings to leadership
-- Performs other related duties as assigned
-**Requirements:**
-- Applicants must be authorized to work in the United States. In alignment with federal contract requirements, certain roles may also require U.S. citizenship and the ability to obtain and maintain a federal background investigation and/or a security clearance.
-**Education:**
-- Bachelor’s degree
-**Benefits:**
-- Fully remote
-- Annual stipend
-- Comprehensive Benefits Package
-- Company Match 401(k) plan
-- Flexible PTO, Paid Holidays
-Oddball is an Equal Opportunity Employer and does not discriminate against applicants based on race, religion, color, disability, medical condition, legally protected genetic information, national origin, gender, sexual orientation, marital status, gender identity or expression, sex (including pregnancy, childbirth or related medical conditions), age, veteran status or other legally protected characteristics. Any applicant with a mental or physical disability who requires an accommodation during the application process should contact an Oddball HR representative to request such an accommodation by emailing [hello@Oddball.io](mailto:hello@Oddball.io)
-**Compensation:**
-At Oddball, it’s important each employee is compensated competitively and fairly. In alignment with state legal requirements. A range for the included position is listed below. Be advised, actual offer details are determined by job category, job location, and candidate skill level.
-United States Wage Range: $120,000 – $155,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>xai</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Infrastructure Security Engineer - London</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Dublin, Ireland; London, England, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5241280007</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>SpaceXAI’s mission is to create AI systems that can accurately understand the universe and aid humanity in its pursuit of knowledge. Our team is small, highly motivated, and focused on engineering excellence. This organization is for individuals who appreciate challenging themselves and thrive on curiosity. We operate with a flat organizational structure. All employees are expected to be hands-on and to contribute directly to the company’s mission. Leadership is given to those who show initiative and consistently deliver excellence. Work ethic and strong prioritization skills are important. All employees are expected to have strong communication skills. They should be able to concisely and accurately share knowledge with their teammates.
-### ABOUT THE ROLE:
-We are seeking a talented and motivated Infrastructure Security Engineer to join our security team. In this role, you will design, implement, and maintain secure cloud and hybrid infrastructure, and ensure the integrity of our cloud-native applications.
-This role focuses on securing critical infrastructure across multi-cloud and hybrid environments, with work that may span platforms such as SpaceXAI, X Social, X Money and related systems. You’ll operate with an automation-first mindset: building secure foundations, hardening platforms at scale, and partnering closely with engineering teams so security is embedded in how we build and run systems—not bolted on after the fact.
-### RESPONSIBILITIES:
-**Cloud &amp; infrastructure security**
-- Design and implement secure cloud architectures across multiple cloud platforms (e.g., AWS, GCP, Azure)
-- Build and secure mission-critical applications in hybrid cloud and on-premises environments
-- Develop and maintain Infrastructure as Code (IaC) templates with embedded security controls
-- Assist with regular security assessments and audits of cloud infrastructure and services
-- Implement and manage cloud security tools and services (e.g., CSPM, CWPP, CASB)
-- Manage identities and roles effectively across cloud and hybrid environments
-- Monitor and remediate infrastructure to comply with regulations and best practices (e.g., PCI, NIST CSF, GDPR, HIPAA)
-**Platform, containers &amp; developer enablement**
-- Design and implement secure container standards and automation that enable frictionless developer workflows
-- Maintain Kubernetes security aligned with current best practices
-- Collaborate with development teams to ensure security best practices are integrated into CI/CD pipelines
-- Secure and enhance CI/CD pipelines; integrate and maintain code scanning platforms
-**Detection, operations &amp; tooling**
-- Monitor and respond to security events and incidents in cloud and hybrid environments
-- Maintain SIEM data pipelines needed for reliable alerting
-- Build, deploy, and maintain security operations infrastructure using Python, Terraform, and configuration management (e.g., Puppet)
-- Develop dashboards and alerts from security metrics
-- Develop and maintain cloud security policies, standards, and procedures
-- Own security projects end to end: identify issues and implement solutions
-- Stay current with emerging cloud security threats and mitigation strategies
-### BASIC QUALIFICATIONS:
-- Bachelor's degree in Computer Science, Cybersecurity, or a related field
-- 3–5 years of experience in cloud security, infrastructure security, or related roles
-- Strong understanding of cloud security principles, compliance frameworks, and best practices
-- Proficiency in at least one cloud platform (AWS, GCP, or Azure) and associated security services
-- Proven experience securing hybrid AWS/on-premises (or multi-cloud) environments, including IAM and overall security posture
-- Experience with Infrastructure as Code tools (e.g., Terraform, CloudFormation)
-- Familiarity with containerization technologies and their security implications
-- Knowledge of network security concepts and protocols
-- Experience with scripting languages (e.g., Python, Bash) for automation and tool development
-- Proactive mindset with strong ownership, critical thinking, and problem-solving skills
-- Located in the EU/UK or willing to relocate
-### PREFERRED SKILLS AND EXPERIENCE:
-- Relevant security certifications (e.g., CCSP, CSSK, AWS Security Specialty)
-- Deep expertise in Kubernetes and container security
-- Experience with multi-cloud environments and cloud-to-cloud security
-- Knowledge of CI/CD best practices and tools
-- Familiarity with regulatory compliance requirements (e.g., GDPR, HIPAA, PCI DSS, NIST CSF)
-- Strong proficiency with Python, Terraform, and configuration management (e.g., Puppet)
-- Hands-on experience building GitHub Actions and workflows
-- Experience with observability and security operations tooling (e.g., Prometheus, Grafana, CloudWatch, Karma; SIEM platforms such as Wazuh)
-- Experience in building custom cloud security tools or integrations
-- Interest in leveraging AI for cloud security monitoring and automation
-- Contributions to open-source cloud security projects
-- Experience with securing AI/ML workloads in cloud environments
-- Experience in banking, money transmission, P2P payments, or similarly regulated financial platforms.
-*SpaceXAI is an equal opportunity employer. For details on data processing, view our* *[Recruitment Privacy Notice](https://x.ai/legal/recruitment-privacy-notice).*</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>patreon</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>$170K – $255.5K • Offers Equity • Multiple Ranges</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/patreon/95a84e99-4405-4cd1-ade4-13c17dc99293/application</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Patreon is a media and community platform where over 300,000 creators give their biggest fans access to exclusive work and experiences. We offer creators a variety of ways to engage with their fans and build a lasting business including: paid memberships, free memberships, community chats, live video, and selling to fans directly with one-time purchases.
-Ultimately our goal is simple: fund the creative class. And we're leaders in that space, with:
-- $10 billion+ generated by creators since Patreon's inception
-- 100 million+ free memberships for fans who may not be ready to pay just yet, and
-- 25 million+ paid memberships on Patreon today.
-We're continuing to invest heavily in building the best creator platform with the best team in the creator economy and are looking for a **Security Engineer** to support our mission.
-*This role is **Fully Remote*** (US only)*, or can be based in **New York or San Francisco** (where it is open to those who are able to be in-office 3 days per week on a hybrid work model.)*
-**About the Team**
-Patreon’s security team works to protect Patreon creators and their fans. The team deals with all facets of Patreon’s security, including application security, infrastructure security, and internal/corporate security. We’re a small but effective team. We write code to solve security problems and work closely with our partners across the engineering organization. We also understand the importance of balancing security risks against business needs. We strive for honest and effective communication and focus on pragmatically reducing risk over checking boxes. The security team is part of Patreon’s Risk Engineering org, which also includes our Safety Engineering and Identity and Access teams. Collectively, the risk org tackles a range of problems including content moderation, internal tooling, identity verification, access control, and account security.
-**About the Role**
-In this role, you’ll be a member of our Security team. You’ll split your time between contributing to security projects and responding to security investigations, vulnerabilities, or questions. The work spans application security, infrastructure security, and internal/corporate security. It includes both proactive and reactive security work. You’ll be part of an on-call rotation and help respond to security incidents and investigations. You’ll write code – both to support security work and to improve the security of the Patreon platform. You’ll work closely with other members of the security team, the wider Risk engineering org, and cross functional partners in engineering, legal, and IT. Your work will help reduce known risks and will protect the security, privacy, and trust of Patreon creators and their fans.
-**What you’ll need:**
-- You have two or more years of experience reducing security risks in the application, infrastructure, or corporate security spaces. You can create a threat model and to explain why a given risk matters and what we might do to reduce it.
-- You have deeper knowledge (three or more years) in at least one security or security-adjacent domain (infrastructure security, application security, cloud security, corporate/IT security, cryptography, privacy, etc.)
-- You can develop software (Python, Rust, Golang, or a similar language). You have experience working in a modern software development environment (git, CI/CD, LLM coding tools, etc.)
-- You have experience using AI tools (LLMs, ML models, etc) to identify and address security issues (software vulnerabilities, detection and response, etc.)
-- You’re energized by fast iteration: shipping MVPs, testing hypotheses, and evolving products based on what creators and fans respond to.
-- You take pride in creating elegant solutions to messy, real-world problems and balancing pragmatic trade-offs between security risks and business needs.
-- You believe in Patreon’s mission: giving creators control over their work and building communities that feel good to be in.
-- Bachelor’s or Master’s degree in Computer Science, Computer Engineering, or a related field, or the equivalent
-**Bonus if you have:**
-- Experience working on large scale Internet platforms that allow users to upload content.
-- Past contributions to large scale, production code bases.
-- Experience responding to security incidents, investigating incident impact, and building out incident mitigations.
-We hire talented and passionate people from different backgrounds because workplace diversity and inclusion is critical to our ability to serve creators worldwide. If you’re excited about a role but your past experience doesn’t match with every bullet point outlined above, we strongly encourage you to apply anyway. If you’re a creator at heart, are energized by our mission, and share our company values, we’d love to hear from you.
-**About Patreon**
-Patreon powers creators to do what they love and get paid by the people who love what they do. Our team is passionate about making this mission and our core values come to life every day in our work. Through this work, our Patronauts:
-- **Put Creators First |** *They’re the reason we’re here. When creators win, we win.*
-- **Build with Craft |** *We sign our name to every deliverable, just like the creators we serve.*
-- **Make it Happen |** *We don’t quit. We learn and deliver.*
-- **Win Together |** *We grow as individuals. We win as a team.*
-*Patreon is proud to be an equal opportunity employer. We provide employment opportunities without regard to age, race, color, ancestry, national origin, religion, disability, sex, gender identity or expression, sexual orientation, veteran status, or any other protected class. If you need a reasonable accommodation during the interview process, please let us know via email at accommodations@patreon.*
-*Patreon offers a competitive benefits package including and not limited to salary, equity plans, healthcare, flexible time off, company holidays and recharge days, commuter benefits, lifestyle stipends, learning and development stipends, patronage, parental leave, and 401k plan with matching.*
-*Patreon operates under a hybrid work model, where employees based in office locations are expected to come into the office three days per week, excluding sick time and paid leave. The goal of this policy is to be intentional about the in-person time we spend together to strengthen the feeling of community at Patreon. Candidates hired into remote-eligible roles are not expected to meet the same requirements.*
-*At Patreon, we believe in fair and transparent pay. In compliance with New York and California pay transparency laws, we are sharing the expected salary range for this role.*
-*The posted salary range is dependent on the location and the level. This range may encompass multiple levels within the role’s job family. The final offer will be based on candidate’s experience, skills, competencies, and geographic location, aligning with the appropriate job level within Patreon’s leveling framework. For remote employees located outside CA and NY, salary may vary based on location and local market conditions.*
-*Patreon reserves the right to modify or update compensation and benefits at any time.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>samsara</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - Threat Detection</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Remote - Dallas</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.samsara.com/company/careers/roles/8237426?gh_jid=8237426</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>**Who we are**
-Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping improve the safety, efficiency and sustainability of the physical operations that power our global economy. Representing more than 40% of global GDP, these industries are the infrastructure of our planet, including agriculture, construction, field services, transportation, and manufacturing — and we are excited to help digitally transform their operations at scale.
-Working at Samsara means you’ll help define the future of physical operations and be on a team that’s shaping an exciting array of product solutions, including Video-Based Safety, Vehicle Telematics, Apps and Driver Workflows, and Equipment Monitoring. As part of a recently public company, you’ll have the autonomy and support to make an impact as we build for the long term.
-### **About the role**
-Samsara Security is looking for a Senior Threat Detection Engineer. This is a hands-on engineering role: you will build and operate the signals, pipelines, and tooling that power how we discover threats against Samsara and our customers.
-The Threat Detection team owns the detection platform end to end — the data pipelines that feed it, the detection content that runs on it, the CI/CD that ships it, and the AI-assisted tooling that scales what a small team can cover. You will write detections, and you will also build the machinery that makes the next detection faster to develop, safer to deploy, and measurable in production.
-You will report to the Director of Threat Detection and Response and work closely with Security Operations, Application Security, and Enterprise Security, as well as engineering teams across the company.
-We are looking for someone who takes projects from idea to proof-of-concept to production, who is comfortable being the first person to build something, and who is genuinely interested in what AI can and cannot do for detection engineering — including where it introduces risk rather than removing it.
-This role is open to candidates residing in the US **except** the San Francisco Bay Metro Area, NYC Metro Area, and Washington, D.C. Metro Area.
-### **You should apply if:**
-- **You want to impact the industries that run our world:** Your efforts will result in real-world impact—helping to keep the lights on, get food into grocery stores, reduce emissions, and most importantly, ensure workers return home safely.
-- **You are the architect of your own career:** If you put in the work, this role won't be your last at Samsara. We set up our employees for success and have built a culture that encourages rapid career development, countless opportunities to experiment and master your craft in a hyper growth environment.
-- **You're energized by our opportunity:** The vision we have to digitize large sectors of the global economy requires your full focus and best efforts to bring forth creative, ambitious ideas for our customers.
-- **You want to be with the best:** At Samsara, we win together, celebrate together and support each other. You will be surrounded by a high-caliber team that will encourage you to do your best.
-### **In this role, you will:**
-- Build, deploy, and continuously improve MITRE ATT&amp;CK–aligned detections across cloud, endpoint, identity, email, and application telemetry, with clear false-positive thresholds.
-- Own the full detection lifecycle—from hypothesis, data validation, and baselining through deployment, tuning, validation, and retirement.
-- Advance our detection-as-code platform through version control, peer review, automated testing, CI/CD, and improved pipeline reliability and observability.
-- Identify emerging threat surfaces and build integrations that strengthen data ingestion, enrichment, and coverage across internal and third-party systems.
-- Evaluate AI-powered security capabilities, including secure MCP integrations, threat hunting, anomaly detection, and response automation.
-- Turn threat intelligence into actionable detection and retrospective scanning.
-- Partner closely with Security Operations during investigations, incidents, table top exercises, detection maintenance, and code pairing.
-- Champion, role model, and embed Samsara’s cultural principles (Focus on Customer Success, Build for the Long Term, Adopt a Growth Mindset, Be Inclusive, Win as a Team) as we scale globally and across new offices.
-### **Minimum requirements for the role:**
-- 6+ years in security engineering, detection engineering, or a related technology discipline.
-- Strong Python and SQL skills, with experience analyzing large datasets to build and validate detections.
-- Hands-on experience with detection-as-code, Git-based workflows, automated testing, and CI/CD deployment.
-- Deep experience with modern SIEM platforms, including data onboarding, advanced queries, dashboards, and threat intelligence enrichment.
-- Working knowledge of AWS, Linux, containers, and EDR.
-- Proven ability to build systems from scratch, lead projects independently, learn new technologies quickly, and communicate technical concepts clearly through documentation, RFCs, and presentations.
-### **An ideal candidate also has:**
-- Experience with data orchestration platforms such as Airflow or Databricks.
-- Applied experience with LLMs, agentic frameworks, and MCP integrations, including their security risks and failure modes.
-- Experience with behavioral analytics, anomaly detection, feature engineering, and model evaluation.
-- Familiarity with risk-based alerting, ChatOps, distributed alerting, and attack simulation.
-- Additional experience with Go, Terraform, malware analysis, digital forensics, or FedRAMP environments.
-#LI-Remote 
-The range of annual base salary for full-time employees for this position is below. Please note that base pay offered may vary depending on factors including your city of residence, job-related knowledge, skills, and experience. This role is also eligible for an initial RSU grant with no vesting cliff, and ongoing refresh opportunities tied to performance, subject to plan terms and conditions. Learn more about our total rewards and benefits below.
-Annual Base Salary
-$157,675—$238,500 USD
-**Total Rewards**
-At Samsara, we build for the people who keep the global economy moving. We want owners, not passengers, which is why [our rewards](https://www.samsara.com/company/careers/benefits) are designed to fuel high-impact builders. Our compensation program delivers above-market total compensation through a combination of base salary, performance-based bonus/variable pay, and equity (for eligible roles) in a high-growth public company. We meaningfully differentiate pay for our top performers, who have the opportunity to earn above-market compensation that can outpace the broader market over time.
-Beyond compensation, we provide the foundations that enable long-term success: a flexible, employee-led remote model, a professional development stipend, comprehensive health and parental leave plans, and more. If you’re ready to build for the long term and own the outcome, your journey starts here.
-**Flexible Working**
-At Samsara, we embrace a flexible working model that caters to the diverse needs of our teams. Our offices are open for those who prefer to work in-person and we also support remote work where it aligns with our operational requirements. For certain positions, being close to one of our offices or within a specific geographic area is important to facilitate collaboration, access to resources, or alignment with our service regions. In these cases, the job description will clearly indicate any working location requirements. Our goal is to ensure that all members of our team can contribute effectively, whether they are working on-site, in a hybrid model, or fully remotely. All offers of employment are contingent upon an individual’s ability to secure and maintain the legal right to work at the company and in the specified work location, if applicable.
-**Belonging at Samsara**
-At Samsara, we welcome everyone regardless of their background. All qualified applicants will receive consideration for employment without regard to race, color, religion, national origin, sex, gender, gender identity, sexual orientation, protected veteran status, disability, age, and other characteristics protected by law. We depend on the unique approaches of our team members to help us solve complex problems and want to ensure that Samsara is a place where people from all backgrounds can make an impact.
-**Accommodations**
-Samsara is an inclusive work environment, and we are committed to ensuring equal opportunity in employment for qualified persons with disabilities. Please email [accessibleinterviewing@samsara.com](mailto:accessibleinterviewing@samsara.com) or [click here](https://forms.gle/DrM6DFQUiSgfPtCVA) if you require any reasonable accommodations throughout the recruiting process.
-**Our Commitment to Authenticity**
-We use [Tofu](https://hiretofu.com/privacyPolicy), a fraud detection tool, to validate the authenticity of applications and protect against identity fraud. This ensures we are connecting with real people and allows us to prioritize genuine candidates. Please see Samsara’s [Candidate Privacy Notice](https://www.samsara.com/legal/candidate-privacy-notice) for more information.
-**Fraudulent Employment Offers**
-Samsara is aware of scams involving fake job interviews and offers. Please know we do not charge fees to applicants at any stage of the hiring process. Official communication about your application will only come from emails ending in @samsara.com, @us-greenhouse-mail.io or @mail3.guide.co. For more information regarding fraudulent employment offers, please visit our [blog post here](https://samsara.com/blog/avoiding-fake-job-offers).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>samsara</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - Enterprise Security</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>London - UK2; Remote - London</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Yes / Mentioned</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.samsara.com/company/careers/roles/8223369?gh_jid=8223369</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>**Who we are**
-Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping improve the safety, efficiency and sustainability of the physical operations that power our global economy. Representing more than 40% of global GDP, these industries are the infrastructure of our planet, including agriculture, construction, field services, transportation, and manufacturing — and we are excited to help digitally transform their operations at scale.
-Working at Samsara means you’ll help define the future of physical operations and be on a team that’s shaping an exciting array of product solutions, including Video-Based Safety, Vehicle Telematics, Apps and Driver Workflows, and Equipment Monitoring. As part of a recently public company, you’ll have the autonomy and support to make an impact as we build for the long term.
-**About the role:**
-The Senior Security Engineer – Enterprise Security shares ownership of the day-to-day operation of the Samsara security environment. You will keep our network access, device trust, and visibility systems running, tuned, and resilient at enterprise scale in partnership with a global team. Utilizing modern principles, you’ll maintain and evolve a modern zero trust program, spend time both on policy design and real-time triage for escalations.
-You take security seriously and believe the best solutions are low-friction and built in partnership with others. You are comfortable owning and maintaining production systems for long term success - troubleshooting systemic issues, tuning policies based on real incidents, and continuously improving what is already built. You bring an automation mindset to repetitive work, whether using Python, SOAR platforms, or AI-assisted tools. You enjoy supporting teammates and helping other engineers build their security knowledge.
-This is a remote position open to candidates residing in the United Kingdom. Relocation assistance will not be provided for this role.
-**About this team:**
-Enterprise Security is a global team spanning the US, EMEA, and India. We work in close partnership with our coworkers as collaborators rather than gatekeepers. Leadership is hands-on and technical, and our culture encourages everyone to contribute across the full stack.
-Executive leadership actively champions security as a competitive advantage that builds customer trust and helps win enterprise partnerships. You will see a direct line between the zero trust systems you operate and the security that protects our physical operations partners worldwide. Our on-call rotation for the highest severity incidents is spread evenly across the team for one week out of every ten.
-#### **In this role, you will:**
-- Co-own the day-to-day operation, triage, and tuning of the Samsara endpoint security environment by responding to escalations, investigating anomalies, and resolving issues
-- Continuously improve existing endpoint visibility tools and workflows in partnership with our Security Operations team, and based on real usage patterns and incident learnings
-- Write clear, concise documentation and runbooks for enterprise security workflows
-- Collaborate with partners across Engineering, IT, and Security to ensure proper implementation of security tools and policies
-- Assist the Security Operations team during security investigations, acting as a technical subject matter expert within your domain
-- Partner with engineering teams to triage and support remediation of vulnerabilities and misconfigurations
-- Mentor engineers on the Security team to grow their domain knowledge, tool-specific skills, and communication abilities
-- Champion, role model, and embed Samsara cultural principles (Focus on Customer Success, Build for the Long Term, Adopt a Growth Mindset, Be Inclusive, Win as a Team)
-**Minimum requirements for the role:**
-- 5+ years of relevant experience in an Enterprise Security role with demonstrated impact
-- Hands-on experience operating and maintaining endpoint security and visibility tools at enterprise scale (e.g. Crowdstrike, osquery, or similar)
-- Exposure to at least one additional enterprise security tool stack beyond endpoint security, such as Secure Access Service Edge (SASE), zero trust systems,  email security, Data Loss Prevention (DLP), or Identity and Access Management (IAM)
-- An automation mindset with experience scripting and debugging code with Python (with or without AIassistance) and using SOAR platforms
-- Strong familiarity with common security challenges and the ability to independently evaluate their severity and business impact
-- Track record of delivering impactful work across multiple quarters and collaborating effectively across teams
-**An ideal candidate also has:**
-- Significant breadth across the endpoint security ecosystem, including designing layered controls with EDR tools, passive telemetry, integration with threat intelligence feeds, and operation in cloud and containerized environments.
-- History of building out security programs using modern SaaS security platforms such as Crowdstrike, Mimecast Incydr, and Splunk
-- Experience with infrastructure as code deployments using Terraform
-- Experience with AI-driven automations
-**Total Rewards**
-At Samsara, we build for the people who keep the global economy moving. We want owners, not passengers, which is why [our rewards](https://www.samsara.com/company/careers/benefits) are designed to fuel high-impact builders. Our compensation program delivers above-market total compensation through a combination of base salary, performance-based bonus/variable pay, and equity (for eligible roles) in a high-growth public company. We meaningfully differentiate pay for our top performers, who have the opportunity to earn above-market compensation that can outpace the broader market over time.
-Beyond compensation, we provide the foundations that enable long-term success: a flexible, employee-led remote model, a professional development stipend, comprehensive health and parental leave plans, and more. If you’re ready to build for the long term and own the outcome, your journey starts here.
-**Flexible Working**
-At Samsara, we embrace a flexible working model that caters to the diverse needs of our teams. Our offices are open for those who prefer to work in-person and we also support remote work where it aligns with our operational requirements. For certain positions, being close to one of our offices or within a specific geographic area is important to facilitate collaboration, access to resources, or alignment with our service regions. In these cases, the job description will clearly indicate any working location requirements. Our goal is to ensure that all members of our team can contribute effectively, whether they are working on-site, in a hybrid model, or fully remotely. All offers of employment are contingent upon an individual’s ability to secure and maintain the legal right to work at the company and in the specified work location, if applicable.
-**Belonging at Samsara**
-At Samsara, we welcome everyone regardless of their background. All qualified applicants will receive consideration for employment without regard to race, color, religion, national origin, sex, gender, gender identity, sexual orientation, protected veteran status, disability, age, and other characteristics protected by law. We depend on the unique approaches of our team members to help us solve complex problems and want to ensure that Samsara is a place where people from all backgrounds can make an impact.
-**Accommodations**
-Samsara is an inclusive work environment, and we are committed to ensuring equal opportunity in employment for qualified persons with disabilities. Please email [accessibleinterviewing@samsara.com](mailto:accessibleinterviewing@samsara.com) or [click here](https://forms.gle/DrM6DFQUiSgfPtCVA) if you require any reasonable accommodations throughout the recruiting process.
-**Our Commitment to Authenticity**
-We use [Tofu](https://hiretofu.com/privacyPolicy), a fraud detection tool, to validate the authenticity of applications and protect against identity fraud. This ensures we are connecting with real people and allows us to prioritize genuine candidates. Please see Samsara’s [Candidate Privacy Notice](https://www.samsara.com/legal/candidate-privacy-notice) for more information.
-**Fraudulent Employment Offers**
-Samsara is aware of scams involving fake job interviews and offers. Please know we do not charge fees to applicants at any stage of the hiring process. Official communication about your application will only come from emails ending in @samsara.com, @us-greenhouse-mail.io or @mail3.guide.co. For more information regarding fraudulent employment offers, please visit our [blog post here](https://samsara.com/blog/avoiding-fake-job-offers).</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>notion</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Security Engineer, Detection and Response</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Dublin, Ireland</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/notion/fbcaf076-830e-4daf-ad39-1e0e8ce9f89c/application</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t># Who We Are
-Notion is the collaborative AI workspace where teams and agents [think together](https://www.youtube.com/watch?v=vkpYpWfEK5s). We're building one place where your knowledge, projects, meetings, and AI tools live side by side, so work is faster, clearer, and less fragmented. Millions of individuals, small teams, and large companies run their work on Notion.
-Notinos (our employees) are customer zero in bringing this future of work to life. We care about craft, building things that last, and the belief that great work is still fundamentally human. Our goal isn’t to ship the next feature. Each and every team of Notinos is working to set the standard for how humans work together in the AI era. From building a business’s system of record to making and managing AI agents to automating away the busy work, we care deeply about giving our customers more time for their life’s work.
-# About The Role
-Millions of people rely on Notion to do their most important work, and protecting that trust is foundational to everything we build.
-We’re looking for a hands-on Detection Engineer to build and operate the systems and workflows we use to detect and respond to attacks across Notion’s cloud-native environment. You’ll ship high-signal detections, improve the platform that powers them, participate in incident response, and help shape how detection and response engineering scales at Notion.
-You’ll work closely with Engineering, Corporate Security, and Infrastructure, with broad latitude to identify gaps, prioritize investments, and build what’s needed next.
-We view detection and response as a software engineering discipline: detections are code, platforms are products, and measurement matters
-# What You'll Achieve
-- Build and tune high-signal detections across cloud, identity, endpoint, and SaaS environments, with review and mentorship from senior teammates as you ramp up.
-- Contribute to the detection platform, including rule lifecycle management, tuning, measurement, and rollout safety.
-- Build tooling and automation that speed up triage, enrichment, investigation, and detection authoring, including LLM-based workflows where useful.
-- Turn threat intelligence and adversary TTPs into detections, telemetry requirements, and response improvements.
-- Take part in investigations, incident response, and postmortems, and help turn what we learn into lasting fixes.
-- Help define and track metrics such as coverage, MTTD, and alert quality.
-- Join a shared on-call rotation for incident response.
-# Skills You'll Need to Bring
-- We're hiring across a range of experience levels. If you have some of these skills but not all, we'd still like to hear from you.
-  - 3+ years of experience in detection engineering, security operations, incident response, threat hunting, or a closely related security or software engineering role.
-  - Have written or tuned detections that run in production, and care about signal quality and cutting noise.
-  - Working knowledge of at least one detection or query language (Sigma, KQL, SPL, YARA-L, EQL, or Panther), or strong SQL or Python skills and the drive to learn one quickly.
-  - An understanding of how attackers operate (for example, MITRE ATT&amp;CK), and the ability to use it to decide what to detect.
-  - Hands-on experience with AWS, GCP, or Azure, ideally including identity and access logs.
-  - Have used SIEM, EDR, or SOAR tools in any size of environment.
-  - Write clearly in runbooks, design docs, and incident notes, and can own well-scoped projects end to end.
-# Nice to Have
-- Have led purple team, blue team, or adversary emulation exercises that improved detections or telemetry.
-- Experience running SIEM, EDR, or SOAR platforms at large scale.
-- Experience building or maintaining detection-as-code workflows (version control, CI, and tests for detections).
-- Experience applying LLMs or agent-style tooling to security workflows.
-- Experience securing AI-enabled systems or endpoint tooling.
-- Kubernetes or container detection experience.
-- Background in threat intelligence, malware analysis, or digital forensics.
-- Contributions to the security community through research, tooling, CTFs, or talks.
-- Experience at a high-growth startup or AI company.
-Notion is committed to providing highly competitive cash compensation, equity, and benefits. The compensation offered for this role will be based on multiple factors such as location, the role's scope and complexity, and the candidate's experience and expertise, and may vary from the range provided below. The estimated base salary range for this role is €75,000–€142,000 per year.
-By clicking “Submit Application”, I understand and agree that Notion and its affiliates and subsidiaries will collect and process my information in accordance with Notion’s [Global Recruiting Privacy Policy](https://notion.notion.site/Notion-Global-Recruiting-Privacy-Policy-fc3eb4e829354a26a2bb6fd5e289b550?pvs=74).
-#LI-Onsite
-# A Note on AI
-You don’t need deep AI expertise for every role, but we do expect every Notino to be intellectually curious, drawn to tinkering and discovery, and excited to use AI as a real collaborator in their work. For some roles, AI fluency is a core requirement — when that’s the case, we'll say so explicitly in the qualifications. People who thrive here don’t treat AI as a novelty. They use it to think better, and make their work easier for others to build on.
-# Equal Opportunity &amp; Accommodations
-We hire talented people from a wide range of backgrounds. If you’re excited about this role but don’t meet every bullet, we still encourage you to apply. Notion is an equal opportunity employer and does not discriminate on the basis of any legally protected characteristic. Consistent with applicable law, we will consider for employment qualified applicants with arrest and conviction records. Notion provides reasonable accommodations during the application process; if you need one, please let your recruiter know.
-Notion is proud to be an equal opportunity employer. We do not discriminate in hiring or any employment decision based on race, color, religion, national origin, age, sex (including pregnancy, childbirth, or related medical conditions), marital status, ancestry, physical or mental disability, genetic information, veteran status, gender identity or expression, sexual orientation, or other applicable legally protected characteristic. Notion considers qualified applicants with criminal histories, consistent with applicable federal, state and local law. Notion is also committed to providing reasonable accommodations for qualified individuals with disabilities and disabled veterans in our job application procedures. If you need assistance or an accommodation due to a disability, please let your recruiter know.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>platacard</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Data Security Engineer - Junior+</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>https://plata.careers/vacancy/details?id=5436264008&amp;gh_jid=5436264008</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>**The Technical Data Protection** function is responsible for implementing and operating technical controls that protect the company’s sensitive, confidential, personal, financial, and payment data.
-**Data Security Enginee**r will be responsible for the practical implementation, configuration, integration, and continuous improvement of DLP and other data protection technologies across endpoints, cloud platforms, collaboration services, data repositories, and business systems. The role will work closely with the Data Security Architect, SOC, IT, DWH, Infrastructure, Product, Legal, Privacy, and Compliance teams.
-**Challenges that await you:**
-- Implementing, configuring, and operating DLP controls across endpoints, cloud services, email, collaboration platforms, and data storage environments.
-- Creating and maintaining DLP policies for personal, financial, payment, confidential, and other sensitive data.
-- Integrating data classification and labelling with technical enforcement and monitoring controls.
-- Developing detection logic based on data types, labels, content patterns, context, user behaviour, destinations, and business processes.
-- Investigating DLP alerts and potential data leakage cases in collaboration with SOC, Legal, Privacy, HR, and relevant business teams.
-- Tuning policies to reduce false positives while maintaining effective protection and monitoring coverage.
-- Implementing data discovery and scanning processes to identify sensitive data stored across corporate environments.
-- Supporting the implementation of encryption, masking, tokenisation, access controls, and other technical data protection mechanisms.
-- Collecting DLP and data security events in SIEM and creating monitoring dashboards, alerts, and operational metrics.
-- Integrating data protection tools with SIEM, Jira, identity platforms, cloud services, and automation workflows.
-- Automating repetitive operational tasks, policy deployment, evidence collection, reporting, and incident enrichment.
-- Testing data protection controls and validating that policies work as expected before production rollout.
-- Maintaining technical documentation, operating procedures, implementation guides, and response playbooks.
-- Supporting onboarding of new systems, repositories, data sources, and business processes into the data protection framework.
-- Identifying control gaps and proposing technical improvements based on incidents, testing results, and monitoring data.
-- Supporting audits and regulatory assessments by providing technical evidence of implemented data protection controls.
-**Our technology stack:**
-**Data Protection**
-- Endpoint, email, cloud, and collaboration DLP.
-- Google Workspace and Google Drive security controls.
-- Data discovery and classification technologies.
-- Encryption, masking, and tokenisation solutions.
-- Data access and activity monitoring.
-**Security Monitoring &amp; Automation**
-- Elastic Stack - Elasticsearch, Kibana, ES|QL, and Detection Rules.
-- Jira Service Management.
-- Python and Bash.
-- n8n and security automation workflows.
-- SOAR technologies.
-**Cloud &amp; Infrastructure**
-- AWS and cloud-native security services.
-- Kubernetes and Docker.
-- Snowflake, PostgreSQL, Amazon Aurora, Amazon S3, and related technologies.
-- GitLab CI/CD.
-- OIDC/SAML SSO and RBAC.
-**What makes you a great fit:**
-- 1+ years of experience in Information Security, Security Engineering, Data Security, DLP, or a related technical role.
-- Practical experience implementing or operating DLP, data classification, data discovery, or cloud security controls.
-- Understanding of sensitive data types, data flows, data handling risks, and common data leakage scenarios.
-- Experience creating, testing, and tuning security policies and detection rules.
-- Understanding of encryption, masking, tokenisation, access control, and secrets protection.
-- Experience analysing security events, investigating alerts, and documenting findings.
-- Familiarity with cloud services, enterprise collaboration platforms, and modern data environments.
-- Basic scripting or automation skills using Python, Bash, APIs, or workflow automation tools.
-- Strong troubleshooting skills, attention to detail, and a structured approach to technical implementation.
-- Ability to collaborate with technical and non-technical teams.
-- English B1+ for working with documentation, tools, and international teams.
-**Your bonus skills:**
-- Experience with Google Workspace DLP, endpoint DLP, CASB, or similar security technologies.
-- Experience with data discovery and classification across cloud storage, databases, or DWH platforms.
-- Familiarity with Elastic Stack or another SIEM platform.
-- Experience with AWS, Snowflake, PostgreSQL, or Kubernetes.
-- Understanding of PCI DSS, privacy regulations, and financial data protection requirements.
-- Experience integrating security products through APIs.
-- Experience building dashboards, reports, or automated security workflows.
-- Relevant security, cloud, or data protection certifications
-**Our ways of working:**
-- **Innovative Spirit:**A commitment to creativity and groundbreaking solutions
-- **Honest Feedback:** valuing open, transparent communication
-- **Supportive Team:**a strong, collaborative community
-- **Celebrating Achievements:**recognizing our wins together
-- **High-Tech Environment:** a team full of smart and revolutionary people who date to challenge the status quo of incumbent finances
-**Our benefits:**
-- **R**elocation support****to one of our hubs — Cyprus, Serbia, Georgia or Kazakhstan — with assistance for the employee and their family
-- **Flexible work**from one of our offices or remote
-- **Healthcare** **Coverage**
-- **Education Budget:** Language lessons, professional training and certifications
-- **Wellness Budget:** Mental health and fitness activity reimbursements
-- **Vacation policy:** 20 days of annual leave and paid sick leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Staff Security Engineer, Detection &amp; Response</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Zürich, CH</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Yes / Mentioned</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5432626008</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>## **About Anthropic**
-Anthropic’s mission is to create reliable, interpretable, and steerable AI systems. We want AI to be safe and beneficial for our users and for society as a whole. Our team is a quickly growing group of committed researchers, engineers, policy experts, and business leaders working together to build beneficial AI systems.
-## About the role
-As Anthropic's models grow more capable, so does the interest of people who want to attack or misuse them. The Detection and Response (D&amp;R) team spots those threats and responds to incidents across every layer of Anthropic's technology stack.
-The team is early-stage, so you'll help build our detection and response capabilities from the ground up and work closely with our security and research teams.
-## Key responsibilities
-- Lead incident response across a range of domains, from external attacks to insider threats, spanning all layers of Anthropic's technology stack
-- Build and deploy tooling, including tools that use large language models, to improve how we detect and respond to threats
-- Create and tune detections, playbooks, and workflows to catch and respond to incidents quickly
-- Review incident response metrics and procedures, and drive improvements
-- Work across security and engineering teams
-- Take part in an on-call rotation
-## Minimum qualifications
-- Experience handling security incidents and investigating anomalies as part of a team
-- Working knowledge of EDR, SIEM, SOAR, or similar security tooling
-- A solid understanding of cloud environments and operations
-- Experience working with engineering teams in a SaaS environment
-- Proficiency with a scripting language such as Python and query languages such as SQL
-- Strong communication and collaboration skills
-- Able to lead projects with little guidance
-- Able to pick up new languages and technologies quickly
-## Preferred qualifications
-- 7+ years of software engineering experience, or 7+ years of detection engineering, incident response, or threat hunting experience
-- Security operations or investigations involving large-scale Kubernetes environments
-- Experience analyzing attack behavior and prototyping high-quality detections
-- Experience with threat intelligence, malware analysis, infrastructure as code, or forensics
-- Experience contributing to a high-growth startup environment
-## **Logistics**
-**Minimum education:** Bachelor’s degree or an equivalent combination of education, training, and/or experience
-**Required field of study:**A field relevant to the role as demonstrated through coursework, training, or professional experience
-**Minimum years of experience:** Years of experience required will correlate with the internal job level requirements for the position
-**Location-based hybrid policy:** Currently, we expect all staff to be in one of our offices at least 25% of the time. However, some roles may require more time in our offices.
-**Visa sponsorship:** We do sponsor visas! However, we aren't able to successfully sponsor visas for every role and every candidate. But if we make you an offer, we will make every reasonable effort to get you a visa, and we retain an immigration lawyer to help with this.
-**We encourage you to apply even if you do not believe you meet every single qualification.** Not all strong candidates will meet every single qualification as listed.  Research shows that people who identify as being from underrepresented groups are more prone to experiencing imposter syndrome and doubting the strength of their candidacy, so we urge you not to exclude yourself prematurely and to submit an application if you're interested in this work. We think AI systems like the ones we're building have enormous social and ethical implications. We think this makes representation even more important, and we strive to include a range of diverse perspectives on our team.  
-**Your safety matters to us.** To protect yourself from potential scams, remember that Anthropic recruiters only contact you from @anthropic.com email addresses. In some cases, we may partner with vetted recruiting agencies who will identify themselves as working on behalf of Anthropic. Be cautious of emails from other domains. Legitimate Anthropic recruiters will never ask for money, fees, or banking information before your first day. If you're ever unsure about a communication, don't click any links—visit [&lt;anthropic.com/careers&gt;](http://anthropic.com/careers) directly for confirmed position openings.
-## **How we're different**
-We believe that the highest-impact AI research will be big science. At Anthropic we work as a single cohesive team on just a few large-scale research efforts. And we value impact — advancing our long-term goals of steerable, trustworthy AI — rather than work on smaller and more specific puzzles. We view AI research as an empirical science, which has as much in common with physics and biology as with traditional efforts in computer science. We're an extremely collaborative group, and we host frequent research discussions to ensure that we are pursuing the highest-impact work at any given time. As such, we greatly value communication skills.
-The easiest way to understand our research directions is to read our recent research. This research continues many of the directions our team worked on prior to Anthropic, including: GPT-3, Circuit-Based Interpretability, Multimodal Neurons, Scaling Laws, AI &amp; Compute, Concrete Problems in AI Safety, and Learning from Human Preferences.
-## **Come work with us!**
-Anthropic is a public benefit corporation headquartered in San Francisco. We offer competitive compensation and benefits, optional equity donation matching, generous vacation and parental leave, flexible working hours, and a lovely office space in which to collaborate with colleagues. **Guidance on Candidates' AI Usage:** Learn about [our policy](https://www.anthropic.com/candidate-ai-guidance) for using AI in our application process.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>gomotive</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Offensive Security Engineer (Red Team)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Canada - Remote</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gomotive/jobs/8849916002</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>**Who we are:**
-Motive empowers the people who run physical operations with tools to make their work safer, more productive, and more profitable. For the first time ever, safety, operations and finance teams can manage their drivers, vehicles, equipment, and fleet related spend in a single system. Combined with industry leading AI, the Motive platform gives you complete visibility and control, and significantly reduces manual workloads by automating and simplifying tasks.
-Motive serves nearly 100,000 customers – from Fortune 500 enterprises to small businesses – across a wide range of industries, including transportation and logistics, construction, energy, field service, manufacturing, agriculture, food and beverage, retail, and the public sector.
-Visit [&lt;gomotive.com&gt;](http://gomotive.com) to learn more.
-### **About the Role:**
-As a Red Team Security Engineer you will be a key member of the Product Security Team. You will be the primary Security partner for software and engineering teams focusing on evaluating security posture across the organization. The Red Team Engineer will be responsible for conducting adversary emulation and offensive security assessments across cloud environments while driving remediation efforts of issues.
-### **What You'll Do:**
-- Plan and execute red team operations, adversary simulations, and targeted security assessments focused on cloud environments.
-- Evaluate the security of cloud infrastructure, identity architectures, CI/CD pipelines, containerized workloads, and cloud-native services.
-- Identify and validate attack paths involving IAM misconfigurations, overprivileged roles, secrets exposure, metadata abuse, insecure automation, and weaknesses in cloud service configurations.
-- Assess detection and response coverage by exercising logging, alerting, monitoring, and incident response processes in partnership with blue team and detection engineering functions.
-- Track emerging attacker techniques, cloud exploitation trends, and new abuse paths relevant to modern enterprise environments.
-### **What We're Looking For:**
-- 5+ years of experience in offensive security, red teaming, penetration testing, and detection validation
-- Familiarity with attacker tactics, techniques, and procedures, and the ability to map findings to frameworks such as MITRE ATT&amp;CK.
-- Ability to write concise, actionable reports and communicate complex technical issues to diverse stakeholders
-- Relevant industry certifications such as OSCP, OSEP, GXPN, GPEN, or cloud security certifications.
-***Pay Transparency***
-*Your compensation may be based on several factors, including education, work experience, and certifications. For certain roles, total compensation may include restricted stock units. Motive offers benefits including health, pharmacy, optical and dental care benefits, paid time off, sick time off, short term and long term disability coverage, life insurance as well as 401k contribution (all benefits are subject to eligibility requirements). Learn more about our benefits by visiting* [*Motive Perks &amp; Benefits*](https://www.comparably.com/companies/motive/perks-and-benefits).
-The compensation range for this position will depend on where you reside. For this role, the compensation range is:
-Canada
-$146,000—$190,000 CAD
-*Creating a diverse and inclusive workplace is one of Motive's core values. We are an equal opportunity employer and welcome people of different backgrounds, experiences, abilities and perspectives.*
-*Please review our Candidate Privacy Notice [here](https://drive.google.com/file/d/1X9AbvQHki8zZCyjDjip1g0NtdZHcykJc/view?usp=drive_link).*
-*UK Candidate Privacy Notice [here](https://drive.google.com/file/d/1nqdWTJ7WJJikhj1Yhlo4jxDRA_6yXZbd/view).*
-*The applicant must be authorized to receive and access those commodities and technologies controlled under U.S. Export Administration Regulations. It is Motive's policy to require that employees be authorized to receive access to Motive products and technology.*
-*Regarding US-based roles, depending on your role and primary work location, Motive Technologies, Inc. (“Employer”) discloses candidates may be required to execute a non-compete covenant with the Employer. This requirement does not apply to lawyers, interns, or employees working in CA, MN, MT, ND, OK, or where otherwise prohibited by law.*
-*Non-compete covenant terms in all other jurisdictions will be subject to the applicable statutory requirements, including but not limited to, procedures, industry related prohibitions, or salary and compensation thresholds.*
-*All job postings are for existing vacancies. Please note; some interviews or new-hire training sessions may be held in person at one of our global offices.*</t>
+          <t>Do you find Threat Hunting, Threat Intelligence, SIEM, and EDR exciting, and do you want to be a deciding factor in IT Security in our internal as well as our customers’ environments? As a Purple Security Engineer, you will ensure operations can perform their security-related tasks based on guidelines you help define. Responsibilities and technologies As a Purple Security Engineer, you will be a part of Netcompany Operations and our dedicated Security team. Your work will involve defending critical infrastructure such as airports, large financial institutions, government systems, and other essential sectors. You will handle tasks ranging from identifying improvements and monitoring servers and applications to optimizing response strategies and advising colleagues. You will be encouraged to solve technical problems creatively to find the best solutions. Open dialogue about different approaches to enhancing security is an important part of your work as a Purple Security Engineer. You will be a trusted advisor for Netcompany’s delivery and project teams regarding how to solve security-related tasks. Your responsibilites will typically include: Implementing safeguards to protect critical solutions and the data infrastructure of Denmark from cyber threats. Engaging in proactive threat hunting to identify and mitigate potential vulnerabilities. Developing and implementing response strategies to effectively handle security incidents. Responding to and following up on alerts generated by our SIEM and EDR solutions, including adjusting these to ensure precision. About you To succeed in this role, you: You hold a degree or diploma in engineering, either bachelor's, master's, or have a similar qualification level in IT. You are motivated by delivering optimal business and critical societal solutions. Full professional proficiency in Danish and English (written and spoken) is a must. Employment is contingent upon your ability to obtain and maintain security clearance from the Danish Security and Intelligence Service (PET). Continue developing with us At Netcompany, we focus on your personal and professional development. When you join us, you will be assigned a personal mentor who will guide you through your development and help you achieve your goals. The close relationship with an experienced colleague helps ensure the well-being of each employee and provides you with concrete insights into the many different career opportunities as you build your experience. Additionally, you will be enrolled in our internal training programme, Netcompany Academy, where you are offered courses and seminars on everything from technologies to customer management. All courses are taught by experienced Netcompany colleagues, ensuring that all content is highly relevant and builds upon your professional skills, preparing you for various tasks and continuously improving your expertise throughout your career with us. Join an inclusive community At Netcompany, we highly prioritise an inclusive community. We actively promote an open and welcoming work culture based on collaboration and mutual trust, where there is always an opportunity for sparring. As part of our culture and values, all employees, regardless of background, identity, and experience, are met with understanding and respect and given equal opportunities for development and well-being. As we are an international company with offices in many countries, you will have the opportunity to learn and collaborate internationally with colleagues from across the world. We offer a shared environment where we engage with each other across departments and projects. Additionally, we have a wide range of social and professional events that provide you with the best opportunities to expand and build a network early in your career. Send us your application Upload your resume and a motivational letter to our recruitment system via the link. If you have unanswered questions, feel free to write to . All qualified candidates are encouraged to apply regardless of gender, gender expression, sexuality, disability, age, religion and belief, political views, nationality, ethnicity, or social background. We are committed to creating an inclusive and diverse environment. Our recruitment processes are based on individual merit. If you require any reasonable adjustments or additional support during the interview process, please email our recruiters at  for assistance. #LI-SA1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M108"/>
+  <autoFilter ref="A1:M81"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"New,Applied,Interview,Rejected,Offer,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10173,33 +7659,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs_latest.xlsx
+++ b/jobs_latest.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Latest Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Jobs'!$A$1:$M$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -525,56 +525,1139 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>vectranetworks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vectra.ai/about/jobs?gh_jid=8256570</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Vectra® is the leader in AI-driven threat detection and response for hybrid and multi-cloud enterprises.
+The Vectra AI Platform delivers integrated signal across public cloud, SaaS, identity, and data center networks in a single platform. Powered by patented Attack Signal Intelligence, it empowers security teams to rapidly prioritize, investigate and respond to the most advanced cyber-attacks. With 35 patents in AI-driven threat detection and the most vendor references in MITRE D3FEND, organizations worldwide rely on the Vectra AI to move at the speed and scale of hybrid attackers. For more information, visit &lt;www.vectra.ai&gt;.
+Position Overview
+As a Security Engineer (Pre‑Sales) at &lt;Vectra.ai&gt;, you will blend deep technical expertise with strong customer‑facing skills to build trust, influence architectural direction, and drive successful outcomes for our clients. You’ll guide prospects through technical discovery, articulate how Vectra’s AI‑driven detection and response platform solves their most critical security challenges, and deliver compelling demonstrations and proofs‑of‑concept that showcase our value.
+**Responsibilities**
+- Pre-Sales support and Technical Account Management associated to your Regional Sales Managers
+- Walk customers and partners through demos and problem solving in clear, concise matter by being the subject matter expert on all things Vectra.
+- Communicate cross functionally constantly to ensure all key stakeholders are in the loop in order to insure best-of-breed products, tools and documentations.
+- Develop and maintain an in-depth technical knowledge of the Vectra product line.
+- Identify new opportunities by creating and developing strong technical relationships with customers and channel partners.
+- Maintain knowledge at a high technical level of the current security landscape.
+- Collaborate with Customers on Technology reviews, product findings, and integration with other technologies they may have.
+- Collaborate with other Vectra Engineers on high-level projects to deliver Vectra technologies to our customers.
+- Explore and maintain knowledge of Vectra's key competitors.
+- Participate in deployment review and forecast calls.
+- Participate in design review and release meetings.
+- Travel as needed within region.
+**Experience and soft skills**
+- Startup DNA is a must: willing and able to do "whatever it takes" with motivation to find solutions rather than admire the challenge.
+- Customer-first behaviour is a must.
+- Ability to work hands-in-hands with your Sales counterpart (RSM)**.**
+- 5+ years experience in a Technical Account Management or Security Engineering role.
+- Large account management experience is required.
+**Technical qualifications**
+- Deep understanding of security-focused product lines (CASB, EDR, SIEM or forensics-type platforms) with the ability to translate into value and security best practices.
+- Strong knowledge in networking and ability to understand L3 to L7 OSI layers.
+- String written (RFP) and verbal communications (Pre-sales presentations and conferences) are a must.
+- Good understanding of an attacker progression (Red Team or Pentest). Certifications such as CEH, OSCP, OSCE is a plus.
+- Good understanding of Incident Response (Blue Team) methodologies. Certifications such as GNFA is a plus.
+- Good understanding of Cloud Security and Network Architectures. Certifications such as AWS Certified Security Specialty (SCS-C01) is a plus.
+- Good understanding of Security Processes and methodologies. Certifications such as CISSP is a plus
+Our competitive total rewards package includes cash compensation within the range provided below. Actual pay for this position may vary based on the hired candidate’s location, experience and relevant incumbent pay position.
+Vectra Total Rewards
+$201,800—$273,100 CAD
+Vectra provides a comprehensive total rewards package that supports the financial, physical, mental and overall health of our employees and their families. Compensation includes competitive base pay, incentive plan eligibility, and participation in the employee equity plan (stock options). Specific benefits offered varies by location, but commonly include health care insurance, income protection / life insurance, access to retirement savings plans, behavioral &amp; emotional wellness services, generous time away from work, and a comprehensive employee recognition program.
+Vectra is committed to creating a diverse environment and is proud to be an equal opportunity employer.
+We are committed to equal employment opportunity regardless of race, color, ancestry, religion, sex, national origin, sexual orientation, age, citizenship, marital status, disability, gender identity or Veteran status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aikido Security</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cloud Security Engineer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Remote job</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://aikidosecurity.recruitee.com/o/cloud-security-engineer/c/new</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🌍 We’re making security suck less for developers. Security tools haven’t kept up with how software is built today. They interrupt teams, slow releases, and turn security into a bottleneck instead of a capability. We built Aikido to change that. Aikido builds developer-first security products that reduce real risk without getting in the way of shipping software. We focus on what actually matters and automate the rest. We’re taking on legacy security tools that teams have been stuck with, and we’re winning. If you want to help us take market share and build products developers actually enjoy using, you’re in the right place. Founded in 2022 by third-time founders, Aikido has $85M in the bank and a long runway ahead. We’re building toward self-securing software. Join an all-star team. Take real ownership. Push boundaries. Build things that matter. We're looking for a Cloud Security Engineer. You'll build new security capabilities for Kubernetes, Linux hosts and cloud environments, research emerging technologies and attack techniques, and ship end-to-end product features together with the product and engineering teams. Responsibilities Build end-to-end features across Aikido's cloud security products (CSPM, Kubernetes Security, Cloud Inventory, Reachability and more) Cover Kubernetes, containers, and IaC (Terraform, CloudFormation, and similar). Ship production-ready user-facing functionality across the entire stack Research AWS, Azure, Google Cloud and Kubernetes to turn complex cloud concepts into intuitive security features Work directly with customers to understand real-world cloud security problems and help solve them Collaborate with the rest of engineering to integrate cloud capabilities into the core Aikido platform Take ownership of features from idea to production, including testing, documentation and maintenance
+Strong software engineering experience with Go (or another backend language and willingness to learn Go) Experience building production software, not just operating infrastructure Comfortable working across the stack when a feature requires it Solid understanding of at least one public cloud provider (AWS, Azure, or Google Cloud) Experience with Kubernetes and modern cloud-native architectures Curious enough to research unfamiliar cloud services and quickly turn that knowledge into product features Comfortable discussing technical problems directly with customers Really comfortable in a fast-moving startup environment Willing to experiment, iterate quickly, and occasionally throw code away Mid-level to Senior: we're growing fast and need people who can own features independently Fluent in English and able to work within the CEST timezone What you can expect Short decision lines. Big ownership. Shape the projects that matter and ship fast. Grow as fast as we do. Take on more, own more, and carve out your own path. Top-tier tech pay and equity. High trust, strong values, zero corporate BS. Flexibility in working hours. A company that sticks to its values in an open and informal atmosphere. We hire for talent, drive, and potential. Everything else is noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>guidepointsecurity</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AI Security Engineer (Remote in the U.S.)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6216717004?gh_jid=6216717004</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>GuidePoint Security provides trusted cybersecurity expertise, solutions and services that help organizations make better decisions and minimize risk. By taking a three-tiered, holistic approach for evaluating security posture and ecosystems, GuidePoint enables some of the nation’s top organizations, such as Fortune 500 companies and U.S. government agencies, to identify threats, optimize resources and integrate best-fit solutions that mitigate risk.
+**General Description**
+The GuidePoint Security North Central region is seeking a skilled AI Security Engineer to join our growing AI Security Services team within the Automation and AI Practice. You will assist customers in the design, implementation, security, and operational management of generative AI security solutions — including AI governance assessments, LLM and agent security testing, shadow AI discovery, agentic workflow development, and architecture reviews.
+**About the North Central AI Security Practice**
+You will work closely with peers across multiple domains including AppSec, Cloud Security, and Identity and Access Management to deliver holistic and secure solutions adhering to industry best practices. This role offers the opportunity to contribute directly to the continued growth of our AI security practice and its expanding service portfolio.
+**Roles and Responsibilities:**
+- **AI Security Architecture &amp; Assessment:** Conduct secure configuration reviews and security assessments of enterprise AI platforms (e.g., Anthropic Claude Enterprise, OpenAI ChatGPT Enterprise, Microsoft Copilot) against established control domains — including identity and provisioning, network and access enforcement, data protection and retention, and audit and compliance — identifying vulnerabilities, attack surfaces, and gaps against industry frameworks (e.g., OWASP LLM Top 10, MITRE ATLAS)
+- **Threat Modeling for AI Systems:** Lead threat modeling exercises specific to AI workloads, covering prompt injection, model inversion, data poisoning, supply chain risks, excessive agency, privilege escalation through tool chaining, and unauthorized cross-application data movement across SaaS, self-hosted, and local AI deployments
+- **AI Coding Tool &amp; Development Environment Security:** Assess AI coding tools and development environments — including Claude Code, OpenAI Codex, Open Code, Cursor, and MCP servers — for sandbox isolation, plugin allowlisting, secrets access, network egress controls, and CI/CD pipeline security
+- **Secure AI Integration Guidance:** Advise client teams on securely integrating SaaS AI services and APIs (e.g., OpenAI, Azure OpenAI, AWS Bedrock) into enterprise applications, including safe handling of credentials, outputs, and user data
+- **Data Security &amp; Privacy Controls:** Evaluate and recommend controls for data ingestion pipelines, RAG architectures, and vector databases to prevent unauthorized data exposure, leakage through model outputs, or non-compliant data processing — including zero data retention enforcement, sensitivity labeling, data classification, and encryption key management
+- **Shadow AI Discovery:** Conduct shadow AI discovery engagements to inventory unsanctioned AI tool usage and assess associated data exposure risks across client environments
+- **Security Controls &amp; Guardrails Evaluation:** Evaluate security controls and guardrails across AI platforms, including identity and access management, DLP integration, conditional access policies, SIEM and logging configurations, human-in-the-loop mechanisms, and AI-specific runtime protections
+- **Agentic Workflow Development:** Design, build, and deploy AI agent workflows including use-case design, agent architecture, and integration with security tooling and automation platforms
+- **Security Architecture Reviews:** Perform security architecture reviews for organizations deploying AI agents that connect to tools, data sources, or other agents via MCP or agentic frameworks, delivering reference architectures and recommendations
+- **Security Documentation &amp; Deliverables:** Develop and deliver engagement artifacts including secure configuration review reports, prioritized findings registers, AI security control matrices, reference architectures, risk assessments, control frameworks, and secure enablement roadmaps
+- **Strategic AI Security Roadmap:** Contribute to the development of long-term AI security strategies for clients, including prioritized remediation roadmaps, capability maturity assessments, and investment recommendations
+- **Collaboration &amp; Stakeholder Engagement:** Serve as a trusted security advisor bridging business stakeholders, AI/ML engineers, IT operations, and information security teams — conducting stakeholder interviews and facilitating knowledge transfer sessions covering AI platform administration, troubleshooting, and operational runbooks
+- **AI Threat Landscape Monitoring:** Continuously track emerging AI security research, adversarial techniques, regulatory developments, and vendor security advisories (e.g., Anthropic, OpenAI, Microsoft feature releases) to keep client guidance relevant and proactive
+**Required Experience and Education:**
+- 3+ years of experience in security engineering with a significant focus on cloud security and/or application security
+- Hands-on experience implementing, managing, securing, and supporting agentic AI solutions within an enterprise context, including enterprise AI platforms such as Anthropic Claude (Enterprise, Desktop, Cowork, Code), OpenAI (ChatGPT Enterprise, Codex, API), or Microsoft Copilot
+- Familiarity with major cloud service provider AI-focused services such as AWS Bedrock, AWS SageMaker, Azure AI Foundry, or Google Vertex
+- Solid understanding of generative AI concepts, Large Language Models (LLMs), context engineering, agentic tool usage, and foundational AI/ML principles
+- Operational experience in the usage of agentic coding assistants such as Claude Code, Open Code, Cursor, or Codex
+- Understanding of AI-specific security challenges including prompt injection, data poisoning, supply chain security, model extraction attacks, excessive agency, and privilege escalation through tool chaining
+- Ability to produce professional client-facing deliverables including assessment reports, findings registers, control matrices, and reference architecture documentation
+- Strong written and verbal communication skills with the ability to explain complex technical concepts to both technical and non-technical audiences
+- Embraces emerging technologies, including AI tools, to work smarter, solve problems, and drive better business outcomes
+**Preferred Experience and Education**
+- Certifications such as AWS Certified AI Practitioner, AWS Certified Machine Learning Engineer, Azure AI Engineer Associate, or Claude Certified Architect
+- Understanding or experience with model fine-tuning techniques
+- Experience with policy as code languages like Cedar or Rego and Infrastructure as Code (IaC) tools like AWS CloudFormation, Terraform, OpenTofu, or equivalent technologies
+- Experience designing and implementing agentic AI architectures that balance security and autonomy
+- Familiarity with MCP client/server architecture vs. agentic skills and the associated security risks of each
+- Experience with AI security tooling categories such as AI Security Posture Management (AISPM), AI runtime protection, or AI control plane platforms
+- Prior experience in a consulting, professional services, or managed services delivery model with direct client engagement
+**Travel Requirements:**
+- Up to 10% travel
+**Physical Requirements:**
+- Sedentary work
+- Substantial movement of the wrists, hands, and/or fingers for a minimum of 8 hours a day
+- Required to have close visual acuity to view computer terminal and/or extensive reading for a minimum of 8 hours a day
+**We use Greenhouse Software as our applicant tracking system and Zoom Scheduler for HR screen request scheduling. At times, your email may block our communication with you. Please be sure to check your SPAM folder so that you don't miss updates on your application.**
+**Why GuidePoint?**GuidePoint Security is a rapidly growing, profitable, privately-held value added reseller that focuses exclusively on Information Security. Since its inception in 2011, GuidePoint has grown to over 1,300 employees, established strategic partnerships with leading security vendors, and serves as a trusted advisor to more than 6,200 customers.
+Firmly-defined core values drive all aspects of the business, which have been paramount to the company’s success and establishment of an enjoyable workplace atmosphere. At GuidePoint, your colleagues are knowledgeable, skilled, and experienced and will seek to collaborate and provide mentorship and guidance at every opportunity.
+This is a unique and rare opportunity to grow your career along with one of the fastest growing companies in the nation.  
+**Some added perks….**
+- Remote workforce primarily (U.S. based only, some travel may be required for certain positions, working on-site may be required for Federal positions)
+- Group Medical Insurance options: Zero Deductible PPO Plan (GuidePoint pays 90% of the premium for employees and 70% for family plans (spouse/children/family) or High Deductible Health Plan with HSA (GuidePoint pays 100% of the employees premiums and 75% for family plans (spouse/children/family). If you choose the High Deductible / HSA plan, GPS will contribute in 4 equal quarterly installments: ($850 per EE annually / $1750 per family annually (includes spouse/children/family options)
+- Group Dental Insurance: GuidePoint pays 100% of the premium for employees and 75% of family plans
+- 12 corporate holidays and a Flexible Time Off (FTO) program
+- Healthy mobile phone and home internet allowance
+- Eligibility for retirement plan after 2 months at open enrollment
+- Pet Benefit Option</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>detectify</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Security Research - LIA/Internship (Unpaid)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>teamtailor</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.detectify.com/jobs/8500343-security-research-lia-internship-unpaid</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>What we do at Detectify We’re Detectify, and we’re not your average cybersecurity company. We’re a team obsessed with building cutting-edge tech that actually makes a difference in making the internet a safer place. We’re talking about real-life hackers who know their stuff—you’ll learn from the best and join a team that combines human ingenuity with automation to streamline asset discovery and vulnerability assessments. The Vulnerability Assessment Research team This team is currently composed of security researchers focused on making sure that the members of Detectify Crowdsource - our network of ethical hackers - are engaged and enjoying the best possible experience when collaborating with Detectify. When our hackers submit a vulnerability through our Crowdsource platform, our team builds a module for it and adds it to the Detectify service. Once a vulnerability is reported to us, it becomes a security test which is then made available to all our customers - this is how Detectify combines automation and crowdsourcing. These tests come in various unique flavors and are driven by crowdsourced security knowledge. We in the Vulnerability Assessment Research team are responsible for validating, configuring, and executing such tests on our customers’ web applications. We aim for the best possible scanning performance with comprehensive coverage of possible security issues, optimizing for flow, fast feedback, and quality. We follow lean and DevOps concepts, aiming to be innovative and helpful, and to have a strong sense of ownership of all the things we build. What you'll get to do As a Security Researcher, your main responsibility will be to validate and implement proof of concepts, uploaded by our Crowdsource and internal researchers, into our scanners. This is a great opportunity to boost your knowledge around hacking and vulnerabilities. Other responsibilities include: Communicate with our internal security researchers in order to gather all necessary information to understand the submitted vulnerabilities. Develop modules from vulnerability reports using a JSON-based DSL or Go. Perform code reviews to ensure accuracy and reduce false positives. Consistently review behavior of implemented modules to identify false positives or negatives. Work with continuous automation of module development. Who you are We believe that you are a student and want to do your LIA (work placement) with us here at Detectify for a period of 6 months. You are a highly versatile and self-motivated individual who can create and drive change. You are involved with the security community and understand how vulnerabilities work. You have a strong interest in internet security and you want to engage with an international network of security researchers. Ideally, you have some hands-on experience with bug bounties, CTFs (Capture the Flag), or similar. So, what do you think? We are proud to foster an inclusive workplace free from discrimination. We strongly believe that diversity of experience, perspectives, and backgrounds will lead to a better environment for our employees and a better product. This is something we value deeply and we encourage everyone to be a part of changing the way the world thinks about security! Go hack yourself! Location This position is for the Stockholm office and we'd like to see you there in person a few times per week. So, what do you think? We are proud to foster an inclusive workplace free from discrimination. We strongly believe that diversity of experience, perspectives, and background will lead to a better environment for our employees and a better product. This is something we value deeply and we encourage everyone to be a part of changing the way the world thinks about security! Go hack yourself!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L'Oréal Groupe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cybersecurity Architect and Engineering &amp; Innovation Manager</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Saint-Ouen, Centre-Val de Loire, France</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>welcometothejungle</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/85DZZr7/jobs/cybersecurity-architect_saint-ouen</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Join L'Oréal, the global leader in beauty, as a Cybersecurity Architect and Engineering &amp; Innovation Manager. In this role, you will define the security architecture, help with the adoption of the Zero Trust strategy, and ensure compliance with L'Oréal's Information Security Policy. You will need a strong technical background in IT security, excellent communication skills, and at least 5 years of experience in information security. L'Oréal offers a hybrid work policy, numerous benefits, and a commitment to diversity and inclusion.
+- Definir y comunicar patrones y plantillas de arquitectura de ciberseguridad, y proporcionar la validación final para las arquitecturas de proyectos.
+- Ayudar a proporcionar soluciones globales para resolver problemas descubiertos por nuestro proceso de Gestión de Amenazas y Vulnerabilidades.
+- Actuar como un evangelista de la ciberseguridad, diseñando y liderando sesiones de concienciación atractivas para el personal de TI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>brunswickgroup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lead Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/brunswickgroup/jobs/8867735002</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>## Opportunity
+The Lead Application Security Engineer will join Brunswick's Information Security team and play a key role in shaping how the firm embeds security into application design, development, deployment, and technology change.
+This is a senior individual contributor role initially, with scope to help establish and mature Brunswick's application security capability over time. The role will focus on providing risk-based security advice and assurance across internally developed applications, enterprise platforms, integrations, cloud services, SaaS solutions, and selected AI-enabled workstreams.
+Working closely with ICT, AI Engineering, application owners, and business stakeholders, the Lead Application Security Engineer will help define practical security standards, guardrails, review processes, and secure design patterns that enable delivery teams to move at pace while managing risk appropriately.
+## About the Role
+In this role, you will provide senior application security and DevSecOps expertise across technology projects, design reviews, cloud-based applications, APIs, integrations, delivery pipelines, and selected AI-enabled solutions.
+You will act as a senior security advisor to technical and business teams, helping establish a repeatable application security model that can scale as demand grows, including the potential introduction of additional team members in the future.
+Key responsibilities include:
+- Lead the development of Brunswick's application security capability, including standards, secure design patterns, review processes, and practical guardrails.
+- Act as a senior security advisor to ICT, AI Engineering, application owners, and business stakeholders.
+- Review and assess application designs, architecture decisions, APIs, integrations, cloud services, and deployment patterns to identify security risks early in the delivery lifecycle.
+- Mature repeatable approaches for application security reviews, threat modelling, and risk-based assurance across new and changed solutions.
+- Provide guidance and oversight on secure development lifecycle practices, including security requirements, design review, code and security review considerations, dependency management, secrets management, testing, and release assurance.
+- Conduct threat modelling for internally developed applications, AI-enabled workflows, integrations, automation use cases, and higher-risk technology changes, using STRIDE or similar methodologies.
+- Advise on secure design principles, including identity and access management, API security, data protection, encryption, logging, monitoring, resilience, secure configuration, and least privilege.
+- Support security review of CI/CD pipelines, infrastructure as code, containerised workloads, and cloud infrastructure, identifying practical controls for engineering and platform teams.
+- Review and assess third-party platforms, SaaS solutions, and new technology features, including AI-enabled tools where there are material application, integration, or data security considerations.
+- Support the development and application of secure patterns and guardrails for emerging technology adoption, including AI-enabled solutions, agents, and automation where relevant.
+- Support security assurance activities, including penetration testing, application security testing, remediation tracking, and ensuring appropriate logging, monitoring, and response considerations are built into new solutions.
+- Define and document security requirements, architecture decisions, design recommendations, and risk-based remediation actions.
+- Support the future growth of the application security function, including helping define ways of working, capability needs, and technical guidance for future team members as the function matures.
+## What We're Looking For
+We're looking for an experienced, technically capable security professional who can lead and mature an application security capability while remaining pragmatic, hands-on, and delivery-focused.
+The ideal candidate will demonstrate:
+- 7+ years' experience in cyber security, application security, DevSecOps, cloud security, security architecture, security engineering, or a related technical security role.
+- Strong understanding of risk management and compensative controls.
+- Experience operating as a senior technical advisor or lead within application security, DevSecOps, cloud security, secure engineering, or a related discipline.
+- Proven experience working alongside software engineering, DevOps, platform, cloud, or ICT teams to secure applications and infrastructure throughout the delivery lifecycle.
+- Strong understanding of secure development lifecycle and application security practices, including threat modelling, secure design, API security, authentication and authorisation, secrets management, dependency management, security testing, and remediation planning.
+- Practical experience reviewing application architectures, APIs, integrations, cloud services, CI/CD pipelines, containerised workloads, or infrastructure as code.
+- Practical understanding of Microsoft 365, Azure, SaaS platforms, and Azure application security controls such as Entra ID, managed identities, Key Vault, API Management, container security, logging, monitoring, and secure configuration.
+- Experience conducting STRIDE-based threat modelling, technical risk assessments, application security reviews, or security design reviews.
+- Experience developing security standards, secure design patterns, review processes, or guardrails that can be adopted by engineering and delivery teams.
+- Ability to translate technical security risks into clear, business-focused recommendations and influence delivery teams without directly owning implementation.
+- Familiarity with AI-related technologies, large language models, AI-enabled applications, and associated risks such as data exposure, prompt injection, insecure integrations, and excessive agent permissions would be beneficial.
+- Strong written and verbal communication skills, sound judgement, attention to detail, and the ability to balance security requirements with business needs.
+- Experience working in an ISO27001-aligned or regulated environment would be beneficial.
+- Preferred, but not essential, certifications:
+- ISC2: CISSP, CCSP, SSCP, CSSLP
+- ISACA: CISM, CISA, CRISC
+- CompTIA: Security+, CySA+, CASP+
+- GIAC, Microsoft Azure, or other relevant application security, cloud security, architecture, or DevSecOps certifications
+## Why Join Us
+Joining Brunswick unlocks a range of employee benefits to support your financial future, health and wellness, family and community, and continuous professional development.
+# About Brunswick
+Brunswick is a global advisory firm. We help companies tackle high-stakes issues, navigate complex stakeholder relationships, and deliver high-impact outcomes.
+Our clients value our ability to anticipate, shape, and respond to the key players and forces in the financial and investment arena, regulatory and geopolitical universe, NGO community, workforce and beyond. They rely on us for deep experience, fresh perspectives and original thinking. So, in Brunswick you will find an exceptional range of experience and talent with a rich mix of backgrounds. From the beginning, we have prioritized attracting, developing, and retaining the best professionals in the industry, united by a culture of inclusivity, excellence, and intellectual curiosity.
+Founded in 1987 in London, the firm has organically grown to 27 offices in 18 countries across the Americas, Europe, Middle East, Africa, Asia and Australia. We operate as a “one-firm firm” with no individual profit centers. This allows us to assemble fully integrated, bespoke teams for each client, able to draw on the full resources of Brunswick anywhere in the world.
+*Brunswick is an equal opportunity employer.  All qualified applicants will be considered without regard to race, religion, color, national origin, gender, sexual orientation, age, disability, pregnancy, genetic information, or any other status protected by applicable law. Please read our [Global Privacy Notice](https://www.brunswickgroup.com/app/uploads/Group-Privacy-Notice-for-Employees_April-2026.pdf) to understand how your data is managed.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>backmarket</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Staff Engineer - Cybersecurity Architect</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/backmarket/3dc7e1be-0451-4119-8f68-85c22a95f50d/application</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>## Hi, we’re Back Market.
+We’re here to help **make tech reliable, affordable, and better than new**. We're a global marketplace for refurbished devices, helping lower our collective environmental impact by providing trustworthy, affordable tech with 92% less carbon emissions than new.
+Yep, you read that right. Turns out refurbished tech is way better for the planet than new. In fact, With every device purchased on Back Market, our positive impact on the planet grows. From our Customer Care representatives to our software engineer, every individual at Back Market cuts the planet — and consumers — a break. **Our mission is simple: to do more with what we already have.**
+Are you ready to join us?
+As our Staff Engineer - Cybersecurity Architect, you will translate Back Market Cyber and IT strategy into a global Cybersecurity architecture by connecting the business processes with the application, data and infrastructure layers. Your ultimate goal is to design an organisation-wide secure architectural plan. You will play a crucial role in the digital transformation within Back Market.  
+You will be the owner for the creation of architecture models that reflect the company's strategies and goals and take responsibility for securing the enterprise architecture within one or more domains.  
+You'll be part of the Platform Dept which covers several squads, including about thirty people working on IT, GRC, SecOps, and other areas.  
+**You will be the owner for the creation of architecture models that reflect the company's strategies and goals and take responsibility for securing the enterprise architecture within one or more domains.**  
+You’ll do this by:
+- Analyzing business needs from an architectural point of view to translate them into performant and coherent ICT solutions
+- Developing, implementing, monitoring, evaluating and adjusting the architecture in order to have a coherent framework within projects and developments
+- Presenting and developing recommendations and translating them into executable roadmaps
+- Creating secure architecture patterns for complex and large technology environments together with stakeholders
+- Identifying and specifying implementation modalities of both existing and new technologies
+**You play a crucial role as a point of contact for both business and IT when it comes to Back Market ICT architecture.**  
+You’ll do this by:
+- Providing guidance on enterprise architecture and systems processing in the data, application, integration, security and technology areas.
+- Promoting continuous improvement and development of methodologies used, among others.
+- Proposing improvements to optimise the functionality of the IT department with a view to cost efficiency, among other things.
+- Building a bridge between IT and business by advising management on complex ICT issues, ensuring decision-making.
+**You identify challenges and opportunities in collaboration with stakeholders to ensure the success of your projects.**  
+You do this by:
+- Reconciling conflicting requirements and functions by finding appropriate technological solutions.
+- Facilitating and leading the substantive decision-making process within the project team. You define and follow the validation mechanisms.
+- You ensure that decisions on the projects are made on the basis of solid governance.
+- You keep abreast of evolutions and developments in IT architecture and relevant technologies. You estimate their usability and possibilities within the context of Back mMarket. In this way, you contribute to defining the future-oriented prevailing principles and frameworks.
+- Conduct technical risk analyses to identify, assess, and mitigate security risks across systems, applications, architectures, and technology initiatives, providing actionable recommendations aligned with security standards and business objectives.  
+  As a **Staff Engineer - Cybersecurity Architect**  at Back Market, you will have a critical responsibility to enhance the security posture of Backmarket's entire IT landscape.   
+  You will be tasked with the following:
+  - Collaborating closely with IT teams to integrate security best practices into both the design and implementation phases of IT projects.
+  - Translate high-level security policies set by the GRC team into detailed technical solutions within project designs and IT changes.
+  - Ensure that all new and existing IT projects are compliant with the latest security standards and practices.
+  - Design and recommend security standards, security architecture principles and technical requirements.
+  - Perform technical risk assessments and provide technical mitigations
+  ## **What makes you the right profile for a** Staff Engineer - Cybersecurity Architect **?**
+- You have at least 10 years of experience within security and tech &amp; you have previous enterprise security architecture experience
+- You breathe security architecture and get your satisfaction from delivering architectural deliverables. As a result, you inspire colleagues and fuel their drive
+- Your analytical mind enables you to understand the complex business model and associated systems. By applying secure architectural patterns, you achieve successful translation into designs and system requirements, among other things
+- You bring simplicity and transparency to communication, subordinating the complexity of the technical solutions to the target architecture
+- You are always attentive to technological developments and know how to translate them into business opportunities. By taking your advisory role within this position, you know how to convince management of the necessary evolutions
+- You keep in touch with the technical implementation aspects, making you an understanding interlocutor for the technical teams
+- You see documentation and communication as essential, so that the architecture is supported by the entire Back Market organisation
+  **Requirements and qualifications**
+- In-depth knowledge of GCP cloud
+- Security by design/Zero trust/Defense in depth
+- IA security (MCP, Claude, Opencode, etc)
+- Security of MAC endpoints
+- Expertise in IAM (Okta) systems and standards.
+- Familiarity with compliance requirements and industry standards such as GDPR, ISO 27001, NIST frameworks.
+## **Hiring Process**
+- Visio call to get to know you better by a TA - 45 min
+- Technical Interview - 60 min
+- Meet your team - 45 min
+- Stakeholder interview - 45 min
+- Meet the Staff community - 30 min
+- BM Values interview - 45 min
+## **WHY SHOULD YOU JOIN US ? ✌🏼**
+At Back Market, we’re committed to hiring and supporting diverse teams of people from all backgrounds, experiences, and perspectives — it’s one of the reasons we’re such a high-scoring certified B Corp company (93.2).
+No matter your role and seniority level, you’ll enjoy impact-driven work with hands-on career development in an innovative, driven, and fast-paced environment — with benefits to match, like:
+- A mission driven work environment where your day to day makes an impact on the planet. Seriously.
+- Hybrid work environment, with 2 remote days a week and 1 remote work week per quarter, plus 3 flex days.
+- Employee Resource Groups, including mentorship programs, comprehensive accessibility policies, and cultural competency training.
+At Back Market, we strive to create a workplace that embodies the world we’re trying to change. We’ve embedded our diversity, equity, and inclusion principles into our DNA — from dedicated staff to employee resource groups to our company values.
+We know that the perfect background for a role doesn’t mean the perfect fit — we encourage you to apply for a role even if you think you may not have all the qualifications.
+If reasonable accommodations are needed for the interview process, please do not hesitate to discuss this with the Talent Acquisition Team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Senior Cloud Security Consultant</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Amsterdam, NH, nl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes / Mentioned</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Sia/744000153471584-senior-cloud-security-consultant?oga=true</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Within Sia, you will join our Cybersecurity &amp; AI Trust Unit. As a Senior Consultant in Cloud Security, you will be required to design, implement and control solutions ensuring the security of applications and data hosted in public, private and hybrid clouds (IaaS, PaaS or SaaS) of our key account customers, in particular on the following issues: Benchmark and decision support for technical choices around Cloud solutions and offers; Design of Cloud solutions both technically and functionally; Realization of PoC/PoV and automation of the installation of technical bases; New architectural principles (micro services, containers, etc.) and new deployment methods induced by Cloud infrastructures (continuous integration and delivery in particular); Training of users and administrators in the deployed solutions. As part of your operational interventions, and your contributions to the internal development of the firm, you will be able to: Innovate within our Sia CyberLab, where you work on the development of new SaaS offers and solutions around advanced technologies and capitalizing on our unique know-how in AI. You will also carry out benchmarks and PoCs of Cyber ​​solutions on the market, while participating in active monitoring of Cyber ​​news. Become a trainer in Cybersecurity within the Cybersecurity &amp; AI Trust institute, where you will intervene in the preparation and animation of certifying training sessions as an approved trainer, as well as in the animation of personalized awareness and coaching sessions. Participate in the influence of the firm, around our Cybersecurity expertise, by actively contributing to the publication plan (articles, insights, white papers, studies, webinar, etc.), and represent the firm at various professional clubs, fairs and events. Take part in the development of the activity by designing and developing commercial proposals, as well as by identifying new opportunities for collaboration with our customers. Manage end-to-end projects, or will be responsible for sub-projects of a complex and/or international project, on which you provide relevant, proactive and regular reporting to the attention of the Manager and the Client in order to guarantee the respect of our commitments. Manage the customer relationship on your missions and build a solid relationship with your contacts on the customer side, at middle management level, who recognize you as an expert on the subjects dealt with. Supervise consultants, Juniors to Confirmed, within the framework of missions, or internal projects, where you will have the role of referent and relay of the Manager / Senior Manager for the follow-up of the sites, the validation of the deliverables, the evaluation of the achievements, and above all you will ensure the development of their soft skills and hard skills.
+You have a Master's degree engineering/computer science/statistics/econometrics. You have 3-6 years relevant working experience within a consultancy firm with experience in cybersecurity projects. You have a strong interest in data and AI-related topics, the ability to quickly build expertise in these areas, and you’re excited about helping our clients seize the opportunities they offer. Knowledge in Python, C++, Java, Ruby, Node, Go, and/or Power Shell. Knowledge in IP Networks, Operating Systems (Unix / Linux, Windows and/or macOs), Cloud (AWS, Azure and/or GCP), Applications (Web Server, BDD, Middleware, etc) as well as Cryptography; knowledge in Blockchain would be a real plus. You're a fast learner, communicative, flexible and entrepreneurial English &amp; Dutch communication and presentation skills. What do we offer? Competitive salary with great extra advantages: a clear and structured yearly salary increase and bonuses. Flexible transport options that match your personal needs. Training plan to develop yourself as an expert in your discipline. You have the opportunity to work from home, the client or from our inspiring office in Amsterdam. Working in an international environment which creates opportunities to share knowledge and work together on international projects with colleagues all over the world.
+We are unable to provide a work permit for this position Non-Dutch speaker will no be accepted Sia is an equal opportunity employer. All aspects of employment, including hiring, promotion, remuneration, or discipline, are based solely on performance, competence, conduct, or business needs. Sia is an equal opportunity employer. All aspects of employment, including hiring, promotion, remuneration, or discipline, are based solely on performance, competence, conduct, or business needs.
+Sia is a next-generation, global management consulting group. Founded in 1999, we were born digital. Today our strategy and management capabilities are augmented by data science, enhanced by creativity and driven by responsibility. We’re optimists for change and we help clients initiate, navigate and benefit from transformation. We believe optimism is a force multiplier, helping clients to mitigate downside and maximize opportunity. With expertise across a broad range of sectors and services, our 3,000 consultants serve clients worldwide from 48 locations in 19 countries. Our expertise delivers results. Our optimism transforms outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>zeely</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/zeely/ec13f026-11a0-47ab-ae1a-bc700e00b7b6/application</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Join **Zeely** as a **Security Engineer** and help us protect our products, infrastructure, and data as we scale.
+This is a hands-on role: you'll find and fix vulnerabilities, close security tickets yourself, and help us defend against attacks. You'll work closely with Secutity Officer, engineering, DevOps, and Platform teams and help strengthen our security function as we grow.  
+**About Us:**  
+Zeely is the agentic AI platform for creating, launching, and scaling paid ads.
+Simply put: we've made the best AI solutions and marketing tools available to small and medium businesses — tools that used to be reserved for big brands with expensive marketing teams.
+The next big step: a B2B solution for large marketing teams and enterprise clients — workflows, creative analytics, and full control over campaigns across the whole team. For companies where performance marketing already runs at scale and needs more efficiency and automation.
+**A few numbers that speak for themselves:**
+- 4 years on the market — a stable, profitable company backed by international investors;
+- 6× growth over the past year;
+- 2,000,000+ businesses already use Zeely;
+- #1 in its category in the US market;
+- 200+ specialists on the team;
+- Markets: US + worldwide.
+**What You'll Do:**
+- Identify, prioritize, and fix vulnerabilities across our product and cloud infrastructure;
+- Respond to security incidents and help defend against attacks in real time;
+- Close security tickets end to end, from investigation to fix in code or infrastructure;
+- Integrate security checks and tooling into our development pipeline (SDLC / CI/CD);
+- Review code and infrastructure changes from a security perspective;
+- Help implement security controls and gather evidence for compliance (SOC 2, CASA);
+- Work with the DevOps and Platform teams on access management, secrets, and hardening of our AWS environment.
+**What Do You Need to Join Us?**
+- 5+ years of engineering experience, with the ability to work fully independently;
+- 2+ years of hands-on experience in security (Security Engineer, or a combined Security/DevOps or Platform role);
+- Backend development background in at least one of: Node.js / JavaScript / TypeScript, Java, C#/.NET, Go, or Rust;
+- Strong practical experience with DevOps and cloud infrastructure (AWS);
+- Hands-on experience finding and fixing vulnerabilities (OWASP Top 10, cloud misconfigurations, dependency issues);
+- Experience handling security incidents;
+- Upper-Intermediate (B2+) English or higher;
+- Fluent Ukrainian.
+**Nice to Have:**
+- A career path from backend to DevOps/Platform to Security;
+- Security certifications (AWS Security Specialty or similar);
+- Experience preparing for SOC 2, ISO 27001, or CASA audits;
+- Understanding of GDPR and/or CCPA (CPRA) requirements.
+**Why It's Worth Joining Us:**
+- A hands-on security role with real impact in a stable, profitable product company;
+- Work with cutting-edge technologies and contribute to building AI-powered tools;
+- A strong team of A-level players who push each other to grow;
+- A remote-first setup with offices in Warsaw and Kyiv;
+- Regular performance reviews to keep your growth transparent and rewarded.
+**Recruitment Process:**
+Intro Call → Technical Interview → Test Task → Final Interview → Reference Check → Offer.
+Send us your CV — we'd love to meet you!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>paconsulting</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Melbourn, gb</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/PAConsulting/744000153431824-ai-security-engineer?oga=true</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Hybrid working - our approach is to be in the office a minimum of 2 days per week. PA’s IT team, internally known as Group Systems, is comprised of a variety of areas that support the wider firm, consisting of four key pillars: Strategy, Architecture and Infrastructure Services; ​Enterprise Solutions; Technology and Operations​; and ​Cyber Security and Compliance​. The successful candidate will be covered two primary areas: the security of AI (protecting the organisation's own AI systems and use of AI) and AI for security (using AI to strengthen protection, detection and response). This role will sit within Cyber Security and Compliance. Technical ownership of AI security tool selection and deployment Define requirements, run structured evaluations and proofs of concept, and judge vendor claims on evidence rather than marketing. That means measuring detection efficacy, false positive rates, latency and operational overhead. The tool categories to cover include AI security posture management, LLM guardrails and firewalls, model and supply-chain scanning, GenAI data loss prevention, and AI-enabled SOC tooling. They should also own the deployment itself: integration with existing SIEM, SOAR, EDR and identity tooling, architecture decisions, and making sure the tools are tuned and producing value after go-live rather than becoming shelfware. Input to vendor risk assessments fits here too, particularly on how vendors handle your data in their own models. Understanding the AI threat landscape They need a working knowledge of AI-specific attack techniques and should be fluent in the reference frameworks, mainly the OWASP Top 10 for LLM Applications and MITRE ATLAS. Key threats include: Direct and indirect prompt injection Data and model poisoning Sensitive data leakage through prompts and outputs Model theft and extraction Malicious model files in the supply chain The growing set of risks from agentic AI, such as excessive permissions and tool misuse They also need to understand how attackers use AI against the organisation (more convincing phishing, deepfake-enabled fraud, faster reconnaissance and exploit development) and how that changes your threat model. Shadow AI, meaning unsanctioned use of AI tools by staff, is a practical, near-term issue they should be able to discover and manage. Demonstrating AI in protection, detection and response This is where the role earns its keep with stakeholders. In protection, that might mean AI-assisted vulnerability prioritisation, secure code review, or posture analysis. In detection, it covers behavioural anomaly detection, alert triage and enrichment, and LLM-assisted threat hunting. In response, it includes AI copilots for investigation and incident summarisation, automated playbooks, and agentic response actions. A good candidate will be clear-eyed about limits: where human-in-the-loop controls are needed, how to validate AI outputs, and how to avoid automating mistakes at speed. The ability to build or run demonstrators that show value concretely is a strong differentiator. Assurance and testing The role should include adversarial testing and red teaming of the organisation's AI systems, whether done directly or by scoping and overseeing third parties. Examples are testing RAG applications for injection and data exposure, or checking that an agent can't be manipulated into acting outside its intended permissions. Alignment with governance and standards This isn't primarily a governance role, but the engineer should translate frameworks into technical controls and evidence. The relevant reference points are: NCSC's Guidelines for Secure AI System Development The UK government's AI Cyber Security Code of Practice NIST AI RMF ISO/IEC 42001 The EU AI Act, where relevant to clients or operations
+Skills and background The ideal profile is a security engineer (typically from cloud security, security architecture, or SOC engineering) who has built genuine ML and LLM literacy. That means understanding how models, RAG pipelines and agents work, reasonable Python or scripting ability, and cloud platform experience. Communication matters more than usual: this person will regularly need to explain AI risk and capability to non-specialist decision-makers without overselling or scaremongering. Measures of success Useful indicators: Tools selected and deployed against defined requirements, with measurable outcomes (reduced triage time, improved detection coverage) An AI asset inventory and threat model in place AI systems tested before deployment Demonstrators that have influenced investment or adoption decisions We know the skill-gap and ‘somewhat need to tick every box’ can get in the way of meeting brilliant candidates, so please don’t hesitate to apply – we’d love to hear from you. Apply today by completing our online application Please be aware that some of our UK roles at PA Consulting require a UK security clearance. All PA people are required to undergo background checks and to achieve the Baseline Personnel Security Standard however, some UK roles also require higher levels of National Security Vetting, where applicants must have at least 5 years of continuous residency in the UK. We therefore ask that you only apply if you meet the residency requirements (i.e. you are a British citizen or have been resident in the UK for the past 5 years), as this is the prerequisite for a security clearance. If you're unsure about your eligibility, we encourage you to review the UK Government’s guidance on security vetting before applying.
+Life At PA encompasses our peoples' experience at PA. It's about how we enrich peoples’ working lives by giving them access to unique people and growth opportunities and purpose led meaningful work. We believe diversity fuels ingenuity. Diversity of thought brings exciting perspectives; diversity of experience brings a wealth of knowledge, and diversity of skills brings the tools we need. When we bring people together with diverse backgrounds, identities, and minds, embracing that difference through an inclusive culture where our people thrive; we unleash the power of diversity – bringing ingenuity to life. Find out more about Life at PA here . We are dedicated to supporting the physical, emotional, social and financial well-being of our people. Check out some of our extensive benefits: Health and lifestyle perks accompanying private healthcare for you and your family 25 days annual leave (plus a bonus half day on Christmas Eve) with the opportunity to buy 5 additional days Generous company pension scheme Opportunity to get involved with community and charity-based initiatives Annual performance-based bonus PA share ownership Tax efficient benefits (cycle to work, give as you earn) We recruit, retain, reward and develop our people based solely on their abilities and contributions and without reference to their age, background, disability, genetic information, parental or family status, religion or belief, race, ethnicity, nationality, sex, sexual orientation, gender identity (or expression), political belief, veteran status, or any other range of human difference brought about by identity and experience. We are on a journey towards ensuring our workforce is diverse at all levels and that our firm is representative of the world around us. We welcome applications from underrepresented groups. Adjustments or accommodations - Should you need any adjustments or accommodations to the recruitment process, at either application or interview, please contact us. #LI-HM3
+We believe in the power of ingenuity to build a positive human future. As strategies, technologies, and innovation collide, we create opportunity from complexity. Our teams of interdisciplinary experts combine innovative thinking and breakthrough technologies to progress further, faster. Our clients adapt and transform, and together we achieve enduring results. We are over 4,000 strategists, innovators, designers, consultants, digital experts, scientists, engineers, and technologists. And we have deep expertise in consumer and manufacturing, defence and security, energy and utilities, financial services, government and public services, health and life sciences, and transport. Our teams operate globally from offices across the UK, Ireland, US, Nordics, and Netherlands. PA. Bringing Ingenuity to Life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nebius</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Offensive Security Engineer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.nebius.com/?gh_jid=4982966101</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>**About Nebius:**
+Nebius is leading a new era in cloud infrastructure for the global AI economy. We are building a full-stack AI cloud platform that supports developers and enterprises from data and model training through to production deployment, without the cost and complexity of building large in-house AI/ML infrastructure.
+Built by engineers, for engineers. From large-scale GPU orchestration to inference optimization, we own the hard problems across compute, storage, networking and applied AI.
+Listed on Nasdaq (NBIS) and headquartered in Amsterdam, we have a global footprint with R&amp;D hubs across Europe, the UK, North America and Israel. Our team of 1,500+ includes hundreds of engineers with deep expertise across hardware, software and AI R&amp;D.
+#### Offensive security
+The internal offensive security team is responsible for the penetration testing program, red team engagements, and offensive research aimed at uncovering sophisticated attack scenarios targeting high-value assets across the Nebius Cloud stack.
+#### The Role
+We're hiring an Offensive Security Engineer to join us at Nebius. You'll design and execute adversarial simulation across our cloud platform - attacking the same infrastructure our customers depend on - and translate findings into measurable security improvements.
+This is a hands-on engineering role within Product Security Team. You will be part of an internal red team, establish a penetration testing program, and conduct research to uncover sophisticated attack scenarios targeting high-value assets across the Nebius tech stack.
+#### What you’ll do
+- Validate and extend early-stage Secure SDLC threat models via **continuous penetration testing**, assessing threat severity and mitigation status while challenging assumptions made during threat modeling and system development. Automate routine validations to keep pace with increasing feature flow, reserving manual analysis for genuinely complex cases.
+- Plan and execute full-scoped **red team engagements** against Nebius cloud platform - including compute, storage, inference, networking, orchestration layers, and internal tooling. Identify threats, which are able to impact an organization's operations. Work closely with Detection &amp; Response and other security engineering teams to run purple team exercises, validate detection coverage, and close gaps collaboratively.
+- **Research novel attacks** against GPU infrastructure (e.g., closed-source firmware and vendor driver binaries, device passthrough exploits, SR-IOV/IOMMU misconfigurations, RDMA/InfiniBand fabric attacks, etc.), the inference stack (e.g., vLLM, TRT-LLM), and AI platform managed services (e.g., managed Slurm). Assess tenant-isolation boundaries and how they can be broken at the low-level stack
+- Conduct targeted assessments of new products and infrastructure changes before they ship.
+- Deliver clear, actionable reports for both technical audiences and leadership - with prioritized findings and remediation guidance.
+- Establish red team processes, tooling, and a methodology that scales as the platform grows.
+#### **What we’re looking for**
+- 6+ years in offensive security - penetration testing, red teaming, or adversary simulation
+- Deep experience attacking cloud-native environments: Kubernetes privilege escalation, cloud IAM abuse, virtualization and container escapes.
+- Strong fundamentals across the attack lifecycle: initial access, persistence, lateral movement, data exfiltration.
+- Proficiency developing custom tooling and post-exploitation capabilities (Python, Go, or similar).
+- Experience running purple team exercises and working constructively with blue teams.
+- Ability to write clear, senior-level reports with business-contextualized risk (not just raw findings) that engineers can easily use.
+#### Nice to have
+- Experience attacking ML infrastructure, model serving pipelines, or GPU clusters.
+- Reverse engineering and exploits development experience
+- Application security experience
+- Familiarity with eBPF bypass techniques or kernel-level exploitation.
+- Background in vulnerability research or CVE discovery.
+- Experience with cloud provider internals (hypervisor/networking layers).
+- Presenting your security research at conferences like BlackHat/DefCon, etc.
+#### Why this role at Nebius
+- Attack surface that's genuinely novel - GPU clusters, AI platforms, multi-tenant cloud at scale.
+- Work alongside world-class engineers on infrastructure that powers frontier AI.
+- Competitive compensation with equity upside in a Nasdaq-listed, high-growth company.
+- Flexible, remote-first culture
+**Benefits &amp; Perks:**
+- Competitive compensation
+- Career growth and learning opportunities
+- Flexibility and ownership
+- Collaborative and innovative culture
+- Opportunity to work on impactful AI projects
+- International environment and talented teams
+**What's it like to work at Nebius:**
+Fast moving - Bold thinking - Constant growth - Meaningful impact - Trust and real ownership - Opportunity to shape the future of AI
+**Equal Opportunity Statement:**
+Nebius is an equal opportunity employer. We are committed to fostering an inclusive and diverse workplace and to providing equal employment opportunities in all aspects of employment. We do not discriminate on the basis of race, color, religion, sex (including pregnancy), national origin, ancestry, age, disability, genetic information, marital status, veteran status, sexual orientation, gender identity or expression, or any other characteristic protected by applicable law.
+Applicants must be authorized to work in the country in which they apply and will be required to provide proof of employment eligibility as a condition of hire.
+If you need accommodations during the application process, please let us know.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rain</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Security Engineer - AppSec</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$190K – $240K • Offers Equity • Offers Bonus</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/rain/7e211b55-5069-45b2-8072-c6555a5b53cd/application</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>## **About the Company**
+Rain is the global stablecoin payments platform for enterprises, neobanks, platforms, developers, and AI agents. Our technology allows partners to move, store, and use stablecoins instantly and compliantly through global payment cards, rewards, on/offramps, wallets, and cross-border rails. As both a Visa and Mastercard Principal Member, Rain issues cards that work at more than 175 million merchant locations in over 220 countries and territories. Built natively for stablecoins and trusted by more than 100 organizations worldwide, Rain delivers secure, scalable infrastructure that makes money move freely and instantly around the world.
+You will have the opportunity to deliver massive impact at a hypergrowth company backed by some of the top investors in fintech, crypto, and SaaS. In January 2026, we closed a $250M Series C led by ICONIQ, valuing Rain at $1.95B, with Sapphire Ventures, Dragonfly, Bessemer Venture Partners, Galaxy Ventures, FirstMark, Lightspeed, Norwest, and Endeavor Catalyst also participating. If you're curious, bold, and excited to help shape a borderless financial future, we'd love to talk.
+## **Our Ethos**
+We believe in an open and flat structure. You will be able to grow into the role that most aligns with your goals. Our team members at all levels have the freedom to explore ideas and impact the roadmap and vision of our company.
+## **About the Team**
+Security Engineering is a small team that answers one question: was it built right? We run our own AI-driven red team against Rain's code and cloud, gate pull requests before they merge, and write the baselines that say how every system should be configured. Our blockchain work is covered. This role owns everything else: the backend services, APIs, cloud, and edge that move real money for real customers.
+We work closely with Security Operations: we give them high-quality findings to coordinate fixes for, and clear configuration rules they can build detections on.
+## **About the Team**
+Security Engineering makes sure Rain is built right. We run our own AI-driven red team against our code and cloud, gate pull requests before they merge, and set the baselines for how every system is configured. This role owns everything outside blockchain: the backend services, APIs, cloud, and edge that move real money. We give Security Operations high-quality findings to coordinate fixes for, and clear configuration rules to build detections on.
+## **About the Role**
+You'll be Rain's application security expert and the quality bar for every non-chain finding we produce. The calls are yours: what's real, how bad it is, and what has to be fixed before launch. You'll hold the line with engineers when it matters, and make the case so they agree, not just comply.
+## **What You'll Do**
+- Review red team findings before they reach engineers: reproduce them, cut false positives, set severity, and write tickets clear enough to fix without a meeting. Improve the scoring that grades them
+- Harden our backend services and APIs, especially the money-moving paths. You'll often write the fix yourself
+- Own edge defenses: DDoS protection, rate limiting, WAF rules, and abuse controls
+- Write secure configuration baselines for our cloud, code, and SaaS, and turn them into automated checks
+- Grow our PR security gate so more bugs are blocked before merge
+- Own attack surface coverage, and run architecture reviews on new and high-risk systems
+- Find, test, and pick the best security tools, whether we buy, adopt, or build
+## **What We're Looking For**
+- 4+ years in application security, product security, or security-minded backend engineering
+- You've owned security decisions. You can tell a senior engineer their design needs to change and keep a good working relationship
+- You can read an unfamiliar codebase (TypeScript/Node.js) and find the bug that matters, and you know a scary-sounding finding from a real one
+- Hands-on cloud security (ideally GCP), Terraform, and edge defenses like WAFs and rate limiting
+- Experience with threat models or architecture reviews. You've run tool bake-offs and dropped tools that didn't earn their cost
+- You'd rather ship a check than write a document, and you use AI tools heavily without trusting them blindly
+## **Bonus Attributes**
+- Fintech, payments, or card issuing background (PCI DSS a plus)
+- Pentest, bug bounty, or red team experience
+- Experience building security scanners, static analysis rules, or LLM-based review tools
+- If you have the background: AI security for our agents and agentic payments, or corporate security alongside IT
+## **Things that enable a fulfilling, healthy and happy experience at Rain:**
+**Unlimited time off** 🌴 Unlimited vacation can be daunting, so we require Rainmakers to take 10 days minimum for themselves.
+**Flexible working** ☕ We support a flexible workplace – work from home, come into an office, or both. We want everyone to work in an environment where they're their most confident and productive selves. New Rainmakers receive a stipend to set up a comfortable home workspace.
+**Easy to access benefits** 🧠 For US Rainmakers, we cover 95% of your health, dental, and vision plan costs and 90% for your dependents, plus a 100% company-subsidized life insurance plan.
+**Retirement goals**💡 Plan for the future with confidence. We offer a 401(k) with a 4% company match.
+**Equity plan** 📦 Every Rainmaker gets an equity option plan so we all benefit from our success.
+**Health and Wellness** 📚 High performance begins from within. Rainmakers receive a monthly stipend to be used for eligible health and wellness spending like gym memberships/fitness classes, massages, acupuncture - whatever recharges you!
+**In-office meals** 🍜 Rainmakers working from the office enjoy lunch and dinner on us, covered with a DoorDash credit.
+**Team summits** ✨ Summits play an important role at Rain. Time together helps us build relationships and a common destiny. Expect team and company offsites, both domestic and international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Naval Group [FR]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>CDI – Ingénieur Infrastructure DevSecOps Data Platform – H/F</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Brest, Brittany, France</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/jj6huE/jobs/cdi-ingenieur-infrastructure-devsecops-data-platform-h-f_brest</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Rejoignez Naval Group, un leader mondial de l'industrie navale. En tant qu'Ingénieur Infrastructure DevSecOps Data Platform, vous serez responsable de la mise en œuvre et de la maintenance de nouvelles solutions informatiques, ainsi que de l'évolution des infrastructures existantes. Vous travaillerez dans un environnement moderne et dynamique, en contribuant à la transformation digitale de l'entreprise.
 - Participer à la transformation et à la modernisation du Système d'Information, en tant qu'ingénieur devSecOps.
@@ -594,68 +1677,656 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>greenboxcapital</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Security Engineer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$190-220K</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bamboohr</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://greenboxcapital.bamboohr.com/careers/176</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Why this Role Matters: At Greenbox Capital, we help small businesses thrive by giving them fast, accessible funding. As a Senior Cloud Platform Security Engineer, you’ll play a critical role in building and protecting the cloud infrastructure that powers our applications, data platforms, and AI capabilities. You’ll serve as the primary technical owner for our Azure platform, cloud security controls, and infrastructure operations. Your work will help ensure our technology environment is secure, reliable, scalable, compliant, and ready to support Greenbox’s continued growth. This role reports to the VP, Technology and is a hands-on senior individual contributor with no direct reports. You’ll partner closely with Technology leadership, Engineering, Data &amp; AI, Compliance, business stakeholders, and external providers. What Success Looks Like: Here’s how your time might break down (actual time can shift depending on business needs): Platform Reliability &amp; Recovery – Maintain ≥99.9% availability for critical platform services within your operational control, support agreed Sev-1/2 response expectations, and validate disaster recovery at least twice annually. Security &amp; Compliance Posture – Maintain strong privileged-access controls, remediate critical findings within established SLAs, and ensure technical evidence is available for SOC 2, NIST, and other compliance needs. Infrastructure as Code &amp; Configuration Management – Drive toward ≥95% of production infrastructure managed through infrastructure as code while reducing configuration drift. Observability &amp; Incident Readiness – Ensure critical services have effective monitoring, actionable alerts, escalation paths, and documented runbooks. Cloud Cost &amp; Operational Efficiency – Maintain ≥98% resource tagging compliance, improve cost visibility, and identify meaningful optimization opportunities. Automation – Reduce repetitive infrastructure work through automated provisioning, remediation, evidence collection, backup validation, and recovery. How you’ll be measured: Own and continuously improve Greenbox Capital’s Azure platform Design, configure, operate, and maintain Azure subscriptions, management groups, networking, compute, storage, platform services, and shared infrastructure. Establish standards for environment separation, naming, tagging, approved services, secure configuration, and change management. Strengthen cloud identity, network, and security controls Design and maintain Microsoft Entra ID, MFA, Conditional Access, PIM, RBAC, managed identities, access reviews, and emergency-access procedures. Apply least-privilege and separation-of-duties principles across cloud, SaaS, administrative, and non-human identities. Own network segmentation, private connectivity, firewalls, DNS security, secure ingress/egress, and secrets management. Improve security operations and incident readiness Operate cloud-security posture management, vulnerability remediation, configuration monitoring, logging, detection, and threat-response capabilities. Build meaningful alerts and dashboards and coordinate containment, recovery, evidence preservation, and corrective action during security events. Build reliable infrastructure through automation Develop and maintain infrastructure using Terraform, Bicep, or comparable infrastructure-as-code practices. Establish reusable modules, peer review, automated testing, deployment controls, and configuration-drift management. Support compliance, technology risk, and audit readiness Translate requirements such as the GLBA Safeguards Rule, SOC 2, NIST Cybersecurity Framework, customer commitments, and internal policies into practical technical controls. Maintain evidence, support audits and customer security reviews, and help address identified control gaps. Enable secure Data &amp; AI operations Partner with Data &amp; AI leadership to implement technical controls supporting Greenbox’s data and AI governance requirements. Support data discovery, classification, lineage, retention, DLP, access governance, and approved AI-service controls. Help secure AI and agent-based workloads, including data boundaries, privileged actions, logging, monitoring, human approval, and incident-response requirements. Drive cloud cost and operational efficiency Own cloud budgets, alerts, tagging standards, forecasting inputs, and recurring optimization recommendations. Evaluate Azure-native and third-party capabilities based on effectiveness, effort, maintenance, licensing cost, and architectural fit. You’re a Strong Fit if You: Demonstrate strong judgment and can make thoughtful, risk-based technical decisions independently. Are naturally curious and enjoy digging into complex systems, identifying root causes, and continuously improving how technology operates. Can balance security, reliability, compliance, cost, and business needs without losing sight of practical execution. Communicate clearly with technical teams, business stakeholders, executives, auditors, vendors, and external partners. Are organized and comfortable managing multiple priorities in a fast-moving growth environment. Adapt well to working across functions and with distributed teams. Bring a growth mindset and actively look for opportunities to automate, simplify, and improve existing processes. What You’ve Done Before: Seven or more years of hands-on cloud infrastructure or security engineering experience, including ownership of production Azure environments and demonstrated senior-level responsibility. Strong experience across Azure subscriptions and management groups, networking, Microsoft Entra ID, RBAC, Azure Policy, monitoring, backup and recovery, security controls, and cost management. Demonstrated infrastructure-as-code experience using Terraform, Bicep, ARM templates, or comparable tooling, including source control and automated deployment practices. Practical experience with cloud security operations, vulnerability remediation, logging and detection, incident response, access governance, and disaster-recovery testing. Working knowledge of Microsoft Purview or comparable data-governance capabilities, including classification, lineage, retention, DLP, and access controls. Experience translating control requirements into technical designs, operating procedures, evidence, and measurable results. Strong documentation experience, including runbooks, architecture diagrams, standards, risk statements, and executive-level updates. Ability to coordinate effectively with internal teams, auditors, managed-service providers, and technology vendors. Experience in financial services or another regulated environment using SOC 2, NIST Cybersecurity Framework, or similar frameworks is preferred. Experience securing AI, machine-learning, large-language-model, or agent-based workloads in production is preferred. Relevant Microsoft certifications such as Azure Security Engineer Associate, Cybersecurity Architect Expert, Security Operations Analyst Associate, or Azure Solutions Architect Expert are preferred. Tools and Expertise You’ll Bring: Microsoft Azure Microsoft Entra ID, RBAC, Conditional Access, MFA, and Privileged Identity Management Terraform, Bicep, ARM templates, or comparable infrastructure-as-code technologies Azure Monitor and Log Analytics Microsoft Defender for Cloud Microsoft Sentinel or comparable SIEM platforms Microsoft Purview or comparable data-governance tools Azure DevOps pipelines Azure Policy and cloud configuration-management practices Backup, disaster-recovery, and environment-restoration technologies Cloud networking, segmentation, firewalls, DNS security, and zero-trust architectures Secrets, certificate, and key management, including Azure Key Vault Cloud cost management and FinOps practices Databricks platform security, Microsoft 365 security, and SaaS identity integrations where applicable What to Expect from Our Interview Process We believe in a respectful, efficient, and transparent hiring experience. Here’s what you can expect: Step 1: Initial Phone Screen (30 minutes) A brief conversation with a recruiter to learn more about your background, interests, and alignment with the role. Step 2: Hiring Manager Interview (1 hour) A deeper discussion about the role, your relevant experience, and how you’d contribute to the team. Step 3: Role-Specific Assessment or Panel Interview (1 hour) Depending on the role, this may include a take-home assignment, technical interview, or live case study with team members. Step 4: Final Interview or Leadership Chat (1 hour) A final conversation with senior leadership or cross-functional team members to ensure alignment with our mission and values. Step 5: Offer &amp; Background Check If it’s a mutual fit, we’ll move forward with background check and present a competitive offer. We aim to complete this process within 2–3 weeks from your first conversation with us. Benefits: 💸 Competitive Pay - We know your worth and we pay accordingly. 🌴 Flexible PTO - Work hard, rest well. Take the time you need to recharge. 🏡 Remote - Fully remote within the U.S., working Eastern Time hours to keep everyone aligned. 🩺 Full Benefits Package - Health, dental, vision 🧠 Smart, Supportive Teammates - Collaborate with sharp minds who are kind, driven and uphold our core values: Commitment, Communication, Teamwork, Service and Integrity!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>remote (any state)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>eightfold</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://caci.eightfold.ai/careers/job/1443153808427</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer – Applications</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/rQQHZWagTS</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer – Applications – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cybersecurity Engineer – Applications Location: 100% Remote (United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are looking for an Cybersecurity Engineer – Applications to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Harry@bvteck.com&gt; or contact us at (908) 676-4399 . Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Security Engineer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/sZ7ioX3F68</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Security Engineer - Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Cloud Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$170,000 Annually Experience Required: 12+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an experienced Oracle Cloud Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Computer Science, Engineering, or a related discipline. 12 or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oracle Security Engineer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/BOWXZ69Ofz</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Oracle Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$130,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;hilda@bvteck.com&gt; Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>testpros</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Software Validation &amp; Data Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>USD 0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PART_TIME</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://testpros.applytojob.com/apply/jobs/details/67EhvaVNYY</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>TestPros delivers innovative independent IT assessment solutions to critical challenges facing the nation and the world. We support the U.S. Federal Government and Commercial clients within the continental USA. TestPros is dedicated to making lives better, safer and more secure. Type: Consulting Duration: Short-Term Project / Project-Based Client Environment: Healthcare / Regulated Software Overview: TestPros is seeking an experienced Software Validation &amp; Data Security Engineer for a part-time, short-term 1099 consulting project supporting hands-on independent validation and verification of a software solution operating in a regulated environment. The ideal candidate will have experience with software validation, functional testing, data integrity, security testing, and regulatory compliance , along with the technical ability to analyze and scan structured datasets such as CSV, JSON, and databases . This is a project-based consulting engagement, not a full-time employee position . The consultant will work with TestPros' security/compliance lead to perform technical testing, document objective evidence, identify exceptions, and support development of the final validation deliverables. Required Qualifications and Skills Perform hands-on software validation and verification testing . Review system requirements, existing validation documentation, and prior IQ/OQ/PQ documentation. Develop and/or execute validation plans, test cases, protocols, and test scripts. Conduct functional testing to confirm system features operate as intended. Validate data integrity, audit trails, access controls, authentication, and security-related functionality . Support validation against applicable requirements, including FDA 21 CFR Part 11 and HIPAA . Perform technical analysis of structured data, including CSV, JSON, and database datasets . Use automated techniques and scripts to query and scan larger datasets. Identify sensitive information and patterns, including PII/PHI and other identifiers . Perform database queries, pattern matching, exception analysis, and data validation. Document test results, findings, supporting evidence, exceptions, and remediation/retesting. Support development of a repeatable validation and testing methodology. Assist with preparation of final validation/IV&amp;V reports and supporting documentation . Participate in client technical discussions and requirements clarification. Required Experience: Experience performing software validation, QA, IV&amp;V, or computer system validation (CSV) . Hands-on experience with functional software testing. Experience developing or executing IQ, OQ, and/or PQ protocols . Knowledge of FDA 21 CFR Part 11 . Understanding of HIPAA, PII, PHI, privacy, and data integrity requirements . Experience with Python and/or SQL for data analysis, querying, or automated testing. Ability to work with CSV, JSON, databases, and large datasets . Experience with data querying, automated scanning, pattern/identifier detection , or sensitive-data discovery. Ability to document testing methodology, evidence, findings, and exceptions in a formal validation environment. Must be comfortable working as a 1099 independent contractor on a part-time, project-based basis . Preferred Experience: Healthcare, pharmaceutical, life sciences, medical device, or other regulated-industry experience. Experience with de-identification, data masking, anonymization, PII/PHI detection, or data classification . Experience developing automated validation scripts or test automation. Familiarity with ISO 16175-1 and/or ISO 14641 . Experience with records management or electronic document/records systems. Security testing experience involving access controls, authentication, logging, audit trails, and data protection. Ideal Candidate: The ideal candidate is not simply a compliance or GRC professional. We are looking for someone who can personally perform the technical testing and validation , work directly with application and data environments, analyze larger CSV/JSON/database datasets, automate testing where appropriate, and produce clear evidence supporting an independent validation conclusion. This is best suited for an experienced consultant who is available for a short-term, part-time 1099 project and can contribute quickly with limited ramp-up time. Rate: $60-100/hr (1099 or Corp. To Corp.). This range represents a good-faith estimate and is not a guarantee; final compensation is determined by factors such as experience, qualifications, and government contract labor rate requirements and may fall outside the stated range. Equal Opportunity Employer TestPros is an equal-opportunity employer and does not discriminate in employment based on race, color, religion, sex (including pregnancy and gender identity), national origin, political affiliation, sexual orientation, marital status, disability, genetic information, age, membership in an employee organization, retaliation, parental status, military service, or any other non-merit factor. Offer Considerations TestPros considers several factors when extending an offer, including but not limited to, Federal Government contract labor categories and contract wage rates, relevant prior work experience, specific skills and competencies, geographic location, education, and certifications. Federal Compliance As a federal contractor, TestPros is subject to all federal and state mandates and/or other customer requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>verticalrelevance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AWS DevSecOps Cloud Consultant</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes / Mentioned</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://verticalrelevance.applytojob.com/apply/jobs/details/q7E8Vst9N9</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Summary Vertical Relevance is looking for an AWS Security &amp; Compliance Consultant, to join our team as a full-time employee in NY Metro area. This person is responsible for the end-to-end planning, building, and deploying of software systems. He/she will be able to drive the programming of well-constructed, testable code. As an AWS Security &amp; Compliance Consultant, you will implement technical solutions as part of a team for customer engagements. This role requires strong teamwork, communication, patience and organization skills needed to drive customer success. At Vertical Relevance we deliver with excellence through teamwork, automating everything, constantly learning and taking ownership for the outcomes our customers experience. Are you ready to join the team? Responsibilities Help customers shape their journey to adopting the cloud and provide our customers with technical and strategic guidance on their “cloud journey”. Consult, plan, design, and implement security solutions on the cloud customers Design and automate security and compliance solutions Become a deep technical resource that earns our customer's trust Develop high-quality technical content such as automation tools, reference architectures, and white papers to help our customers build on the cloud Innovate on behalf of customers and translate your thoughts into action yielding measurable results. Support solution development by conveying customer needs and feedback as input to technology roadmaps. Share real world implementation challenges and recommend expansion of capabilities through enhanced and new offerings. Assist with technical briefs that document solutions Assist with reference architecture implementations Support internal and external brand development through thought leadership: Work with Marketing/Alliances to write blog posts Work with Marketing/Alliances to develop internal case studies Qualifications Professional experience architecting/operating automated Security &amp; Compliance / DevSecOps solutions built on AWS Experience in software/technology customer facing experience You must be legally authorized to work in the United States without the need for employer sponsorship, now or at any time in the future. Sample Activities You’ll Do Creating a Self-Service Account Framework Assist Customer with organizational hierarchy design and configuration templates Assist Customer in the development of referenceable playbooks, supported by relevant code examples Assist Customer in the development of sample runbooks to automate the implementation of AWS account setup and configuration Account Framework - Developing an automated Continuous Delivery Pipeline framework that will be used to establish AWS Accounts to configured, tested infrastructure on AWS in a repeatable, reliable and secure manner eliminating the need for manual intervention. Security Control Policies - Development of the Service Control Policies and account baselines associated with the Customer’s security and compliance requirements Assist Customer with the development of a report and supporting sample code addressing the controls as part of the playbook Creating Security Threat Analytics and Dashboard Solutions Creating a framework to automatically gather, transform and interpret security event data in AWS. Selecting, defining, identifying security requirements and determine where: Macie can be leveraged GuardDuty can be leveraged Inspector can be leveraged Security Hub can be leveraged Alternative security products can be leveraged Codify the provisioning of security analytics and reporting workflow: Implement Security Hub with in a central account with inputs from all accounts Implement GuardDuty for global security events Implement Macie for detection of sensitive data in 23 buckets Develop AWS Config rules to enforce security configurations in CIS AWS Foundations standard Implementing Inspector to gather findings from EC2 instances Enable CloudTrail for monitoring API activity Enable FlowLogs for VPC traffic Creating a Self-Service Compliance Framework Selecting tools for building Policy-as-Code controls (preventative, detective, and responsive) Development of referenceable playbooks, supported by relevant code examples for controls Development of sample runbooks to automate the implementation of controls: Policy Definition – Identification and documentation of Customer Policy in the form of specific statements that must be true about configuration of AWS resources Policy-as-Code Development – Development of the logical tests associated with each of the policies established to be used to assert the configuration state of infrastructure on AWS in order to block a build in the pipeline, take automated reactive action, or alert on violations to the policy Framework Development – A design allowing for the execution of logical tests against infrastructure code or running AWS infrastructure in order to assert the configuration state of infrastructure resources on AWS and block a build in the pipeline, take automated reactive action, or alert on violations to the policy Development of a report and supporting sample code addressing the controls as part of the playbook U.S. work authorization required. Candidates must be legally authorized to work in the United States without current or future employer sponsorship. Relevant Technical Tools Primary Languages – Python, Java, Bash Tooling, Services &amp; Libraries – Jenkins, Gitlab, Terraform, Vault, Git, Splunk, OWASP, Trend Micro, Palo Alto, Fortify, Twistlock, Aqua Security Relevant AWS Services AWS Infrastructure Scripting – CloudFormation, AWS CLI, AWS CDK AWS Storage Services – S3 AWS Compute Services – Lambda, EC2, EKS, ECS, ECR AWS Networking Services – VPC, Route53, API Gateway, Direct Connect AWS Developer Services – CodePipeline, CodeBuild, CodeCommit, CodeDeploy AWS Management and Governance Services – Control Tower, Organizations, CloudWatch, Auto Scaling, Config, CloudTrail, Service Catalog, Systems Manager AWS Security, Identity, Compliance Services – IAM, Inspector, KMS, Secrets Manager, Security Hub, Detective, GuardDuty, Macie, HSM, Certificate Manager, WAF &amp; Shield, Firewall Manager, Detective AWS Frameworks – Landing Zone The Company Vertical Relevance was founded to help business leaders drive value through the design and delivery of effective transformation programs across people, processes, and systems. Our mission is to help firms at any stage of their journey develop custom solutions for success and growth. We provide a full range of services from strategy and design through to implementation and training. Our collective industry expertise is our greatest asset - our professionals have an average of 20+ years’ experience within Financial Services, across Wealth Management, Asset Management, Insurance, and Banking. Within our Customer Experience practice, we add complementary industry expertise (technology and media) synergizing the most relevant and successful customer trends. We focus wholly on your success by first rigorously assessing your business and technology challenges, and then right-sizing solutions that provide a meaningful ROI. With our industry experts hitting the ground running and focusing on nimble, quality delivery, we can see rapid, tangible improvements with our clients in productivity and effectiveness. When it makes sense for your company, we leverage our product partnerships in the areas of CRM, Sales Acceleration, Predictive Analytics, Digital Knowledge Management, and Cloud Transformation. Vertical Relevance is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to sex, gender identity, sexual orientation, race, color, religion, national origin, disability, protected Veteran status, age, or any other characteristic protected by law.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>careers.statestreet.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cybersecurity Automation Engineer ,Assistant Vice President</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kilkenny, Kilkenny, Ireland</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>phenom</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.statestreet.com/job/R-796935</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Become part of our team as a Cybersecurity Automation Engineer, where you will identify and implement automation opportunities to enhance SOC processes and incident response workflows. Collaborate with analysts to develop user stories and test solutions. Ideal for candidates with experience in cybersecurity and strong programming skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Security Engineering Manager - Incident Response, AWS CloudOps</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>London, England, GBR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://account.amazon.jobs/jobs/10568807/apply</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>We are looking for an experienced security leader to join the CloudOps team. As a security leader, you will own building and managing a team of incident managers and technical leaders, fostering a strong team culture. You and your team will be expected to drive engineering teams to take the right actions in the right time frames to mitigate risks.   
+We're looking for a leader that's highly passionate about the potential of cloud computing and building a high performing incident management team, working closely with our incident responders. Ideally you have a track record of delivering high quality technology products and services in a hyper-growth environment where priorities shift quickly. You should know how to prioritize, communicate clearly and compellingly, and understand how to drive a high level of focus and excellence with a strong team. Cloud Incident Management in particular, operates at very large scale and demands high standards, so a passion and discipline around security and delivery is critical. A high level of ownership and accountability is a must.  
+Key job responsibilities  
+- Build and lead a high-performing team of security engineers, focusing on recruitment, development, and retention of top security talent.  
+- Drive operational excellence in incident management processes, establishing and maintaining SLAs, metrics, and quality standards for security response activities.  
+- Partner with service teams and stakeholders across AWS to ensure security issues are properly prioritized and remediated according to risk levels and customer impact.  
+- Develop and implement strategic initiatives to improve security response capabilities, including automation, process improvements, and scaling mechanisms.  
+- Foster a culture of ownership, continuous learning, and psychological safety while maintaining high security standards and operational excellence.  
+- Manage cross-organizational relationships and communication channels to ensure effective escalation paths and resolution of complex security challenges.  
+- Lead the development and implementation of security frameworks and controls that balance risk mitigation with business objectives and builder experience.  
+- Establish and maintain mechanisms for measuring team performance, operational metrics, and security program effectiveness.  
+- Guide architectural decisions and technical strategy for security solutions across multiple organizations and services.  
+- Mentor and develop future security leaders while creating growth opportunities for team members.  
+A day in the life  
+As a Security Manager, your day typically starts with reviewing overnight security incidents and operational metrics during the team's daily standup. You'll spend time in 1:1s with your direct reports, providing guidance on complex security issues and career development. Throughout the day, you'll participate in strategic planning sessions with service teams, review architectural proposals, and work on improving incident response processes. You'll also engage with senior leadership to provide updates on critical security initiatives and handle escalations when necessary. The role requires balancing tactical incident management with long-term strategic planning while ensuring your team maintains high security standards at scale.  
+About the team  
+Diverse Experiences  
+Amazon Security values diverse experiences. Even if you do not meet all of the qualifications and skills listed in the job description, we encourage candidates to apply. If your career is just starting, hasn’t followed a traditional path, or includes alternative experiences, don’t let it stop you from applying.  
+Why Amazon Security?  
+At Amazon, security is central to maintaining customer trust and delivering delightful customer experiences. Our organization is responsible for creating and maintaining a high bar for security across all of Amazon’s products and services. We offer talented security professionals the chance to accelerate their careers with opportunities to build experience in a wide variety of areas including cloud, devices, retail, entertainment, healthcare, operations, and physical stores.  
+Inclusive Team Culture  
+In Amazon Security, it’s in our nature to learn and be curious. Ongoing DEI events and learning experiences inspire us to continue learning and to embrace our uniqueness. Addressing the toughest security challenges requires that we seek out and celebrate a diversity of ideas, perspectives, and voices.  
+Training &amp; Career Growth  
+We’re continuously raising our performance bar as we strive to become Earth’s Best Employer. That’s why you’ll find endless knowledge-sharing, training, and other career-advancing resources here to help you develop into a better-rounded professional.  
+Work/Life Balance  
+We value work-life harmony. Achieving success at work should never come at the expense of sacrifices at home, which is why flexible work hours and arrangements are part of our culture. When we feel supported in the workplace and at home, there’s nothing we can’t achieve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Crédit Mutuel Arkéa</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Product Owner DevSecOps H/F</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Bordeaux, Nouvelle-Aquitaine, France</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/zDakzV3/jobs/product-owner-devsecops-h-f_bordeaux</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>Rejoignez notre équipe en tant que Product Owner DevSecOps. Vous serez responsable de la gestion fonctionnelle globale des produits liés à l'amélioration continue de la sécurité tout au long du cycle de développement logiciel. Vous travaillerez en étroite collaboration avec le Product Manager pour élaborer la trajectoire des produits et identifier les impacts des sujets à venir. Une expérience de 3 ans dans un rôle agile est requise, ainsi qu'une connaissance de la méthodologie Agile et des pratiques de développement applicatif.
 - Assurer le pilotage fonctionnel global des produits liés à l'amélioration continue de la sécurité sur l'ensemble du SDLC.
@@ -664,64 +2335,64 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Deutsche Bank</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Senior Security Engineer (Data Platform)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/37tGzn/jobs/senior-security-engineer_berlin_lzb2wpri</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>Join DWS's data infrastructure team as a Senior Security Engineer. In this role, you will focus on understanding the threat landscape, architecting integrations with security tools, collaborating with vendors, security monitoring, threat remediation, and cloud infrastructure automation. You will design and integrate secure cloud and on-premises infrastructure, deploy and manage scalable cloud infrastructure solutions, and configure and manage internal security solutions. The ideal candidate will have extensive experience in securing critical enterprise data flows, hands-on experience in cloud security, and strong collaboration and communication skills.
 - Understand the threat landscape and architect integrations with security tools to enhance security monitoring and threat remediation.
@@ -737,68 +2408,68 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Atos</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Principal Security Architect - H/F</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Hérouville-Saint-Clair, Normandy, France</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>EUR 80,000 - 95,000</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bKGYqPm/jobs/principal-security-architect-h-f_sophia-antipolis_ATOS_dWMgOeZ</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Rejoignez une entreprise innovante à la pointe de l'IA et des usines souveraines. En tant que Principal Security Architect, vous serez responsable de la définition de l'architecture de sécurité, de la préparation aux certifications, de la souveraineté cloud et IA, de l'avant-vente et de la sécurité de la chaîne d'approvisionnement logicielle. Vous aurez un impact direct sur le succès commercial et technologique de la Business Unit &lt;E.AI&gt;.
 - Définir l'architecture de sécurité à travers la plateforme, établir les exigences de contrôle et les modèles de référence adoptés par défaut par les équipes produit.
@@ -824,123 +2495,123 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Vercel</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Security Engineer, Cloud</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Anywhere in the World</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>weworkremotely</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/vercel-security-engineer-cloud</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Headquarters: Remote - United States About Vercel: Vercel is the agentic infrastructure company, freeing people and agents to ship what's next. For more than a decade we've helped builders move from idea to production with speed, security, and exceptional developer experience. Now we're scaling our products for both agents and people to ship and run software, built in the open and trusted by OpenAI, PayPal, Ramp, Supreme, and millions of developers worldwide. About the role: We're looking for a Security Engineer to join our Cloud Security Engineering team. In this role, you'll help strengthen the security of our platform by building and improving the controls that protect our infrastructure. You'll play a key role in making security a core part of how we build, deploy, and scale our systems, while helping the company grow securely and confidently. You'll report to the Security Operations Manager, and this is a hybrid or fully remote within the United States. If you're based within commuting distance of our SF or NY offices, the role includes in-office anchor days on Monday, Tuesday, and Friday. What you will do: Design and implement scalable security controls across our cloud-native platform. Harden infrastructure components using infrastructure-as-code, policy enforcement, and service isolation. Build secure by default infrastructure and code CI/CD pipelines. Collaborate with platform and infrastructure teams to integrate security best practices into architecture and workflows. Stay ahead of cloud security trends and adopt cutting-edge technologies to enhance platform resilience. Conduct threat modeling, risk analysis, and mitigation planning for critical systems. Drive improvements in monitoring, detection, and incident response at the platform level. Build, deploy and maintain relevant tooling. About you: 8+ years of experience in infrastructure or platform security roles. Deep understanding of secure cloud infrastructure (AWS/GCP), identity and access management, and system hardening. Proficient with tools like Terraform, CDK, Kubernetes, and CI/CD security. Skilled at balancing engineering realities with principled security practices. Proven track record of shipping secure, resilient systems at scale. Bonus if you: Have built or scaled security automation pipelines. Contributed to open-source security projects or tools. Hold certifications such as GCP Security Engineer, AWS certifications, CISSP, or OSCP. Hold a bachelors or masters degree in Cybersecurity or similar disciplines. Benefits &amp; Compensation: Competitive compensation package, including equity. Inclusive Healthcare Package. Learn and Grow - we provide mentorship and send you to events that help you build your network and skills. Flexible Time Off. We will provide you the gear you need to do your role, and a WFH budget for you to outfit your space as needed. The San Francisco, CA base pay range for this role is $208,000.00 - $312,000.00. This salary range is an estimate. Actual salary will be based on job related skills, experience and location. Pay ranges outside San Francisco may be adjusted based on employee location. The total compensation package also includes benefits and equity-based compensation. Your recruiter can share more about the specific pay range for your location during the hiring process. Disclosures: Privacy: Please review our Job Applicant Privacy Policy for more information on how we handle your data. Equal Opportunity: Vercel is committed to fostering and empowering an inclusive community within our organization. We do not discriminate on the basis of race, religion, color, gender expression or identity, sexual orientation, national origin, citizenship, age, marital status, veteran status, disability status, or any other characteristic protected by law. Vercel encourages everyone to apply for our available positions, even if they don't necessarily check every box on the job description. To apply:</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Headquarters: Remote - United States About Vercel: Vercel is the agentic infrastructure company, freeing people and agents to ship what's next. For more than a decade we've helped builders move from idea to production with speed, security, and exceptional developer experience. Now we're scaling our products for both agents and people to ship and run software, built in the open and trusted by OpenAI, PayPal, Ramp, Supreme, and millions of developers worldwide. About the role: We're looking for a Security Engineer to join our Cloud Security Engineering team. In this role, you'll help strengthen the security of our platform by building and improving the controls that protect our infrastructure. You'll play a key role in making security a core part of how we build, deploy, and scale our systems, while helping the company grow securely and confidently. You'll report to the Security Operations Manager, and this is a hybrid or fully remote within the United States. If you're based within commuting distance of our SF or NY offices, the role includes in-office anchor days on Monday, Tuesday, and Friday. What you will do: Design and implement scalable security controls across our cloud-native platform. Harden infrastructure components using infrastructure-as-code, policy enforcement, and service isolation. Build secure by default infrastructure and code CI/CD pipelines. Collaborate with platform and infrastructure teams to integrate security best practices into architecture and workflows. Stay ahead of cloud security trends and adopt cutting-edge technologies to enhance platform resilience. Conduct threat modeling, risk analysis, and mitigation planning for critical systems. Drive improvements in monitoring, detection, and incident response at the platform level. Build, deploy and maintain relevant tooling. About you: 8+ years of experience in infrastructure or platform security roles. Deep understanding of secure cloud infrastructure (AWS/GCP), identity and access management, and system hardening. Proficient with tools like Terraform, CDK, Kubernetes, and CI/CD security. Skilled at balancing engineering realities with principled security practices. Proven track record of shipping secure, resilient systems at scale. Bonus if you: Have built or scaled security automation pipelines. Contributed to open-source security projects or tools. Hold certifications such as GCP Security Engineer, AWS certifications, CISSP, or OSCP. Hold a bachelors or masters degree in Cybersecurity or similar disciplines. Benefits &amp; Compensation: Competitive compensation package, including equity. Inclusive Healthcare Package. Learn and Grow - we provide mentorship and send you to events that help you build your network and skills. Flexible Time Off. We will provide you the gear you need to do your role, and a WFH budget for you to outfit your space as needed. The San Francisco, CA base pay range for this role is $208,000.00 - $312,000.00. This salary range is an estimate. Actual salary will be based on job related skills, experience and location. Pay ranges outside San Francisco may be adjusted based on employee location. The total compensation package also includes benefits and equity-based compensation. Your recruiter can share more about the specific pay range for your location during the hiring process. Disclosures: Privacy: Please review our Job Applicant Privacy Policy for more information on how we handle your data. Equal Opportunity: Vercel is committed to fostering and empowering an inclusive community within our organization. We do not discriminate on the basis of race, religion, color, gender expression or identity, sexual orientation, national origin, citizenship, age, marital status, veteran status, disability status, or any other characteristic protected by law. Vercel encourages everyone to apply for our available positions, even if they don't necessarily check every box on the job description. To apply: &lt;https://weworkremotely.com/remote-jobs/vercel-security-engineer-cloud&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>xAI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Infrastructure Security Engineer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/JBHAzj/jobs/infrastructure-security-engineer_ie_ceqs7o3s</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Join our security team as an Infrastructure Security Engineer. In this role, you will design, implement, and maintain secure cloud and hybrid infrastructure, ensuring the integrity of our cloud-native applications. You will work across multi-cloud and hybrid environments, focusing on securing critical infrastructure. Your responsibilities will include designing secure cloud architectures, developing Infrastructure as Code templates, managing cloud security tools, and collaborating with development teams to integrate security best practices.
 - Design, implement, and maintain secure cloud and hybrid infrastructure, ensuring the integrity of cloud-native applications.
@@ -973,69 +2644,69 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>PASQAL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>IT Security Engineer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/4uAgeC/jobs/it-security-engineer_gb_3ojbzy3l</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Join PASQAL, a leading company in the Neutral Atom Quantum Computing space, as a Senior IT Security Engineer. In this role, you will design, operate, and continuously improve security across various environments, including workplace, identity, networks, SaaS, infrastructure, and cloud. You will work closely with the Information Security Manager to turn security requirements and risks into pragmatic solutions that support business needs. This is a full-time, direct hire position with a hybrid work model and competitive benefits.
-- Concevoir, exploiter et améliorer continuellement la sécurité des environnements de travail, d'identité, de réseau, de SaaS, d'infrastructure et de cloud.
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Join PASQAL, a leading company in the Neutral Atom Quantum Computing space, as a Senior IT Security Engineer. In this role, you will design, operate, and continuously improve security across various environments, including workplace, identity, networks, SaaS, infrastructure, and cloud. You will work closely with the Information Security Manager to turn security requirements and risks into pragmatic solutions that support business needs. The position offers flexible schedules, a dynamic international team, competitive benefits, and opportunities for career growth.
+- Concevoir, exploiter et améliorer continuellement la sécurité dans divers environnements, y compris le cloud et l'infrastructure.
 - Renforcer la sécurité des identités, des points de terminaison, des réseaux et du cloud grâce à des contrôles d'accès, au durcissement, à la segmentation, à la surveillance et à la gestion des vulnérabilités.
-- Déployer et exploiter des capacités de protection et de détection telles que EDR/XDR, SIEM, IDS/IPS, en gérant les incidents de sécurité et les remédiations.
+- Automatiser et standardiser les contrôles de sécurité en utilisant des outils tels que Python/Bash, Terraform, Ansible, et les pratiques DevSecOps.
  - Ability to document controls, decisions, and technical activities so they remain measurable, traceable, and auditable
 - Active technology and cybersecurity watch, with the ability to assess emerging threats and solutions and turn relevant insights into continuous security improvements
 - 5–7 years of hands-on experience in cybersecurity, IT security, or a closely related infrastructure engineering role
@@ -1053,68 +2724,68 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Trainline</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Senior Product Security Engineer</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>GBP 90,000 - 100,000</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/3TgGLb/jobs/senior-product-security-engineer_london_n3i4chnd</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>Join Trainline, Europe's leading independent rail platform, as a Senior Product Security Engineer. In this role, you will define and own the product security roadmap, establish and manage the application security vulnerability management process, and work with teams across the business to carry out threat modeling. You will also assess the security posture of our applications and APIs, strengthen the security of our mobile apps, and implement and automate security tools. Additionally, you will build secure coding and deployment knowledge across the organization and ensure our product security practices align with relevant frameworks and standards.
 - Definir y ser responsable de la hoja de ruta de seguridad del producto, alineando prioridades con los objetivos comerciales.
@@ -1123,127 +2794,127 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>jobs.msd.com</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Senior Cyber Security Engineer</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Prague, Central Bohemian, Czechia</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>phenom</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>https://jobs.msd.com/job/R419147</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>We are seeking a Senior Cyber Security Engineer to lead the deployment and enhancement of secrets management and privileged access systems for a global biopharmaceutical leader. Drive innovation in security, collaborate with international teams, and apply your expertise in identity management and cloud security. Ideal for experienced professionals in IT security.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>turquoise-health</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Senior Application Security Engineer</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>$172K – $200K • Offers Equity</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/turquoise-health/21ccc42d-aa61-47d0-8764-aee7cf6ff7ba/application</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>*This is a fully remote role in the United States.*
 Turquoise is hiring a Senior Application Security Engineer to drive security for the applications and data our customers rely on. This role owns application-layer security across Turquoise's platform and is the software counterpart to our infrastructure security. You'll build and tune our code scanning program, driving vulnerabilities from discovery to remediation. Day to day, you'll work closely with engineering teams on the design, architecture, and services our product teams build.
@@ -1294,68 +2965,68 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>namespace</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>$200K – $250K • Offers Equity</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/namespace/41599db0-2a55-4d97-bc92-62636eb3c5bd/application</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t># **Join our mission**
 **We're proud to work with many incredible companies, accelerating their ability to build their products.**
@@ -1391,208 +3062,123 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>wizinc</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sr. Manager, Security Engineering</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Remote - United Kingdom</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>millgroupinc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer – DevSecOps</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Yes / Mentioned</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wiz.io/careers/job/4671799006/:title?gh_jid=4671799006</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Come join the organization that is redefining security for the AI era. As one of the [fastest-growing startups ever,](https://www.wiz.io/blog/100m-arr-in-18-months-wiz-becomes-the-fastest-growing-software-company-ever) we enable teams to secure cloud and AI applications by connecting code, cloud, and runtime into a single shared context. Trusted by security teams all over the world, we have a proven [track record of success](https://www.g2.com/products/wiz-wiz/reviews) and a culture that values world-class talent. Not to mention, we're now [powered by Google](https://cloud.google.com/blog/products/identity-security/google-completes-acquisition-of-wiz), meaning we offer our customers an AI-powered platform that harnesses Google’s Threat Intelligence and Security Operations to better detect, prevent, and respond to threats across all environments, allowing for further innovation.
-Our Wizards from all over the globe work together to protect the infrastructure of our customers, including over 65% of the Fortune 100, who trust us to scan and secure over 230 billion files daily. We’re honored to be a leading player in a massive and growing market, and we continue to look for exceptional Wizards who are eager to make a significant impact on our team. At Wiz, you’ll have the freedom to think creatively, dream big, and use your full range of skills to contribute to our momentous growth. Come join our team and help us create secure cloud environments that allow even the best companies to move faster, all while having some fun!
-**Role Description**
-As a Security Engineering Manager for Product &amp; Production Infrastructure, you will lead and grow a team of talented Security Engineers responsible for protecting cloud-native environments, CI/CD pipelines, and core production infrastructure. In this role, you will act as a technical leader and people manager—providing strategic direction, mentorship, and operational excellence while staying close to modern cloud and container technologies across AWS, Azure, and GCP. You will build deep partnerships with Software Development, DevOps, and Product Management teams to embed secure-by-design principles into developer workflows, drive proactive vulnerability management, and champion our internal dogfooding program to assess, monitor, and influence product roadmaps.
-**Responsibilities**
-- Team Leadership &amp; Talent Development: Recruit, retain, develop, and coach a high-performing, globally distributed team of Security Engineers; establish performance goals, conduct 1:1s, and support career progression.
-- Technical Strategy &amp; Architecture: Lead threat modeling and technical security reviews across product architectures and multi-cloud infrastructure to identify attack surfaces and design scalable mitigation strategies.
-- Security Automation &amp; "Shift-Left": Drive the creation of automation, policy-as-code, and developer-friendly security tooling to integrate continuous, end-to-end security checks into CI/CD workflows.
-- Infrastructure &amp; Container Hardening: Define, implement, and govern secure baselines for multi-cloud resources and managed Kubernetes infrastructure (EKS, GKE, AKS).
-- Vulnerability &amp; Supply Chain Management: Oversee end-to-end vulnerability management and remediation programs, establishing preventative controls across software supply chains from development to production.
-- Detection &amp; Incident Response: Partner with detection and response functions to scale alert triage, investigation capabilities, and automated incident remediation.
-- Cross-Functional Partnership: Build deep functional relationships with Engineering and DevOps leadership to balance security requirements with product delivery velocity.
-**Minimum qualifications**
-- Leadership Experience: 2+ years of experience leading, managing, or mentoring security engineering, DevOps, or technical cloud infrastructure teams.
-- Technical Experience: 7+ years of experience in security engineering or security operations within cloud-native environments.
-- Cloud &amp; Container Security: Strong hands-on cloud security experience in AWS (with working knowledge of Azure or GCP), along with deep knowledge of Kubernetes (EKS/GKE/AKS) and container security principles.
-- Identity &amp; Access Management: In-depth understanding of cloud IAM architecture and identity security at enterprise scale.
-- Infrastructure as Code &amp; Automation: Hands-on experience with IaC frameworks (Terraform, CloudFormation, Helm, or Pulumi) and automation scripting/tooling in Python, Go, Shell, HCL, or Rego.
-- Application Security: Practical knowledge of web application security fundamentals and threat modeling (e.g., OWASP Top 10, software supply chain security).
-**Preferred qualifications**
-- Bachelor's degree in Computer Science, Cybersecurity, a related technical field, or equivalent practical experience.
-- Experience managing and scaling remote, globally distributed engineering teams.
-- Prior experience in organizations that develop and operate large-scale SaaS or managed cloud services.
-- Experience with CNAPP, CSPM, CIEM, or CDR platforms and methodologies.
-*Applicants must have the legal right to work in the country where the position is based, without the need for visa sponsorship. This role does not offer visa sponsorship.*
-Wiz is an equal opportunity employer. We do not discriminate based upon race, religion, color, national origin, sex (including pregnancy, childbirth, reproductive health decisions, or related medical conditions), sexual orientation, gender identity, gender expression, age, status as a protected veteran, status as an individual with a disability, genetic information, political views or activity, or other applicable legally protected characteristics.
-By submitting your application, you acknowledge that Wiz will process your personal data in accordance with [Wiz's Privacy Policy.](https://www.wiz.io/legal/privacy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>icims</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>https://careers-millgroupinc.icims.com/jobs/3134/cybersecurity-engineer-%e2%80%93-devsecops/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Millennium is proud to be part of the Markon enterprise, a network of specialized organizations united in support of critical national security missions. This partnership strengthens our ability to deliver results by expanding our technical depth, operational reach, and access to a broader bench of proven experts, ensuring our customers continue to receive best-in-class cybersecurity support. Since 2004, Millennium has operated at the forefront of cybersecurity. Our elite team of over 300 professionals brings an unmatched record of performance across Red Team Operations, Defensive Cyber Operations, Software Engineering, and Technical Engineering. As home to the...</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>millgroupinc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer – DevSecOps</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>US-Remote</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>InPost</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AI Security Engineer (m/f/n)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Warszawa, Województwo mazowieckie, pl</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>icims</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://careers-millgroupinc.icims.com/jobs/3134/cybersecurity-engineer-%e2%80%93-devsecops/job?in_iframe=1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Millennium is proud to be part of the Markon enterprise, a network of specialized organizations united in support of critical national security missions. This partnership strengthens our ability to deliver results by expanding our technical depth, operational reach, and access to a broader bench of proven experts, ensuring our customers continue to receive best-in-class cybersecurity support. Since 2004, Millennium has operated at the forefront of cybersecurity. Our elite team of over 300 professionals brings an unmatched record of performance across Red Team Operations, Defensive Cyber Operations, Software Engineering, and Technical Engineering. As home to the...</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>InPost</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AI Security Engineer (m/f/n)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Warszawa, Województwo mazowieckie, pl</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/InPost/744000153204239-ai-security-engineer-m-f-n-?oga=true</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>Your responsibilities: Work on the security assessment and secure design review of AI, LLM and agentic systems across InPost's technology estate. Identify, reproduce and reason about real vulnerabilities in AI-powered and agentic systems, and work with engineering teams to fix them at the root cause. Define and build engineered security controls for AI/ML and LLM-related risks. Build security automation and developer-facing tooling that helps product and engineering teams build securely by default. Review new AI solutions and system architectures for security risk, and represent security in AI governance forums and the AI solutions catalogue. Apply hands-on cloud and container security practices across AWS, Azure and GCP to secure the infrastructure AI systems run on. Act as a go-to expert on AI-specific attack classes, keeping InPost's defences ahead of an evolving threat landscape. Translate complex technical and security findings into clear, practical guidance for stakeholders across the business.
 Must have: 5+ years of experience in application security or product security. 5+ years of coding experience in one or more general-purpose languages , including shipping and operating production services. 5+ years of experience with security assessments, secure design reviews or threat modelling. Solid understanding of generative AI, LLMs and AI agents , and how they're built and deployed in production. Deep knowledge of AI-specific attack classes and how they apply to real systems. Experience securing agentic, code-execution or LLM-integrated systems. A track record of finding and reasoning about real vulnerabilities in real systems. Experience building engineered security controls, not just flagging issues. Hands-on cloud and container security experience on AWS, Azure or GCP. Strong presentation skills, with the ability to translate complex technical and security topics into clear business terms for a wide range of stakeholders. Good English skills , enabling confident communication in an international environment. Nice to have: Background building security automation or developer-facing security tooling. Working knowledge of the OWASP Top 10 for LLM Applications and OWASP Top 10 for Agentic Applications. Working knowledge of MITRE ATLAS.
@@ -1601,64 +3187,64 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/8812b7f5-0d7f-4a7a-bc69-2730071a26d8/apply</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Netherlands.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1709,64 +3295,64 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/564da8a5-89ec-4536-9e5f-c86a99793f3d/apply</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Ireland.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1817,64 +3403,64 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/b52ca408-713f-4d50-b4ee-3fd8b866bd80/apply</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Switzerland.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -1925,64 +3511,64 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/4ba6089c-3318-4188-b146-82ba27cff1fd/apply</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in France.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2033,64 +3619,64 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/c9b6d010-a351-4e24-a51e-3f50effcf13f/apply</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Spain.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2141,64 +3727,64 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/0cb3482e-758e-4af2-8aba-1dff0aae89d3/apply</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in United Kingdom.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2249,64 +3835,64 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Staff Security Researcher</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/8770cdc2-d817-4516-89ca-c82aa0889904/apply</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Staff Security Researcher based in Germany.**
 This role is designed for a hands-on offensive security researcher who can turn advanced vulnerability and malware research into production-ready detection capabilities. You will investigate emerging threats across web applications, APIs, cloud-native environments, and AI-powered systems, translating discoveries into accurate security checks with low false-positive rates. The position combines deep technical research with practical engineering, from exploit proof-of-concepts to detection rules, evaluation frameworks, and attack-chain methodologies. You will also contribute to research standards, security tooling, and the broader application security community through publications and technical contributions. Working across engineering, product, AI/ML, and infrastructure teams, you will help ensure research moves efficiently from discovery to production. The role offers a high degree of ownership in a fast-evolving security environment where technical curiosity and measurable detection quality are highly valued.
@@ -2357,187 +3943,187 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Enjoy Gaming LLC</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Application Security Engineer</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Remote job</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>recruitee</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>https://enjoygaming.recruitee.com/o/application-security-engineer/c/new</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>Enjoy Gaming is a software provider focused on creating high-quality digital entertainment experiences, including Slots and Live Games. Our team brings together experienced professionals in game development, product, and design, driven by a passion for innovation and quality. At Enjoy Gaming , we value ownership , excellence , and drive . These principles shape the way we work, collaborate, and build products. Join us and be part of our innovative journey in the gaming world! We’re looking for a sharp Application Security Engineer to join our team and act as the technical guardian for our games and platforms. If you have an attacker's mindset but know how to build and defend alongside engineering teams, this role is for you. In this position, you won’t just be sending reports to the teams or management. You’ll be diving deep into web and desktop applications, hunting down game-level vulnerabilities, and collaborating closely with our Architects, Studio, Slots, and Platform Developers to engineer more resilient systems.
 What we're looking for: 5+ years of Application Security Engineer experience Background in red teaming, penetration testing, application security, and software development Able to independently find vulnerabilities in web and desktop applications, triage them, and, where needed, fix them Solid grounding in data structures, algorithms, and systems architecture designs Previous security testing experience with Kafka/Redis/BullMQ/PubSub as message/streaming tools Codes independently, can navigate unfamiliar web application frameworks Experience using AI tools to aid with vulnerability hunting Comfortable talking to developers and turning findings into practical, actionable advice Nice to have: CRTO, OSCP, or OSWE certifications or similar Knowledge of Cloud Platforms (GCP/AWS) Understanding of CI/CD pipelines Hands-on experience with Trivy, Nessus, Acunetix, or Wiz Experience in iGaming or another regulated industry What You Will Do: Own and maintain our application security pipelines: SCA (Github/Trivy), DAST (Nessus, Acunetix, Wiz), and SAST Triage findings from these tools and drive them to remediation Perform penetration tests on new platform features, new internal applications, and new slots and live games Run basic red team activities, including leaked credential reviews and external attack surface audits Review complex auth flows with various third parties for cryptographic and security issues Review/Triage application code for security issues ( 85% NestJS / 15% .NET ) Own security risk in existing code and applications Act as the application-level security expert during incident response and be ready to deliver hotfixes yourself when needed Prepare our quarterly SAST/DAST vulnerability scan reports for stakeholders/regulators and take part in audit meetings Own the Secure Coding and Application Security areas of our ISMS Meet regularly with development teams, learn about upcoming features early, and advise on secure design What We Offer: Competitive Salary in EUR : with annual performance reviews to recognize your growth Flexible Remote Work : balance productivity and comfort Comprehensive Benefits : including medical insurance, psychologist support, and Polish, Slovak-speaking clubs Generous Paid Time Off : 20 working days of paid vacation, plus 10 additional paid days off, 10 paid sick days, and all national holidays in your country Professional Development Support : reimbursement for courses, trainings, and certifications Well-being Perks: support for language classes, sports, massages, or life coaching Please note that feedback on your application will be provided within two weeks if a positive decision is made regarding your candidacy. I give my consent following the Law on the Protection of Personal Data dated June 1, 2010, No. 2297, effective from January 1, 2011, for the processing of information classified as personal data.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>cyberone-security</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Senior Azure Security Engineer</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>teamtailor</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>https://cyberone-security.teamtailor.com/jobs/8491321-senior-azure-security-engineer</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>“I am hugely excited about my future and the future of CyberOne. I have enjoyed my time here immensely and have learnt a huge amount in a short space of time, year-for-year I've learnt more here than I have at Microsoft and PwC.” - CyberOne Consultant About CyberOne CyberOne is a pure-play Microsoft security partner dedicated to helping enterprises realise the full value of the Microsoft Security portfolio—across Defender XDR, Sentinel, Entra, Purview, Intune, Copilot for Security and more. We combine deep technical expertise with outcome-driven services that accelerate secure cloud adoption, modernise threat protection and simplify compliance. Job Title: Senior Azure Security Engineer Location: Hybrid ; 1 day per month reporting in London office Employment Type: Full-time Purpose of Role We are seeking an experienced Senior Azure Security Engineer to join the Cyber Security team. The role is responsible for designing, implementing, securing and supporting Microsoft security technologies across cloud, identity, endpoint, infrastructure and security monitoring platforms. The engineer will work closely with Security Operations, Infrastructure, Cloud Engineering, Architecture, Identity and Application teams to strengthen security controls, improve monitoring capabilities, automate security processes and support the organisation's cyber resilience. The role combines Azure security engineering, Microsoft Sentinel, Microsoft Defender, cloud security architecture, automation and operational support across a hybrid enterprise environment. Main Duties and Responsibilities Act as a Subject Matter Expert for Microsoft Azure security, Microsoft Sentinel, Microsoft Defender XDR and associated Microsoft security technologies. Design, implement and support enterprise security controls across Azure, Microsoft Entra ID and the Microsoft security ecosystem. Engineer and maintain Microsoft Sentinel capabilities, including data connectors, analytics rules, KQL queries, workbooks, watchlists, automation rules and playbooks. Design, implement and optimise Microsoft Defender capabilities, including Defender for Endpoint, Defender for Identity, Defender for Cloud, Defender for Office 365 and Defender XDR. Develop security monitoring use cases, threat detections and hunting queries aligned to business risks, threat intelligence and MITRE ATT&amp;CK. Design secure cloud and hybrid architecture patterns and provide practical technical guidance to projects and engineering teams. Engineer telemetry and logging solutions using Azure Monitor, Log Analytics, Azure Monitor Agent, Data Collection Rules, custom tables and API-based integrations. Design and implement security automation using Logic Apps, Azure Functions, REST APIs, PowerShell and Python. Perform technical security assessments and review cloud solutions against enterprise security standards, control requirements and secure-by-design principles. Implement and maintain cloud security baselines, hardening standards, policy controls and configuration-management practices. Support vulnerability and configuration-risk remediation across Azure and Microsoft security platforms. Support cyber incident investigations and provide security expertise during critical incidents and major technology changes. Produce and maintain High-Level Designs, Low-Level Designs, engineering standards, operating procedures, support documentation and implementation records. Lead platform enhancements, proof-of-concepts, migrations, upgrades, troubleshooting and service-improvement activities. Build platform health monitoring, operational dashboards and KPI/KRI reporting for the Proactive Security function. Person Specification Essential Experience Proven Azure security engineering experience within a large, complex enterprise environment. Strong hands-on experience implementing and supporting Azure security services across IaaS, PaaS and hybrid environments. Practical experience with Microsoft Entra ID security, including Conditional Access, Privileged Identity Management, Identity Protection and hybrid identity controls. Strong experience with Microsoft Sentinel and Microsoft Defender XDR, including Endpoint, Identity, Cloud and Office 365 security capabilities. Experience designing and implementing cloud security architecture, platform hardening, technical security controls and security baselines. Experience onboarding and validating infrastructure, cloud, application, identity and security telemetry. Experience developing KQL queries, analytics rules, workbooks, automation and threat-hunting content. Experience conducting technical risk assessments, security-control validation and vulnerability-remediation support. Experience with REST APIs, PowerShell, Python, automation, enterprise troubleshooting and operational support. Experience working with Security Operations, Incident Response, Cloud, Infrastructure, Identity and Architecture teams. Technical Knowledge and Skills Azure security and governance: Azure Policy, Defender for Cloud, Azure Monitor, Log Analytics, Azure Arc, Key Vault, managed identities, role-based access control, landing-zone security and cloud security posture management. Cloud and network security: Virtual Networks, Network Security Groups, Azure Firewall, Private Endpoints, Private Link, secure connectivity, segmentation and hybrid-cloud security patterns. Identity security: Microsoft Entra ID, Conditional Access, Privileged Identity Management, Identity Protection, authentication, access control, federation and identity governance. Microsoft security platform: Microsoft Sentinel, Defender XDR, Defender for Endpoint, Defender for Identity, Defender for Office 365 and Defender for Cloud. Security monitoring: KQL, analytics rules, hunting queries, workbooks, data connectors, Data Collection Rules, watchlists, automation rules, playbooks and ingestion optimisation. Automation and engineering: Logic Apps, Azure Functions, REST APIs, PowerShell, Python, Azure DevOps, Git, CI/CD and Infrastructure-as-Code concepts. Secure engineering: Security architecture, technical risk assessment, platform hardening, vulnerability remediation, control validation, secure development practices and operational readiness. Desirable Experience Experience securing Azure landing zones and enterprise-scale cloud platforms. Experience with Security Orchestration, Automation and Response solutions and automated control validation. Experience with Privileged Access Management and Zero Trust security principles. Experience supporting security platforms in a regulated financial-services environment. Exposure to multi-cloud or hybrid-cloud environments, including AWS or GCP. Qualifications Degree or equivalent professional experience in Information Technology, Cyber Security, Engineering or a related discipline. Microsoft AZ-500 and SC-200 certifications are strongly preferred. Microsoft SC-100, SC-300 or AZ-104 certifications are desirable. Additional cloud-security certifications such as CISSP, CCSP or relevant GIAC qualifications are advantageous.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Security Engineer (Threat Response), Sophos Security Team (IDR)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Yes / Mentioned</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/6627c9a0-ec93-442d-89de-f9d7202f13a5/apply</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Security Engineer (Threat Response), Sophos Security Team (IDR) based in Canada.**
 This is a senior security engineering role combining hands-on incident response with detection engineering, automation, and threat research. You will investigate complex cyber threats across endpoints, identity, cloud, networks, and security products while helping strengthen internal detection and response capabilities. The role goes beyond traditional incident response, with a strong focus on building scalable automations, reusable workflows, and agentic security tooling. You will use modern AI-assisted development tools while applying rigorous safety, observability, and validation practices. Collaboration spans security, engineering, product, and business teams in a globally coordinated environment. The position is remote-first and offers the opportunity to shape how advanced security operations evolve through engineering and responsible AI adoption.
@@ -2588,60 +4174,60 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>purestorage</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/purestorage/jobs/8191920</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>Everpure (NYSE: P) has evolved from storage pioneer to data platform, closing fiscal 2026 with $3.7 billion in revenue, its first billion-dollar quarter, and accelerating growth into FY27. Our strategic agenda spans the companies defining the next era of technology - hyperscalers, AI labs, the AI hardware supply chain, data platform providers, and the broader AI ecosystem.
 This type of work—work that changes the world—is what the tech industry was founded on. So, if you're ready to seize the endless opportunities and leave your mark, come join us.
@@ -2675,60 +4261,60 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>align</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>DevSecOps Engineer</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Panama - Remote</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/align/jobs/8859924002</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>#### **About the Role**
 The DevSecOps Engineer works to execute security engineering activities across A-LIGN's cloud infrastructure, CI/CD pipelines, and production applications. In this role, you will be responsible for implementing and continuously validating security controls, delivering infrastructure and application improvements, and supporting continuous audit readiness. As the DevSecOps Engineer, you will provide exceptional technical and security strategies to help support the continued growth of our fast-paced company. A-LIGN will depend on you as the DevSecOps Engineer to support management, translate security and compliance requirements into practical engineering solutions, and automate security and audit evidence workflows.
@@ -2794,64 +4380,64 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Ki</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Senior Application Security Engineer (AI)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/lNcmq3/jobs/senior-application-security-engineer-ai_london_hatyplwl</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>Join Ki, the fastest growing algorithmic insurance carrier in the Lloyd's of London market. As a Senior Application Security Engineer, you will empower our engineering and product teams to safely adopt AI and embed robust technical security controls directly into our services and workflows. Your work will span our entire development lifecycle, protecting everything from agentic LLM integrations to the everyday tools we use.
 - Provide practical implementation advice and guidance on securing AI-powered applications, aligning with frameworks like OWASP ASVS and the OWASP Top 10 for LLM Applications.
@@ -2860,64 +4446,64 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Naval Group [FR]</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>CDI - Developpeur DevSecOps Programme Sous-Marin - H/F</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Ollioules, Provence-Alpes-Cote d'Azur, France</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/jj6huE/jobs/cdi-developpeur-devsecops-programme-sous-marin-h-f_ollioules</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>Rejoignez Naval Group, un leader mondial de l'industrie navale de défense. En tant que Développeur DevSecOps, vous serez responsable de la conception, du développement, de l'intégration et du déploiement d'applications, en intégrant les exigences de sécurité dès les premières étapes du cycle de développement. Vous travaillerez en étroite collaboration avec les équipes de développement, d'intégration, d'exploitation et de cybersécurité.
 - Concevoir, développer et maintenir des composants logiciels et des scripts d’automatisation.
@@ -2954,292 +4540,356 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>CACI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>DevSecOps Lead Engineer</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>remote (any state)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>eightfold</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>https://caci.eightfold.ai/careers/job/1443153785475</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>CACI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>SAP Security Engineer</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>remote (any state)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>eightfold</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>https://caci.eightfold.ai/careers/job/1443153781490</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>brightvisiontechnologies</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>ML Security Engineer</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>jazzhr</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/5Izo29N73O</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Jenny@bvteck.com&gt; or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ML Security Engineer- Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: ML Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Six or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3544. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>jobs.msd.com</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Senior Specialist - SAP Authorizations and Security Architect</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Boxmeer, North Brabant, Netherlands</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
         <is>
           <t>phenom</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>https://jobs.msd.com/job/R390393</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>We are currently hiring a Senior Specialist - SAP Authorisations and Security Architect to support the strategy, design, and implementation of SAP authorisations and security across multiple platforms. You will collaborate with cross-functional teams and lead technical projects. Ideal candidates have significant SAP authorisation and security experience.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>anaconda</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sr. Security Engineer - Platform &amp; Shared Services</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>rippling</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/anaconda/jobs/081aabf7-7c04-431b-87f5-91e79b971bad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Summary: Anaconda's Security team protects and enables our platform, serving 50 million users and supporting our transition into an AI-native development platform. As a Security Engineer, you'll build secure-by-default systems through hands-on engineering—designing controls that reduce systemic risk while helping engineering teams ship faster. Your work spans firewalls, IAM, endpoint detection, secrets management, and CI/CD pipeline security across hybrid and multi-cloud environments. What You'll Do: Design and implement security controls across firewalls, IAM, endpoint detection and response, and secrets management in hybrid and multi-cloud environments Build security automation and tooling using Python, Go, or Bash, managing infrastructure as code with Terraform to scale security operations Conduct vulnerability and threat management by triaging scanner output, investigating root causes, and driving risk reduction across the platform Perform code reviews and architecture assessments to identify security risks early in the development lifecycle Embed security into CI/CD pipelines through static analysis, dynamic testing, and dependency scanning Respond to security incidents as an escalation point, perform forensic analysis, and maintain tested runbooks for critical risks and zero-day events Partner with Legal, IT, Platform Engineering, and Developer Experience teams to balance security rigor with developer velocity Develop secure-by-default templates, libraries, and tooling that add velocity rather than friction Your Impact Will Be Measured By: Design and implement security controls across firewalls, IAM, endpoint detection and response, and secrets management in hybrid and multi-cloud environments Risk reduction velocity measured by mean time to remediate high-severity vulnerabilities and percentage of defects caught in development versus production Operational automation measured by reduction in false positive rates and percentage of security baselines managed through infrastructure as code Cross-functional partnership measured by adoption of secure-by-default templates and feedback from engineering teams Incident preparedness measured by runbook coverage and response effectiveness during critical risks or zero-day events What You Need: 6+ years hands-on experience in systems administration, DevOps, network engineering, or software development prior to or alongside security work Proficiency with cloud platforms such as AWS, Azure, or GCP Experience managing infrastructure as code using Terraform Experience writing scripts and automation in Python, Go, or Bash Working knowledge of IAM, PKI, cryptography basics, network protocol analysis, and threat modeling frameworks Experience working in containerized environments with Docker or Kubernetes Ability to communicate technical security risks to non-security audiences and design workflows that respect developer experience What Will Make You Stand Out: Offensive security experience through penetration testing, red teaming, bug bounty programs, or reverse engineering Experience with advanced container security tools such as Falco or eBPF-based monitoring Implemented zero trust architecture and network isolation in production environments Production engineering, SRE, or software engineering background with experience writing custom static or dynamic analysis rules, or managing SBOM and supply chain security Specialized expertise in HSMs, hardware tokens (YubiKeys, FIDO2), applied cryptography, or identity provider integrations Contributed to security culture through training programs, threat modeling workshops, CTF events, conference talks, or open-source security projects Thrived in fast-paced startup environments balancing speed with pragmatic risk managementExperience working in a fast-paced startup environment Experience working in an open-source, AI, or data science-oriented company Why You'll Like Working Here: You'll thrive in a high-performance environment where results are recognized and rewarded Your work directly contributes to shaping the future of data science, machine learning, and AI in the enterprise. You'll work alongside a collaborative team that values diverse, thoughtful discussion, clarity and candor. You'll be supported by a culture that puts employees first - with flexible hours, a fully remote setup, and a genuine commitment to your wellbeing and growth. We accept applications on an ongoing basis. In addition to base salary, we offer a comprehensive benefits package that includes: Office setup reimbursement Monthly productivity stipend Learning and Development reimbursement Open vacation policy* Public holidays Snake Days-quarterly extra day off company wide An Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, or protected veteran status and will not be discriminated against on the basis of disability. Anaconda, Inc. (“We”, “Us”) are committed to protecting and respecting your privacy. This Privacy Notice sets out the basis on which the personal data collected from you, or that you provide to Us, will be processed by Us in connection with Our recruitment processes. By clicking “Submit Application”, you acknowledge you have read our Privacy Policy and that Anaconda can retain your application data for up to 1-year, unless otherwise stated. For the purpose of the General Data Protection Regulation (“GDPR”) ”) and the version of the GDPR retained in UK law (the “UK GDPR”) the Data Controller is Vanessa Macilwaine. Anaconda is an EEO/AA employer M/F/V/D.
+About Anaconda Be at the center of AI Anaconda is built to advance AI with open source at scale, giving builders and organizations the confidence to increase productivity, and save time, spend and risk associated with open source. 95% of the Fortune 500 including Panasonic, AmTrust, Booz Allen Hamilton and over 50 million users rely on the value The Anaconda AI Platform delivers through a centralized approach to sourcing, securing, building, and deploying AI. With 21 billion downloads and growing, Anaconda has established itself as the gold standard for Python, data science, and AI and the enterprise-ready solution of choice for AI innovation. Anaconda is backed by world-class investors including Insight Partners. Learn more at &lt;https://www.anaconda.com&gt; .</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>samsara</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Senior AI Security Engineer</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Remote - Dallas</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>https://www.samsara.com/company/careers/roles/8247429?gh_jid=8247429</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>**Who we are**
 Samsara (NYSE: IOT) is the pioneer of the Connected Operations™ Cloud, which is a platform that enables organizations that depend on physical operations to harness Internet of Things (IoT) data to develop actionable insights and improve their operations. At Samsara, we are helping improve the safety, efficiency and sustainability of the physical operations that power our global economy. Representing more than 40% of global GDP, these industries are the infrastructure of our planet, including agriculture, construction, field services, transportation, and manufacturing — and we are excited to help digitally transform their operations at scale.
@@ -3290,60 +4940,60 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>bloomreach</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bloomreach/jobs/8247118</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>Bloomreach is building the world’s premier **agentic platform for personalization**.We’re revolutionizing how businesses connect with their customers, building and deploying AI agents to personalize the ***entire*** customer journey.
 - We're taking **autonomous search** mainstream, making product discovery more intuitive and conversational for customers, and more profitable for businesses.
@@ -3437,60 +5087,60 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>bloomreach</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/bloomreach/jobs/8247117</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>Bloomreach is building the world’s premier **agentic platform for personalization**.We’re revolutionizing how businesses connect with their customers, building and deploying AI agents to personalize the ***entire*** customer journey.
 - We're taking **autonomous search** mainstream, making product discovery more intuitive and conversational for customers, and more profitable for businesses.
@@ -3584,60 +5234,60 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>catawiki</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Lead Security Engineer</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/8245606</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>At Catawiki, every day brings the extraordinary! Whether it’s [Daniel Ricciardo’s Formula 1 Car](https://www.catawiki.com/en/c/583-sports-memorabilia), a [Woolly Mammoth’s Skeleton](https://www.catawiki.com/en/c/579-fossils), [Lady Gaga's Jumpsuit](https://www.catawiki.com/en/l/10035805) or [Usain Bolt’s running shoe](https://www.catawiki.com/en/c/583-sports-memorabilia), we encounter exceptional objects every day.
 We’re a one-of-a-kind marketplace for buying and selling special objects. Each week, more than 100,000 unique items are auctioned, all carefully curated by our passionate in-house experts.
@@ -3684,68 +5334,68 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>The Adecco Group</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>CYBERSECURITY ENGINEER H/F</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Montpellier, Occitanie, France</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/ZMet0N/jobs/cybersecurity-engineer-h-f_montpellier</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>Rejoignez Akkodis, une entreprise leader dans le domaine de la technologie et de l'ingénierie. En tant qu'Ingénieur Cybersécurité, vous serez au cœur d'un projet industriel majeur dans le secteur de l'énergie. Vous serez responsable de la supervision et de l'analyse du trafic réseau, du développement et de la mise en œuvre de mesures de sécurité, ainsi que de la gestion des outils et technologies de sécurité. Vous travaillerez dans un environnement exigeant et collaborerez avec les équipes IT et opérationnelles pour garantir la cohérence et la sécurité des installations.
 - Superviser et analyser le trafic réseau afin de détecter et répondre aux incidents de sécurité.
@@ -3756,64 +5406,64 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>aboutyougmbh</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Junior Application Security Engineer (all genders)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Hamburg, HH, de</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/ABOUTYOUGmbH/744000152882199-junior-application-security-engineer-all-genders-?oga=true</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>Wir suchen einen Junior Application Security Engineer (all genders) zur Verstärkung unseres Application-Security-Teams innerhalb der IT-Sicherheitseinheit, die sich dem Schutz unseres Onlineshops, unserer Unternehmenssysteme und unserer Kunden widmet. In dieser Rolle gehst du gezielt gegen interne Systeme vor (Pentesting/Ethical Hacking) sowie planst und implementierst Sicherheitsmaßnahmen zum Schutz unserer Infrastruktur, Anwendungen und Daten. Du arbeitest eng mit anderen Security Engineers, Entwickler:innen und IT-Teams zusammen, um Security Best Practices zu gewährleisten, Sicherheitsprozesse zu automatisieren und auf neue Bedrohungen zu reagieren. Die Stelle umfasst folgende Aufgaben: Durchführung regelmäßiger Penetrationstests und Code-Reviews Beratung bei der Einrichtung und Wartung von Anwendungen und Infrastruktur (in der Regel gehostet in AWS/Kubernetes) Triage und Behebung/Verfolgung von Überwachungsereignissen (Monitoring Events) Optimierung und Automatisierung von Sicherheitsprüfprozessen. Dies kann auch den Aufbau von Angriffsinfrastruktur, das Schreiben von Python-Skripten und die Implementierung von Security Scans in GitLab CI beinhalten Mitwirkung an Incident-Response-Aktivitäten im SOC, einschließlich gelegentlicher 24/7-Rufbereitschaft
 Mindestens ein Jahr Erfahrung im Bereich Application Security Fähigkeit zur Durchführung aktiver Sicherheitsbewertungen von Anwendungen (Application Security Assessments) und Penetrationstests Nice to have: Entwicklung und Scripting in Python (erforderlich; PHP, JavaScript oder Go bevorzugt) Architektur sicherer Systeme mittels Bedrohungsmodellierung (Threat Modeling) und Security-Engineering-Praktiken Durchführung sicherer Code-Reviews über verschiedene Cloud-Umgebungen hinweg (AWS/GCP bevorzugt; Azure von Vorteil) Durchführung von Red-Teaming-Operationen und offensiven Sicherheitsstrategien Zertifikate: z. B. OSCP, OSWP etc. Kenntnisse in Laravel / PHP Fähigkeit, JavaScript zu lesen und zu verstehen Fähigkeit, Go zu lesen und zu verstehen Erfahrung mit Incident-Response-Aktivitäten Erfahrung mit Web Application Firewalls (WAF) und CDN-Anbietern (z. B. Cloudflare, Akamai) Erfahrung mit GitLab CI/CD-Pipelines
@@ -3822,64 +5472,64 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>jobgether</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Senior Software Engineer (Product Security)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>lever</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/jobgether/9664e737-bd33-49c7-82c7-62b370e3cddb/apply</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>**This position is listed on behalf of a partner company, who manages all applications and next steps. Our partner is looking for a Senior Software Engineer (Product Security) based in Canada.**
 This role combines senior-level software engineering with a strong product security focus in a cloud-native infrastructure environment. You will design, build, and maintain production features while helping embed security directly into the product and engineering lifecycle. Your work will span vulnerability response, threat modeling, security-sensitive design reviews, and technical decision-making across the platform. You will work deeply within the codebase and architecture rather than focusing primarily on security tooling or compliance operations. The role offers significant technical ownership and the opportunity to influence secure engineering practices across a distributed, remote-first team.
@@ -3913,194 +5563,194 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Accso – Accelerated Solutions GmbH</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Senior Software Security Engineer*</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Frankfurt am Main, Hessen, Deutschland</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>87500 - 125500 EUR</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>recruitee</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>https://accso.recruitee.com/o/senior-software-security-engineer-4/c/new</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über langjährige Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Du repräsentierst Accso als verlässlicher Partner entlang des gesamten Projektlebenszyklus - von der Akquise bis zur Abnahme - und gibst dein Wissen proaktiv weite r Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst fundierte, tiefgreifende Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über profundes Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du handelst unternehmerisch, übernimmst Verantwortung und überzeugst durch souveräne, zielgruppengerechte Kommunikation mit unterschiedlichsten Stakeholdern bis auf Vorstandsebene Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email:</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über langjährige Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Du repräsentierst Accso als verlässlicher Partner entlang des gesamten Projektlebenszyklus - von der Akquise bis zur Abnahme - und gibst dein Wissen proaktiv weite r Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst fundierte, tiefgreifende Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über profundes Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du handelst unternehmerisch, übernimmst Verantwortung und überzeugst durch souveräne, zielgruppengerechte Kommunikation mit unterschiedlichsten Stakeholdern bis auf Vorstandsebene Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email: &lt;bewerben@accso.de&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Accso – Accelerated Solutions GmbH</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Software Security Engineer*</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Frankfurt am Main, Hessen, Deutschland</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>61500 - 85500 EUR</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>recruitee</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>https://accso.recruitee.com/o/software-security-engineer-6/c/new</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst tiefgehende, praktische Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du arbeitest eigenverantwortlich und trägst aktiv zum Erfolg deines Projektteams bei Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email:</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Das erwartet dich bei uns: Du arbeitest in Beratungs- und Softwareentwicklungsprojekten bei Kunden wie AXA, BMW, der Deutschen Bahn und ZDF Du konzipierst, entwickelst und implementierst Softwarelösungen, in dem du AI-Methoden und Tools im gesamten Softwareentwicklungsprozess anwendest (z.B. LLMs, agentische Frameworks, Codegenerierung und Testautomatisierung) Du verfügst über Erfahrung und Expertise in der sicheren Software Entwicklung, um Best Principles und Practices für sichere Softwareentwicklung, z. B. NCSC, OWASP oder Mitre, in den Projekten einzusetzen und an uns anzupassen Du arbeitest mit modernen Technologien wie C#, Java, JavaScript, Spring oder Vue – je nach deinen Stärken und Interessen bringst du einen Teil davon in unsere Projekte ein und bist verantwortlich für die IT-Sicherheit Du entwirfst und baust sichere Infrastrukturen in der Cloud (z. B. AWS, Azure, IONOS, Google) für die von uns entwickelten Anwendungen Das zeichnet dich aus: Du hast einen Hochschulabschluss in Informatik oder in einer vergleichbaren Disziplin erfolgreich abgeschlossen​ Du bringst tiefgehende, praktische Kenntnisse im Software Engineering mit und fühlst dich sowohl im Backend als auch im Frontend wohl Du beherrscht Secure by Design, Zero Trust und andere Prinzipien der IT-Sicherheit hast diese bereits erfolgreich in komplexen und anspruchvollen Projekten eingebracht Du verfügst über Wissen zu den OWASP Top 10 und Mitre CWE Top 25, wendest diese Praktiken an und vermeidest entsprechende Risiken. Du besitzt Erfahrungen mit Automatisierung im Sinne von DevOps und die Integration von Sicherheitstools (SAST, SCA, IAST, DAST) damit Du arbeitest eigenverantwortlich und trägst aktiv zum Erfolg deines Projektteams bei Du sprichst fließend Deutsch (mindestens C1 Level) und sehr gut Englisch (mindestens B2) Unser Angebot an dich: Wertschätzung &amp; Zusammenarbeit auf Augenhöhe 12 Weiterbildungstage pro Jahr Fachlicher Austausch &amp; Wissenstransfer: 14 interne Communities &amp; Netzwerke (z. B. ML, Green IT, Architektur, IoT) Familienfreundliche Arbeitszeiten und hybrides Arbeiten mit Homeoffice-Anteil Jobrad, Workation, Sabbatical, Kinderbetreuungszuschuss, Gesundheitsprogramme und vieles mehr Faires Gehaltsmodell: Finale Vergütung richtet sich nach deiner Qualifikation und bisherigen Erfahrung Das ist Accso:​ Accso ist Digitalpartner für anspruchsvolle Softwarelösungen nach Maß – mit AI Native Mindset . Wir verbinden exzellentes Engineering und Qualitätsbewusstsein mit pragmatischem KI-Einsatz, von der Konzeption über die Entwicklung bis hin zum Betrieb. Uns treibt eine klare Vision: die Welt ein Stück besser machen , indem wir gemeinsam mit unseren Kunden zukunftssichere Softwareentwicklung und messbaren Impact schaffen. Dabei steht der Mensch im Fokus – bei unseren Kunden genauso wie in unseren Teams. Wir arbeiten partnerschaftlich, lösungsorientiert, exzellenzgetrieben, mit offener Kommunikation auf Augenhöhe. In interdisziplinären Teams bringst du dich direkt beim Kunden ein – mit viel Gestaltungsspielraum, aktivem Wissenstransfer und einer Kultur, die Neugier, Verantwortung und Lernen fördert. Bei uns kannst du dich einbringen, wie du bist, moderne Technologien verantwortungsbewusst einsetzen und dich fachlich wie persönlich stetig weiterentwickeln. Wir freuen uns auf deine Bewerbung. Deine Bewerbung: Es ist uns nicht so wichtig, dass du die Stellenanforderungen zu 100% erfüllst, sondern dass du unser Team mit deinen Talenten, deinem Wissen und deiner Art bereicherst und wir gemeinsam wachsen. ​ *Für uns ist dein Talent entscheidend, nicht dein Geschlecht, deine Herkunft, Glaubensrichtung, sexuelle Orientierung oder eine eventuelle Behinderung.​ Kontakt Nadja Groß Talent Manager Mobil: +49 1514 0230948 Email: &lt;bewerben@accso.de&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008035003</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4152,60 +5802,60 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008034003</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4256,60 +5906,60 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008033003</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4363,60 +6013,60 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008030003</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4473,60 +6123,60 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>sentinellabs</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Staff Cloud Security Researcher</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>https://www.sentinelone.com/jobs/?gh_jid=8008029003</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>### Our Purpose
 At SentinelOne, we are driven by a clear purpose: to give the advantage to those who secure our future. As AI reshapes how organizations build, operate, and innovate, the responsibility to protect them becomes more critical than ever. When you join SentinelOne, your work helps protect global enterprises, critical infrastructure, and the technologies shaping tomorrow. If you are motivated by meaningful challenges and want your impact to be real, measurable, and global, you will find purpose here.
@@ -4584,64 +6234,64 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>System Engineer – Data &amp; Cloud Security</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Milan, Lombardy, Italy</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bVBkJa/jobs/system-engineer-data-cloud-security_milan_ND_8VrqXdV</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>Unisciti a NTT DATA, un'azienda globale leader nei servizi di business e tecnologici. Stiamo cercando un Cybersecurity System Engineer da inserire in attività di System Integration e Managed Security Services (MSS) in ambito Data &amp; Cloud Security. In questo ruolo, supporterai la progettazione e realizzazione di infrastrutture di sicurezza per clienti enterprise, lavorando su soluzioni CNAPP, progetti DLP, PKI e crittografia. La sede di lavoro è Milano e Roma, con possibilità di modalità di lavoro ibrida.
 - Supportare la progettazione e realizzazione di infrastrutture di sicurezza per clienti enterprise, in affiancamento a figure senior di Security Architecture.
@@ -4650,64 +6300,64 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Architect Cloud Security (w/m/x)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Erfurt, Thuringia, Germany</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/bVBkJa/jobs/architect-cloud-security-w-m-x_erfurt_ND_PlrW1dL</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>Werde Teil von NTT DATA, einem führenden Anbieter von Unternehmens- und Technologiedienstleistungen. In der Rolle des Cloud Security Architects berätst du unsere Kunden bei der technischen Konzeption, Beratung und Implementierung von Cloud-Sicherheitsmaßnahmen. Du konzipierst und implementierst robuste Public und Hybrid-Cloud-Architekturen und steuerst aktiv unsere Projekte. Du solltest über mehrjährige Erfahrung im IT-Sicherheitsumfeld, insbesondere in den Bereichen Cloud- und Sicherheitsarchitektur, verfügen.
 - Beratung von Kunden bei der technischen Konzeption, Beratung und Implementierung von Cloud Security Maßnahmen.
@@ -4716,68 +6366,68 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Our Future Health</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Security Architect</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>London, United Kingdom</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>GBP 90,000 - 103,500</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/VHxfW6/jobs/security-architect_london_epmiiacl</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>Join our team as a Security Architect, where you'll play a key role in supporting our Researcher pillar. In this hands-on position, you'll influence the security architecture that underpins our products, platforms, and cloud-first environment. You'll act as a trusted advisor to squads, partner with engineers to build security into solutions from the outset, and lead threat modeling activities. You'll also communicate security risks, opportunities, and recommendations to different audiences and support strategic Researcher initiatives.
 - Collaborer avec les équipes pour façonner l'architecture sécurisée de l'organisation, influencer les décisions de conception et garantir la cohérence de l'approche de sécurité.
@@ -4801,68 +6451,68 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Thought Machine</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Senior Application  Security Engineer</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Lisbonne, Portugal</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>EUR 75,000 - 95,000</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/JNjyxB/jobs/senior-application-security-engineer_lisbonne_qikdpj4z</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>Join Thought Machine, a rapidly growing fintech company on a mission to revolutionize banking technology. As a Senior Application Security Engineer, you will play a key role in ensuring the security of our products and protecting customer data. You will have the opportunity to engage and lead cross-functionally, and contribute to the development of cutting-edge security measures. This is a full-time, permanent position based in our Lisbon office.
 - Drive improvements to Thought Machine's product security posture through strategic planning and collaboration with both development and infrastructure teams.
@@ -4871,308 +6521,249 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Centre for Information Resilience</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>IT Systems &amp; Security Engineer - London (Westminster)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>London, England, United Kingdom</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Information Systems Security Engineer (ISSE)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>remote (any state)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>eightfold</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>https://caci.eightfold.ai/careers/job/1443153775821</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oracle Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/UBjJgjGK6n</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Oracle Cybersecurity Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Cybersecurity Engineer Location: 100% Remote (United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Cloud Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;jaya@bvteck.com&gt; or contact us at (908) 505-3545 . Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>brightvisiontechnologies</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Software Security Engineer</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>USD 145,000–165,000 / year</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>FULL_TIME</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>jazzhr</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/HfvUed4IZs</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;Harry@bvteck.com&gt; or contact us at (908)676-4399. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stage – Stratégie DevSecOps – F/H</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Grenoble, Auvergne-Rhone-Alpes, France</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>workable</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>https://apply.workable.com/j/53829801C1/apply</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CACI</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Information Systems Security Engineer (ISSE)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>remote (any state)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>eightfold</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>https://caci.eightfold.ai/careers/job/1443153775821</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Oracle Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/UBjJgjGK6n</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Oracle Cybersecurity Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Oracle Cybersecurity Engineer Location: 100% Remote (United States) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Oracle Cloud Security Engineer responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. In this role you will define security architecture, harden cloud workloads, manage identity and access, lead vulnerability and compliance programs, and respond to security incidents. The ideal candidate will combine deep technical expertise in OCI security services with strong experience in cloud-native security frameworks, regulatory compliance, and threat detection. In this role you will work closely with cross-functional partners — product, design, engineering, operations, and business stakeholders — to translate ambiguous requirements into well-engineered solutions, and will be expected to raise the bar through code review, design review, and mentorship of more junior engineers. The successful candidate brings strong engineering discipline, a clear communication style, and a track record of shipping meaningful work that holds up well in production. Required Qualifications Bachelor’s degree in Cybersecurity, Computer Science, Engineering, or a related discipline. Five or more years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Excellent troubleshooting, communication, and documentation skills. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908) 505-3545 . Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Software Security Engineer</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>USD 145,000–165,000 / year</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/HfvUed4IZs</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Software Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $145,000–$165,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Software Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Five or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to or contact us at (908)676-4399. Learn more about Bright Vision Technologies at . Bright Vision Technologies is an Equal Opportunity Employer Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Schneider Electric</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Stage – Stratégie DevSecOps – F/H</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Grenoble, Auvergne-Rhone-Alpes, France</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
         <is>
           <t>INTERN</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>welcometothejungle</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/WRUVr2/jobs/stage-strategie-devsecops-f-h_grenoble</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>Rejoignez Schneider Electric, une entreprise engagée pour l'inclusion et la diversité. En tant que stagiaire dans notre équipe EcoStruxure Control Engineering, vous participerez à la mise en œuvre de pratiques DevOps et bénéficierez d'un environnement d'apprentissage stimulant.
 - Réaliser un état des lieux de l'existant sur la base de code et l'environnement GitHub, et analyser les bonnes pratiques DevOps adaptées au contexte.
@@ -5181,60 +6772,60 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>guidepointsecurity</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Vulnerability Management Engineer (ServiceNow) - Mid-Atlantic region (Remote)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6212201004?gh_jid=6212201004</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>GuidePoint Security provides trusted cybersecurity expertise, solutions and services that help organizations make better decisions and minimize risk. By taking a three-tiered, holistic approach for evaluating security posture and ecosystems, GuidePoint enables some of the nation’s top organizations, such as Fortune 500 companies and U.S. government agencies, to identify threats, optimize resources and integrate best-fit solutions that mitigate risk.
 **General Description**
@@ -5319,60 +6910,60 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>isaraerospace</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer (m/f/d)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4994562101</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>**Mission Brief**
 You are a technical guardian of our digital environment. At Isar Aerospace, the systems, data and people that build our rockets are mission critical and protecting them takes someone who builds controls and then proves they hold. 
@@ -5421,60 +7012,60 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>mongodb</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Senior Software Engineer, Product Security</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>https://www.mongodb.com/careers/job/?gh_jid=8241351</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>The MongoDB Product Security team is looking for a full-stack senior software engineer to help us build and scale the next generation of security practices, enabling hundreds of MongoDB engineers to build secure products for our customers.
 The Product Security team empowers product teams to build secure products for MongoDB customers by providing security enablement, such as AI-powered code analysis, threat modeling and security finding triaging and verification, fuzzing infrastructure, and finding management solutions. Our goal is to incorporate security early in product development at scale without introducing friction. With the emerging capabilities of AI models, we are proactively adopting our security practices to be prepared for the newly introduced challenges.
@@ -5511,60 +7102,60 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>brandwatch</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Remote - Hungary; Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/brandwatch/jobs/4994458101</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>At Cision, we believe in empowering every individual to make an impact. Here, your voice is heard, your ideas are valued, and your unique perspective fuels our collective success. As part of our global team, you'll thrive in an environment that champions curiosity, collaboration, and innovation, all while making meaningful contributions to the brands we accelerate.
 Join us in shaping the future of communication and building authentic connections that matter. Whether you're solving complex problems or driving bold innovations, your growth is our success, and together, we’ll create the conversations of tomorrow.
@@ -5608,60 +7199,60 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>cision</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Senior Security Engineer</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Remote - Hungary; Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/cision/jobs/4889283101</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>At Cision, we believe in empowering every individual to make an impact. Here, your voice is heard, your ideas are valued, and your unique perspective fuels our collective success. As part of our global team, you'll thrive in an environment that champions curiosity, collaboration, and innovation, all while making meaningful contributions to the brands we accelerate.
 Join us in shaping the future of communication and building authentic connections that matter. Whether you're solving complex problems or driving bold innovations, your growth is our success, and together, we’ll create the conversations of tomorrow.
@@ -5705,64 +7296,64 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Meilleurtaux</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Cloud Security Engineer F/H</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Courbevoie, IDF, fr</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>smartrecruiters</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/Meilleurtaux/744000152686070-cloud-security-engineer-f-h?oga=true</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>Contexte L'équipe Engineering Platform porte l'architecture cloud hub &amp; spoke du groupe, les landing zones mises à disposition des équipes, et l'administration des outils transverses (GitHub, SonarCloud, Datadog). Dans une démarche d'homogénéisation des pratiques de sécurité, nous recherchons un profil capable de structurer la gouvernance Cloud Security à l'échelle du groupe. Missions Vous concevez et faites évoluer les briques de la plateforme (landing zones, modules Terraform, pipelines CI/CD) au même titre que l'ensemble de l'équipe, en y intégrant les exigences de sécurité. Vous mettez en place et faites évoluer les outils de sécurité Cloud du groupe relevant des approches CSPM et CNAPP (posture de sécurité, scanning de configuration et d'infrastructure as code, protection des workloads, gestion des vulnérabilités, gestion des secrets). Vous définissez en relation avec l'équipe cyber les policies de sécurité applicables aux landing zones et aux workloads (politiques d'accès, segmentation réseau, chiffrement, gestion des identités). Vous intégrez ces policies dans les modules d'infrastructure as code et les pipelines CI/CD afin de les rendre natives et non bloquantes pour les équipes. Vous accompagnez les équipes dans la mise en conformité de leurs environnements et participez aux audits de sécurité Cloud.
 Vous avez une expérience confirmée (5 ans et plus) en sécurité Cloud (Azure et/ou GCP), idéalement dans un rôle de type Cloud Security Engineer, DevSecOps ou Platform Engineer avec une forte composante sécurité, en contexte multi-équipes. Vous maîtrisez les approches zéro trust et moindre privilège, la gestion des identités (IAM, SSO, CIEM), ainsi que les outils de policy as code (type Azure Policy, OPA, Checkov ou équivalents). Vous avez une bonne pratique de Terraform, GitHub et CI/CD, et savez intégrer des contrôles de sécurité dans des pipelines et modules sans dégrader l'expérience développeur. Une expérience avec des plateformes CSPM/CNAPP (Microsoft Defender for Cloud, Wiz, Prisma Cloud, Orca Security ou équivalents) est un atout. Une connaissance des référentiels de sécurité Cloud (CIS Benchmarks, NIST, ISO 27001) est un plus.
@@ -5771,68 +7362,68 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>thought-machine</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Senior Application  Security Engineer</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Portugal, Lisbon</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Not mentioned</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>€75K – €95K</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>FULL_TIME</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/thought-machine/ab2745ac-35d2-4639-a957-fefbb2b17867/application</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t>Thought Machine's mission is bold – to properly and permanently rid the world's banks of legacy technology. To achieve this, we have developed the foundations of modern banking through core and payments technology which run natively in the cloud. What we are attempting is hard and means we need great people working together to build great technology.
 We have grown rapidly in the past few years – growing our team to more than 550 individuals across offices in London, New York, Singapore, Sydney and our newly established Engineering Hub in Lisbon. We have raised more than £500m in funding and our investors include Molten Ventures, Eurazeo, Intesa Sanpaolo, Temasek, Nyca Partners, JPMorgan Chase Strategic Investments, Standard Chartered Ventures, and more.
@@ -5883,1698 +7474,10 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>grafanalabs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, Spain)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Spain (Remote)</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211674004</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
-We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
-You may not meet every requirement, and that’s okay. If this role excites you, we’d love you to raise your hand for what could be a truly career-defining opportunity.
-*This is a remote position and we're considering candidates in the UK, Spain, and Ireland.*
-**About the role:**
-We are looking for an engineering manager to lead our application security engineering team.  You will be responsible for developing and implementing security strategies, as well as liaising with other teams delivering parts of our overall security posture. You'll be accountable for the security of software you don't write, in teams that don't report to you. The people who do well in this role get there by making the secure path the easiest one.
-The ideal candidate will have a proven track record of implementing and improving the maturity of security programs, through the use of automation and systematic approaches in Cloud-based SaaS organizations, and possess excellent leadership and communication skills.  You can tell the difference between a finding and a risk, and know how to prioritise risk mitigation, guiding the squad towards the most effective use of their time.
-You must have significant engineering acumen as this is a highly technology-driven role.  Your main role will be to support your engineering team and to do that you should be able to review a threat model, challenge a severity rating, and contribute to a design review.
-**Responsibilities**:
-- Lead our application security team covering a range of areas, including application security, cloud security, and internal tooling development.
-- Lead 1st and 3rd party vulnerability management, including coordinated disclosure with external reporters and embargoed fixes.
-- Define, optimize, and implement the engineering strategy in concert with the security leadership team, ICs and stakeholders across the business.
-- Regular 1:1s, coaching and mentoring to ensure your team members are motivated, happy and engaged. Providing continuous feedback to ensure that they can add value while maintaining high standards.
-- Collaborating with our engineering leaders and other organization stakeholders to help define and influence wider product strategy, roadmaps and designs.
-- Be actively engaged with significant incidents, including preparation, simulation, response, and affected customer notification and communications.
-- Contributing to and reviewing design documents for upcoming projects. Ensuring projects are well-defined and ready for development. Advise on how to break down projects into tasks.
-**Requirements**:
-- Prior experience running a security engineering team.
-- You have a strong engineering background and are capable of engaging in technical conversations and challenging teams to arrive at strong technical decisions themselves.
-- You will be comfortable working with engineering teams who have a strong sense of autonomy in their decision-making, be it technical or product-focused.
-- While you’re great with people and adept at managing relationships, you still keep up-to-date with the latest technical trends and shifts to maintain and enhance your understanding of the challenges your teams face.
-- You approach security with a DevOps mindset. You prefer security by enablement, automation, and guardrails over gates and roadblocks.
-- You have familiarity with securing and operating on public Cloud (AWS, GCP, Azure) providers, with Kubernetes, and with securing combined open-source software (OSS) and SaaS products.
-- You are an excellent written and verbal communicator. You can articulate complex cybersecurity concepts to both technical and non-technical audiences. You are adept at translating security problems to business impact.
-**Bonus Points:**
-- A technical background, ideally with programming or software engineering experience, before transitioning into security &amp; leadership.
-- Working knowledge of Grafana Labs OSS projects and products. Experience in using observability tooling to solve security problems.
-- Experience working with OSS communities.
-- Experience securing large-scale distributed systems.
-**Compensation &amp; Rewards:**
-In Spain, the Base compensation range for this role is €94,025 - €112,830. Actual compensation may vary based on level, experience, and skillset as assessed throughout the interview process. All of our roles include Restricted Stock Units (RSUs), giving every team member ownership in Grafana Labs' success. We believe in shared outcomes—RSUs help us stay aligned and invested as we scale globally.
-#LI-Remote
-*\*Compensation ranges are country specific. If you are applying for this role from a different location than listed above, your recruiter will discuss your specific market’s defined pay range &amp; benefits at the beginning of the process.*
-**Why You’ll Thrive at Grafana Labs:**
-- **100% Remote, Global Culture -**As a remote-only company, we bring together talent from around the world, united by a culture of collaboration and shared purpose.
-- **Scaling Organization** – Tackle meaningful work in a high-growth, ever-evolving environment.
-- **Transparent Communication** – Expect open decision-making and regular company-wide updates.
-- **Innovation-Driven** – Autonomy and support to ship great work and try new things.
-- **Open Source Roots** – Built on community-driven values that shape how we work.
-- **Empowered Teams** – High trust, low ego culture that values outcomes over optics.
-- **Career Growth Pathways** – Defined opportunities to grow and develop your career.
-- **Approachable Leadership** – Transparent execs who are involved, visible, and human.
-- **Passionate People** – Join a team of smart, supportive folks who care deeply about what they do.
-- **In-Person onboarding** - We want you to thrive from day 1 with your fellow new ‘Grafanistas’ to learn all about what we do and how we do it.
-- **Balance is Key** - We operate a global annual leave policy of 30 days per annum. 3 days of your annual leave entitlement are reserved for Grafana Shutdown Days to allow the team to really disconnect. *\*We will comply with local legislation where applicable.*
-**Equal Opportunity Employer:** *Grafana Labs is an equal opportunities employer. We welcome applications from everyone regardless of race, colour, nationality, origin, caste, sex, gender reassignment identity or expression, sexual orientation, age, religion or belief, disability, veteran status, genetic information, pregnancy, maternity, marital, family or carer status, or any other characteristic which is protected by local law. We believe that equality and diversity build a strong organisation, and we work hard to ensure that is the foundation of our organisation as we grow.*
-*Grafana Labs may utilize AI tools in its recruitment process to assist in matching information provided in CVs to job postings. The recruitment team will continue to review inbound CVs manually to identify alignment with current openings.*
-#LI-Remote
-*For information about how your personal data is used once you’ve applied to a job, check out our [privacy policy](https://grafana.com/legal/applicant-and-candidate-privacy-policy/).*</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>grafanalabs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, Ireland)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Republic of Ireland (Remote)</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211672004</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
-We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
-You may not meet every requirement, and that’s okay. If this role excites you, we’d love you to raise your hand for what could be a truly career-defining opportunity.
-*This is a remote position and we're considering candidates in the UK, Spain, and Ireland.*
-**About the role:**
-We are looking for an engineering manager to lead our application security engineering team.  You will be responsible for developing and implementing security strategies, as well as liaising with other teams delivering parts of our overall security posture. You'll be accountable for the security of software you don't write, in teams that don't report to you. The people who do well in this role get there by making the secure path the easiest one.
-The ideal candidate will have a proven track record of implementing and improving the maturity of security programs, through the use of automation and systematic approaches in Cloud-based SaaS organizations, and possess excellent leadership and communication skills.  You can tell the difference between a finding and a risk, and know how to prioritise risk mitigation, guiding the squad towards the most effective use of their time.
-You must have significant engineering acumen as this is a highly technology-driven role.  Your main role will be to support your engineering team and to do that you should be able to review a threat model, challenge a severity rating, and contribute to a design review.
-**Responsibilities**:
-- Lead our application security team covering a range of areas, including application security, cloud security, and internal tooling development.
-- Lead 1st and 3rd party vulnerability management, including coordinated disclosure with external reporters and embargoed fixes.
-- Define, optimize, and implement the engineering strategy in concert with the security leadership team, ICs and stakeholders across the business.
-- Regular 1:1s, coaching and mentoring to ensure your team members are motivated, happy and engaged. Providing continuous feedback to ensure that they can add value while maintaining high standards.
-- Collaborating with our engineering leaders and other organization stakeholders to help define and influence wider product strategy, roadmaps and designs.
-- Be actively engaged with significant incidents, including preparation, simulation, response, and affected customer notification and communications.
-- Contributing to and reviewing design documents for upcoming projects. Ensuring projects are well-defined and ready for development. Advise on how to break down projects into tasks.
-**Requirements**:
-- Prior experience running a security engineering team.
-- You have a strong engineering background and are capable of engaging in technical conversations and challenging teams to arrive at strong technical decisions themselves.
-- You will be comfortable working with engineering teams who have a strong sense of autonomy in their decision-making, be it technical or product-focused.
-- While you’re great with people and adept at managing relationships, you still keep up-to-date with the latest technical trends and shifts to maintain and enhance your understanding of the challenges your teams face.
-- You approach security with a DevOps mindset. You prefer security by enablement, automation, and guardrails over gates and roadblocks.
-- You have familiarity with securing and operating on public Cloud (AWS, GCP, Azure) providers, with Kubernetes, and with securing combined open-source software (OSS) and SaaS products.
-- You are an excellent written and verbal communicator. You can articulate complex cybersecurity concepts to both technical and non-technical audiences. You are adept at translating security problems to business impact.
-**Bonus Points:**
-- A technical background, ideally with programming or software engineering experience, before transitioning into security &amp; leadership.
-- Working knowledge of Grafana Labs OSS projects and products. Experience in using observability tooling to solve security problems.
-- Experience working with OSS communities.
-- Experience securing large-scale distributed systems.
-**Compensation &amp; Rewards:**
-In Ireland, the Base compensation range for this role is €117,600 - €141,120. Actual compensation may vary based on level, experience, and skillset as assessed throughout the interview process. All of our roles include Restricted Stock Units (RSUs), giving every team member ownership in Grafana Labs' success. We believe in shared outcomes—RSUs help us stay aligned and invested as we scale globally.
-#LI-Remote
-*\*Compensation ranges are country specific. If you are applying for this role from a different location than listed above, your recruiter will discuss your specific market’s defined pay range &amp; benefits at the beginning of the process.*
-**Why You’ll Thrive at Grafana Labs:**
-- **100% Remote, Global Culture -**As a remote-only company, we bring together talent from around the world, united by a culture of collaboration and shared purpose.
-- **Scaling Organization** – Tackle meaningful work in a high-growth, ever-evolving environment.
-- **Transparent Communication** – Expect open decision-making and regular company-wide updates.
-- **Innovation-Driven** – Autonomy and support to ship great work and try new things.
-- **Open Source Roots** – Built on community-driven values that shape how we work.
-- **Empowered Teams** – High trust, low ego culture that values outcomes over optics.
-- **Career Growth Pathways** – Defined opportunities to grow and develop your career.
-- **Approachable Leadership** – Transparent execs who are involved, visible, and human.
-- **Passionate People** – Join a team of smart, supportive folks who care deeply about what they do.
-- **In-Person onboarding** - We want you to thrive from day 1 with your fellow new ‘Grafanistas’ to learn all about what we do and how we do it.
-- **Balance is Key** - We operate a global annual leave policy of 30 days per annum. 3 days of your annual leave entitlement are reserved for Grafana Shutdown Days to allow the team to really disconnect. *\*We will comply with local legislation where applicable.*
-**Equal Opportunity Employer:** *Grafana Labs is an equal opportunities employer. We welcome applications from everyone regardless of race, colour, nationality, origin, caste, sex, gender reassignment identity or expression, sexual orientation, age, religion or belief, disability, veteran status, genetic information, pregnancy, maternity, marital, family or carer status, or any other characteristic which is protected by local law. We believe that equality and diversity build a strong organisation, and we work hard to ensure that is the foundation of our organisation as we grow.*
-*Grafana Labs may utilize AI tools in its recruitment process to assist in matching information provided in CVs to job postings. The recruitment team will continue to review inbound CVs manually to identify alignment with current openings.*
-#LI-Remote
-*For information about how your personal data is used once you’ve applied to a job, check out our [privacy policy](https://grafana.com/legal/applicant-and-candidate-privacy-policy/).*</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>grafanalabs</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Engineering Manager - Grafana Application Security | EMEA | (Remote, UK)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>United Kingdom (Remote)</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/6211670004</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Grafana Labs is the company behind Grafana Cloud, the fully managed observability platform trusted by more than 10,000 organizations to ensure reliability, resolve incidents faster, and optimize telemetry at scale. Built on open source and open standards and designed for interoperability across any stack, Grafana Cloud brings AI to observability and observability to AI, giving teams (and their agents) unified visibility so they can see, understand, and act on all their disparate data, wherever it lives, and move at the speed of their ambitions. Customers, including Anthropic, Bloomberg, NVIDIA, Microsoft, and Salesforce, rely on Grafana Labs. We are a 100% remote company with team members across 40+ countries, backed by leading investors including Lightspeed Venture Partners, Sequoia Capital, GIC, Coatue, J.P. Morgan, CapitalG, and Lead Edge Capital. Learn more at [&lt;grafana.com&gt;](http://grafana.com) and follow us on [LinkedIn](https://www.linkedin.com/company/grafana-labs/) and [X](https://twitter.com/grafana).
-We’re scaling fast and staying true to what makes us different: an open-source legacy, a global collaborative culture, and a passion for meaningful work. Our team thrives in an innovation-driven environment where transparency, autonomy, and trust fuel everything we do.
-You may not meet every requirement, and that’s okay. If this role excites you, we’d love you to raise your hand for what could be a truly career-defining opportunity.
-*This is a remote position and we're considering candidates in the UK, Spain, and Ireland.*
-**About the role:**
-We are looking for an engineering manager to lead our application security engineering team.  You will be responsible for developing and implementing security strategies, as well as liaising with other teams delivering parts of our overall security posture. You'll be accountable for the security of software you don't write, in teams that don't report to you. The people who do well in this role get there by making the secure path the easiest one.
-The ideal candidate will have a proven track record of implementing and improving the maturity of security programs, through the use of automation and systematic approaches in Cloud-based SaaS organizations, and possess excellent leadership and communication skills.  You can tell the difference between a finding and a risk, and know how to prioritise risk mitigation, guiding the squad towards the most effective use of their time.
-You must have significant engineering acumen as this is a highly technology-driven role.  Your main role will be to support your engineering team and to do that you should be able to review a threat model, challenge a severity rating, and contribute to a design review.
-**Responsibilities**:
-- Lead our application security team covering a range of areas, including application security, cloud security, and internal tooling development.
-- Lead 1st and 3rd party vulnerability management, including coordinated disclosure with external reporters and embargoed fixes.
-- Define, optimize, and implement the engineering strategy in concert with the security leadership team, ICs and stakeholders across the business.
-- Regular 1:1s, coaching and mentoring to ensure your team members are motivated, happy and engaged. Providing continuous feedback to ensure that they can add value while maintaining high standards.
-- Collaborating with our engineering leaders and other organization stakeholders to help define and influence wider product strategy, roadmaps and designs.
-- Be actively engaged with significant incidents, including preparation, simulation, response, and affected customer notification and communications.
-- Contributing to and reviewing design documents for upcoming projects. Ensuring projects are well-defined and ready for development. Advise on how to break down projects into tasks.
-**Requirements**:
-- Prior experience running a security engineering team.
-- You have a strong engineering background and are capable of engaging in technical conversations and challenging teams to arrive at strong technical decisions themselves.
-- You will be comfortable working with engineering teams who have a strong sense of autonomy in their decision-making, be it technical or product-focused.
-- While you’re great with people and adept at managing relationships, you still keep up-to-date with the latest technical trends and shifts to maintain and enhance your understanding of the challenges your teams face.
-- You approach security with a DevOps mindset. You prefer security by enablement, automation, and guardrails over gates and roadblocks.
-- You have familiarity with securing and operating on public Cloud (AWS, GCP, Azure) providers, with Kubernetes, and with securing combined open-source software (OSS) and SaaS products.
-- You are an excellent written and verbal communicator. You can articulate complex cybersecurity concepts to both technical and non-technical audiences. You are adept at translating security problems to business impact.
-**Bonus Points:**
-- A technical background, ideally with programming or software engineering experience, before transitioning into security &amp; leadership.
-- Working knowledge of Grafana Labs OSS projects and products. Experience in using observability tooling to solve security problems.
-- Experience working with OSS communities.
-- Experience securing large-scale distributed systems.
-**Compensation &amp; Rewards:**
-In the UK, the Base compensation range for this role is £103,958 - £124,750. Actual compensation may vary based on level, experience, and skillset as assessed throughout the interview process. All of our roles include Restricted Stock Units (RSUs), giving every team member ownership in Grafana Labs' success. We believe in shared outcomes—RSUs help us stay aligned and invested as we scale globally.
-#LI-Remote
-*\*Compensation ranges are country specific. If you are applying for this role from a different location than listed above, your recruiter will discuss your specific market’s defined pay range &amp; benefits at the beginning of the process.*
-**Why You’ll Thrive at Grafana Labs:**
-- **100% Remote, Global Culture -**As a remote-only company, we bring together talent from around the world, united by a culture of collaboration and shared purpose.
-- **Scaling Organization** – Tackle meaningful work in a high-growth, ever-evolving environment.
-- **Transparent Communication** – Expect open decision-making and regular company-wide updates.
-- **Innovation-Driven** – Autonomy and support to ship great work and try new things.
-- **Open Source Roots** – Built on community-driven values that shape how we work.
-- **Empowered Teams** – High trust, low ego culture that values outcomes over optics.
-- **Career Growth Pathways** – Defined opportunities to grow and develop your career.
-- **Approachable Leadership** – Transparent execs who are involved, visible, and human.
-- **Passionate People** – Join a team of smart, supportive folks who care deeply about what they do.
-- **In-Person onboarding** - We want you to thrive from day 1 with your fellow new ‘Grafanistas’ to learn all about what we do and how we do it.
-- **Balance is Key** - We operate a global annual leave policy of 30 days per annum. 3 days of your annual leave entitlement are reserved for Grafana Shutdown Days to allow the team to really disconnect. *\*We will comply with local legislation where applicable.*
-**Equal Opportunity Employer:** *Grafana Labs is an equal opportunities employer. We welcome applications from everyone regardless of race, colour, nationality, origin, caste, sex, gender reassignment identity or expression, sexual orientation, age, religion or belief, disability, veteran status, genetic information, pregnancy, maternity, marital, family or carer status, or any other characteristic which is protected by local law. We believe that equality and diversity build a strong organisation, and we work hard to ensure that is the foundation of our organisation as we grow.*
-*Grafana Labs may utilize AI tools in its recruitment process to assist in matching information provided in CVs to job postings. The recruitment team will continue to review inbound CVs manually to identify alignment with current openings.*
-#LI-Remote
-*For information about how your personal data is used once you’ve applied to a job, check out our [privacy policy](https://grafana.com/legal/applicant-and-candidate-privacy-policy/).*</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Network &amp; Security Engineer Senior Aix-en-Provence</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Aix-en-Provence, Provence-Alpes-Cote d'Azur, France</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/oGmK9Lp/jobs/network-security-engineer-senior-aix-en-provence_aix-en-provence_CAPGE_rDlJRNO</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Rejoignez notre équipe en tant qu'Ingénieur Réseau et Sécurité Senior. Vous serez responsable de l'exploitation et de la maintenance des équipements et services réseau, de la gestion de projets réseaux, du traitement des incidents N2/N3, de l'administration des équipements de sécurité, et de l'élaboration des architectures techniques. Vous devez avoir au moins 3 ans d'expérience dans un poste similaire et être autonome, impliqué et avoir un bon esprit d'équipe.
-- Assurer l'exploitation et la MCO des équipements et services réseau, gestion du BUILD et pilotage de projets réseaux.
-- Traiter les incidents N2/N3 et réaliser les mises en production, participer à la mise en œuvre et à l'exploitation des infrastructures réseau.
-- Administrer des équipements et solutions de sécurité réseaux, serveurs, plateformes virtuelles et dispositifs de sécurité.
-Description du profil :  
-***Votre profil :***
-- Vous disposez d’au moins 3 années d’expérience sur des postes d’administrateur réseaux et sécurité ou équivalent.
-- Vous avez des bases en construction d'architectures, en gestion de projets et/ou d'équipe.
-- Pour finir, nous recherchons des collaborateurs autonomes, impliqué(e)s et avec un bon esprit d’équipe.
-- Disposer de certifications et de notions de performance soumises au KPI et/ou SLA sont des +
-Nous proposons :  
-**3 raisons de nous rejoindre :**
-**Qualité de vie au travail** : accord de télétravail en France et à l’international, accord sur l’égalité professionnelle, la parentalité, l’équilibre des temps et la mobilité durable.
-**Apprentissage en continu** : certifications et formations en libre accès, accompagnement sur mesure avec votre people manager, parcours d’intégration sur 9 mois.
-**Avantages groupe &amp; CSE** : plan actionnariat, tarif préférentiels, remboursement partiel vacances, remboursement de votre abonnement sportif ou culturel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Security Engineer (Incident Response)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/oRcFvn/jobs/security-engineer-incident-response_ie_ktrn554v</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Join Twilio's Security Incident Response Team (SIRT) as a Security Engineer. In this role, you will lead the technical response to security events and incidents across Twilio's global infrastructure, services, and applications. You will work collaboratively with R&amp;D Engineering and R&amp;D Business teams to develop scalable processes and technical solutions. Your responsibilities will include documenting incidents and projects, improving Twilio's security and reliability posture, and providing mentorship and support to the team. Enjoy benefits such as work-from-home opportunities, generous annual time off, comprehensive health programs, and more.
-- Lead and support the response to all security events and incidents across Twilio’s complex global infrastructure, services, and applications.
-- Work cross-collaboratively to understand and help solve challenges related to a broad spectrum of threat actors and activity.
-- Own the security incident lifecycle, respond to incidents and participate in on-call rotation and participate in RCAs for security incidents.
- - Ability to utilize AI for comprehensive, complex security incident response activities delivering high fidelity detections
-- Experience with SOAR tools and automating manual security processes
-- Excellent written and verbal communication skills
-- Ability to influence and build effective working relationships with every level of the organization
-- Proven experience: 3+ years of security incident response in a production-cloud environment
-- Experience working across a technology stack on difficult security challenges and initiatives
-- Advanced knowledge of service-oriented architectures, as well as experience with security tools and technologies fit for a cloud environment
-- Experience with SIEM platforms and the ability to extend their functionality
-- Subject-matter expert on security issues and technologies
-- Experience in either AWS, GCP, or other large cloud platform
-- AI Model Security &amp; Posture Management: Support Implementation of  controls and safeguards to prevent AI vulnerabilities, such as prompt injections, model evasion, and data poisoning
-- AI-Driven Threat Response: Utilize GenAI and LLM-based security use cases to rapidly interpret alerts, reduce false positives, and contextualize threat data
-- Threat Intelligence Integration: Monitors external vendor data and threat intelligence to analyze trends and proactively defend against emerging risks
-- Artifact &amp; Evidence Triage: Collects intrusion artifacts and forensically sound images to analyze malware, trojans, and source code</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Pantheon</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>welcometothejungle</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/en/companies/fdsSTg/jobs/security-engineer_ca_emny6wrd</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Join Pantheon's Security Engineering team as a Security Engineer II. In this hands-on engineering role, you will be responsible for safeguarding, auditing, and testing the security of Pantheon's entire platform. You will own security domains end-to-end, build automation and processes, and write detection rules. This position offers a flexible work environment, health and wellness benefits, and opportunities for professional development.
-- Assurer la sécurité, l'audit et les tests de la plateforme cloud de Pantheon, en mettant l'accent sur la sécurité dès la conception.
-- Développer et maintenir des outils de sécurité et des pipelines d'automatisation pour améliorer l'efficacité de l'équipe.
-- Agir en tant qu'expert en la matière, en mentorant et en soutenant les efforts d'ingénierie de sécurité au sein de l'organisation.
- - Grit: Understanding that establishing security best practices is a marathon requiring persistence across many stakeholders
-- Commitment: Demonstrated commitment to teamwork, professionalism, and authenticity, fostering trust and accountability
-- Builder Orientation: You measure impact by what you ship — tooling that engineering teams adopt, automation that replaces manual work, detection rules that catch real threats. Not by tickets closed or alerts triaged
-- Communication: Strong communication skills essential for partnering with engineering teams across the organization. You advocate for security priorities and tradeoffs across functions without being prompted
-- CI/CD Fundamentals: Hands-on experience with Jenkins, Cloud Build, CircleCI, or similar (bonus points for experience with reusable workflows)
-- Coding Proficiency: Ability to build maintainable components in Python or Go. You write tools, not just policies
-- Security Tooling: Demonstrated experience building security automation — vulnerability management scripts, CI/CD pipeline integrations, detection rules, or similar tooling that engineering teams use in production
-- Development Practices: Hands-on experience with Secure by Design development practices, including participating in security architecture and design reviews
-- Cloud Proficiency: Experience securing production systems in cloud environments (GCP preferred; AWS or Azure also valuable)
-- Education: Bachelor's degree (preferred) in Computer Science or equivalent practical experience
-- Security Tooling Platforms: Experience with SAST/DAST/SCA/CSPM tools. Familiarity with CodeQL, Wiz, or similar platforms is a plus
-- Cloud &amp; Infrastructure: Experience working with containerization (e.g., Docker, OCI), Terraform, and Kubernetes (K8s)
-- Overall Experience: Minimum of 4+ years of overall experience, with at least 2+ years dedicated to Application Security or Security Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/0F3Za69HVM</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>AI Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: AI Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 8+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are seeking an AI Security Engineer to lead the design and implementation of security controls, threat models, and incident response capabilities specifically tailored to AI and machine learning systems. The role addresses the unique security challenges posed by LLMs, model APIs, training data pipelines, and AI-powered applications, including prompt injection, model abuse, data exfiltration, and supply chain risks. The ideal candidate has strong security engineering fundamentals and a deep understanding of how modern AI systems work in practice, with hands-on experience designing defenses for both AI-powered applications and the AI infrastructure that supports them. Key Responsibilities Define and implement security controls specifically targeting LLM and AI-powered application risks. Build threat models for AI systems, including prompt injection, jailbreaks, data exfiltration, and abuse patterns. Design and deploy guardrails, content filters, and policy enforcement layers around model endpoints. Implement runtime detection and response capabilities for adversarial prompts and abusive behavior. Secure training and fine-tuning pipelines, including data provenance, integrity, and access controls. Design controls for sensitive data handling, retention, and redaction in LLM workflows. Lead red-team exercises against AI systems and drive remediation of identified weaknesses. Evaluate and harden third-party AI services and open-source AI components used internally. Implement identity, authorization, and tenant-isolation patterns for multi-tenant AI services. Drive supply chain security for ML artifacts including weights, datasets, and inference dependencies. Collaborate with privacy, legal, and compliance teams to ensure AI systems meet regulatory obligations. Develop monitoring, logging, and detection strategies tailored to AI workloads. Lead incident response for AI-specific security events and drive durable improvements. Stay current with adversarial ML, LLM security research, and emerging regulatory developments. Required Qualifications Bachelor’s or Master’s degree in Computer Science, Cybersecurity, or a related discipline. Eight or more years of security engineering experience, including significant work on AI or ML systems. Strong understanding of LLM internals, modern AI architectures, and common failure modes. Hands-on experience designing security controls for AI-powered applications. Deep knowledge of application security, identity, and cryptography fundamentals. Experience with threat modeling and security architecture review processes. Familiarity with adversarial ML, prompt injection, and model abuse research. Proficiency in Python and at least one systems language. Strong understanding of cloud security and modern infrastructure controls. Excellent written and verbal communication skills. Preferred Qualifications Publications, talks, or CTF participation in AI security topics. Experience with red-teaming LLM-based products. Familiarity with privacy-preserving ML techniques such as differential privacy. Exposure to regulated industries with strict data handling requirements. Open-source contributions to AI security tooling. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/S5bS7lykdZ</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Application Security Engineer – Remote Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Application Security Engineer Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$160,000 Annually Experience Required: 10+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary: We are looking for an Application Security Engineer to embed security throughout the software development lifecycle, partnering with engineering teams to design secure systems, identify vulnerabilities, and reduce risk across our application portfolio. The role blends hands-on offensive and defensive skills with strong communication and collaboration, helping development teams build secure software efficiently rather than slowing them down. The ideal candidate brings deep technical security expertise, strong software engineering fundamentals, and a track record of shipping security improvements that meaningfully reduce risk in production. Key Responsibilities Conduct threat modeling and security architecture reviews for new and existing applications and services. Perform manual code reviews, secure design consultations, and pair with engineering teams on hardening critical components. Operate and tune SAST, DAST, IAST, SCA, and secret-scanning tools across CI/CD pipelines. Drive vulnerability management workflows including triage, prioritization, owner assignment, and SLA tracking. Build paved-road libraries and frameworks that make secure patterns the default for engineering teams. Lead red-team and purple-team exercises against internal applications and drive remediation of identified weaknesses. Implement and operate runtime protections including WAF, RASP, bot protection, and abuse-detection mechanisms. Design and enforce secure authentication, authorization, session management, and cryptographic patterns. Partner with infrastructure and platform teams to harden container, Kubernetes, and cloud environments. Develop and deliver application security training, lunch-and-learns, and onboarding content for engineering staff. Respond to security incidents involving application vulnerabilities or active exploitation. Track and apply emerging threats and CVEs that may affect the application portfolio. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Stay current with application security research and emerging defensive tooling. Required Qualifications Bachelor’s degree in Computer Science, Cybersecurity, or a related field. Ten or more years of application security or security engineering experience. Strong understanding of OWASP Top 10, common vulnerability classes, and modern exploit patterns. Hands-on experience performing code review across at least two major languages. Deep familiarity with SAST, DAST, SCA, and CI/CD-integrated security tooling. Strong understanding of authentication, authorization, and cryptographic primitives. Experience with cloud security and modern infrastructure controls. Strong communication skills with technical and non-technical audiences. Proficiency in at least one programming language for tooling and automation. Experience working closely with engineering teams in an Agile environment. Preferred Qualifications Industry certifications such as OSCP, OSCE, GWAPT, or CISSP. Experience with offensive security tooling and red-team operations. Bug bounty experience, public CVEs, or open-source security contributions. Familiarity with AI/LLM application security considerations. Exposure to regulated industries with strict compliance requirements. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;venkat.r@bvteck.com&gt; or contact us at (908) 505-3899. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt; . Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>brightvisiontechnologies</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer – Oracle</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>jazzhr</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://brightvisiontechnologies.applytojob.com/apply/jobs/details/qLisMzMIxC</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Bright Vision Technologies is a technology consulting and software development company delivering cloud, AI, data, and enterprise solutions across the United States. This is a fantastic opportunity to join an established and well-respected organization offering tremendous career growth potential. Job Title: Cloud Security Engineer - Oracle Location: 100% Remote (U.S.) Position Type: Full-time, Direct W2 Salary Range: $100,000–$150,000 Annually Experience Required: 6+ years Sponsorship: U.S. Citizens, Green Card Holders, EAD Holders, and H-1B transfer candidates are encouraged to apply. We are unable to sponsor new H-1B visa petitions for this position. Job Summary We are seeking an experienced Cloud Security Engineer - Oracle responsible for designing, implementing, and operating security controls across Oracle Cloud Infrastructure (OCI), Oracle Cloud Applications, and hybrid Oracle environments. Key Responsibilities Design and implement enterprise security architectures for OCI tenancies, including landing-zone guardrails, security zones, and compartment policies. Configure and operate OCI Identity Domains, federation with corporate IdPs, and strong RBAC strategies across the tenancy. Implement strong key management and secrets handling using OCI Vault, including key rotation and HSM integration where appropriate. Harden OCI compute, networking, and database workloads using CIS benchmarks, OCI Security Zones, and internal security standards. Operate OCI Cloud Guard for continuous detection and response, tuning detectors and remediating findings. Configure and operate OCI Logging, OCI Audit, and integration with SIEM platforms for centralized monitoring and forensics. Implement data security controls using OCI Data Safe, including data masking, sensitive data discovery, and privileged user analysis. Lead vulnerability management programs, including image scanning, patching, and remediation tracking. Drive compliance with regulatory frameworks such as PCI-DSS, HIPAA, SOC 2, ISO 27001, or FedRAMP. Conduct threat modeling and architecture reviews for new OCI workloads. Lead security incident response on OCI, including containment, investigation, and post-incident review. Develop security automation tooling using Python, Terraform, and OCI CLI/SDK. Maintain comprehensive, current technical documentation — including architecture diagrams, design decisions, configuration references, runbooks, and operational procedures — so that the system remains supportable, auditable, and easy to onboard new engineers onto over time. Provide mentorship and security guidance across application and infrastructure teams. Required Qualifications 5+ years of cloud security experience, with strong hands-on time on OCI. Deep experience with OCI Identity, IAM policies, and identity federation. Hands-on experience with OCI Cloud Guard, Security Zones, Vault, and Data Safe. Solid understanding of cloud-native security frameworks and CIS benchmarks. Experience with vulnerability management and patching tooling. Working knowledge of regulatory frameworks (PCI-DSS, HIPAA, SOC 2, ISO 27001). Strong scripting skills (Python, Bash) and Terraform. Experience integrating cloud workloads with SIEM platforms. Preferred Qualifications Oracle Cloud Security Professional certification. CISSP, CCSP, or equivalent industry security certifications. Experience with multi-cloud security architectures. Familiarity with SOAR platforms and automated incident response. Exposure to zero-trust architecture patterns. How to Apply Would you like to know more about this opportunity? For immediate consideration, please send your resume to &lt;jaya@bvteck.com&gt; or contact us at (908) 505-3545. Learn more about Bright Vision Technologies at &lt;www.bvteck.com&gt;. Bright Vision Technologies is an Equal Opportunity Employer. Equal Employment Opportunity (EEO) Statement Bright Vision Technologies (BV Teck) is committed to equal employment opportunity (EEO) for all employees and applicants without regard to race, color, religion, sex, sexual orientation, gender identity or expression, national origin, age, genetic information, disability, veteran status, or any other protected status as defined by applicable federal, state, or local laws. This commitment extends to all aspects of employment, including recruitment, hiring, training, compensation, promotion, transfer, leaves of absence, termination, layoffs, and recall. BV Teck expressly prohibits any form of workplace harassment or discrimination. Any improper interference with employees' ability to perform their job duties may result in disciplinary action up to and including termination of employment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Remote Sweden</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237824</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Sweden
-512 925 kr—683 900 kr SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Remote Netherlands</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237818</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Netherlands
-€66.000—€88.000 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Remote Spain</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237816</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Spain
-€58.000—€77.000 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Remote Belgium</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237815</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Belgium
-€56.000—€74.000 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Remote Finland</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237812</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Finland
-€45.000—€60.000 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Remote UK</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8237810</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote UK
-£66,000—£87,000 GBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Remote Germany</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8191473</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-REMOTE
-Req ID: R3224
-**Hiring Ranges:**
-Remote Germany
-€68.000—€91.000 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>mozilla</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer - SecOps</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/mozilla/jobs/8189048</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>To learn the Hiring Ranges for this position, please select your location from the **Apply Now** dropdown menu.
-To learn more about our Hiring Range System, please click this [**link.**](https://docs.google.com/document/d/1ylUe7Ou0EbsOtGRBtUv1sSld3lbZ4mrYzo59tEkSjY8/edit?usp=sharing)
-**Why Mozilla?**
-Mozilla Corporation is the non-profit-backed technology company that has shaped the internet for the better over the last 25 years. We make pioneering brands like Firefox, the privacy-minded web browser. Now, with more than 225 million people around the world using our products each month, we’re shaping the next 25 years of technology and helping to reclaim an internet built for people, not companies. Our work focuses on diverse areas including AI, social media, security and more. And we’re doing this while never losing our focus on our core mission – to make the internet better for people. 
-The Mozilla Corporation is wholly owned by the non-profit 501(c) Mozilla Foundation. This means we aren’t beholden to any shareholders — only to our mission. Along with thousands of volunteer contributors and collaborators all over the world, Mozillians design, build and distribute **open-source** software that enables people to enjoy the internet on their terms. 
-**About this team and role:**
-Mozilla is looking for an Incident Responder to monitor and mitigate attacks across Mozilla’s products and services. In this position, you will be a part of a flexible team responsible for handling security incidents. As such, you’ll need to have years of practical security experience and knowledge of the state of the art for detecting and responding to attacks. You’ll be someone Mozillians across the company depend on and trust to respond quickly and effectively in a crunch, with the outstanding communication and collaboration skills needed to work in partnership with diverse stakeholders. Most importantly, you will become a critical member of the team responsible for ensuring the integrity of Mozilla’s products and for keeping Mozilla’s users safe, within a company dedicated to building a more secure internet.
-**What you'll do:**
-- Identify and respond to security incidents on a global scale.
-- Act as an incident commander to drive incidents through the entire response lifecycle.
-- Design and maintain a portfolio of security alerts, automated actions, playbooks and escalation workflows in support of a high-performing 24/7 incident response capability.
-- Conduct threat hunting activities, anticipate future threats, and maintain forward-thinking strategies for tools/technology/processes that combat sophisticated threat actors.
-- Research threat intelligence reports, triage and manage resulting workflows.
-- Partner with key stakeholders and communicate effectively to maintain a continuously improving feedback loop of preparation, identification, analysis, containment, and post mortem activities.
-- Participate in on-call rotation.
-**What you'll bring:**
-- 5+ years of demonstrated ability managing security incidents at a global scale and/or experience working in Security Operations Centers (SOC), Product Security Incident Response Teams (PSIRT), and Computer Security Incident Response Teams (CSIRT).
-- Expertise with security information and event management (SIEM) systems (eg. ELK, Google BigQuery, Splunk, etc.). Splunk proficiency is preferred.
-- Expertise with endpoint detection and investigation. Hands-on experience with leading EDR tools and demonstrated ability to leverage endpoint telemetry to find root cause.
-- Expertise with security orchestration and automation (SOAR) platforms such as Tines or Splunk SOAR.
-- Superb communication and leadership capacity; ability to partner effectively with diverse company stakeholders.
-- Real-world experience in software development and/or engineering operations for consumer products and services; B.S. in a technology-focused field is helpful.
-- Practical experience working with cloud technologies (eg. Google Cloud Platform, Amazon Web Services, Heroku, Microsoft Azure, etc.).
-**Competencies:**
-- Ownership and Accountability
-- Autonomy
-- High Level of Integrity
-- Clear Communication
-- Creative Problem Solver
-- Passionate about Security
-**What you’ll get:**
-- Generous performance-based bonus plans to all eligible employees - we share in our success as one team
-- Rich medical, dental, and vision coverage
-- Generous retirement contributions with 100% immediate vesting (regardless of whether you contribute)
-- Quarterly all-company wellness days where everyone takes a pause together
-- Country specific holidays plus a day off for your birthday
-- One-time home office stipend
-- Annual professional development budget
-- Quarterly well-being stipend
-- Considerable paid parental leave
-- Employee referral bonus program
-- Other benefits (life/AD&amp;D, disability, EAP, etc. - varies by country)
-**About Mozilla**
-Mozilla exists to build the Internet as a public resource accessible to all because we believe that open and free is better than closed and controlled. When you work at Mozilla, you give yourself a chance to make a difference in the lives of Web users everywhere. And you give us a chance to make a difference in your life every single day. Join us to work on the Web as the platform and help create more opportunity and innovation for everyone online.
-**Commitment to diversity, equity, inclusion, and belonging**
-Mozilla understands that valuing diverse creative practices and forms of knowledge are crucial to and enrich the company’s core mission.  We encourage applications from everyone, including members of all equity-seeking communities, such as (but certainly not limited to) women, racialized and Indigenous persons, persons with disabilities, persons of all sexual orientations, gender identities, and expressions.
-We will ensure that qualified individuals with disabilities are provided reasonable accommodations to participate in the job application or interview process, to perform essential job functions, and to receive other benefits and privileges of employment, as appropriate. Please contact us at [hiringaccommodation@mozilla.com](mailto:hiringaccommodation@mozilla.com) to request accommodation.
-We are an equal opportunity employer. We do not discriminate on the basis of race (including hairstyle and texture), religion (including religious grooming and dress practices), gender, gender identity, gender expression, color, national origin, pregnancy, ancestry, domestic partner status, disability, sexual orientation, age, genetic predisposition, medical condition, marital status, citizenship status, military or veteran status, or any other basis covered by applicable laws.  Mozilla will not tolerate discrimination or harassment based on any of these characteristics or any other unlawful behavior, conduct, or purpose.
-Group: D
-#LI-DNI
-Req ID: R3224</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>netcompany1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Purple Security Engineer</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Copenhagen, dk</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>FULL_TIME</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>smartrecruiters</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Netcompany1/744000152447554-purple-security-engineer?oga=true</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Do you find Threat Hunting, Threat Intelligence, SIEM, and EDR exciting, and do you want to be a deciding factor in IT Security in our internal as well as our customers’ environments? As a Purple Security Engineer, you will ensure operations can perform their security-related tasks based on guidelines you help define. Responsibilities and technologies As a Purple Security Engineer, you will be a part of Netcompany Operations and our dedicated Security team. Your work will involve defending critical infrastructure such as airports, large financial institutions, government systems, and other essential sectors. You will handle tasks ranging from identifying improvements and monitoring servers and applications to optimizing response strategies and advising colleagues. You will be encouraged to solve technical problems creatively to find the best solutions. Open dialogue about different approaches to enhancing security is an important part of your work as a Purple Security Engineer. You will be a trusted advisor for Netcompany’s delivery and project teams regarding how to solve security-related tasks. Your responsibilites will typically include: Implementing safeguards to protect critical solutions and the data infrastructure of Denmark from cyber threats. Engaging in proactive threat hunting to identify and mitigate potential vulnerabilities. Developing and implementing response strategies to effectively handle security incidents. Responding to and following up on alerts generated by our SIEM and EDR solutions, including adjusting these to ensure precision. About you To succeed in this role, you: You hold a degree or diploma in engineering, either bachelor's, master's, or have a similar qualification level in IT. You are motivated by delivering optimal business and critical societal solutions. Full professional proficiency in Danish and English (written and spoken) is a must. Employment is contingent upon your ability to obtain and maintain security clearance from the Danish Security and Intelligence Service (PET). Continue developing with us At Netcompany, we focus on your personal and professional development. When you join us, you will be assigned a personal mentor who will guide you through your development and help you achieve your goals. The close relationship with an experienced colleague helps ensure the well-being of each employee and provides you with concrete insights into the many different career opportunities as you build your experience. Additionally, you will be enrolled in our internal training programme, Netcompany Academy, where you are offered courses and seminars on everything from technologies to customer management. All courses are taught by experienced Netcompany colleagues, ensuring that all content is highly relevant and builds upon your professional skills, preparing you for various tasks and continuously improving your expertise throughout your career with us. Join an inclusive community At Netcompany, we highly prioritise an inclusive community. We actively promote an open and welcoming work culture based on collaboration and mutual trust, where there is always an opportunity for sparring. As part of our culture and values, all employees, regardless of background, identity, and experience, are met with understanding and respect and given equal opportunities for development and well-being. As we are an international company with offices in many countries, you will have the opportunity to learn and collaborate internationally with colleagues from across the world. We offer a shared environment where we engage with each other across departments and projects. Additionally, we have a wide range of social and professional events that provide you with the best opportunities to expand and build a network early in your career. Send us your application Upload your resume and a motivational letter to our recruitment system via the link. If you have unanswered questions, feel free to write to . All qualified candidates are encouraged to apply regardless of gender, gender expression, sexuality, disability, age, religion and belief, political views, nationality, ethnicity, or social background. We are committed to creating an inclusive and diverse environment. Our recruitment processes are based on individual merit. If you require any reasonable adjustments or additional support during the interview process, please email our recruiters at  for assistance. #LI-SA1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M81"/>
+  <autoFilter ref="A1:M83"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"New,Applied,Interview,Rejected,Offer,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7659,6 +7562,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
